--- a/PLC/IO List.xlsx
+++ b/PLC/IO List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EZENIC\Desktop\Project-Second\PLC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8940AD66-DDF9-4C02-8B4B-B01664DF04EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{437F9249-419E-4C29-8284-EFD8FAA65E9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E8A3CD3B-D612-4B37-A180-F6C335096DC9}"/>
+    <workbookView xWindow="10950" yWindow="0" windowWidth="17955" windowHeight="15585" activeTab="1" xr2:uid="{E8A3CD3B-D612-4B37-A180-F6C335096DC9}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,6 @@
     <sheet name="기타 장비" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="420">
   <si>
     <t>X10</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -206,10 +205,6 @@
     <t>X44</t>
   </si>
   <si>
-    <t>마스터 비상정지</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>라인 Ready 상태</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1269,10 +1264,6 @@
   </si>
   <si>
     <t>X205</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>공정 작업 완료</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1555,6 +1546,54 @@
   </si>
   <si>
     <t>챔버6 도어 클로즈</t>
+  </si>
+  <si>
+    <t>시작버튼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가동중</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>X207</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도착 완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>X89</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Area Sensor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>X93</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>X9E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>X129</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>X13B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>X175</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1718,7 +1757,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1740,49 +1779,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1811,6 +1811,36 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2146,34 +2176,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{228BF0B7-E586-4CC1-BF31-0F024BABECA2}">
-  <dimension ref="B3:E57"/>
+  <dimension ref="B3:G57"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="3" max="3" width="30.625" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="30.625" customWidth="1"/>
+    <col min="7" max="7" width="30.625" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:5">
+    <row r="3" spans="2:7">
       <c r="B3" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" s="8"/>
-      <c r="E3" s="9"/>
-    </row>
-    <row r="4" spans="2:5">
+      <c r="C3" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+    </row>
+    <row r="4" spans="2:7">
       <c r="B4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="9"/>
-    </row>
-    <row r="5" spans="2:5">
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+    </row>
+    <row r="5" spans="2:7">
       <c r="B5" s="4" t="s">
         <v>9</v>
       </c>
@@ -2186,679 +2221,793 @@
       <c r="E5" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="2:5">
+      <c r="F5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7">
       <c r="B6" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>408</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>409</v>
+      </c>
+      <c r="G6" s="23" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7">
+      <c r="B7" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C7" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" s="23" t="s">
+      <c r="D7" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="10" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="7" spans="2:5">
-      <c r="B7" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="C7" s="23" t="s">
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+    </row>
+    <row r="8" spans="2:7">
+      <c r="B8" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+    </row>
+    <row r="9" spans="2:7">
+      <c r="B9" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+    </row>
+    <row r="10" spans="2:7">
+      <c r="B10" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+    </row>
+    <row r="11" spans="2:7">
+      <c r="B11" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+    </row>
+    <row r="12" spans="2:7">
+      <c r="B12" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+    </row>
+    <row r="13" spans="2:7">
+      <c r="B13" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+    </row>
+    <row r="14" spans="2:7">
+      <c r="B14" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+    </row>
+    <row r="15" spans="2:7">
+      <c r="B15" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+    </row>
+    <row r="16" spans="2:7">
+      <c r="B16" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+    </row>
+    <row r="17" spans="2:7">
+      <c r="B17" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+    </row>
+    <row r="18" spans="2:7">
+      <c r="B18" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+    </row>
+    <row r="19" spans="2:7">
+      <c r="B19" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+    </row>
+    <row r="20" spans="2:7">
+      <c r="B20" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+    </row>
+    <row r="21" spans="2:7">
+      <c r="B21" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+    </row>
+    <row r="22" spans="2:7">
+      <c r="B22" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+    </row>
+    <row r="23" spans="2:7">
+      <c r="B23" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+    </row>
+    <row r="24" spans="2:7">
+      <c r="B24" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+    </row>
+    <row r="25" spans="2:7">
+      <c r="B25" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+    </row>
+    <row r="26" spans="2:7">
+      <c r="B26" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C26" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="D7" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="23" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5">
-      <c r="B8" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="D8" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="23" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5">
-      <c r="B9" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="C9" s="23" t="s">
-        <v>106</v>
-      </c>
-      <c r="D9" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="E9" s="23" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5">
-      <c r="B10" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="C10" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="D10" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="23" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5">
-      <c r="B11" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="D11" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" s="23" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5">
-      <c r="B12" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="C12" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="D12" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="E12" s="23" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5">
-      <c r="B13" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="C13" s="23" t="s">
-        <v>110</v>
-      </c>
-      <c r="D13" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" s="23" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5">
-      <c r="B14" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="C14" s="23" t="s">
-        <v>111</v>
-      </c>
-      <c r="D14" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="E14" s="23" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5">
-      <c r="B15" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="C15" s="23" t="s">
-        <v>112</v>
-      </c>
-      <c r="D15" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="E15" s="23" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5">
-      <c r="B16" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="C16" s="23" t="s">
+      <c r="D26" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+    </row>
+    <row r="27" spans="2:7">
+      <c r="B27" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+    </row>
+    <row r="28" spans="2:7">
+      <c r="B28" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+    </row>
+    <row r="29" spans="2:7">
+      <c r="B29" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="D16" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="E16" s="23" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5">
-      <c r="B17" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="C17" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="D17" s="22" t="s">
-        <v>155</v>
-      </c>
-      <c r="E17" s="23" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5">
-      <c r="B18" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="C18" s="23" t="s">
-        <v>97</v>
-      </c>
-      <c r="D18" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="E18" s="23" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5">
-      <c r="B19" s="22" t="s">
-        <v>93</v>
-      </c>
-      <c r="C19" s="23" t="s">
-        <v>98</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5">
-      <c r="B20" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="C20" s="23" t="s">
-        <v>99</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5">
-      <c r="B21" s="22" t="s">
-        <v>95</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5">
-      <c r="B22" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="C22" s="23" t="s">
-        <v>101</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5">
-      <c r="B23" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C23" s="23" t="s">
-        <v>102</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5">
-      <c r="B24" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5">
-      <c r="B25" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="C25" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5">
-      <c r="B26" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="C26" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5">
-      <c r="B27" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="C27" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="D27" s="5" t="s">
+      <c r="C29" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D29" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="E27" s="6" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5">
-      <c r="B28" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E28" s="6" t="s">
+      <c r="E29" s="6" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="29" spans="2:5">
-      <c r="B29" s="11" t="s">
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+    </row>
+    <row r="30" spans="2:7">
+      <c r="B30" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C30" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D30" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="E30" s="6" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="30" spans="2:5">
-      <c r="B30" s="11" t="s">
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+    </row>
+    <row r="31" spans="2:7">
+      <c r="B31" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C31" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="D31" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E31" s="6" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="31" spans="2:5">
-      <c r="B31" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="C31" s="10" t="s">
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+    </row>
+    <row r="32" spans="2:7">
+      <c r="B32" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C32" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="D32" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="E32" s="6" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="32" spans="2:5">
-      <c r="B32" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C32" s="10" t="s">
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+    </row>
+    <row r="33" spans="2:7">
+      <c r="B33" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C33" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D33" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="E32" s="6" t="s">
+      <c r="E33" s="6" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="33" spans="2:5">
-      <c r="B33" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C33" s="10" t="s">
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+    </row>
+    <row r="34" spans="2:7">
+      <c r="B34" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C34" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="D34" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="E33" s="6" t="s">
+      <c r="E34" s="6" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="34" spans="2:5">
-      <c r="B34" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="C34" s="23" t="s">
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+    </row>
+    <row r="35" spans="2:7">
+      <c r="B35" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C35" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="D35" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="E34" s="6" t="s">
+      <c r="E35" s="6" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="35" spans="2:5">
-      <c r="B35" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="C35" s="23" t="s">
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
+    </row>
+    <row r="36" spans="2:7">
+      <c r="B36" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D36" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="E35" s="6" t="s">
+      <c r="E36" s="6" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="36" spans="2:5">
-      <c r="B36" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="C36" s="23" t="s">
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+    </row>
+    <row r="37" spans="2:7">
+      <c r="B37" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C37" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="D37" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="E36" s="6" t="s">
+      <c r="E37" s="6" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="37" spans="2:5">
-      <c r="B37" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="C37" s="23" t="s">
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+    </row>
+    <row r="38" spans="2:7">
+      <c r="B38" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C38" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="D38" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="E37" s="6" t="s">
+      <c r="E38" s="6" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="38" spans="2:5">
-      <c r="B38" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="C38" s="23" t="s">
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+    </row>
+    <row r="39" spans="2:7">
+      <c r="B39" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C39" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="D39" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="E38" s="6" t="s">
+      <c r="E39" s="6" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="39" spans="2:5">
-      <c r="B39" s="22" t="s">
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+    </row>
+    <row r="40" spans="2:7">
+      <c r="B40" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="C39" s="23" t="s">
-        <v>128</v>
-      </c>
-      <c r="D39" s="5" t="s">
+      <c r="C40" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="D40" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="E39" s="6" t="s">
+      <c r="E40" s="6" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="40" spans="2:5">
-      <c r="B40" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="C40" s="10" t="s">
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+    </row>
+    <row r="41" spans="2:7">
+      <c r="B41" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C41" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="D40" s="5" t="s">
+      <c r="D41" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="E40" s="6" t="s">
+      <c r="E41" s="6" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="41" spans="2:5">
-      <c r="B41" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="C41" s="10" t="s">
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
+    </row>
+    <row r="42" spans="2:7">
+      <c r="B42" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C42" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="D41" s="5" t="s">
+      <c r="D42" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="E41" s="6" t="s">
+      <c r="E42" s="6" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="42" spans="2:5">
-      <c r="B42" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="C42" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="43" spans="2:5">
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
+    </row>
+    <row r="43" spans="2:7">
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
       <c r="D43" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="44" spans="2:5">
+        <v>204</v>
+      </c>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
+    </row>
+    <row r="44" spans="2:7">
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
       <c r="D44" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="45" spans="2:5">
+        <v>205</v>
+      </c>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
+    </row>
+    <row r="45" spans="2:7">
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
       <c r="D45" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="46" spans="2:5">
+        <v>206</v>
+      </c>
+      <c r="F45" s="6"/>
+      <c r="G45" s="6"/>
+    </row>
+    <row r="46" spans="2:7">
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
       <c r="D46" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="47" spans="2:5">
+        <v>207</v>
+      </c>
+      <c r="F46" s="6"/>
+      <c r="G46" s="6"/>
+    </row>
+    <row r="47" spans="2:7">
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
       <c r="D47" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="48" spans="2:5">
+        <v>208</v>
+      </c>
+      <c r="F47" s="6"/>
+      <c r="G47" s="6"/>
+    </row>
+    <row r="48" spans="2:7">
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
-      <c r="D48" s="11" t="s">
-        <v>183</v>
+      <c r="D48" s="5" t="s">
+        <v>182</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="49" spans="2:5">
+        <v>209</v>
+      </c>
+      <c r="F48" s="6"/>
+      <c r="G48" s="6"/>
+    </row>
+    <row r="49" spans="2:7">
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
-      <c r="D49" s="11" t="s">
-        <v>184</v>
+      <c r="D49" s="5" t="s">
+        <v>183</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="50" spans="2:5">
+        <v>210</v>
+      </c>
+      <c r="F49" s="6"/>
+      <c r="G49" s="6"/>
+    </row>
+    <row r="50" spans="2:7">
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
-      <c r="D50" s="11" t="s">
-        <v>185</v>
+      <c r="D50" s="5" t="s">
+        <v>184</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="51" spans="2:5">
+        <v>211</v>
+      </c>
+      <c r="F50" s="6"/>
+      <c r="G50" s="6"/>
+    </row>
+    <row r="51" spans="2:7">
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
-      <c r="D51" s="11" t="s">
-        <v>186</v>
+      <c r="D51" s="5" t="s">
+        <v>185</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="52" spans="2:5">
+        <v>212</v>
+      </c>
+      <c r="F51" s="6"/>
+      <c r="G51" s="6"/>
+    </row>
+    <row r="52" spans="2:7">
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
       <c r="D52" s="5" t="s">
-        <v>400</v>
-      </c>
-      <c r="E52" s="10" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="53" spans="2:5">
+        <v>398</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="F52" s="6"/>
+      <c r="G52" s="6"/>
+    </row>
+    <row r="53" spans="2:7">
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
       <c r="D53" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="E53" s="10" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="54" spans="2:5">
+        <v>180</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="F53" s="6"/>
+      <c r="G53" s="6"/>
+    </row>
+    <row r="54" spans="2:7">
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
       <c r="D54" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="E54" s="10" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="55" spans="2:5">
+        <v>181</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="F54" s="6"/>
+      <c r="G54" s="6"/>
+    </row>
+    <row r="55" spans="2:7">
       <c r="B55" s="6"/>
       <c r="C55" s="6"/>
       <c r="D55" s="5" t="s">
-        <v>401</v>
-      </c>
-      <c r="E55" s="10" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="56" spans="2:5">
+        <v>399</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="F55" s="6"/>
+      <c r="G55" s="6"/>
+    </row>
+    <row r="56" spans="2:7">
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
       <c r="D56" s="5" t="s">
-        <v>402</v>
-      </c>
-      <c r="E56" s="10" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="57" spans="2:5">
+        <v>400</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="F56" s="6"/>
+      <c r="G56" s="6"/>
+    </row>
+    <row r="57" spans="2:7">
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
       <c r="D57" s="5" t="s">
-        <v>403</v>
-      </c>
-      <c r="E57" s="10" t="s">
-        <v>409</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="F57" s="6"/>
+      <c r="G57" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2867,7 +3016,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEB7259B-DE41-4F32-9D2C-8EEFF1CE7AAD}">
-  <dimension ref="B2:R49"/>
+  <dimension ref="B2:R53"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="3" max="3" width="9" style="1"/>
@@ -2888,69 +3037,69 @@
     <col min="22" max="22" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18">
-      <c r="C2" s="15"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="15"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="15"/>
-      <c r="R2" s="16"/>
-    </row>
-    <row r="3" spans="2:18" s="3" customFormat="1">
+    <row r="2" spans="3:18">
+      <c r="C2" s="7"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="7"/>
+      <c r="R2" s="8"/>
+    </row>
+    <row r="3" spans="3:18" s="3" customFormat="1">
       <c r="C3" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="9"/>
+      <c r="D3" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" s="19"/>
+      <c r="F3" s="20"/>
       <c r="I3" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="J3" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="K3" s="8"/>
-      <c r="L3" s="9"/>
+      <c r="J3" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="K3" s="19"/>
+      <c r="L3" s="20"/>
       <c r="O3" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="P3" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="9"/>
-    </row>
-    <row r="4" spans="2:18" s="3" customFormat="1">
+      <c r="P3" s="18" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q3" s="19"/>
+      <c r="R3" s="20"/>
+    </row>
+    <row r="4" spans="3:18" s="3" customFormat="1">
       <c r="C4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="9"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="20"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="J4" s="7"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="9"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="20"/>
       <c r="O4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="8"/>
-      <c r="R4" s="9"/>
-    </row>
-    <row r="5" spans="2:18" s="2" customFormat="1">
+      <c r="P4" s="18"/>
+      <c r="Q4" s="19"/>
+      <c r="R4" s="20"/>
+    </row>
+    <row r="5" spans="3:18" s="2" customFormat="1">
       <c r="C5" s="4" t="s">
         <v>9</v>
       </c>
@@ -2988,1373 +3137,1406 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="2:18">
+    <row r="6" spans="3:18">
       <c r="C6" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>20</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J6" s="6" t="s">
         <v>7</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>20</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P6" s="6" t="s">
         <v>7</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="2:18">
+    <row r="7" spans="3:18">
       <c r="C7" s="5" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>13</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J7" s="6" t="s">
         <v>8</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>13</v>
       </c>
       <c r="O7" s="5" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="P7" s="6" t="s">
         <v>8</v>
       </c>
       <c r="Q7" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="2:18">
-      <c r="C8" s="22" t="s">
-        <v>314</v>
-      </c>
-      <c r="D8" s="23" t="s">
+    <row r="8" spans="3:18">
+      <c r="C8" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="D8" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="11" t="s">
-        <v>60</v>
+      <c r="E8" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I8" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="J8" s="23" t="s">
+      <c r="I8" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="J8" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="K8" s="11" t="s">
-        <v>77</v>
+      <c r="K8" s="5" t="s">
+        <v>76</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="O8" s="22" t="s">
-        <v>259</v>
-      </c>
-      <c r="P8" s="23" t="s">
+      <c r="O8" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="P8" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="Q8" s="11" t="s">
-        <v>258</v>
+      <c r="Q8" s="5" t="s">
+        <v>257</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="2:18">
-      <c r="C9" s="22" t="s">
-        <v>315</v>
-      </c>
-      <c r="D9" s="23" t="s">
+    <row r="9" spans="3:18">
+      <c r="C9" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="D9" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="F9" s="23" t="s">
+      <c r="E9" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="J9" s="23" t="s">
+      <c r="I9" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="J9" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="K9" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="L9" s="23" t="s">
+      <c r="K9" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="L9" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="O9" s="22" t="s">
+      <c r="O9" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="P9" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q9" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="P9" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q9" s="22" t="s">
-        <v>254</v>
-      </c>
-      <c r="R9" s="23" t="s">
+      <c r="R9" s="10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="2:18">
-      <c r="C10" s="11" t="s">
-        <v>369</v>
+    <row r="10" spans="3:18">
+      <c r="C10" s="5" t="s">
+        <v>367</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="F10" s="23" t="s">
+      <c r="E10" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="I10" s="11" t="s">
-        <v>72</v>
+      <c r="I10" s="5" t="s">
+        <v>71</v>
       </c>
       <c r="J10" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="K10" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="L10" s="23" t="s">
+      <c r="K10" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="L10" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="O10" s="11" t="s">
-        <v>255</v>
+      <c r="O10" s="5" t="s">
+        <v>254</v>
       </c>
       <c r="P10" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="Q10" s="22" t="s">
-        <v>256</v>
-      </c>
-      <c r="R10" s="23" t="s">
+      <c r="Q10" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="R10" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:18">
-      <c r="C11" s="22" t="s">
-        <v>316</v>
-      </c>
-      <c r="D11" s="23"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="23"/>
-      <c r="I11" s="22" t="s">
+    <row r="11" spans="3:18">
+      <c r="C11" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="D11" s="10"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="10"/>
+      <c r="I11" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="J11" s="10"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="10"/>
+      <c r="O11" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="P11" s="10"/>
+      <c r="Q11" s="9"/>
+      <c r="R11" s="10"/>
+    </row>
+    <row r="12" spans="3:18">
+      <c r="C12" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="L12" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="O12" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="P12" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q12" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="R12" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="3:18">
+      <c r="C13" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="L13" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="O13" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="P13" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q13" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="R13" s="10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="3:18">
+      <c r="C14" s="5" t="s">
         <v>73</v>
-      </c>
-      <c r="J11" s="23"/>
-      <c r="K11" s="22"/>
-      <c r="L11" s="23"/>
-      <c r="O11" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="P11" s="23"/>
-      <c r="Q11" s="22"/>
-      <c r="R11" s="23"/>
-    </row>
-    <row r="12" spans="2:18">
-      <c r="C12" s="22" t="s">
-        <v>370</v>
-      </c>
-      <c r="D12" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="F12" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="I12" s="22" t="s">
-        <v>214</v>
-      </c>
-      <c r="J12" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="K12" s="22" t="s">
-        <v>80</v>
-      </c>
-      <c r="L12" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="O12" s="22" t="s">
-        <v>220</v>
-      </c>
-      <c r="P12" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q12" s="22" t="s">
-        <v>223</v>
-      </c>
-      <c r="R12" s="23" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="2:18">
-      <c r="C13" s="22" t="s">
-        <v>371</v>
-      </c>
-      <c r="D13" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="F13" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="I13" s="22" t="s">
-        <v>372</v>
-      </c>
-      <c r="J13" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="K13" s="22" t="s">
-        <v>81</v>
-      </c>
-      <c r="L13" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="O13" s="22" t="s">
-        <v>221</v>
-      </c>
-      <c r="P13" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q13" s="22" t="s">
-        <v>224</v>
-      </c>
-      <c r="R13" s="23" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="2:18">
-      <c r="C14" s="5" t="s">
-        <v>74</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="F14" s="23" t="s">
+      <c r="E14" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="F14" s="10" t="s">
         <v>24</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="J14" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="K14" s="22" t="s">
-        <v>215</v>
-      </c>
-      <c r="L14" s="23" t="s">
+      <c r="K14" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="L14" s="10" t="s">
         <v>24</v>
       </c>
       <c r="O14" s="5" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="P14" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="Q14" s="22" t="s">
-        <v>225</v>
-      </c>
-      <c r="R14" s="23" t="s">
+      <c r="Q14" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="R14" s="10" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="2:18">
-      <c r="B15" s="12"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="16"/>
-      <c r="K15" s="15"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="12"/>
-      <c r="N15" s="12"/>
-      <c r="O15" s="15"/>
-      <c r="P15" s="16"/>
-      <c r="Q15" s="15"/>
-      <c r="R15" s="16"/>
-    </row>
-    <row r="16" spans="2:18">
-      <c r="B16" s="12"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="13"/>
-      <c r="L16" s="12"/>
-      <c r="M16" s="12"/>
-      <c r="N16" s="12"/>
-      <c r="O16" s="13"/>
-      <c r="P16" s="12"/>
-      <c r="Q16" s="13"/>
-      <c r="R16" s="12"/>
-    </row>
-    <row r="17" spans="2:18">
-      <c r="B17" s="12"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="12"/>
-      <c r="M17" s="12"/>
-      <c r="N17" s="12"/>
-      <c r="O17" s="13"/>
+    <row r="15" spans="3:18">
+      <c r="C15" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>414</v>
+      </c>
+      <c r="E15" s="9"/>
+      <c r="F15" s="10"/>
+      <c r="I15" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="J15" s="23" t="s">
+        <v>414</v>
+      </c>
+      <c r="K15" s="25"/>
+      <c r="L15" s="26"/>
+      <c r="O15" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="P15" s="23" t="s">
+        <v>414</v>
+      </c>
+      <c r="Q15" s="25"/>
+      <c r="R15" s="26"/>
+    </row>
+    <row r="16" spans="3:18">
+      <c r="C16" s="24"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="26"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="27"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="26"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="23"/>
+      <c r="Q16" s="25"/>
+      <c r="R16" s="26"/>
+    </row>
+    <row r="17" spans="3:18">
+      <c r="C17" s="7"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="8"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="8"/>
+      <c r="O17" s="11"/>
       <c r="P17" s="12"/>
-      <c r="Q17" s="13"/>
-      <c r="R17" s="12"/>
-    </row>
-    <row r="18" spans="2:18">
-      <c r="B18" s="12"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="12"/>
-      <c r="M18" s="12"/>
-      <c r="N18" s="12"/>
-      <c r="O18" s="13"/>
-      <c r="P18" s="12"/>
-      <c r="Q18" s="13"/>
-      <c r="R18" s="12"/>
-    </row>
-    <row r="19" spans="2:18">
-      <c r="B19" s="12"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="18"/>
-      <c r="K19" s="17"/>
-      <c r="L19" s="18"/>
-      <c r="M19" s="12"/>
-      <c r="N19" s="12"/>
-      <c r="O19" s="17"/>
-      <c r="P19" s="18"/>
-      <c r="Q19" s="17"/>
-      <c r="R19" s="18"/>
-    </row>
-    <row r="20" spans="2:18">
-      <c r="C20" s="4" t="s">
+      <c r="Q17" s="7"/>
+      <c r="R17" s="8"/>
+    </row>
+    <row r="18" spans="3:18">
+      <c r="I18" s="1"/>
+      <c r="J18"/>
+      <c r="K18" s="1"/>
+      <c r="L18"/>
+    </row>
+    <row r="19" spans="3:18">
+      <c r="I19" s="1"/>
+      <c r="J19"/>
+      <c r="K19" s="1"/>
+      <c r="L19"/>
+    </row>
+    <row r="20" spans="3:18">
+      <c r="I20" s="1"/>
+      <c r="J20"/>
+      <c r="K20" s="1"/>
+      <c r="L20"/>
+    </row>
+    <row r="21" spans="3:18">
+      <c r="C21" s="7"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="8"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="8"/>
+      <c r="O21" s="7"/>
+      <c r="P21" s="8"/>
+      <c r="Q21" s="7"/>
+      <c r="R21" s="8"/>
+    </row>
+    <row r="22" spans="3:18">
+      <c r="C22" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D20" s="14" t="s">
+      <c r="D22" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="I22" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J22" s="21" t="s">
         <v>227</v>
       </c>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="I20" s="4" t="s">
+      <c r="K22" s="21"/>
+      <c r="L22" s="21"/>
+      <c r="O22" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="J20" s="14" t="s">
+      <c r="P22" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="K20" s="14"/>
-      <c r="L20" s="14"/>
-      <c r="O20" s="4" t="s">
+      <c r="Q22" s="21"/>
+      <c r="R22" s="21"/>
+    </row>
+    <row r="23" spans="3:18">
+      <c r="C23" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="I23" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J23" s="21"/>
+      <c r="K23" s="21"/>
+      <c r="L23" s="21"/>
+      <c r="O23" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="P23" s="21"/>
+      <c r="Q23" s="21"/>
+      <c r="R23" s="21"/>
+    </row>
+    <row r="24" spans="3:18">
+      <c r="C24" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="L24" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="O24" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="P24" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q24" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="R24" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18">
+      <c r="C25" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="L25" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="O25" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="P25" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q25" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="R25" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18">
+      <c r="C26" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="O26" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="P26" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q26" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="R26" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18">
+      <c r="C27" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="J27" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="L27" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="O27" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="P27" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q27" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="R27" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18">
+      <c r="C28" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="J28" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="K28" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="L28" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="O28" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="P28" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q28" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="R28" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18">
+      <c r="C29" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K29" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="L29" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="O29" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="P29" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q29" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="R29" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18">
+      <c r="C30" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="D30" s="10"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="10"/>
+      <c r="I30" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="J30" s="10"/>
+      <c r="K30" s="9"/>
+      <c r="L30" s="10"/>
+      <c r="O30" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="P30" s="10"/>
+      <c r="Q30" s="9"/>
+      <c r="R30" s="10"/>
+    </row>
+    <row r="31" spans="3:18">
+      <c r="C31" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="J31" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="K31" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="L31" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="O31" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="P31" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q31" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="R31" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18">
+      <c r="C32" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="J32" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K32" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="L32" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="O32" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="P32" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q32" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="R32" s="10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18">
+      <c r="C33" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="K33" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="L33" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="O33" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="P33" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q33" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="R33" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18">
+      <c r="C34" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="D34" s="23" t="s">
+        <v>414</v>
+      </c>
+      <c r="E34" s="25"/>
+      <c r="F34" s="26"/>
+      <c r="I34" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="J34" s="23" t="s">
+        <v>414</v>
+      </c>
+      <c r="K34" s="25"/>
+      <c r="L34" s="26"/>
+      <c r="O34" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="P34" s="23" t="s">
+        <v>414</v>
+      </c>
+      <c r="Q34" s="25"/>
+      <c r="R34" s="26"/>
+    </row>
+    <row r="35" spans="2:18">
+      <c r="C35" s="7"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="8"/>
+      <c r="I35" s="7"/>
+      <c r="J35" s="8"/>
+      <c r="K35" s="7"/>
+      <c r="L35" s="8"/>
+      <c r="O35" s="7"/>
+      <c r="P35" s="8"/>
+      <c r="Q35" s="7"/>
+      <c r="R35" s="8"/>
+    </row>
+    <row r="39" spans="2:18">
+      <c r="B39" s="8"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="7"/>
+      <c r="H39" s="7"/>
+      <c r="I39" s="8"/>
+      <c r="J39" s="7"/>
+      <c r="K39" s="8"/>
+      <c r="L39" s="7"/>
+      <c r="M39" s="8"/>
+      <c r="O39" s="7"/>
+      <c r="P39" s="8"/>
+      <c r="Q39" s="7"/>
+      <c r="R39" s="8"/>
+    </row>
+    <row r="40" spans="2:18">
+      <c r="B40" s="8"/>
+      <c r="C40" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="P20" s="14" t="s">
+      <c r="D40" s="18" t="s">
         <v>229</v>
       </c>
-      <c r="Q20" s="14"/>
-      <c r="R20" s="14"/>
-    </row>
-    <row r="21" spans="2:18">
-      <c r="C21" s="4" t="s">
+      <c r="E40" s="19"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="7"/>
+      <c r="H40" s="7"/>
+      <c r="I40" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J40" s="18" t="s">
+        <v>230</v>
+      </c>
+      <c r="K40" s="19"/>
+      <c r="L40" s="20"/>
+      <c r="M40" s="8"/>
+      <c r="O40" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P40" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q40" s="19"/>
+      <c r="R40" s="20"/>
+    </row>
+    <row r="41" spans="2:18">
+      <c r="B41" s="8"/>
+      <c r="C41" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="I21" s="4" t="s">
+      <c r="D41" s="18"/>
+      <c r="E41" s="19"/>
+      <c r="F41" s="20"/>
+      <c r="G41" s="7"/>
+      <c r="H41" s="7"/>
+      <c r="I41" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="J21" s="14"/>
-      <c r="K21" s="14"/>
-      <c r="L21" s="14"/>
-      <c r="O21" s="4" t="s">
+      <c r="J41" s="18"/>
+      <c r="K41" s="19"/>
+      <c r="L41" s="20"/>
+      <c r="M41" s="8"/>
+      <c r="O41" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="P21" s="14"/>
-      <c r="Q21" s="14"/>
-      <c r="R21" s="14"/>
-    </row>
-    <row r="22" spans="2:18">
-      <c r="C22" s="4" t="s">
+      <c r="P41" s="18"/>
+      <c r="Q41" s="19"/>
+      <c r="R41" s="20"/>
+    </row>
+    <row r="42" spans="2:18">
+      <c r="B42" s="8"/>
+      <c r="C42" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D42" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E42" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F42" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="I22" s="4" t="s">
+      <c r="G42" s="7"/>
+      <c r="H42" s="7"/>
+      <c r="I42" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J22" s="4" t="s">
+      <c r="J42" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K22" s="4" t="s">
+      <c r="K42" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="L22" s="4" t="s">
+      <c r="L42" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="O22" s="4" t="s">
+      <c r="M42" s="8"/>
+      <c r="O42" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="P22" s="4" t="s">
+      <c r="P42" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="Q22" s="4" t="s">
+      <c r="Q42" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="R22" s="4" t="s">
+      <c r="R42" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="2:18">
-      <c r="C23" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="D23" s="6" t="s">
+    <row r="43" spans="2:18">
+      <c r="B43" s="8"/>
+      <c r="C43" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="D43" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E23" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="F23" s="6" t="s">
+      <c r="E43" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="F43" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="I23" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="J23" s="6" t="s">
+      <c r="G43" s="7"/>
+      <c r="H43" s="7"/>
+      <c r="I43" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="J43" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="K23" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="L23" s="6" t="s">
+      <c r="K43" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="L43" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="O23" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="P23" s="6" t="s">
+      <c r="M43" s="8"/>
+      <c r="O43" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="P43" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="Q23" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="R23" s="6" t="s">
+      <c r="Q43" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="R43" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="2:18">
-      <c r="C24" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="D24" s="6" t="s">
+    <row r="44" spans="2:18">
+      <c r="B44" s="8"/>
+      <c r="C44" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="D44" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E24" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="F24" s="6" t="s">
+      <c r="E44" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="F44" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I24" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="J24" s="6" t="s">
+      <c r="G44" s="7"/>
+      <c r="H44" s="7"/>
+      <c r="I44" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="J44" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="K24" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="L24" s="6" t="s">
+      <c r="K44" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="L44" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O24" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="P24" s="6" t="s">
+      <c r="M44" s="8"/>
+      <c r="O44" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="P44" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="Q24" s="5" t="s">
+      <c r="Q44" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="R24" s="6" t="s">
+      <c r="R44" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="2:18">
-      <c r="C25" s="22" t="s">
-        <v>363</v>
-      </c>
-      <c r="D25" s="23" t="s">
+    <row r="45" spans="2:18">
+      <c r="B45" s="8"/>
+      <c r="C45" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="D45" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="E25" s="11" t="s">
-        <v>236</v>
-      </c>
-      <c r="F25" s="6" t="s">
+      <c r="E45" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="F45" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I25" s="22" t="s">
-        <v>283</v>
-      </c>
-      <c r="J25" s="23" t="s">
+      <c r="G45" s="7"/>
+      <c r="H45" s="7"/>
+      <c r="I45" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="J45" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="K25" s="11" t="s">
-        <v>245</v>
-      </c>
-      <c r="L25" s="6" t="s">
+      <c r="K45" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="L45" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="O25" s="22" t="s">
-        <v>357</v>
-      </c>
-      <c r="P25" s="23" t="s">
+      <c r="M45" s="8"/>
+      <c r="O45" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="P45" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="Q25" s="11" t="s">
-        <v>261</v>
-      </c>
-      <c r="R25" s="6" t="s">
+      <c r="Q45" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="R45" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="2:18">
-      <c r="C26" s="22" t="s">
-        <v>364</v>
-      </c>
-      <c r="D26" s="23" t="s">
+    <row r="46" spans="2:18">
+      <c r="B46" s="8"/>
+      <c r="C46" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="D46" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E26" s="22" t="s">
-        <v>237</v>
-      </c>
-      <c r="F26" s="23" t="s">
+      <c r="E46" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="F46" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="I26" s="22" t="s">
-        <v>284</v>
-      </c>
-      <c r="J26" s="23" t="s">
+      <c r="G46" s="7"/>
+      <c r="H46" s="7"/>
+      <c r="I46" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="J46" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="K26" s="22" t="s">
-        <v>246</v>
-      </c>
-      <c r="L26" s="23" t="s">
+      <c r="K46" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="L46" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="O26" s="22" t="s">
-        <v>358</v>
-      </c>
-      <c r="P26" s="23" t="s">
+      <c r="M46" s="8"/>
+      <c r="O46" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="P46" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="Q26" s="22" t="s">
-        <v>262</v>
-      </c>
-      <c r="R26" s="23" t="s">
+      <c r="Q46" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="R46" s="10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="2:18">
-      <c r="C27" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="D27" s="6" t="s">
+    <row r="47" spans="2:18">
+      <c r="B47" s="8"/>
+      <c r="C47" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="D47" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E27" s="22" t="s">
-        <v>238</v>
-      </c>
-      <c r="F27" s="23" t="s">
+      <c r="E47" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="F47" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="I27" s="11" t="s">
-        <v>285</v>
-      </c>
-      <c r="J27" s="6" t="s">
+      <c r="G47" s="7"/>
+      <c r="H47" s="7"/>
+      <c r="I47" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="J47" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="K27" s="22" t="s">
-        <v>247</v>
-      </c>
-      <c r="L27" s="23" t="s">
+      <c r="K47" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="L47" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="O27" s="11" t="s">
-        <v>359</v>
-      </c>
-      <c r="P27" s="6" t="s">
+      <c r="M47" s="8"/>
+      <c r="O47" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="P47" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="Q27" s="22" t="s">
-        <v>263</v>
-      </c>
-      <c r="R27" s="23" t="s">
+      <c r="Q47" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="R47" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="2:18">
-      <c r="C28" s="22" t="s">
-        <v>366</v>
-      </c>
-      <c r="D28" s="23"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="23"/>
-      <c r="I28" s="22" t="s">
-        <v>286</v>
-      </c>
-      <c r="J28" s="23"/>
-      <c r="K28" s="22"/>
-      <c r="L28" s="23"/>
-      <c r="O28" s="22" t="s">
-        <v>360</v>
-      </c>
-      <c r="P28" s="23"/>
-      <c r="Q28" s="22"/>
-      <c r="R28" s="23"/>
-    </row>
-    <row r="29" spans="2:18">
-      <c r="C29" s="22" t="s">
-        <v>367</v>
-      </c>
-      <c r="D29" s="23" t="s">
+    <row r="48" spans="2:18">
+      <c r="B48" s="8"/>
+      <c r="C48" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="D48" s="10"/>
+      <c r="E48" s="9"/>
+      <c r="F48" s="10"/>
+      <c r="G48" s="7"/>
+      <c r="H48" s="7"/>
+      <c r="I48" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="J48" s="10"/>
+      <c r="K48" s="9"/>
+      <c r="L48" s="10"/>
+      <c r="M48" s="8"/>
+      <c r="O48" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="P48" s="10"/>
+      <c r="Q48" s="9"/>
+      <c r="R48" s="10"/>
+    </row>
+    <row r="49" spans="2:18">
+      <c r="B49" s="8"/>
+      <c r="C49" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="D49" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E29" s="22" t="s">
-        <v>239</v>
-      </c>
-      <c r="F29" s="23" t="s">
+      <c r="E49" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="F49" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I29" s="22" t="s">
-        <v>287</v>
-      </c>
-      <c r="J29" s="23" t="s">
+      <c r="G49" s="7"/>
+      <c r="H49" s="7"/>
+      <c r="I49" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="J49" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K29" s="22" t="s">
-        <v>248</v>
-      </c>
-      <c r="L29" s="23" t="s">
+      <c r="K49" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="L49" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="O29" s="22" t="s">
-        <v>361</v>
-      </c>
-      <c r="P29" s="23" t="s">
+      <c r="M49" s="8"/>
+      <c r="O49" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="P49" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="Q29" s="22" t="s">
-        <v>250</v>
-      </c>
-      <c r="R29" s="23" t="s">
+      <c r="Q49" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="R49" s="10" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="2:18">
-      <c r="C30" s="22" t="s">
-        <v>368</v>
-      </c>
-      <c r="D30" s="23" t="s">
+    <row r="50" spans="2:18">
+      <c r="B50" s="8"/>
+      <c r="C50" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="D50" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="E30" s="22" t="s">
-        <v>240</v>
-      </c>
-      <c r="F30" s="23" t="s">
+      <c r="E50" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="F50" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="I30" s="22" t="s">
-        <v>288</v>
-      </c>
-      <c r="J30" s="23" t="s">
+      <c r="G50" s="7"/>
+      <c r="H50" s="7"/>
+      <c r="I50" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="J50" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="K30" s="22" t="s">
-        <v>260</v>
-      </c>
-      <c r="L30" s="23" t="s">
+      <c r="K50" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="L50" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="O30" s="22" t="s">
-        <v>362</v>
-      </c>
-      <c r="P30" s="23" t="s">
+      <c r="M50" s="8"/>
+      <c r="O50" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="P50" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="Q30" s="22" t="s">
-        <v>251</v>
-      </c>
-      <c r="R30" s="23" t="s">
+      <c r="Q50" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="R50" s="10" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="31" spans="2:18">
-      <c r="C31" s="5" t="s">
-        <v>377</v>
-      </c>
-      <c r="D31" s="6" t="s">
+    <row r="51" spans="2:18">
+      <c r="B51" s="8"/>
+      <c r="C51" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="D51" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E31" s="22" t="s">
-        <v>241</v>
-      </c>
-      <c r="F31" s="23" t="s">
+      <c r="E51" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="F51" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="I31" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="J31" s="6" t="s">
+      <c r="G51" s="7"/>
+      <c r="H51" s="7"/>
+      <c r="I51" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="J51" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="K31" s="22" t="s">
-        <v>242</v>
-      </c>
-      <c r="L31" s="23" t="s">
+      <c r="K51" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="L51" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="O31" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="P31" s="6" t="s">
+      <c r="M51" s="8"/>
+      <c r="O51" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="P51" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="Q31" s="22" t="s">
-        <v>252</v>
-      </c>
-      <c r="R31" s="23" t="s">
+      <c r="Q51" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="R51" s="10" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="32" spans="2:18">
-      <c r="C32" s="15"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="16"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="16"/>
-      <c r="K32" s="15"/>
-      <c r="L32" s="16"/>
-      <c r="O32" s="15"/>
-      <c r="P32" s="16"/>
-      <c r="Q32" s="15"/>
-      <c r="R32" s="16"/>
-    </row>
-    <row r="36" spans="2:18">
-      <c r="B36" s="16"/>
-      <c r="C36" s="15"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="15"/>
-      <c r="H36" s="15"/>
-      <c r="I36" s="16"/>
-      <c r="J36" s="15"/>
-      <c r="K36" s="16"/>
-      <c r="L36" s="15"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="19"/>
-      <c r="O36" s="15"/>
-      <c r="P36" s="16"/>
-      <c r="Q36" s="15"/>
-      <c r="R36" s="16"/>
-    </row>
-    <row r="37" spans="2:18">
-      <c r="B37" s="16"/>
-      <c r="C37" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="E37" s="8"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="15"/>
-      <c r="H37" s="15"/>
-      <c r="I37" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J37" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="K37" s="8"/>
-      <c r="L37" s="9"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="19"/>
-      <c r="O37" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="P37" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="Q37" s="8"/>
-      <c r="R37" s="9"/>
-    </row>
-    <row r="38" spans="2:18">
-      <c r="B38" s="16"/>
-      <c r="C38" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D38" s="7"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="15"/>
-      <c r="H38" s="15"/>
-      <c r="I38" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J38" s="7"/>
-      <c r="K38" s="8"/>
-      <c r="L38" s="9"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="19"/>
-      <c r="O38" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="P38" s="7"/>
-      <c r="Q38" s="8"/>
-      <c r="R38" s="9"/>
-    </row>
-    <row r="39" spans="2:18">
-      <c r="B39" s="16"/>
-      <c r="C39" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G39" s="15"/>
-      <c r="H39" s="15"/>
-      <c r="I39" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J39" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K39" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="L39" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="M39" s="16"/>
-      <c r="N39" s="19"/>
-      <c r="O39" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="P39" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q39" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="R39" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" spans="2:18">
-      <c r="B40" s="16"/>
-      <c r="C40" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G40" s="15"/>
-      <c r="H40" s="15"/>
-      <c r="I40" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="J40" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="K40" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="L40" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="M40" s="16"/>
-      <c r="N40" s="19"/>
-      <c r="O40" s="5" t="s">
+    <row r="52" spans="2:18">
+      <c r="B52" s="8"/>
+      <c r="C52" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="D52" s="23" t="s">
+        <v>414</v>
+      </c>
+      <c r="E52" s="25"/>
+      <c r="F52" s="26"/>
+      <c r="G52" s="7"/>
+      <c r="H52" s="7"/>
+      <c r="I52" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="P40" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q40" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="R40" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="41" spans="2:18">
-      <c r="B41" s="16"/>
-      <c r="C41" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G41" s="15"/>
-      <c r="H41" s="15"/>
-      <c r="I41" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="J41" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="K41" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="L41" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="M41" s="16"/>
-      <c r="N41" s="19"/>
-      <c r="O41" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="P41" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q41" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="R41" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="42" spans="2:18">
-      <c r="B42" s="16"/>
-      <c r="C42" s="22" t="s">
-        <v>292</v>
-      </c>
-      <c r="D42" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="E42" s="11" t="s">
-        <v>266</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G42" s="15"/>
-      <c r="H42" s="15"/>
-      <c r="I42" s="22" t="s">
-        <v>352</v>
-      </c>
-      <c r="J42" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="K42" s="11" t="s">
-        <v>274</v>
-      </c>
-      <c r="L42" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="M42" s="16"/>
-      <c r="N42" s="19"/>
-      <c r="O42" s="22" t="s">
-        <v>303</v>
-      </c>
-      <c r="P42" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q42" s="11" t="s">
-        <v>347</v>
-      </c>
-      <c r="R42" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="43" spans="2:18">
-      <c r="B43" s="16"/>
-      <c r="C43" s="22" t="s">
-        <v>293</v>
-      </c>
-      <c r="D43" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="E43" s="22" t="s">
-        <v>267</v>
-      </c>
-      <c r="F43" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="G43" s="15"/>
-      <c r="H43" s="15"/>
-      <c r="I43" s="22" t="s">
-        <v>353</v>
-      </c>
-      <c r="J43" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="K43" s="22" t="s">
-        <v>275</v>
-      </c>
-      <c r="L43" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="M43" s="16"/>
-      <c r="N43" s="19"/>
-      <c r="O43" s="22" t="s">
-        <v>304</v>
-      </c>
-      <c r="P43" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q43" s="22" t="s">
-        <v>348</v>
-      </c>
-      <c r="R43" s="23" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="44" spans="2:18">
-      <c r="B44" s="16"/>
-      <c r="C44" s="11" t="s">
-        <v>294</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E44" s="22" t="s">
-        <v>268</v>
-      </c>
-      <c r="F44" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="G44" s="15"/>
-      <c r="H44" s="15"/>
-      <c r="I44" s="11" t="s">
-        <v>354</v>
-      </c>
-      <c r="J44" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="K44" s="22" t="s">
-        <v>276</v>
-      </c>
-      <c r="L44" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="M44" s="16"/>
-      <c r="N44" s="19"/>
-      <c r="O44" s="11" t="s">
-        <v>305</v>
-      </c>
-      <c r="P44" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q44" s="22" t="s">
-        <v>349</v>
-      </c>
-      <c r="R44" s="23" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="45" spans="2:18">
-      <c r="B45" s="16"/>
-      <c r="C45" s="22" t="s">
-        <v>295</v>
-      </c>
-      <c r="D45" s="23"/>
-      <c r="E45" s="22"/>
-      <c r="F45" s="23"/>
-      <c r="G45" s="15"/>
-      <c r="H45" s="15"/>
-      <c r="I45" s="22" t="s">
-        <v>355</v>
-      </c>
-      <c r="J45" s="23"/>
-      <c r="K45" s="22"/>
-      <c r="L45" s="23"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="19"/>
-      <c r="O45" s="22" t="s">
-        <v>306</v>
-      </c>
-      <c r="P45" s="23"/>
-      <c r="Q45" s="22"/>
-      <c r="R45" s="23"/>
-    </row>
-    <row r="46" spans="2:18">
-      <c r="B46" s="16"/>
-      <c r="C46" s="22" t="s">
-        <v>296</v>
-      </c>
-      <c r="D46" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="E46" s="22" t="s">
-        <v>269</v>
-      </c>
-      <c r="F46" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="G46" s="15"/>
-      <c r="H46" s="15"/>
-      <c r="I46" s="22" t="s">
-        <v>299</v>
-      </c>
-      <c r="J46" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="K46" s="22" t="s">
-        <v>277</v>
-      </c>
-      <c r="L46" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="M46" s="16"/>
-      <c r="N46" s="19"/>
-      <c r="O46" s="22" t="s">
-        <v>307</v>
-      </c>
-      <c r="P46" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q46" s="22" t="s">
-        <v>350</v>
-      </c>
-      <c r="R46" s="23" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="47" spans="2:18">
-      <c r="B47" s="16"/>
-      <c r="C47" s="22" t="s">
-        <v>297</v>
-      </c>
-      <c r="D47" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="E47" s="22" t="s">
-        <v>270</v>
-      </c>
-      <c r="F47" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="G47" s="15"/>
-      <c r="H47" s="15"/>
-      <c r="I47" s="22" t="s">
-        <v>300</v>
-      </c>
-      <c r="J47" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="K47" s="22" t="s">
-        <v>345</v>
-      </c>
-      <c r="L47" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="M47" s="16"/>
-      <c r="N47" s="19"/>
-      <c r="O47" s="22" t="s">
-        <v>308</v>
-      </c>
-      <c r="P47" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q47" s="22" t="s">
-        <v>280</v>
-      </c>
-      <c r="R47" s="23" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="48" spans="2:18">
-      <c r="B48" s="16"/>
-      <c r="C48" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E48" s="22" t="s">
-        <v>271</v>
-      </c>
-      <c r="F48" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="G48" s="15"/>
-      <c r="H48" s="15"/>
-      <c r="I48" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="J48" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="K48" s="22" t="s">
-        <v>278</v>
-      </c>
-      <c r="L48" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="M48" s="16"/>
-      <c r="N48" s="19"/>
-      <c r="O48" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="P48" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q48" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="R48" s="23" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="49" spans="2:18">
-      <c r="B49" s="16"/>
-      <c r="C49" s="15"/>
-      <c r="D49" s="16"/>
-      <c r="E49" s="15"/>
-      <c r="F49" s="16"/>
-      <c r="G49" s="15"/>
-      <c r="H49" s="15"/>
-      <c r="I49" s="16"/>
-      <c r="J49" s="15"/>
-      <c r="K49" s="16"/>
-      <c r="L49" s="15"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="19"/>
-      <c r="O49" s="20"/>
-      <c r="P49" s="21"/>
-      <c r="Q49" s="20"/>
-      <c r="R49" s="21"/>
+      <c r="J52" s="23" t="s">
+        <v>414</v>
+      </c>
+      <c r="K52" s="25"/>
+      <c r="L52" s="26"/>
+      <c r="M52" s="8"/>
+      <c r="O52" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="P52" s="23" t="s">
+        <v>414</v>
+      </c>
+      <c r="Q52" s="25"/>
+      <c r="R52" s="26"/>
+    </row>
+    <row r="53" spans="2:18">
+      <c r="B53" s="8"/>
+      <c r="C53" s="7"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="7"/>
+      <c r="F53" s="8"/>
+      <c r="G53" s="7"/>
+      <c r="H53" s="7"/>
+      <c r="I53" s="8"/>
+      <c r="J53" s="7"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="7"/>
+      <c r="M53" s="8"/>
+      <c r="O53" s="7"/>
+      <c r="P53" s="8"/>
+      <c r="Q53" s="7"/>
+      <c r="R53" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="J37:L37"/>
-    <mergeCell ref="P37:R37"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="J38:L38"/>
-    <mergeCell ref="P38:R38"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="J20:L20"/>
-    <mergeCell ref="J21:L21"/>
-    <mergeCell ref="P20:R20"/>
-    <mergeCell ref="P21:R21"/>
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="J3:L3"/>
     <mergeCell ref="J4:L4"/>
     <mergeCell ref="P3:R3"/>
     <mergeCell ref="P4:R4"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="P22:R22"/>
+    <mergeCell ref="P23:R23"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="J40:L40"/>
+    <mergeCell ref="P40:R40"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="J41:L41"/>
+    <mergeCell ref="P41:R41"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4363,7 +4545,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EA47EA4-7B31-40FE-9AED-CE45ED8264B2}">
-  <dimension ref="B2:O28"/>
+  <dimension ref="B2:O23"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="3" max="3" width="20.625" customWidth="1"/>
@@ -4375,52 +4557,52 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:15">
-      <c r="B2" s="15"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="16"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="8"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
     </row>
     <row r="3" spans="2:15">
       <c r="B3" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="D3" s="8"/>
-      <c r="E3" s="9"/>
+      <c r="C3" s="18" t="s">
+        <v>308</v>
+      </c>
+      <c r="D3" s="19"/>
+      <c r="E3" s="20"/>
       <c r="G3" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H3" s="14" t="s">
-        <v>324</v>
-      </c>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
+      <c r="H3" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
+      <c r="L3" s="21"/>
     </row>
     <row r="4" spans="2:15">
       <c r="B4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="9"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="20"/>
       <c r="G4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
     </row>
     <row r="5" spans="2:15">
       <c r="B5" s="4" t="s">
@@ -4453,74 +4635,74 @@
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="N5" s="30" t="s">
-        <v>399</v>
+      <c r="N5" s="17" t="s">
+        <v>397</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="6" spans="2:15">
       <c r="B6" s="5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>20</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>7</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J6" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="K6" s="29" t="s">
-        <v>380</v>
+      <c r="K6" s="16" t="s">
+        <v>378</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="N6" s="5">
         <v>0</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="7" spans="2:15">
       <c r="B7" s="22" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="D7" s="22" t="s">
-        <v>327</v>
-      </c>
-      <c r="E7" s="23" t="s">
+        <v>311</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="E7" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G7" s="11" t="s">
-        <v>334</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>339</v>
-      </c>
-      <c r="I7" s="22" t="s">
-        <v>323</v>
-      </c>
-      <c r="J7" s="23" t="s">
+      <c r="G7" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="J7" s="10" t="s">
         <v>13</v>
       </c>
       <c r="K7" s="6"/>
@@ -4529,32 +4711,32 @@
         <v>1</v>
       </c>
       <c r="O7" s="6" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="8" spans="2:15">
-      <c r="B8" s="22" t="s">
-        <v>319</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>311</v>
-      </c>
-      <c r="D8" s="22" t="s">
-        <v>328</v>
-      </c>
-      <c r="E8" s="23" t="s">
+      <c r="B8" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="G8" s="22" t="s">
-        <v>335</v>
-      </c>
-      <c r="H8" s="23" t="s">
-        <v>340</v>
-      </c>
-      <c r="I8" s="22" t="s">
-        <v>331</v>
-      </c>
-      <c r="J8" s="23" t="s">
+      <c r="G8" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="J8" s="10" t="s">
         <v>14</v>
       </c>
       <c r="K8" s="6"/>
@@ -4563,33 +4745,33 @@
         <v>2</v>
       </c>
       <c r="O8" s="6" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="9" spans="2:15">
-      <c r="B9" s="22" t="s">
-        <v>320</v>
-      </c>
-      <c r="C9" s="23" t="s">
+      <c r="B9" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="C9" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="22" t="s">
-        <v>322</v>
-      </c>
-      <c r="E9" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="G9" s="22" t="s">
-        <v>336</v>
-      </c>
-      <c r="H9" s="23" t="s">
+      <c r="D9" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="H9" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="I9" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J9" s="23" t="s">
-        <v>338</v>
+      <c r="I9" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>337</v>
       </c>
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
@@ -4597,32 +4779,32 @@
         <v>3</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="10" spans="2:15">
       <c r="B10" s="22" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="22" t="s">
-        <v>329</v>
-      </c>
-      <c r="E10" s="23" t="s">
+      <c r="D10" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="E10" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="22" t="s">
-        <v>337</v>
-      </c>
-      <c r="H10" s="23" t="s">
+      <c r="G10" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="H10" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="I10" s="22" t="s">
-        <v>333</v>
-      </c>
-      <c r="J10" s="23" t="s">
+      <c r="I10" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="J10" s="10" t="s">
         <v>15</v>
       </c>
       <c r="K10" s="6"/>
@@ -4631,24 +4813,22 @@
         <v>4</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="11" spans="2:15">
       <c r="B11" s="5" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="11"/>
+      <c r="D11" s="5"/>
       <c r="E11" s="6"/>
       <c r="G11" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>342</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="H11" s="6"/>
       <c r="I11" s="5"/>
       <c r="J11" s="6"/>
       <c r="K11" s="6"/>
@@ -4657,7 +4837,7 @@
         <v>5</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="12" spans="2:15">
@@ -4666,7 +4846,7 @@
       <c r="D12" s="5"/>
       <c r="E12" s="6"/>
       <c r="G12" s="5" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>19</v>
@@ -4679,7 +4859,7 @@
         <v>6</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="13" spans="2:15">
@@ -4687,8 +4867,12 @@
       <c r="C13" s="6"/>
       <c r="D13" s="5"/>
       <c r="E13" s="6"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="6"/>
+      <c r="G13" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>412</v>
+      </c>
       <c r="I13" s="5"/>
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
@@ -4697,7 +4881,7 @@
         <v>7</v>
       </c>
       <c r="O13" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="14" spans="2:15">
@@ -4715,14 +4899,14 @@
         <v>8</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="15" spans="2:15">
-      <c r="B15" s="15"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="16"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="8"/>
       <c r="G15" s="5"/>
       <c r="H15" s="6"/>
       <c r="I15" s="5"/>
@@ -4733,7 +4917,7 @@
         <v>9</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="16" spans="2:15">
@@ -4747,7 +4931,7 @@
         <v>10</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="17" spans="7:15">
@@ -4761,7 +4945,7 @@
         <v>11</v>
       </c>
       <c r="O17" s="6" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="18" spans="7:15">
@@ -4775,7 +4959,7 @@
         <v>12</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="19" spans="7:15">
@@ -4789,7 +4973,7 @@
         <v>13</v>
       </c>
       <c r="O19" s="6" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="20" spans="7:15">
@@ -4803,7 +4987,7 @@
         <v>14</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="21" spans="7:15">
@@ -4817,7 +5001,7 @@
         <v>15</v>
       </c>
       <c r="O21" s="6" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="22" spans="7:15">
@@ -4829,52 +5013,12 @@
       <c r="L22" s="6"/>
     </row>
     <row r="23" spans="7:15">
-      <c r="G23" s="5"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
-    </row>
-    <row r="24" spans="7:15">
-      <c r="G24" s="5"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6"/>
-    </row>
-    <row r="25" spans="7:15">
-      <c r="G25" s="5"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="5"/>
-      <c r="J25" s="6"/>
-      <c r="K25" s="6"/>
-      <c r="L25" s="6"/>
-    </row>
-    <row r="26" spans="7:15">
-      <c r="G26" s="5"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="6"/>
-      <c r="K26" s="6"/>
-      <c r="L26" s="6"/>
-    </row>
-    <row r="27" spans="7:15">
-      <c r="G27" s="5"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="6"/>
-      <c r="K27" s="6"/>
-      <c r="L27" s="6"/>
-    </row>
-    <row r="28" spans="7:15">
-      <c r="G28" s="28"/>
-      <c r="H28" s="25"/>
-      <c r="I28" s="24"/>
-      <c r="J28" s="25"/>
-      <c r="K28" s="25"/>
-      <c r="L28" s="25"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
+      <c r="L23" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/PLC/IO List.xlsx
+++ b/PLC/IO List.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EZENIC\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4D24A0B-87B2-4047-854A-73ACBE4FBCC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D6731B3-A9FE-42EB-B153-3414E0B41A9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="12405" windowHeight="15585" firstSheet="1" activeTab="2" xr2:uid="{E8A3CD3B-D612-4B37-A180-F6C335096DC9}"/>
+    <workbookView xWindow="3990" yWindow="3555" windowWidth="21600" windowHeight="11295" xr2:uid="{E8A3CD3B-D612-4B37-A180-F6C335096DC9}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="2" r:id="rId1"/>
     <sheet name="ROBOT" sheetId="1" r:id="rId2"/>
     <sheet name="기타 장비" sheetId="3" r:id="rId3"/>
+    <sheet name="공정별 로봇 티칭맵" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1012" uniqueCount="738">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="775">
   <si>
     <t>X10</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2643,12 +2644,158 @@
   <si>
     <t>M2224</t>
   </si>
+  <si>
+    <t>경유지점
+P[1]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>원점
+P[0]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>셀 대차
+P[2]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGV
+P[3]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하우징
+대차
+P[2]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGV
+P[2]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2공정(접착제)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6공정(접착제)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8공정(접착제)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGV
+P[2~5]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>볼트공급
+P[2]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGV
+P[3~4]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGV
+P[3~8]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M301</t>
+  </si>
+  <si>
+    <t>M302</t>
+  </si>
+  <si>
+    <t>M303</t>
+  </si>
+  <si>
+    <t>M304</t>
+  </si>
+  <si>
+    <t>M305</t>
+  </si>
+  <si>
+    <t>M306</t>
+  </si>
+  <si>
+    <t>M307</t>
+  </si>
+  <si>
+    <t>M308</t>
+  </si>
+  <si>
+    <t>M309</t>
+  </si>
+  <si>
+    <t>M310</t>
+  </si>
+  <si>
+    <t>M311</t>
+  </si>
+  <si>
+    <t>M312</t>
+  </si>
+  <si>
+    <t>M313</t>
+  </si>
+  <si>
+    <t>경화1 공정 완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경화공정1 AGV 배출 신호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경화공정1 완료 후 문닫힘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경화2 공정 완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경화공정2 AGV 배출 신호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경화공정2 완료 후 문닫힘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경화3 공정 완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경화공정3 AGV 배출 신호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경화공정3 완료 후 문닫힘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2715,7 +2862,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2746,8 +2893,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="36">
     <border>
       <left/>
       <right/>
@@ -2818,13 +2983,349 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2890,6 +3391,168 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3238,7 +3901,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{228BF0B7-E586-4CC1-BF31-0F024BABECA2}">
   <dimension ref="B3:K57"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="3" width="9" style="1"/>
     <col min="4" max="4" width="30.625" customWidth="1"/>
@@ -3250,48 +3913,48 @@
     <col min="11" max="11" width="30.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B3" s="23" t="s">
+    <row r="3" spans="2:11">
+      <c r="B3" s="77" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="24"/>
-      <c r="D3" s="22" t="s">
+      <c r="C3" s="78"/>
+      <c r="D3" s="76" t="s">
         <v>55</v>
       </c>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="22"/>
-    </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B4" s="23" t="s">
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
+      <c r="K3" s="76"/>
+    </row>
+    <row r="4" spans="2:11">
+      <c r="B4" s="77" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="24"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="22"/>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B5" s="23" t="s">
+      <c r="C4" s="78"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
+      <c r="K4" s="76"/>
+    </row>
+    <row r="5" spans="2:11">
+      <c r="B5" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="24"/>
+      <c r="C5" s="78"/>
       <c r="D5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="E5" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="24"/>
+      <c r="F5" s="78"/>
       <c r="G5" s="4" t="s">
         <v>10</v>
       </c>
@@ -3308,7 +3971,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:11">
       <c r="B6" s="5" t="s">
         <v>47</v>
       </c>
@@ -3336,7 +3999,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:11">
       <c r="B7" s="9" t="s">
         <v>48</v>
       </c>
@@ -3364,7 +4027,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:11">
       <c r="B8" s="5" t="s">
         <v>81</v>
       </c>
@@ -3392,7 +4055,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:11">
       <c r="B9" s="5" t="s">
         <v>82</v>
       </c>
@@ -3420,7 +4083,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:11">
       <c r="B10" s="5" t="s">
         <v>83</v>
       </c>
@@ -3448,7 +4111,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:11">
       <c r="B11" s="5" t="s">
         <v>84</v>
       </c>
@@ -3474,7 +4137,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:11">
       <c r="B12" s="5" t="s">
         <v>85</v>
       </c>
@@ -3500,7 +4163,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:11">
       <c r="B13" s="5" t="s">
         <v>86</v>
       </c>
@@ -3526,7 +4189,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:11">
       <c r="B14" s="5" t="s">
         <v>87</v>
       </c>
@@ -3548,7 +4211,7 @@
       <c r="J14" s="5"/>
       <c r="K14" s="6"/>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:11">
       <c r="B15" s="5" t="s">
         <v>88</v>
       </c>
@@ -3566,7 +4229,7 @@
       <c r="J15" s="5"/>
       <c r="K15" s="6"/>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:11">
       <c r="B16" s="5" t="s">
         <v>89</v>
       </c>
@@ -3584,7 +4247,7 @@
       <c r="J16" s="5"/>
       <c r="K16" s="6"/>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:11">
       <c r="B17" s="9" t="s">
         <v>90</v>
       </c>
@@ -3612,7 +4275,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:11">
       <c r="B18" s="9" t="s">
         <v>91</v>
       </c>
@@ -3640,7 +4303,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:11">
       <c r="B19" s="9" t="s">
         <v>92</v>
       </c>
@@ -3670,7 +4333,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:11">
       <c r="B20" s="9" t="s">
         <v>93</v>
       </c>
@@ -3696,7 +4359,7 @@
       <c r="J20" s="5"/>
       <c r="K20" s="6"/>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:11">
       <c r="B21" s="9" t="s">
         <v>94</v>
       </c>
@@ -3722,7 +4385,7 @@
       <c r="J21" s="5"/>
       <c r="K21" s="6"/>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:11">
       <c r="B22" s="9" t="s">
         <v>0</v>
       </c>
@@ -3748,7 +4411,7 @@
       <c r="J22" s="5"/>
       <c r="K22" s="6"/>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:11">
       <c r="B23" s="9" t="s">
         <v>1</v>
       </c>
@@ -3774,7 +4437,7 @@
       <c r="J23" s="5"/>
       <c r="K23" s="6"/>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:11">
       <c r="B24" s="9" t="s">
         <v>2</v>
       </c>
@@ -3800,7 +4463,7 @@
       <c r="J24" s="5"/>
       <c r="K24" s="6"/>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:11">
       <c r="B25" s="9" t="s">
         <v>3</v>
       </c>
@@ -3824,7 +4487,7 @@
       <c r="J25" s="5"/>
       <c r="K25" s="6"/>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:11">
       <c r="B26" s="9" t="s">
         <v>4</v>
       </c>
@@ -3848,7 +4511,7 @@
       <c r="J26" s="5"/>
       <c r="K26" s="6"/>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:11">
       <c r="B27" s="9" t="s">
         <v>5</v>
       </c>
@@ -3868,7 +4531,7 @@
       <c r="J27" s="5"/>
       <c r="K27" s="6"/>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:11">
       <c r="B28" s="5" t="s">
         <v>6</v>
       </c>
@@ -3890,7 +4553,7 @@
       <c r="J28" s="5"/>
       <c r="K28" s="6"/>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:11">
       <c r="B29" s="5" t="s">
         <v>104</v>
       </c>
@@ -3912,7 +4575,7 @@
       <c r="J29" s="5"/>
       <c r="K29" s="6"/>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:11">
       <c r="B30" s="5" t="s">
         <v>105</v>
       </c>
@@ -3934,7 +4597,7 @@
       <c r="J30" s="5"/>
       <c r="K30" s="6"/>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:11">
       <c r="B31" s="5" t="s">
         <v>106</v>
       </c>
@@ -3960,7 +4623,7 @@
       <c r="J31" s="5"/>
       <c r="K31" s="6"/>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:11">
       <c r="B32" s="5" t="s">
         <v>25</v>
       </c>
@@ -3986,7 +4649,7 @@
       <c r="J32" s="5"/>
       <c r="K32" s="6"/>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:11">
       <c r="B33" s="5" t="s">
         <v>26</v>
       </c>
@@ -4012,7 +4675,7 @@
       <c r="J33" s="5"/>
       <c r="K33" s="6"/>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:11">
       <c r="B34" s="5" t="s">
         <v>27</v>
       </c>
@@ -4036,7 +4699,7 @@
       <c r="J34" s="5"/>
       <c r="K34" s="6"/>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:11">
       <c r="B35" s="5" t="s">
         <v>28</v>
       </c>
@@ -4060,7 +4723,7 @@
       <c r="J35" s="5"/>
       <c r="K35" s="6"/>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:11">
       <c r="B36" s="5" t="s">
         <v>29</v>
       </c>
@@ -4084,7 +4747,7 @@
       <c r="J36" s="5"/>
       <c r="K36" s="6"/>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:11">
       <c r="B37" s="5" t="s">
         <v>30</v>
       </c>
@@ -4108,7 +4771,7 @@
       <c r="J37" s="5"/>
       <c r="K37" s="6"/>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:11">
       <c r="B38" s="5" t="s">
         <v>41</v>
       </c>
@@ -4132,7 +4795,7 @@
       <c r="J38" s="5"/>
       <c r="K38" s="6"/>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:11">
       <c r="B39" s="5" t="s">
         <v>113</v>
       </c>
@@ -4156,7 +4819,7 @@
       <c r="J39" s="5"/>
       <c r="K39" s="6"/>
     </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:11">
       <c r="B40" s="5" t="s">
         <v>114</v>
       </c>
@@ -4180,7 +4843,7 @@
       <c r="J40" s="5"/>
       <c r="K40" s="6"/>
     </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:11">
       <c r="B41" s="5" t="s">
         <v>42</v>
       </c>
@@ -4200,7 +4863,7 @@
       <c r="J41" s="5"/>
       <c r="K41" s="6"/>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:11">
       <c r="B42" s="5" t="s">
         <v>43</v>
       </c>
@@ -4215,12 +4878,16 @@
       <c r="G42" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="H42" s="5"/>
-      <c r="I42" s="6"/>
+      <c r="H42" s="5" t="s">
+        <v>752</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>766</v>
+      </c>
       <c r="J42" s="5"/>
       <c r="K42" s="6"/>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:11">
       <c r="B43" s="5" t="s">
         <v>419</v>
       </c>
@@ -4235,12 +4902,16 @@
       <c r="G43" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="H43" s="5"/>
-      <c r="I43" s="6"/>
+      <c r="H43" s="5" t="s">
+        <v>753</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>767</v>
+      </c>
       <c r="J43" s="5"/>
       <c r="K43" s="6"/>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:11">
       <c r="B44" s="5" t="s">
         <v>420</v>
       </c>
@@ -4255,12 +4926,16 @@
       <c r="G44" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="H44" s="5"/>
-      <c r="I44" s="6"/>
+      <c r="H44" s="5" t="s">
+        <v>754</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>768</v>
+      </c>
       <c r="J44" s="5"/>
       <c r="K44" s="6"/>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:11">
       <c r="B45" s="5" t="s">
         <v>421</v>
       </c>
@@ -4275,12 +4950,16 @@
       <c r="G45" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="H45" s="5"/>
-      <c r="I45" s="6"/>
+      <c r="H45" s="5" t="s">
+        <v>755</v>
+      </c>
+      <c r="I45" s="6" t="s">
+        <v>769</v>
+      </c>
       <c r="J45" s="5"/>
       <c r="K45" s="6"/>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:11">
       <c r="B46" s="5" t="s">
         <v>422</v>
       </c>
@@ -4295,12 +4974,16 @@
       <c r="G46" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="H46" s="5"/>
-      <c r="I46" s="6"/>
+      <c r="H46" s="5" t="s">
+        <v>756</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>770</v>
+      </c>
       <c r="J46" s="5"/>
       <c r="K46" s="6"/>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:11">
       <c r="B47" s="5" t="s">
         <v>423</v>
       </c>
@@ -4315,12 +4998,16 @@
       <c r="G47" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="H47" s="5"/>
-      <c r="I47" s="6"/>
+      <c r="H47" s="5" t="s">
+        <v>757</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>771</v>
+      </c>
       <c r="J47" s="5"/>
       <c r="K47" s="6"/>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:11">
       <c r="B48" s="5" t="s">
         <v>424</v>
       </c>
@@ -4335,12 +5022,16 @@
       <c r="G48" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="H48" s="5"/>
-      <c r="I48" s="6"/>
+      <c r="H48" s="5" t="s">
+        <v>758</v>
+      </c>
+      <c r="I48" s="6" t="s">
+        <v>772</v>
+      </c>
       <c r="J48" s="5"/>
       <c r="K48" s="6"/>
     </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:11">
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
       <c r="D49" s="6"/>
@@ -4351,12 +5042,16 @@
       <c r="G49" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="H49" s="5"/>
-      <c r="I49" s="6"/>
+      <c r="H49" s="5" t="s">
+        <v>759</v>
+      </c>
+      <c r="I49" s="6" t="s">
+        <v>773</v>
+      </c>
       <c r="J49" s="5"/>
       <c r="K49" s="6"/>
     </row>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:11">
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
       <c r="D50" s="6"/>
@@ -4367,12 +5062,16 @@
       <c r="G50" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="H50" s="5"/>
-      <c r="I50" s="6"/>
+      <c r="H50" s="5" t="s">
+        <v>760</v>
+      </c>
+      <c r="I50" s="6" t="s">
+        <v>774</v>
+      </c>
       <c r="J50" s="5"/>
       <c r="K50" s="6"/>
     </row>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:11">
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
       <c r="D51" s="6"/>
@@ -4383,12 +5082,16 @@
       <c r="G51" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="H51" s="5"/>
-      <c r="I51" s="6"/>
+      <c r="H51" s="5" t="s">
+        <v>761</v>
+      </c>
+      <c r="I51" s="6" t="s">
+        <v>766</v>
+      </c>
       <c r="J51" s="5"/>
       <c r="K51" s="6"/>
     </row>
-    <row r="52" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:11">
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
       <c r="D52" s="6"/>
@@ -4401,12 +5104,16 @@
       <c r="G52" s="6" t="s">
         <v>383</v>
       </c>
-      <c r="H52" s="5"/>
-      <c r="I52" s="6"/>
+      <c r="H52" s="5" t="s">
+        <v>762</v>
+      </c>
+      <c r="I52" s="6" t="s">
+        <v>767</v>
+      </c>
       <c r="J52" s="5"/>
       <c r="K52" s="6"/>
     </row>
-    <row r="53" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:11">
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
       <c r="D53" s="6"/>
@@ -4419,12 +5126,16 @@
       <c r="G53" s="6" t="s">
         <v>384</v>
       </c>
-      <c r="H53" s="5"/>
-      <c r="I53" s="6"/>
+      <c r="H53" s="5" t="s">
+        <v>763</v>
+      </c>
+      <c r="I53" s="6" t="s">
+        <v>768</v>
+      </c>
       <c r="J53" s="5"/>
       <c r="K53" s="6"/>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:11">
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
       <c r="D54" s="6"/>
@@ -4437,12 +5148,16 @@
       <c r="G54" s="6" t="s">
         <v>385</v>
       </c>
-      <c r="H54" s="5"/>
-      <c r="I54" s="6"/>
+      <c r="H54" s="5" t="s">
+        <v>764</v>
+      </c>
+      <c r="I54" s="6" t="s">
+        <v>766</v>
+      </c>
       <c r="J54" s="5"/>
       <c r="K54" s="6"/>
     </row>
-    <row r="55" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:11">
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
       <c r="D55" s="6"/>
@@ -4455,12 +5170,16 @@
       <c r="G55" s="6" t="s">
         <v>386</v>
       </c>
-      <c r="H55" s="5"/>
-      <c r="I55" s="6"/>
+      <c r="H55" s="5" t="s">
+        <v>765</v>
+      </c>
+      <c r="I55" s="6" t="s">
+        <v>767</v>
+      </c>
       <c r="J55" s="5"/>
       <c r="K55" s="6"/>
     </row>
-    <row r="56" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:11">
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
       <c r="D56" s="6"/>
@@ -4474,11 +5193,13 @@
         <v>387</v>
       </c>
       <c r="H56" s="5"/>
-      <c r="I56" s="6"/>
+      <c r="I56" s="6" t="s">
+        <v>768</v>
+      </c>
       <c r="J56" s="5"/>
       <c r="K56" s="6"/>
     </row>
-    <row r="57" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:11">
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
       <c r="D57" s="6"/>
@@ -4513,7 +5234,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEB7259B-DE41-4F32-9D2C-8EEFF1CE7AAD}">
   <dimension ref="B2:X56"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="3" max="4" width="9" style="1"/>
     <col min="5" max="5" width="20.625" customWidth="1"/>
@@ -4533,7 +5254,7 @@
     <col min="28" max="28" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="2" spans="3:24">
       <c r="C2" s="11"/>
       <c r="D2" s="11"/>
       <c r="E2" s="12"/>
@@ -4553,111 +5274,111 @@
       <c r="W2" s="11"/>
       <c r="X2" s="12"/>
     </row>
-    <row r="3" spans="3:24" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C3" s="22" t="s">
+    <row r="3" spans="3:24" s="3" customFormat="1">
+      <c r="C3" s="76" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22" t="s">
+      <c r="D3" s="76"/>
+      <c r="E3" s="76" t="s">
         <v>65</v>
       </c>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
-      <c r="K3" s="22" t="s">
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="K3" s="76" t="s">
         <v>40</v>
       </c>
-      <c r="L3" s="22"/>
-      <c r="M3" s="22" t="s">
+      <c r="L3" s="76"/>
+      <c r="M3" s="76" t="s">
         <v>66</v>
       </c>
-      <c r="N3" s="22"/>
-      <c r="O3" s="22"/>
-      <c r="P3" s="22"/>
-      <c r="S3" s="22" t="s">
+      <c r="N3" s="76"/>
+      <c r="O3" s="76"/>
+      <c r="P3" s="76"/>
+      <c r="S3" s="76" t="s">
         <v>40</v>
       </c>
-      <c r="T3" s="22"/>
-      <c r="U3" s="22" t="s">
+      <c r="T3" s="76"/>
+      <c r="U3" s="76" t="s">
         <v>209</v>
       </c>
-      <c r="V3" s="22"/>
-      <c r="W3" s="22"/>
-      <c r="X3" s="22"/>
-    </row>
-    <row r="4" spans="3:24" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="22" t="s">
+      <c r="V3" s="76"/>
+      <c r="W3" s="76"/>
+      <c r="X3" s="76"/>
+    </row>
+    <row r="4" spans="3:24" s="3" customFormat="1">
+      <c r="C4" s="76" t="s">
         <v>39</v>
       </c>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
-      <c r="K4" s="22" t="s">
+      <c r="K4" s="76" t="s">
         <v>39</v>
       </c>
-      <c r="L4" s="22"/>
-      <c r="M4" s="22"/>
-      <c r="N4" s="22"/>
-      <c r="O4" s="22"/>
-      <c r="P4" s="22"/>
-      <c r="S4" s="22" t="s">
+      <c r="L4" s="76"/>
+      <c r="M4" s="76"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="76"/>
+      <c r="P4" s="76"/>
+      <c r="S4" s="76" t="s">
         <v>39</v>
       </c>
-      <c r="T4" s="22"/>
-      <c r="U4" s="22"/>
-      <c r="V4" s="22"/>
-      <c r="W4" s="22"/>
-      <c r="X4" s="22"/>
-    </row>
-    <row r="5" spans="3:24" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C5" s="22" t="s">
+      <c r="T4" s="76"/>
+      <c r="U4" s="76"/>
+      <c r="V4" s="76"/>
+      <c r="W4" s="76"/>
+      <c r="X4" s="76"/>
+    </row>
+    <row r="5" spans="3:24" s="2" customFormat="1">
+      <c r="C5" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="22"/>
+      <c r="D5" s="76"/>
       <c r="E5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="22" t="s">
+      <c r="F5" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="22"/>
+      <c r="G5" s="76"/>
       <c r="H5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K5" s="22" t="s">
+      <c r="K5" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="L5" s="22"/>
+      <c r="L5" s="76"/>
       <c r="M5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="N5" s="22" t="s">
+      <c r="N5" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="O5" s="22"/>
+      <c r="O5" s="76"/>
       <c r="P5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="S5" s="22" t="s">
+      <c r="S5" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="T5" s="22"/>
+      <c r="T5" s="76"/>
       <c r="U5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="V5" s="22" t="s">
+      <c r="V5" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="W5" s="22"/>
+      <c r="W5" s="76"/>
       <c r="X5" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="3:24" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:24" s="2" customFormat="1">
       <c r="C6" s="4" t="s">
         <v>523</v>
       </c>
@@ -4689,7 +5410,7 @@
       <c r="W6" s="4"/>
       <c r="X6" s="4"/>
     </row>
-    <row r="7" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:24">
       <c r="C7" s="5" t="s">
         <v>56</v>
       </c>
@@ -4745,7 +5466,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="8" spans="3:24">
       <c r="C8" s="5" t="s">
         <v>296</v>
       </c>
@@ -4801,7 +5522,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="9" spans="3:24">
       <c r="C9" s="9" t="s">
         <v>297</v>
       </c>
@@ -4857,7 +5578,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="10" spans="3:24">
       <c r="C10" s="9" t="s">
         <v>298</v>
       </c>
@@ -4913,7 +5634,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="11" spans="3:24">
       <c r="C11" s="5" t="s">
         <v>351</v>
       </c>
@@ -4969,7 +5690,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="12" spans="3:24">
       <c r="C12" s="9" t="s">
         <v>299</v>
       </c>
@@ -5007,7 +5728,7 @@
       </c>
       <c r="X12" s="10"/>
     </row>
-    <row r="13" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="13" spans="3:24">
       <c r="C13" s="9" t="s">
         <v>352</v>
       </c>
@@ -5063,7 +5784,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="14" spans="3:24">
       <c r="C14" s="9" t="s">
         <v>353</v>
       </c>
@@ -5119,7 +5840,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="15" spans="3:24">
       <c r="C15" s="5" t="s">
         <v>73</v>
       </c>
@@ -5175,7 +5896,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="16" spans="3:24">
       <c r="C16" s="5" t="s">
         <v>394</v>
       </c>
@@ -5213,7 +5934,7 @@
       <c r="W16" s="9"/>
       <c r="X16" s="10"/>
     </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:24">
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="6"/>
@@ -5233,7 +5954,7 @@
       <c r="W17" s="9"/>
       <c r="X17" s="10"/>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:24">
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
       <c r="E18" s="12"/>
@@ -5253,7 +5974,7 @@
       <c r="W18" s="11"/>
       <c r="X18" s="12"/>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:24">
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19"/>
@@ -5261,7 +5982,7 @@
       <c r="O19" s="1"/>
       <c r="P19"/>
     </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:24">
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20"/>
@@ -5269,7 +5990,7 @@
       <c r="O20" s="1"/>
       <c r="P20"/>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:24">
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21"/>
@@ -5277,7 +5998,7 @@
       <c r="O21" s="1"/>
       <c r="P21"/>
     </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:24">
       <c r="C22" s="11"/>
       <c r="D22" s="11"/>
       <c r="E22" s="12"/>
@@ -5297,109 +6018,109 @@
       <c r="W22" s="11"/>
       <c r="X22" s="12"/>
     </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.3">
-      <c r="C23" s="22" t="s">
+    <row r="23" spans="3:24">
+      <c r="C23" s="76" t="s">
         <v>40</v>
       </c>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22" t="s">
+      <c r="D23" s="76"/>
+      <c r="E23" s="76" t="s">
         <v>210</v>
       </c>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
-      <c r="K23" s="22" t="s">
+      <c r="F23" s="76"/>
+      <c r="G23" s="76"/>
+      <c r="H23" s="76"/>
+      <c r="K23" s="76" t="s">
         <v>40</v>
       </c>
-      <c r="L23" s="22"/>
-      <c r="M23" s="22" t="s">
+      <c r="L23" s="76"/>
+      <c r="M23" s="76" t="s">
         <v>211</v>
       </c>
-      <c r="N23" s="22"/>
-      <c r="O23" s="22"/>
-      <c r="P23" s="22"/>
-      <c r="S23" s="22" t="s">
+      <c r="N23" s="76"/>
+      <c r="O23" s="76"/>
+      <c r="P23" s="76"/>
+      <c r="S23" s="76" t="s">
         <v>40</v>
       </c>
-      <c r="T23" s="22"/>
-      <c r="U23" s="22" t="s">
+      <c r="T23" s="76"/>
+      <c r="U23" s="76" t="s">
         <v>212</v>
       </c>
-      <c r="V23" s="22"/>
-      <c r="W23" s="22"/>
-      <c r="X23" s="22"/>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.3">
-      <c r="C24" s="22" t="s">
+      <c r="V23" s="76"/>
+      <c r="W23" s="76"/>
+      <c r="X23" s="76"/>
+    </row>
+    <row r="24" spans="3:24">
+      <c r="C24" s="76" t="s">
         <v>39</v>
       </c>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
-      <c r="K24" s="22" t="s">
+      <c r="D24" s="76"/>
+      <c r="E24" s="76"/>
+      <c r="F24" s="76"/>
+      <c r="G24" s="76"/>
+      <c r="H24" s="76"/>
+      <c r="K24" s="76" t="s">
         <v>39</v>
       </c>
-      <c r="L24" s="22"/>
-      <c r="M24" s="22"/>
-      <c r="N24" s="22"/>
-      <c r="O24" s="22"/>
-      <c r="P24" s="22"/>
-      <c r="S24" s="22" t="s">
+      <c r="L24" s="76"/>
+      <c r="M24" s="76"/>
+      <c r="N24" s="76"/>
+      <c r="O24" s="76"/>
+      <c r="P24" s="76"/>
+      <c r="S24" s="76" t="s">
         <v>39</v>
       </c>
-      <c r="T24" s="22"/>
-      <c r="U24" s="22"/>
-      <c r="V24" s="22"/>
-      <c r="W24" s="22"/>
-      <c r="X24" s="22"/>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.3">
-      <c r="C25" s="22" t="s">
+      <c r="T24" s="76"/>
+      <c r="U24" s="76"/>
+      <c r="V24" s="76"/>
+      <c r="W24" s="76"/>
+      <c r="X24" s="76"/>
+    </row>
+    <row r="25" spans="3:24">
+      <c r="C25" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="D25" s="22"/>
+      <c r="D25" s="76"/>
       <c r="E25" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F25" s="22" t="s">
+      <c r="F25" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="G25" s="22"/>
+      <c r="G25" s="76"/>
       <c r="H25" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K25" s="22" t="s">
+      <c r="K25" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="L25" s="22"/>
+      <c r="L25" s="76"/>
       <c r="M25" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="N25" s="22" t="s">
+      <c r="N25" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="O25" s="22"/>
+      <c r="O25" s="76"/>
       <c r="P25" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="S25" s="22" t="s">
+      <c r="S25" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="T25" s="22"/>
+      <c r="T25" s="76"/>
       <c r="U25" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="V25" s="22" t="s">
+      <c r="V25" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="W25" s="22"/>
+      <c r="W25" s="76"/>
       <c r="X25" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:24">
       <c r="C26" s="4" t="s">
         <v>523</v>
       </c>
@@ -5431,7 +6152,7 @@
       <c r="W26" s="4"/>
       <c r="X26" s="4"/>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:24">
       <c r="C27" s="5" t="s">
         <v>200</v>
       </c>
@@ -5487,7 +6208,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:24">
       <c r="C28" s="5" t="s">
         <v>201</v>
       </c>
@@ -5543,7 +6264,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:24">
       <c r="C29" s="9" t="s">
         <v>345</v>
       </c>
@@ -5599,7 +6320,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:24">
       <c r="C30" s="9" t="s">
         <v>346</v>
       </c>
@@ -5655,7 +6376,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:24">
       <c r="C31" s="5" t="s">
         <v>347</v>
       </c>
@@ -5711,7 +6432,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:24">
       <c r="C32" s="9" t="s">
         <v>348</v>
       </c>
@@ -5749,7 +6470,7 @@
       </c>
       <c r="X32" s="10"/>
     </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:24">
       <c r="C33" s="9" t="s">
         <v>349</v>
       </c>
@@ -5805,7 +6526,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:24">
       <c r="C34" s="9" t="s">
         <v>350</v>
       </c>
@@ -5861,7 +6582,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:24">
       <c r="C35" s="5" t="s">
         <v>359</v>
       </c>
@@ -5917,7 +6638,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="36" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:24">
       <c r="C36" s="5" t="s">
         <v>398</v>
       </c>
@@ -5955,7 +6676,7 @@
       <c r="W36" s="9"/>
       <c r="X36" s="10"/>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:24">
       <c r="C37" s="11"/>
       <c r="D37" s="11"/>
       <c r="E37" s="12"/>
@@ -5975,7 +6696,7 @@
       <c r="W37" s="11"/>
       <c r="X37" s="12"/>
     </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:24">
       <c r="B41" s="8"/>
       <c r="C41" s="11"/>
       <c r="D41" s="11"/>
@@ -5999,121 +6720,121 @@
       <c r="W41" s="11"/>
       <c r="X41" s="12"/>
     </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:24">
       <c r="B42" s="8"/>
-      <c r="C42" s="22" t="s">
+      <c r="C42" s="76" t="s">
         <v>40</v>
       </c>
-      <c r="D42" s="22"/>
-      <c r="E42" s="22" t="s">
+      <c r="D42" s="76"/>
+      <c r="E42" s="76" t="s">
         <v>213</v>
       </c>
-      <c r="F42" s="22"/>
-      <c r="G42" s="22"/>
-      <c r="H42" s="22"/>
+      <c r="F42" s="76"/>
+      <c r="G42" s="76"/>
+      <c r="H42" s="76"/>
       <c r="I42" s="7"/>
       <c r="J42" s="7"/>
       <c r="K42" s="4" t="s">
         <v>40</v>
       </c>
       <c r="L42" s="4"/>
-      <c r="M42" s="22" t="s">
+      <c r="M42" s="76" t="s">
         <v>214</v>
       </c>
-      <c r="N42" s="22"/>
-      <c r="O42" s="22"/>
-      <c r="P42" s="22"/>
+      <c r="N42" s="76"/>
+      <c r="O42" s="76"/>
+      <c r="P42" s="76"/>
       <c r="Q42" s="8"/>
       <c r="S42" s="4" t="s">
         <v>40</v>
       </c>
       <c r="T42" s="4"/>
-      <c r="U42" s="22" t="s">
+      <c r="U42" s="76" t="s">
         <v>215</v>
       </c>
-      <c r="V42" s="22"/>
-      <c r="W42" s="22"/>
-      <c r="X42" s="22"/>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="V42" s="76"/>
+      <c r="W42" s="76"/>
+      <c r="X42" s="76"/>
+    </row>
+    <row r="43" spans="2:24">
       <c r="B43" s="8"/>
-      <c r="C43" s="22" t="s">
+      <c r="C43" s="76" t="s">
         <v>39</v>
       </c>
-      <c r="D43" s="22"/>
-      <c r="E43" s="22"/>
-      <c r="F43" s="22"/>
-      <c r="G43" s="22"/>
-      <c r="H43" s="22"/>
+      <c r="D43" s="76"/>
+      <c r="E43" s="76"/>
+      <c r="F43" s="76"/>
+      <c r="G43" s="76"/>
+      <c r="H43" s="76"/>
       <c r="I43" s="7"/>
       <c r="J43" s="7"/>
       <c r="K43" s="4" t="s">
         <v>39</v>
       </c>
       <c r="L43" s="4"/>
-      <c r="M43" s="22"/>
-      <c r="N43" s="22"/>
-      <c r="O43" s="22"/>
-      <c r="P43" s="22"/>
+      <c r="M43" s="76"/>
+      <c r="N43" s="76"/>
+      <c r="O43" s="76"/>
+      <c r="P43" s="76"/>
       <c r="Q43" s="8"/>
       <c r="S43" s="4" t="s">
         <v>39</v>
       </c>
       <c r="T43" s="4"/>
-      <c r="U43" s="22"/>
-      <c r="V43" s="22"/>
-      <c r="W43" s="22"/>
-      <c r="X43" s="22"/>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="U43" s="76"/>
+      <c r="V43" s="76"/>
+      <c r="W43" s="76"/>
+      <c r="X43" s="76"/>
+    </row>
+    <row r="44" spans="2:24">
       <c r="B44" s="8"/>
-      <c r="C44" s="22" t="s">
+      <c r="C44" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="D44" s="22"/>
+      <c r="D44" s="76"/>
       <c r="E44" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F44" s="22" t="s">
+      <c r="F44" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="G44" s="22"/>
+      <c r="G44" s="76"/>
       <c r="H44" s="4" t="s">
         <v>10</v>
       </c>
       <c r="I44" s="7"/>
       <c r="J44" s="7"/>
-      <c r="K44" s="22" t="s">
+      <c r="K44" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="L44" s="22"/>
+      <c r="L44" s="76"/>
       <c r="M44" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="N44" s="22" t="s">
+      <c r="N44" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="O44" s="22"/>
+      <c r="O44" s="76"/>
       <c r="P44" s="4" t="s">
         <v>10</v>
       </c>
       <c r="Q44" s="8"/>
-      <c r="S44" s="22" t="s">
+      <c r="S44" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="T44" s="22"/>
+      <c r="T44" s="76"/>
       <c r="U44" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="V44" s="22" t="s">
+      <c r="V44" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="W44" s="22"/>
+      <c r="W44" s="76"/>
       <c r="X44" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:24">
       <c r="B45" s="8"/>
       <c r="C45" s="4" t="s">
         <v>523</v>
@@ -6149,7 +6870,7 @@
       <c r="W45" s="4"/>
       <c r="X45" s="4"/>
     </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:24">
       <c r="B46" s="8"/>
       <c r="C46" s="5" t="s">
         <v>273</v>
@@ -6209,7 +6930,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:24">
       <c r="B47" s="8"/>
       <c r="C47" s="5" t="s">
         <v>274</v>
@@ -6269,7 +6990,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:24">
       <c r="B48" s="8"/>
       <c r="C48" s="9" t="s">
         <v>275</v>
@@ -6329,7 +7050,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="49" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:24">
       <c r="B49" s="8"/>
       <c r="C49" s="9" t="s">
         <v>276</v>
@@ -6389,7 +7110,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:24">
       <c r="B50" s="8"/>
       <c r="C50" s="5" t="s">
         <v>277</v>
@@ -6449,7 +7170,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:24">
       <c r="B51" s="8"/>
       <c r="C51" s="9" t="s">
         <v>278</v>
@@ -6491,7 +7212,7 @@
       </c>
       <c r="X51" s="10"/>
     </row>
-    <row r="52" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:24">
       <c r="B52" s="8"/>
       <c r="C52" s="9" t="s">
         <v>279</v>
@@ -6551,7 +7272,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:24">
       <c r="B53" s="8"/>
       <c r="C53" s="9" t="s">
         <v>280</v>
@@ -6611,7 +7332,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="54" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:24">
       <c r="B54" s="8"/>
       <c r="C54" s="5" t="s">
         <v>281</v>
@@ -6671,7 +7392,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="55" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:24">
       <c r="B55" s="8"/>
       <c r="C55" s="5" t="s">
         <v>333</v>
@@ -6713,7 +7434,7 @@
       <c r="W55" s="9"/>
       <c r="X55" s="10"/>
     </row>
-    <row r="56" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:24">
       <c r="B56" s="8"/>
       <c r="C56" s="11"/>
       <c r="D56" s="11"/>
@@ -6739,13 +7460,45 @@
     </row>
   </sheetData>
   <mergeCells count="50">
+    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="M42:P42"/>
+    <mergeCell ref="U42:X42"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="M3:P3"/>
+    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="S5:T5"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="M4:P4"/>
+    <mergeCell ref="V5:W5"/>
+    <mergeCell ref="V25:W25"/>
+    <mergeCell ref="N25:O25"/>
     <mergeCell ref="U3:X3"/>
     <mergeCell ref="U4:X4"/>
     <mergeCell ref="K3:L3"/>
-    <mergeCell ref="E42:H42"/>
-    <mergeCell ref="M42:P42"/>
-    <mergeCell ref="U42:X42"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="C23:D23"/>
     <mergeCell ref="E43:H43"/>
+    <mergeCell ref="N44:O44"/>
+    <mergeCell ref="V44:W44"/>
+    <mergeCell ref="S44:T44"/>
+    <mergeCell ref="K44:L44"/>
+    <mergeCell ref="C5:D5"/>
     <mergeCell ref="M43:P43"/>
     <mergeCell ref="U43:X43"/>
     <mergeCell ref="E23:H23"/>
@@ -6754,41 +7507,9 @@
     <mergeCell ref="M24:P24"/>
     <mergeCell ref="U23:X23"/>
     <mergeCell ref="U24:X24"/>
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="M3:P3"/>
-    <mergeCell ref="S3:T3"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="C23:D23"/>
     <mergeCell ref="S23:T23"/>
     <mergeCell ref="S24:T24"/>
     <mergeCell ref="S25:T25"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="S5:T5"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:P4"/>
-    <mergeCell ref="V5:W5"/>
-    <mergeCell ref="V25:W25"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="N44:O44"/>
-    <mergeCell ref="V44:W44"/>
-    <mergeCell ref="S44:T44"/>
-    <mergeCell ref="K44:L44"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6797,8 +7518,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EA47EA4-7B31-40FE-9AED-CE45ED8264B2}">
-  <dimension ref="B2:U32"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="B2:U28"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="4" max="4" width="20.625" customWidth="1"/>
     <col min="7" max="7" width="20.625" customWidth="1"/>
@@ -6809,7 +7530,7 @@
     <col min="21" max="21" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:21">
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
       <c r="D2" s="8"/>
@@ -6825,100 +7546,125 @@
       <c r="O2" s="14"/>
       <c r="P2" s="14"/>
       <c r="Q2" s="14"/>
-    </row>
-    <row r="3" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B3" s="23" t="s">
+      <c r="S2" s="17" t="s">
+        <v>414</v>
+      </c>
+      <c r="T2" s="18" t="s">
+        <v>378</v>
+      </c>
+      <c r="U2" s="18" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="3" spans="2:21">
+      <c r="B3" s="77" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="24"/>
-      <c r="D3" s="23" t="s">
+      <c r="C3" s="78"/>
+      <c r="D3" s="77" t="s">
         <v>292</v>
       </c>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="24"/>
-      <c r="I3" s="23" t="s">
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="78"/>
+      <c r="I3" s="77" t="s">
         <v>40</v>
       </c>
-      <c r="J3" s="24"/>
-      <c r="K3" s="22" t="s">
+      <c r="J3" s="78"/>
+      <c r="K3" s="76" t="s">
         <v>307</v>
       </c>
-      <c r="L3" s="22"/>
-      <c r="M3" s="22"/>
-      <c r="N3" s="22"/>
-      <c r="O3" s="22"/>
-      <c r="P3" s="22"/>
-      <c r="Q3" s="22"/>
-    </row>
-    <row r="4" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B4" s="23" t="s">
+      <c r="L3" s="76"/>
+      <c r="M3" s="76"/>
+      <c r="N3" s="76"/>
+      <c r="O3" s="76"/>
+      <c r="P3" s="76"/>
+      <c r="Q3" s="76"/>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+      <c r="T3" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="U3" s="6"/>
+    </row>
+    <row r="4" spans="2:21">
+      <c r="B4" s="77" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="24"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="24"/>
-      <c r="I4" s="23" t="s">
+      <c r="C4" s="78"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="79"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="78"/>
+      <c r="I4" s="77" t="s">
         <v>39</v>
       </c>
-      <c r="J4" s="24"/>
-      <c r="K4" s="22"/>
-      <c r="L4" s="22"/>
-      <c r="M4" s="22"/>
-      <c r="N4" s="22"/>
-      <c r="O4" s="22"/>
-      <c r="P4" s="22"/>
-      <c r="Q4" s="22"/>
-    </row>
-    <row r="5" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B5" s="23" t="s">
+      <c r="J4" s="78"/>
+      <c r="K4" s="76"/>
+      <c r="L4" s="76"/>
+      <c r="M4" s="76"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="76"/>
+      <c r="P4" s="76"/>
+      <c r="Q4" s="76"/>
+      <c r="S4" s="5">
+        <v>100</v>
+      </c>
+      <c r="T4" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="U4" s="6" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="5" spans="2:21">
+      <c r="B5" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="24"/>
+      <c r="C5" s="78"/>
       <c r="D5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="E5" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="24"/>
+      <c r="F5" s="78"/>
       <c r="G5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="I5" s="23" t="s">
+      <c r="I5" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="24"/>
+      <c r="J5" s="78"/>
       <c r="K5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L5" s="23" t="s">
+      <c r="L5" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="M5" s="24"/>
+      <c r="M5" s="78"/>
       <c r="N5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="O5" s="23" t="s">
+      <c r="O5" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="P5" s="24"/>
+      <c r="P5" s="78"/>
       <c r="Q5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="S5" s="17" t="s">
-        <v>414</v>
-      </c>
-      <c r="T5" s="18" t="s">
-        <v>378</v>
-      </c>
-      <c r="U5" s="18" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="6" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="S5" s="5">
+        <v>200</v>
+      </c>
+      <c r="T5" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="U5" s="6" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="6" spans="2:21">
       <c r="B6" s="4" t="s">
         <v>523</v>
       </c>
@@ -6954,11 +7700,17 @@
         <v>524</v>
       </c>
       <c r="Q6" s="4"/>
-      <c r="S6" s="17"/>
-      <c r="T6" s="18"/>
-      <c r="U6" s="18"/>
-    </row>
-    <row r="7" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="S6" s="5">
+        <v>300</v>
+      </c>
+      <c r="T6" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="U6" s="6" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="7" spans="2:21">
       <c r="B7" s="5" t="s">
         <v>300</v>
       </c>
@@ -7003,14 +7755,16 @@
         <v>363</v>
       </c>
       <c r="S7" s="5">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="T7" s="6" t="s">
-        <v>364</v>
-      </c>
-      <c r="U7" s="6"/>
-    </row>
-    <row r="8" spans="2:21" x14ac:dyDescent="0.3">
+        <v>368</v>
+      </c>
+      <c r="U7" s="6" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="8" spans="2:21">
       <c r="B8" s="5" t="s">
         <v>301</v>
       </c>
@@ -7051,16 +7805,16 @@
       <c r="P8" s="6"/>
       <c r="Q8" s="6"/>
       <c r="S8" s="5">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="T8" s="6" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="U8" s="6" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="9" spans="2:21" x14ac:dyDescent="0.3">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="9" spans="2:21">
       <c r="B9" s="9" t="s">
         <v>302</v>
       </c>
@@ -7101,16 +7855,16 @@
       <c r="P9" s="6"/>
       <c r="Q9" s="6"/>
       <c r="S9" s="5">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="T9" s="6" t="s">
-        <v>366</v>
+        <v>437</v>
       </c>
       <c r="U9" s="6" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="10" spans="2:21" x14ac:dyDescent="0.3">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="10" spans="2:21">
       <c r="B10" s="5" t="s">
         <v>303</v>
       </c>
@@ -7150,17 +7904,17 @@
       <c r="O10" s="6"/>
       <c r="P10" s="6"/>
       <c r="Q10" s="6"/>
-      <c r="S10" s="5">
-        <v>300</v>
+      <c r="S10" s="19">
+        <v>601</v>
       </c>
       <c r="T10" s="6" t="s">
-        <v>367</v>
-      </c>
-      <c r="U10" s="6" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="11" spans="2:21" x14ac:dyDescent="0.3">
+        <v>437</v>
+      </c>
+      <c r="U10" s="20" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="11" spans="2:21">
       <c r="B11" s="5" t="s">
         <v>304</v>
       </c>
@@ -7201,16 +7955,16 @@
       <c r="P11" s="6"/>
       <c r="Q11" s="6"/>
       <c r="S11" s="5">
-        <v>400</v>
+        <v>610</v>
       </c>
       <c r="T11" s="6" t="s">
-        <v>368</v>
+        <v>438</v>
       </c>
       <c r="U11" s="6" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="12" spans="2:21" x14ac:dyDescent="0.3">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="12" spans="2:21">
       <c r="B12" s="5" t="s">
         <v>361</v>
       </c>
@@ -7236,17 +7990,17 @@
       <c r="O12" s="6"/>
       <c r="P12" s="6"/>
       <c r="Q12" s="6"/>
-      <c r="S12" s="5">
-        <v>500</v>
+      <c r="S12" s="19">
+        <v>611</v>
       </c>
       <c r="T12" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="U12" s="6" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="13" spans="2:21" x14ac:dyDescent="0.3">
+        <v>438</v>
+      </c>
+      <c r="U12" s="20" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="13" spans="2:21">
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="D13" s="6"/>
@@ -7269,16 +8023,16 @@
       <c r="P13" s="6"/>
       <c r="Q13" s="6"/>
       <c r="S13" s="5">
-        <v>600</v>
+        <v>620</v>
       </c>
       <c r="T13" s="6" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="U13" s="6" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="14" spans="2:21" x14ac:dyDescent="0.3">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="14" spans="2:21">
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
       <c r="D14" s="6"/>
@@ -7301,16 +8055,16 @@
       <c r="P14" s="6"/>
       <c r="Q14" s="6"/>
       <c r="S14" s="19">
-        <v>601</v>
+        <v>621</v>
       </c>
       <c r="T14" s="6" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="U14" s="20" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="15" spans="2:21" x14ac:dyDescent="0.3">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="15" spans="2:21">
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
       <c r="D15" s="6"/>
@@ -7327,16 +8081,16 @@
       <c r="P15" s="6"/>
       <c r="Q15" s="6"/>
       <c r="S15" s="5">
-        <v>610</v>
+        <v>630</v>
       </c>
       <c r="T15" s="6" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="16" spans="2:21" x14ac:dyDescent="0.3">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="16" spans="2:21">
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
       <c r="D16" s="8"/>
@@ -7353,16 +8107,16 @@
       <c r="P16" s="6"/>
       <c r="Q16" s="6"/>
       <c r="S16" s="19">
-        <v>611</v>
+        <v>631</v>
       </c>
       <c r="T16" s="6" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="U16" s="20" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="17" spans="9:21" x14ac:dyDescent="0.3">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="17" spans="9:21">
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
       <c r="K17" s="6"/>
@@ -7373,16 +8127,16 @@
       <c r="P17" s="6"/>
       <c r="Q17" s="6"/>
       <c r="S17" s="5">
-        <v>620</v>
+        <v>640</v>
       </c>
       <c r="T17" s="6" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="U17" s="6" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="18" spans="9:21" x14ac:dyDescent="0.3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="18" spans="9:21">
       <c r="I18" s="5"/>
       <c r="J18" s="5"/>
       <c r="K18" s="6"/>
@@ -7393,16 +8147,16 @@
       <c r="P18" s="6"/>
       <c r="Q18" s="6"/>
       <c r="S18" s="19">
-        <v>621</v>
+        <v>641</v>
       </c>
       <c r="T18" s="6" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="U18" s="20" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="19" spans="9:21" x14ac:dyDescent="0.3">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="19" spans="9:21">
       <c r="I19" s="5"/>
       <c r="J19" s="5"/>
       <c r="K19" s="6"/>
@@ -7413,16 +8167,16 @@
       <c r="P19" s="6"/>
       <c r="Q19" s="6"/>
       <c r="S19" s="5">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="T19" s="6" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="U19" s="6" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="20" spans="9:21" x14ac:dyDescent="0.3">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="20" spans="9:21">
       <c r="I20" s="5"/>
       <c r="J20" s="5"/>
       <c r="K20" s="6"/>
@@ -7433,16 +8187,16 @@
       <c r="P20" s="6"/>
       <c r="Q20" s="6"/>
       <c r="S20" s="19">
-        <v>631</v>
+        <v>651</v>
       </c>
       <c r="T20" s="6" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="U20" s="20" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="21" spans="9:21" x14ac:dyDescent="0.3">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="21" spans="9:21">
       <c r="I21" s="5"/>
       <c r="J21" s="5"/>
       <c r="K21" s="6"/>
@@ -7453,16 +8207,16 @@
       <c r="P21" s="6"/>
       <c r="Q21" s="6"/>
       <c r="S21" s="5">
-        <v>640</v>
+        <v>700</v>
       </c>
       <c r="T21" s="6" t="s">
-        <v>441</v>
+        <v>370</v>
       </c>
       <c r="U21" s="6" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="22" spans="9:21" x14ac:dyDescent="0.3">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="22" spans="9:21">
       <c r="I22" s="5"/>
       <c r="J22" s="5"/>
       <c r="K22" s="6"/>
@@ -7472,17 +8226,17 @@
       <c r="O22" s="6"/>
       <c r="P22" s="6"/>
       <c r="Q22" s="6"/>
-      <c r="S22" s="19">
-        <v>641</v>
+      <c r="S22" s="5">
+        <v>800</v>
       </c>
       <c r="T22" s="6" t="s">
-        <v>441</v>
-      </c>
-      <c r="U22" s="20" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="23" spans="9:21" x14ac:dyDescent="0.3">
+        <v>371</v>
+      </c>
+      <c r="U22" s="6" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="23" spans="9:21">
       <c r="I23" s="5"/>
       <c r="J23" s="5"/>
       <c r="K23" s="6"/>
@@ -7493,16 +8247,16 @@
       <c r="P23" s="6"/>
       <c r="Q23" s="6"/>
       <c r="S23" s="5">
-        <v>650</v>
+        <v>900</v>
       </c>
       <c r="T23" s="6" t="s">
-        <v>442</v>
+        <v>372</v>
       </c>
       <c r="U23" s="6" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="24" spans="9:21" x14ac:dyDescent="0.3">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="24" spans="9:21">
       <c r="I24" s="15"/>
       <c r="J24" s="15"/>
       <c r="K24" s="12"/>
@@ -7512,101 +8266,57 @@
       <c r="O24" s="12"/>
       <c r="P24" s="12"/>
       <c r="Q24" s="12"/>
-      <c r="S24" s="19">
-        <v>651</v>
+      <c r="S24" s="5">
+        <v>1000</v>
       </c>
       <c r="T24" s="6" t="s">
-        <v>442</v>
-      </c>
-      <c r="U24" s="20" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="25" spans="9:21" x14ac:dyDescent="0.3">
+        <v>373</v>
+      </c>
+      <c r="U24" s="6" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="25" spans="9:21">
       <c r="S25" s="5">
-        <v>700</v>
+        <v>1100</v>
       </c>
       <c r="T25" s="6" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="U25" s="6" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="26" spans="9:21" x14ac:dyDescent="0.3">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="26" spans="9:21">
       <c r="S26" s="5">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="T26" s="6" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="U26" s="6" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="27" spans="9:21" x14ac:dyDescent="0.3">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="27" spans="9:21">
       <c r="S27" s="5">
-        <v>900</v>
+        <v>1300</v>
       </c>
       <c r="T27" s="6" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="U27" s="6" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="28" spans="9:21" x14ac:dyDescent="0.3">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="28" spans="9:21">
       <c r="S28" s="5">
-        <v>1000</v>
+        <v>1400</v>
       </c>
       <c r="T28" s="6" t="s">
-        <v>373</v>
-      </c>
-      <c r="U28" s="6" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="29" spans="9:21" x14ac:dyDescent="0.3">
-      <c r="S29" s="5">
-        <v>1100</v>
-      </c>
-      <c r="T29" s="6" t="s">
-        <v>374</v>
-      </c>
-      <c r="U29" s="6" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="30" spans="9:21" x14ac:dyDescent="0.3">
-      <c r="S30" s="5">
-        <v>1200</v>
-      </c>
-      <c r="T30" s="6" t="s">
-        <v>375</v>
-      </c>
-      <c r="U30" s="6" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="31" spans="9:21" x14ac:dyDescent="0.3">
-      <c r="S31" s="5">
-        <v>1300</v>
-      </c>
-      <c r="T31" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="U31" s="6" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="32" spans="9:21" x14ac:dyDescent="0.3">
-      <c r="S32" s="5">
-        <v>1400</v>
-      </c>
-      <c r="T32" s="6" t="s">
         <v>377</v>
       </c>
-      <c r="U32" s="6"/>
+      <c r="U28" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -7627,4 +8337,474 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E804508-4978-40A9-8170-B191052641B8}">
+  <dimension ref="D6:X47"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetData>
+    <row r="6" spans="4:20" ht="17.25" thickBot="1">
+      <c r="D6" s="32" t="s">
+        <v>365</v>
+      </c>
+      <c r="E6" s="32"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="32"/>
+      <c r="I6" s="32" t="s">
+        <v>744</v>
+      </c>
+      <c r="J6" s="32"/>
+      <c r="K6" s="32"/>
+      <c r="M6" s="32" t="s">
+        <v>367</v>
+      </c>
+      <c r="N6" s="32"/>
+      <c r="O6" s="32"/>
+      <c r="P6" s="32"/>
+      <c r="R6" s="32" t="s">
+        <v>745</v>
+      </c>
+      <c r="S6" s="32"/>
+      <c r="T6" s="32"/>
+    </row>
+    <row r="7" spans="4:20" ht="16.5" customHeight="1">
+      <c r="D7" s="63" t="s">
+        <v>742</v>
+      </c>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="23"/>
+      <c r="I7" s="27"/>
+      <c r="J7" s="22"/>
+      <c r="K7" s="23"/>
+      <c r="M7" s="63" t="s">
+        <v>740</v>
+      </c>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22"/>
+      <c r="P7" s="23"/>
+      <c r="R7" s="27"/>
+      <c r="S7" s="22"/>
+      <c r="T7" s="23"/>
+    </row>
+    <row r="8" spans="4:20">
+      <c r="D8" s="64"/>
+      <c r="G8" s="24"/>
+      <c r="I8" s="25"/>
+      <c r="K8" s="24"/>
+      <c r="M8" s="64"/>
+      <c r="P8" s="24"/>
+      <c r="R8" s="25"/>
+      <c r="T8" s="24"/>
+    </row>
+    <row r="9" spans="4:20" ht="16.5" customHeight="1">
+      <c r="D9" s="64"/>
+      <c r="F9" s="41" t="s">
+        <v>739</v>
+      </c>
+      <c r="G9" s="24"/>
+      <c r="I9" s="25"/>
+      <c r="J9" s="41" t="s">
+        <v>739</v>
+      </c>
+      <c r="K9" s="24"/>
+      <c r="M9" s="64"/>
+      <c r="O9" s="41" t="s">
+        <v>739</v>
+      </c>
+      <c r="P9" s="24"/>
+      <c r="R9" s="25"/>
+      <c r="S9" s="41" t="s">
+        <v>739</v>
+      </c>
+      <c r="T9" s="24"/>
+    </row>
+    <row r="10" spans="4:20">
+      <c r="D10" s="64"/>
+      <c r="F10" s="52"/>
+      <c r="G10" s="24"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="52"/>
+      <c r="K10" s="24"/>
+      <c r="M10" s="64"/>
+      <c r="O10" s="52"/>
+      <c r="P10" s="24"/>
+      <c r="R10" s="25"/>
+      <c r="S10" s="52"/>
+      <c r="T10" s="24"/>
+    </row>
+    <row r="11" spans="4:20" ht="16.5" customHeight="1">
+      <c r="D11" s="64"/>
+      <c r="E11" s="39" t="s">
+        <v>738</v>
+      </c>
+      <c r="G11" s="24"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="39" t="s">
+        <v>738</v>
+      </c>
+      <c r="K11" s="24"/>
+      <c r="M11" s="64"/>
+      <c r="N11" s="39" t="s">
+        <v>738</v>
+      </c>
+      <c r="P11" s="24"/>
+      <c r="R11" s="25"/>
+      <c r="S11" s="39" t="s">
+        <v>738</v>
+      </c>
+      <c r="T11" s="24"/>
+    </row>
+    <row r="12" spans="4:20">
+      <c r="D12" s="64"/>
+      <c r="E12" s="66"/>
+      <c r="G12" s="24"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="40"/>
+      <c r="K12" s="24"/>
+      <c r="M12" s="64"/>
+      <c r="N12" s="66"/>
+      <c r="P12" s="24"/>
+      <c r="R12" s="25"/>
+      <c r="S12" s="40"/>
+      <c r="T12" s="24"/>
+    </row>
+    <row r="13" spans="4:20">
+      <c r="D13" s="65"/>
+      <c r="G13" s="24"/>
+      <c r="I13" s="25"/>
+      <c r="K13" s="24"/>
+      <c r="M13" s="65"/>
+      <c r="P13" s="24"/>
+      <c r="R13" s="25"/>
+      <c r="T13" s="24"/>
+    </row>
+    <row r="14" spans="4:20" ht="16.5" customHeight="1">
+      <c r="D14" s="25"/>
+      <c r="E14" s="67" t="s">
+        <v>741</v>
+      </c>
+      <c r="F14" s="68"/>
+      <c r="G14" s="69"/>
+      <c r="I14" s="53" t="s">
+        <v>747</v>
+      </c>
+      <c r="J14" s="54"/>
+      <c r="K14" s="59"/>
+      <c r="M14" s="25"/>
+      <c r="N14" s="67" t="s">
+        <v>750</v>
+      </c>
+      <c r="O14" s="68"/>
+      <c r="P14" s="69"/>
+      <c r="R14" s="53" t="s">
+        <v>747</v>
+      </c>
+      <c r="S14" s="54"/>
+      <c r="T14" s="59"/>
+    </row>
+    <row r="15" spans="4:20">
+      <c r="D15" s="25"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="71"/>
+      <c r="G15" s="72"/>
+      <c r="I15" s="46"/>
+      <c r="J15" s="47"/>
+      <c r="K15" s="48"/>
+      <c r="M15" s="25"/>
+      <c r="N15" s="70"/>
+      <c r="O15" s="71"/>
+      <c r="P15" s="72"/>
+      <c r="R15" s="46"/>
+      <c r="S15" s="47"/>
+      <c r="T15" s="48"/>
+    </row>
+    <row r="16" spans="4:20">
+      <c r="D16" s="25"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="71"/>
+      <c r="G16" s="72"/>
+      <c r="I16" s="46"/>
+      <c r="J16" s="47"/>
+      <c r="K16" s="48"/>
+      <c r="M16" s="25"/>
+      <c r="N16" s="70"/>
+      <c r="O16" s="71"/>
+      <c r="P16" s="72"/>
+      <c r="R16" s="46"/>
+      <c r="S16" s="47"/>
+      <c r="T16" s="48"/>
+    </row>
+    <row r="17" spans="4:20" ht="17.25" thickBot="1">
+      <c r="D17" s="26"/>
+      <c r="E17" s="73"/>
+      <c r="F17" s="74"/>
+      <c r="G17" s="75"/>
+      <c r="I17" s="60"/>
+      <c r="J17" s="61"/>
+      <c r="K17" s="62"/>
+      <c r="M17" s="26"/>
+      <c r="N17" s="73"/>
+      <c r="O17" s="74"/>
+      <c r="P17" s="75"/>
+      <c r="R17" s="60"/>
+      <c r="S17" s="61"/>
+      <c r="T17" s="62"/>
+    </row>
+    <row r="19" spans="4:20" ht="17.25" thickBot="1">
+      <c r="D19" s="32" t="s">
+        <v>376</v>
+      </c>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="H19" s="32" t="s">
+        <v>375</v>
+      </c>
+      <c r="I19" s="32"/>
+      <c r="J19" s="32"/>
+      <c r="K19" s="32"/>
+      <c r="R19" s="32" t="s">
+        <v>746</v>
+      </c>
+      <c r="S19" s="32"/>
+      <c r="T19" s="32"/>
+    </row>
+    <row r="20" spans="4:20">
+      <c r="D20" s="43" t="s">
+        <v>743</v>
+      </c>
+      <c r="E20" s="44"/>
+      <c r="F20" s="45"/>
+      <c r="H20" s="27"/>
+      <c r="I20" s="58" t="s">
+        <v>739</v>
+      </c>
+      <c r="J20" s="22"/>
+      <c r="K20" s="23"/>
+      <c r="M20" s="27"/>
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
+      <c r="P20" s="23"/>
+      <c r="R20" s="43" t="s">
+        <v>747</v>
+      </c>
+      <c r="S20" s="44"/>
+      <c r="T20" s="45"/>
+    </row>
+    <row r="21" spans="4:20">
+      <c r="D21" s="46"/>
+      <c r="E21" s="47"/>
+      <c r="F21" s="48"/>
+      <c r="H21" s="25"/>
+      <c r="I21" s="52"/>
+      <c r="K21" s="24"/>
+      <c r="M21" s="25"/>
+      <c r="P21" s="24"/>
+      <c r="R21" s="46"/>
+      <c r="S21" s="47"/>
+      <c r="T21" s="48"/>
+    </row>
+    <row r="22" spans="4:20">
+      <c r="D22" s="46"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="48"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="39" t="s">
+        <v>738</v>
+      </c>
+      <c r="J22" s="37" t="s">
+        <v>748</v>
+      </c>
+      <c r="K22" s="24"/>
+      <c r="M22" s="25"/>
+      <c r="P22" s="24"/>
+      <c r="R22" s="46"/>
+      <c r="S22" s="47"/>
+      <c r="T22" s="48"/>
+    </row>
+    <row r="23" spans="4:20">
+      <c r="D23" s="49"/>
+      <c r="E23" s="50"/>
+      <c r="F23" s="51"/>
+      <c r="H23" s="25"/>
+      <c r="I23" s="40"/>
+      <c r="J23" s="38"/>
+      <c r="K23" s="24"/>
+      <c r="M23" s="25"/>
+      <c r="P23" s="24"/>
+      <c r="R23" s="49"/>
+      <c r="S23" s="50"/>
+      <c r="T23" s="51"/>
+    </row>
+    <row r="24" spans="4:20">
+      <c r="D24" s="25"/>
+      <c r="F24" s="24"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="31"/>
+      <c r="J24" s="31"/>
+      <c r="K24" s="24"/>
+      <c r="M24" s="25"/>
+      <c r="P24" s="24"/>
+      <c r="R24" s="25"/>
+      <c r="T24" s="24"/>
+    </row>
+    <row r="25" spans="4:20" ht="16.5" customHeight="1">
+      <c r="D25" s="25"/>
+      <c r="E25" s="39" t="s">
+        <v>738</v>
+      </c>
+      <c r="F25" s="24"/>
+      <c r="H25" s="53" t="s">
+        <v>751</v>
+      </c>
+      <c r="I25" s="54"/>
+      <c r="J25" s="55"/>
+      <c r="K25" s="24"/>
+      <c r="M25" s="25"/>
+      <c r="P25" s="24"/>
+      <c r="R25" s="25"/>
+      <c r="S25" s="39" t="s">
+        <v>738</v>
+      </c>
+      <c r="T25" s="24"/>
+    </row>
+    <row r="26" spans="4:20">
+      <c r="D26" s="25"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="24"/>
+      <c r="H26" s="46"/>
+      <c r="I26" s="47"/>
+      <c r="J26" s="56"/>
+      <c r="K26" s="24"/>
+      <c r="M26" s="25"/>
+      <c r="P26" s="24"/>
+      <c r="R26" s="25"/>
+      <c r="S26" s="40"/>
+      <c r="T26" s="24"/>
+    </row>
+    <row r="27" spans="4:20">
+      <c r="D27" s="25"/>
+      <c r="E27" s="41" t="s">
+        <v>739</v>
+      </c>
+      <c r="F27" s="24"/>
+      <c r="H27" s="46"/>
+      <c r="I27" s="47"/>
+      <c r="J27" s="56"/>
+      <c r="K27" s="33" t="s">
+        <v>740</v>
+      </c>
+      <c r="M27" s="25"/>
+      <c r="P27" s="24"/>
+      <c r="R27" s="25"/>
+      <c r="S27" s="41" t="s">
+        <v>739</v>
+      </c>
+      <c r="T27" s="24"/>
+    </row>
+    <row r="28" spans="4:20" ht="16.5" customHeight="1">
+      <c r="D28" s="25"/>
+      <c r="E28" s="52"/>
+      <c r="F28" s="24"/>
+      <c r="H28" s="49"/>
+      <c r="I28" s="50"/>
+      <c r="J28" s="57"/>
+      <c r="K28" s="34"/>
+      <c r="M28" s="25"/>
+      <c r="P28" s="24"/>
+      <c r="R28" s="25"/>
+      <c r="S28" s="52"/>
+      <c r="T28" s="24"/>
+    </row>
+    <row r="29" spans="4:20">
+      <c r="D29" s="25"/>
+      <c r="F29" s="24"/>
+      <c r="H29" s="25"/>
+      <c r="K29" s="35"/>
+      <c r="M29" s="25"/>
+      <c r="P29" s="24"/>
+      <c r="R29" s="25"/>
+      <c r="T29" s="24"/>
+    </row>
+    <row r="30" spans="4:20" ht="17.25" thickBot="1">
+      <c r="D30" s="26"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="29"/>
+      <c r="H30" s="25"/>
+      <c r="I30" s="39" t="s">
+        <v>738</v>
+      </c>
+      <c r="K30" s="35"/>
+      <c r="M30" s="26"/>
+      <c r="N30" s="28"/>
+      <c r="O30" s="28"/>
+      <c r="P30" s="29"/>
+      <c r="R30" s="26"/>
+      <c r="S30" s="28"/>
+      <c r="T30" s="29"/>
+    </row>
+    <row r="31" spans="4:20">
+      <c r="H31" s="25"/>
+      <c r="I31" s="40"/>
+      <c r="K31" s="35"/>
+    </row>
+    <row r="32" spans="4:20">
+      <c r="H32" s="25"/>
+      <c r="I32" s="41" t="s">
+        <v>739</v>
+      </c>
+      <c r="K32" s="35"/>
+    </row>
+    <row r="33" spans="8:24" ht="17.25" thickBot="1">
+      <c r="H33" s="26"/>
+      <c r="I33" s="42"/>
+      <c r="J33" s="28"/>
+      <c r="K33" s="36"/>
+    </row>
+    <row r="47" spans="8:24">
+      <c r="X47" t="s">
+        <v>749</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="34">
+    <mergeCell ref="D7:D13"/>
+    <mergeCell ref="E14:G17"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="I14:K17"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="S11:S12"/>
+    <mergeCell ref="R14:T17"/>
+    <mergeCell ref="M7:M13"/>
+    <mergeCell ref="O9:O10"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="N14:P17"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="H25:J28"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="R6:T6"/>
+    <mergeCell ref="R19:T19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="K27:K33"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="H19:K19"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="I32:I33"/>
+    <mergeCell ref="R20:T23"/>
+    <mergeCell ref="S25:S26"/>
+    <mergeCell ref="S27:S28"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="M6:P6"/>
+    <mergeCell ref="D20:F23"/>
+    <mergeCell ref="E27:E28"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/PLC/IO List.xlsx
+++ b/PLC/IO List.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EZENIC\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EZENIC\Desktop\Project-Second\PLC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D6731B3-A9FE-42EB-B153-3414E0B41A9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B138645-277F-4831-8CB3-8D4F1F601279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3990" yWindow="3555" windowWidth="21600" windowHeight="11295" xr2:uid="{E8A3CD3B-D612-4B37-A180-F6C335096DC9}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="775">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="815">
   <si>
     <t>X10</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2789,6 +2789,131 @@
   <si>
     <t>경화공정3 완료 후 문닫힘</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M120</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M121</t>
+  </si>
+  <si>
+    <t>M122</t>
+  </si>
+  <si>
+    <t>M123</t>
+  </si>
+  <si>
+    <t>M124</t>
+  </si>
+  <si>
+    <t>M125</t>
+  </si>
+  <si>
+    <t>M126</t>
+  </si>
+  <si>
+    <t>M127</t>
+  </si>
+  <si>
+    <t>M128</t>
+  </si>
+  <si>
+    <t>AGV 내부 펄스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>T20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>T21</t>
+  </si>
+  <si>
+    <t>T22</t>
+  </si>
+  <si>
+    <t>T23</t>
+  </si>
+  <si>
+    <t>T24</t>
+  </si>
+  <si>
+    <t>T25</t>
+  </si>
+  <si>
+    <t>T26</t>
+  </si>
+  <si>
+    <t>T27</t>
+  </si>
+  <si>
+    <t>T28</t>
+  </si>
+  <si>
+    <t>T29</t>
+  </si>
+  <si>
+    <t>1공정 agv 신호 딜레이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2공정 agv 신호 딜레이</t>
+  </si>
+  <si>
+    <t>3공정 agv 신호 딜레이</t>
+  </si>
+  <si>
+    <t>4공정 agv 신호 딜레이</t>
+  </si>
+  <si>
+    <t>5공정 agv 신호 딜레이</t>
+  </si>
+  <si>
+    <t>6공정 agv 신호 딜레이</t>
+  </si>
+  <si>
+    <t>7공정 agv 신호 딜레이</t>
+  </si>
+  <si>
+    <t>8공정 agv 신호 딜레이</t>
+  </si>
+  <si>
+    <t>9공정 agv 신호 딜레이</t>
+  </si>
+  <si>
+    <t>10공정 agv 신호 딜레이</t>
+  </si>
+  <si>
+    <t>M129</t>
+  </si>
+  <si>
+    <t>로봇1 타이머</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로봇2 타이머</t>
+  </si>
+  <si>
+    <t>로봇3 타이머</t>
+  </si>
+  <si>
+    <t>로봇4 타이머</t>
+  </si>
+  <si>
+    <t>로봇5 타이머</t>
+  </si>
+  <si>
+    <t>로봇6 타이머</t>
+  </si>
+  <si>
+    <t>로봇7 타이머</t>
+  </si>
+  <si>
+    <t>로봇8 타이머</t>
+  </si>
+  <si>
+    <t>로봇9 타이머</t>
   </si>
 </sst>
 </file>
@@ -3325,7 +3450,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3422,98 +3547,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3522,9 +3566,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3554,16 +3595,103 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3900,7 +4028,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{228BF0B7-E586-4CC1-BF31-0F024BABECA2}">
-  <dimension ref="B3:K57"/>
+  <dimension ref="B3:K77"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="3" width="9" style="1"/>
@@ -3914,47 +4042,47 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:11">
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="78"/>
-      <c r="D3" s="76" t="s">
+      <c r="C3" s="34"/>
+      <c r="D3" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="76"/>
-      <c r="K3" s="76"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
     </row>
     <row r="4" spans="2:11">
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="78"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="76"/>
-      <c r="K4" s="76"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="32"/>
+      <c r="K4" s="32"/>
     </row>
     <row r="5" spans="2:11">
-      <c r="B5" s="77" t="s">
+      <c r="B5" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="78"/>
+      <c r="C5" s="34"/>
       <c r="D5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="77" t="s">
+      <c r="E5" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="78"/>
+      <c r="F5" s="34"/>
       <c r="G5" s="4" t="s">
         <v>10</v>
       </c>
@@ -4408,8 +4536,12 @@
       <c r="I22" s="6" t="s">
         <v>487</v>
       </c>
-      <c r="J22" s="5"/>
-      <c r="K22" s="6"/>
+      <c r="J22" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>795</v>
+      </c>
     </row>
     <row r="23" spans="2:11">
       <c r="B23" s="9" t="s">
@@ -4434,8 +4566,12 @@
       <c r="I23" s="6" t="s">
         <v>488</v>
       </c>
-      <c r="J23" s="5"/>
-      <c r="K23" s="6"/>
+      <c r="J23" s="5" t="s">
+        <v>786</v>
+      </c>
+      <c r="K23" s="6" t="s">
+        <v>796</v>
+      </c>
     </row>
     <row r="24" spans="2:11">
       <c r="B24" s="9" t="s">
@@ -4460,8 +4596,12 @@
       <c r="I24" s="6" t="s">
         <v>489</v>
       </c>
-      <c r="J24" s="5"/>
-      <c r="K24" s="6"/>
+      <c r="J24" s="5" t="s">
+        <v>787</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>797</v>
+      </c>
     </row>
     <row r="25" spans="2:11">
       <c r="B25" s="9" t="s">
@@ -4484,8 +4624,12 @@
       <c r="I25" s="6" t="s">
         <v>490</v>
       </c>
-      <c r="J25" s="5"/>
-      <c r="K25" s="6"/>
+      <c r="J25" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>798</v>
+      </c>
     </row>
     <row r="26" spans="2:11">
       <c r="B26" s="9" t="s">
@@ -4508,8 +4652,12 @@
       <c r="I26" s="6" t="s">
         <v>500</v>
       </c>
-      <c r="J26" s="5"/>
-      <c r="K26" s="6"/>
+      <c r="J26" s="5" t="s">
+        <v>789</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>799</v>
+      </c>
     </row>
     <row r="27" spans="2:11">
       <c r="B27" s="9" t="s">
@@ -4528,8 +4676,12 @@
       </c>
       <c r="H27" s="5"/>
       <c r="I27" s="6"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="6"/>
+      <c r="J27" s="5" t="s">
+        <v>790</v>
+      </c>
+      <c r="K27" s="6" t="s">
+        <v>800</v>
+      </c>
     </row>
     <row r="28" spans="2:11">
       <c r="B28" s="5" t="s">
@@ -4550,8 +4702,12 @@
       </c>
       <c r="H28" s="5"/>
       <c r="I28" s="6"/>
-      <c r="J28" s="5"/>
-      <c r="K28" s="6"/>
+      <c r="J28" s="5" t="s">
+        <v>791</v>
+      </c>
+      <c r="K28" s="6" t="s">
+        <v>801</v>
+      </c>
     </row>
     <row r="29" spans="2:11">
       <c r="B29" s="5" t="s">
@@ -4572,8 +4728,12 @@
       </c>
       <c r="H29" s="5"/>
       <c r="I29" s="6"/>
-      <c r="J29" s="5"/>
-      <c r="K29" s="6"/>
+      <c r="J29" s="5" t="s">
+        <v>792</v>
+      </c>
+      <c r="K29" s="6" t="s">
+        <v>802</v>
+      </c>
     </row>
     <row r="30" spans="2:11">
       <c r="B30" s="5" t="s">
@@ -4594,8 +4754,12 @@
       </c>
       <c r="H30" s="5"/>
       <c r="I30" s="6"/>
-      <c r="J30" s="5"/>
-      <c r="K30" s="6"/>
+      <c r="J30" s="5" t="s">
+        <v>793</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>803</v>
+      </c>
     </row>
     <row r="31" spans="2:11">
       <c r="B31" s="5" t="s">
@@ -4620,8 +4784,12 @@
       <c r="I31" s="6" t="s">
         <v>464</v>
       </c>
-      <c r="J31" s="5"/>
-      <c r="K31" s="6"/>
+      <c r="J31" s="5" t="s">
+        <v>794</v>
+      </c>
+      <c r="K31" s="6" t="s">
+        <v>804</v>
+      </c>
     </row>
     <row r="32" spans="2:11">
       <c r="B32" s="5" t="s">
@@ -4827,7 +4995,7 @@
       <c r="D40" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="E40" s="5" t="s">
+      <c r="E40" s="80" t="s">
         <v>157</v>
       </c>
       <c r="F40" s="5"/>
@@ -4851,7 +5019,7 @@
       <c r="D41" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E41" s="5" t="s">
+      <c r="E41" s="80" t="s">
         <v>158</v>
       </c>
       <c r="F41" s="5"/>
@@ -4871,7 +5039,7 @@
       <c r="D42" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="E42" s="5" t="s">
+      <c r="E42" s="80" t="s">
         <v>159</v>
       </c>
       <c r="F42" s="5"/>
@@ -4879,10 +5047,10 @@
         <v>187</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>752</v>
+        <v>775</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>766</v>
+        <v>784</v>
       </c>
       <c r="J42" s="5"/>
       <c r="K42" s="6"/>
@@ -4895,7 +5063,7 @@
       <c r="D43" s="6" t="s">
         <v>430</v>
       </c>
-      <c r="E43" s="5" t="s">
+      <c r="E43" s="80" t="s">
         <v>160</v>
       </c>
       <c r="F43" s="5"/>
@@ -4903,10 +5071,10 @@
         <v>188</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>753</v>
+        <v>776</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>767</v>
+        <v>806</v>
       </c>
       <c r="J43" s="5"/>
       <c r="K43" s="6"/>
@@ -4919,7 +5087,7 @@
       <c r="D44" s="6" t="s">
         <v>429</v>
       </c>
-      <c r="E44" s="5" t="s">
+      <c r="E44" s="80" t="s">
         <v>418</v>
       </c>
       <c r="F44" s="5"/>
@@ -4927,10 +5095,10 @@
         <v>189</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>754</v>
+        <v>777</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>768</v>
+        <v>807</v>
       </c>
       <c r="J44" s="5"/>
       <c r="K44" s="6"/>
@@ -4943,7 +5111,7 @@
       <c r="D45" s="6" t="s">
         <v>428</v>
       </c>
-      <c r="E45" s="5" t="s">
+      <c r="E45" s="80" t="s">
         <v>161</v>
       </c>
       <c r="F45" s="5"/>
@@ -4951,10 +5119,10 @@
         <v>190</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>755</v>
+        <v>778</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>769</v>
+        <v>808</v>
       </c>
       <c r="J45" s="5"/>
       <c r="K45" s="6"/>
@@ -4967,7 +5135,7 @@
       <c r="D46" s="6" t="s">
         <v>427</v>
       </c>
-      <c r="E46" s="5" t="s">
+      <c r="E46" s="80" t="s">
         <v>162</v>
       </c>
       <c r="F46" s="5"/>
@@ -4975,10 +5143,10 @@
         <v>191</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>756</v>
+        <v>779</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>770</v>
+        <v>809</v>
       </c>
       <c r="J46" s="5"/>
       <c r="K46" s="6"/>
@@ -4991,7 +5159,7 @@
       <c r="D47" s="6" t="s">
         <v>426</v>
       </c>
-      <c r="E47" s="5" t="s">
+      <c r="E47" s="80" t="s">
         <v>163</v>
       </c>
       <c r="F47" s="5"/>
@@ -4999,10 +5167,10 @@
         <v>192</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>757</v>
+        <v>780</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>771</v>
+        <v>810</v>
       </c>
       <c r="J47" s="5"/>
       <c r="K47" s="6"/>
@@ -5015,7 +5183,7 @@
       <c r="D48" s="6" t="s">
         <v>425</v>
       </c>
-      <c r="E48" s="5" t="s">
+      <c r="E48" s="80" t="s">
         <v>166</v>
       </c>
       <c r="F48" s="5"/>
@@ -5023,10 +5191,10 @@
         <v>193</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>758</v>
+        <v>781</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>772</v>
+        <v>811</v>
       </c>
       <c r="J48" s="5"/>
       <c r="K48" s="6"/>
@@ -5035,7 +5203,7 @@
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
       <c r="D49" s="6"/>
-      <c r="E49" s="5" t="s">
+      <c r="E49" s="80" t="s">
         <v>167</v>
       </c>
       <c r="F49" s="5"/>
@@ -5043,10 +5211,10 @@
         <v>194</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>759</v>
+        <v>782</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>773</v>
+        <v>812</v>
       </c>
       <c r="J49" s="5"/>
       <c r="K49" s="6"/>
@@ -5055,7 +5223,7 @@
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
       <c r="D50" s="6"/>
-      <c r="E50" s="5" t="s">
+      <c r="E50" s="80" t="s">
         <v>168</v>
       </c>
       <c r="F50" s="5"/>
@@ -5063,10 +5231,10 @@
         <v>195</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>760</v>
+        <v>783</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>774</v>
+        <v>813</v>
       </c>
       <c r="J50" s="5"/>
       <c r="K50" s="6"/>
@@ -5075,7 +5243,7 @@
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
       <c r="D51" s="6"/>
-      <c r="E51" s="5" t="s">
+      <c r="E51" s="80" t="s">
         <v>169</v>
       </c>
       <c r="F51" s="5"/>
@@ -5083,10 +5251,10 @@
         <v>196</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>761</v>
+        <v>805</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>766</v>
+        <v>814</v>
       </c>
       <c r="J51" s="5"/>
       <c r="K51" s="6"/>
@@ -5095,7 +5263,7 @@
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
       <c r="D52" s="6"/>
-      <c r="E52" s="5" t="s">
+      <c r="E52" s="80" t="s">
         <v>379</v>
       </c>
       <c r="F52" s="5" t="s">
@@ -5104,12 +5272,8 @@
       <c r="G52" s="6" t="s">
         <v>383</v>
       </c>
-      <c r="H52" s="5" t="s">
-        <v>762</v>
-      </c>
-      <c r="I52" s="6" t="s">
-        <v>767</v>
-      </c>
+      <c r="H52" s="5"/>
+      <c r="I52" s="6"/>
       <c r="J52" s="5"/>
       <c r="K52" s="6"/>
     </row>
@@ -5117,7 +5281,7 @@
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
       <c r="D53" s="6"/>
-      <c r="E53" s="5" t="s">
+      <c r="E53" s="80" t="s">
         <v>164</v>
       </c>
       <c r="F53" s="5" t="s">
@@ -5126,12 +5290,8 @@
       <c r="G53" s="6" t="s">
         <v>384</v>
       </c>
-      <c r="H53" s="5" t="s">
-        <v>763</v>
-      </c>
-      <c r="I53" s="6" t="s">
-        <v>768</v>
-      </c>
+      <c r="H53" s="5"/>
+      <c r="I53" s="6"/>
       <c r="J53" s="5"/>
       <c r="K53" s="6"/>
     </row>
@@ -5139,7 +5299,7 @@
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
       <c r="D54" s="6"/>
-      <c r="E54" s="5" t="s">
+      <c r="E54" s="80" t="s">
         <v>165</v>
       </c>
       <c r="F54" s="5" t="s">
@@ -5148,12 +5308,8 @@
       <c r="G54" s="6" t="s">
         <v>385</v>
       </c>
-      <c r="H54" s="5" t="s">
-        <v>764</v>
-      </c>
-      <c r="I54" s="6" t="s">
-        <v>766</v>
-      </c>
+      <c r="H54" s="5"/>
+      <c r="I54" s="6"/>
       <c r="J54" s="5"/>
       <c r="K54" s="6"/>
     </row>
@@ -5161,7 +5317,7 @@
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
       <c r="D55" s="6"/>
-      <c r="E55" s="5" t="s">
+      <c r="E55" s="80" t="s">
         <v>380</v>
       </c>
       <c r="F55" s="5" t="s">
@@ -5170,12 +5326,8 @@
       <c r="G55" s="6" t="s">
         <v>386</v>
       </c>
-      <c r="H55" s="5" t="s">
-        <v>765</v>
-      </c>
-      <c r="I55" s="6" t="s">
-        <v>767</v>
-      </c>
+      <c r="H55" s="5"/>
+      <c r="I55" s="6"/>
       <c r="J55" s="5"/>
       <c r="K55" s="6"/>
     </row>
@@ -5183,7 +5335,7 @@
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
       <c r="D56" s="6"/>
-      <c r="E56" s="5" t="s">
+      <c r="E56" s="80" t="s">
         <v>381</v>
       </c>
       <c r="F56" s="5" t="s">
@@ -5193,9 +5345,7 @@
         <v>387</v>
       </c>
       <c r="H56" s="5"/>
-      <c r="I56" s="6" t="s">
-        <v>768</v>
-      </c>
+      <c r="I56" s="6"/>
       <c r="J56" s="5"/>
       <c r="K56" s="6"/>
     </row>
@@ -5203,7 +5353,7 @@
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
       <c r="D57" s="6"/>
-      <c r="E57" s="5" t="s">
+      <c r="E57" s="80" t="s">
         <v>382</v>
       </c>
       <c r="F57" s="5" t="s">
@@ -5216,6 +5366,224 @@
       <c r="I57" s="6"/>
       <c r="J57" s="5"/>
       <c r="K57" s="6"/>
+    </row>
+    <row r="58" spans="2:11">
+      <c r="F58" s="5"/>
+      <c r="G58" s="6"/>
+      <c r="H58" s="5"/>
+      <c r="I58" s="6"/>
+      <c r="J58" s="6"/>
+      <c r="K58" s="6"/>
+    </row>
+    <row r="59" spans="2:11">
+      <c r="F59" s="5"/>
+      <c r="G59" s="6"/>
+      <c r="H59" s="5"/>
+      <c r="I59" s="6"/>
+      <c r="J59" s="6"/>
+      <c r="K59" s="6"/>
+    </row>
+    <row r="60" spans="2:11">
+      <c r="F60" s="5"/>
+      <c r="G60" s="6"/>
+      <c r="H60" s="5"/>
+      <c r="I60" s="6"/>
+      <c r="J60" s="6"/>
+      <c r="K60" s="6"/>
+    </row>
+    <row r="61" spans="2:11">
+      <c r="F61" s="5"/>
+      <c r="G61" s="6"/>
+      <c r="H61" s="5"/>
+      <c r="I61" s="6"/>
+      <c r="J61" s="6"/>
+      <c r="K61" s="6"/>
+    </row>
+    <row r="62" spans="2:11">
+      <c r="F62" s="5"/>
+      <c r="G62" s="6"/>
+      <c r="H62" s="5"/>
+      <c r="I62" s="6"/>
+      <c r="J62" s="6"/>
+      <c r="K62" s="6"/>
+    </row>
+    <row r="63" spans="2:11">
+      <c r="F63" s="5"/>
+      <c r="G63" s="6"/>
+      <c r="H63" s="5" t="s">
+        <v>752</v>
+      </c>
+      <c r="I63" s="6" t="s">
+        <v>766</v>
+      </c>
+      <c r="J63" s="6"/>
+      <c r="K63" s="6"/>
+    </row>
+    <row r="64" spans="2:11">
+      <c r="F64" s="5"/>
+      <c r="G64" s="6"/>
+      <c r="H64" s="5" t="s">
+        <v>753</v>
+      </c>
+      <c r="I64" s="6" t="s">
+        <v>767</v>
+      </c>
+      <c r="J64" s="6"/>
+      <c r="K64" s="6"/>
+    </row>
+    <row r="65" spans="6:11">
+      <c r="F65" s="5"/>
+      <c r="G65" s="6"/>
+      <c r="H65" s="5" t="s">
+        <v>754</v>
+      </c>
+      <c r="I65" s="6" t="s">
+        <v>768</v>
+      </c>
+      <c r="J65" s="6"/>
+      <c r="K65" s="6"/>
+    </row>
+    <row r="66" spans="6:11">
+      <c r="F66" s="5"/>
+      <c r="G66" s="6"/>
+      <c r="H66" s="5" t="s">
+        <v>755</v>
+      </c>
+      <c r="I66" s="6" t="s">
+        <v>769</v>
+      </c>
+      <c r="J66" s="6"/>
+      <c r="K66" s="6"/>
+    </row>
+    <row r="67" spans="6:11">
+      <c r="F67" s="5"/>
+      <c r="G67" s="6"/>
+      <c r="H67" s="5" t="s">
+        <v>756</v>
+      </c>
+      <c r="I67" s="6" t="s">
+        <v>770</v>
+      </c>
+      <c r="J67" s="6"/>
+      <c r="K67" s="6"/>
+    </row>
+    <row r="68" spans="6:11">
+      <c r="F68" s="5"/>
+      <c r="G68" s="6"/>
+      <c r="H68" s="5" t="s">
+        <v>757</v>
+      </c>
+      <c r="I68" s="6" t="s">
+        <v>771</v>
+      </c>
+      <c r="J68" s="6"/>
+      <c r="K68" s="6"/>
+    </row>
+    <row r="69" spans="6:11">
+      <c r="F69" s="5"/>
+      <c r="G69" s="6"/>
+      <c r="H69" s="5" t="s">
+        <v>758</v>
+      </c>
+      <c r="I69" s="6" t="s">
+        <v>772</v>
+      </c>
+      <c r="J69" s="6"/>
+      <c r="K69" s="6"/>
+    </row>
+    <row r="70" spans="6:11">
+      <c r="F70" s="5"/>
+      <c r="G70" s="6"/>
+      <c r="H70" s="5" t="s">
+        <v>759</v>
+      </c>
+      <c r="I70" s="6" t="s">
+        <v>773</v>
+      </c>
+      <c r="J70" s="6"/>
+      <c r="K70" s="6"/>
+    </row>
+    <row r="71" spans="6:11">
+      <c r="F71" s="5"/>
+      <c r="G71" s="6"/>
+      <c r="H71" s="5" t="s">
+        <v>760</v>
+      </c>
+      <c r="I71" s="6" t="s">
+        <v>774</v>
+      </c>
+      <c r="J71" s="6"/>
+      <c r="K71" s="6"/>
+    </row>
+    <row r="72" spans="6:11">
+      <c r="F72" s="5"/>
+      <c r="G72" s="6"/>
+      <c r="H72" s="5" t="s">
+        <v>761</v>
+      </c>
+      <c r="I72" s="6" t="s">
+        <v>766</v>
+      </c>
+      <c r="J72" s="6"/>
+      <c r="K72" s="6"/>
+    </row>
+    <row r="73" spans="6:11">
+      <c r="F73" s="5"/>
+      <c r="G73" s="6"/>
+      <c r="H73" s="5" t="s">
+        <v>762</v>
+      </c>
+      <c r="I73" s="6" t="s">
+        <v>767</v>
+      </c>
+      <c r="J73" s="6"/>
+      <c r="K73" s="6"/>
+    </row>
+    <row r="74" spans="6:11">
+      <c r="F74" s="5"/>
+      <c r="G74" s="6"/>
+      <c r="H74" s="5" t="s">
+        <v>763</v>
+      </c>
+      <c r="I74" s="6" t="s">
+        <v>768</v>
+      </c>
+      <c r="J74" s="6"/>
+      <c r="K74" s="6"/>
+    </row>
+    <row r="75" spans="6:11">
+      <c r="F75" s="5"/>
+      <c r="G75" s="6"/>
+      <c r="H75" s="5" t="s">
+        <v>764</v>
+      </c>
+      <c r="I75" s="6" t="s">
+        <v>766</v>
+      </c>
+      <c r="J75" s="6"/>
+      <c r="K75" s="6"/>
+    </row>
+    <row r="76" spans="6:11">
+      <c r="F76" s="5"/>
+      <c r="G76" s="6"/>
+      <c r="H76" s="5" t="s">
+        <v>765</v>
+      </c>
+      <c r="I76" s="6" t="s">
+        <v>767</v>
+      </c>
+      <c r="J76" s="6"/>
+      <c r="K76" s="6"/>
+    </row>
+    <row r="77" spans="6:11">
+      <c r="F77" s="5"/>
+      <c r="G77" s="6"/>
+      <c r="H77" s="5"/>
+      <c r="I77" s="6" t="s">
+        <v>768</v>
+      </c>
+      <c r="J77" s="6"/>
+      <c r="K77" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -5275,105 +5643,105 @@
       <c r="X2" s="12"/>
     </row>
     <row r="3" spans="3:24" s="3" customFormat="1">
-      <c r="C3" s="76" t="s">
+      <c r="C3" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76" t="s">
+      <c r="D3" s="32"/>
+      <c r="E3" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="K3" s="76" t="s">
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="K3" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="L3" s="76"/>
-      <c r="M3" s="76" t="s">
+      <c r="L3" s="32"/>
+      <c r="M3" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="N3" s="76"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="76"/>
-      <c r="S3" s="76" t="s">
+      <c r="N3" s="32"/>
+      <c r="O3" s="32"/>
+      <c r="P3" s="32"/>
+      <c r="S3" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="T3" s="76"/>
-      <c r="U3" s="76" t="s">
+      <c r="T3" s="32"/>
+      <c r="U3" s="32" t="s">
         <v>209</v>
       </c>
-      <c r="V3" s="76"/>
-      <c r="W3" s="76"/>
-      <c r="X3" s="76"/>
+      <c r="V3" s="32"/>
+      <c r="W3" s="32"/>
+      <c r="X3" s="32"/>
     </row>
     <row r="4" spans="3:24" s="3" customFormat="1">
-      <c r="C4" s="76" t="s">
+      <c r="C4" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
-      <c r="K4" s="76" t="s">
+      <c r="K4" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="L4" s="76"/>
-      <c r="M4" s="76"/>
-      <c r="N4" s="76"/>
-      <c r="O4" s="76"/>
-      <c r="P4" s="76"/>
-      <c r="S4" s="76" t="s">
+      <c r="L4" s="32"/>
+      <c r="M4" s="32"/>
+      <c r="N4" s="32"/>
+      <c r="O4" s="32"/>
+      <c r="P4" s="32"/>
+      <c r="S4" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="T4" s="76"/>
-      <c r="U4" s="76"/>
-      <c r="V4" s="76"/>
-      <c r="W4" s="76"/>
-      <c r="X4" s="76"/>
+      <c r="T4" s="32"/>
+      <c r="U4" s="32"/>
+      <c r="V4" s="32"/>
+      <c r="W4" s="32"/>
+      <c r="X4" s="32"/>
     </row>
     <row r="5" spans="3:24" s="2" customFormat="1">
-      <c r="C5" s="76" t="s">
+      <c r="C5" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="76"/>
+      <c r="D5" s="32"/>
       <c r="E5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="76" t="s">
+      <c r="F5" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="76"/>
+      <c r="G5" s="32"/>
       <c r="H5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K5" s="76" t="s">
+      <c r="K5" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="L5" s="76"/>
+      <c r="L5" s="32"/>
       <c r="M5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="N5" s="76" t="s">
+      <c r="N5" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="O5" s="76"/>
+      <c r="O5" s="32"/>
       <c r="P5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="S5" s="76" t="s">
+      <c r="S5" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="T5" s="76"/>
+      <c r="T5" s="32"/>
       <c r="U5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="V5" s="76" t="s">
+      <c r="V5" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="W5" s="76"/>
+      <c r="W5" s="32"/>
       <c r="X5" s="4" t="s">
         <v>10</v>
       </c>
@@ -6019,103 +6387,103 @@
       <c r="X22" s="12"/>
     </row>
     <row r="23" spans="3:24">
-      <c r="C23" s="76" t="s">
+      <c r="C23" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="D23" s="76"/>
-      <c r="E23" s="76" t="s">
+      <c r="D23" s="32"/>
+      <c r="E23" s="32" t="s">
         <v>210</v>
       </c>
-      <c r="F23" s="76"/>
-      <c r="G23" s="76"/>
-      <c r="H23" s="76"/>
-      <c r="K23" s="76" t="s">
+      <c r="F23" s="32"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="32"/>
+      <c r="K23" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="L23" s="76"/>
-      <c r="M23" s="76" t="s">
+      <c r="L23" s="32"/>
+      <c r="M23" s="32" t="s">
         <v>211</v>
       </c>
-      <c r="N23" s="76"/>
-      <c r="O23" s="76"/>
-      <c r="P23" s="76"/>
-      <c r="S23" s="76" t="s">
+      <c r="N23" s="32"/>
+      <c r="O23" s="32"/>
+      <c r="P23" s="32"/>
+      <c r="S23" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="T23" s="76"/>
-      <c r="U23" s="76" t="s">
+      <c r="T23" s="32"/>
+      <c r="U23" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="V23" s="76"/>
-      <c r="W23" s="76"/>
-      <c r="X23" s="76"/>
+      <c r="V23" s="32"/>
+      <c r="W23" s="32"/>
+      <c r="X23" s="32"/>
     </row>
     <row r="24" spans="3:24">
-      <c r="C24" s="76" t="s">
+      <c r="C24" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="D24" s="76"/>
-      <c r="E24" s="76"/>
-      <c r="F24" s="76"/>
-      <c r="G24" s="76"/>
-      <c r="H24" s="76"/>
-      <c r="K24" s="76" t="s">
+      <c r="D24" s="32"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="32"/>
+      <c r="K24" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="L24" s="76"/>
-      <c r="M24" s="76"/>
-      <c r="N24" s="76"/>
-      <c r="O24" s="76"/>
-      <c r="P24" s="76"/>
-      <c r="S24" s="76" t="s">
+      <c r="L24" s="32"/>
+      <c r="M24" s="32"/>
+      <c r="N24" s="32"/>
+      <c r="O24" s="32"/>
+      <c r="P24" s="32"/>
+      <c r="S24" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="T24" s="76"/>
-      <c r="U24" s="76"/>
-      <c r="V24" s="76"/>
-      <c r="W24" s="76"/>
-      <c r="X24" s="76"/>
+      <c r="T24" s="32"/>
+      <c r="U24" s="32"/>
+      <c r="V24" s="32"/>
+      <c r="W24" s="32"/>
+      <c r="X24" s="32"/>
     </row>
     <row r="25" spans="3:24">
-      <c r="C25" s="76" t="s">
+      <c r="C25" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="D25" s="76"/>
+      <c r="D25" s="32"/>
       <c r="E25" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F25" s="76" t="s">
+      <c r="F25" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="G25" s="76"/>
+      <c r="G25" s="32"/>
       <c r="H25" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K25" s="76" t="s">
+      <c r="K25" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="L25" s="76"/>
+      <c r="L25" s="32"/>
       <c r="M25" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="N25" s="76" t="s">
+      <c r="N25" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="O25" s="76"/>
+      <c r="O25" s="32"/>
       <c r="P25" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="S25" s="76" t="s">
+      <c r="S25" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="T25" s="76"/>
+      <c r="T25" s="32"/>
       <c r="U25" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="V25" s="76" t="s">
+      <c r="V25" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="W25" s="76"/>
+      <c r="W25" s="32"/>
       <c r="X25" s="4" t="s">
         <v>10</v>
       </c>
@@ -6722,114 +7090,114 @@
     </row>
     <row r="42" spans="2:24">
       <c r="B42" s="8"/>
-      <c r="C42" s="76" t="s">
+      <c r="C42" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="D42" s="76"/>
-      <c r="E42" s="76" t="s">
+      <c r="D42" s="32"/>
+      <c r="E42" s="32" t="s">
         <v>213</v>
       </c>
-      <c r="F42" s="76"/>
-      <c r="G42" s="76"/>
-      <c r="H42" s="76"/>
+      <c r="F42" s="32"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="32"/>
       <c r="I42" s="7"/>
       <c r="J42" s="7"/>
       <c r="K42" s="4" t="s">
         <v>40</v>
       </c>
       <c r="L42" s="4"/>
-      <c r="M42" s="76" t="s">
+      <c r="M42" s="32" t="s">
         <v>214</v>
       </c>
-      <c r="N42" s="76"/>
-      <c r="O42" s="76"/>
-      <c r="P42" s="76"/>
+      <c r="N42" s="32"/>
+      <c r="O42" s="32"/>
+      <c r="P42" s="32"/>
       <c r="Q42" s="8"/>
       <c r="S42" s="4" t="s">
         <v>40</v>
       </c>
       <c r="T42" s="4"/>
-      <c r="U42" s="76" t="s">
+      <c r="U42" s="32" t="s">
         <v>215</v>
       </c>
-      <c r="V42" s="76"/>
-      <c r="W42" s="76"/>
-      <c r="X42" s="76"/>
+      <c r="V42" s="32"/>
+      <c r="W42" s="32"/>
+      <c r="X42" s="32"/>
     </row>
     <row r="43" spans="2:24">
       <c r="B43" s="8"/>
-      <c r="C43" s="76" t="s">
+      <c r="C43" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="D43" s="76"/>
-      <c r="E43" s="76"/>
-      <c r="F43" s="76"/>
-      <c r="G43" s="76"/>
-      <c r="H43" s="76"/>
+      <c r="D43" s="32"/>
+      <c r="E43" s="32"/>
+      <c r="F43" s="32"/>
+      <c r="G43" s="32"/>
+      <c r="H43" s="32"/>
       <c r="I43" s="7"/>
       <c r="J43" s="7"/>
       <c r="K43" s="4" t="s">
         <v>39</v>
       </c>
       <c r="L43" s="4"/>
-      <c r="M43" s="76"/>
-      <c r="N43" s="76"/>
-      <c r="O43" s="76"/>
-      <c r="P43" s="76"/>
+      <c r="M43" s="32"/>
+      <c r="N43" s="32"/>
+      <c r="O43" s="32"/>
+      <c r="P43" s="32"/>
       <c r="Q43" s="8"/>
       <c r="S43" s="4" t="s">
         <v>39</v>
       </c>
       <c r="T43" s="4"/>
-      <c r="U43" s="76"/>
-      <c r="V43" s="76"/>
-      <c r="W43" s="76"/>
-      <c r="X43" s="76"/>
+      <c r="U43" s="32"/>
+      <c r="V43" s="32"/>
+      <c r="W43" s="32"/>
+      <c r="X43" s="32"/>
     </row>
     <row r="44" spans="2:24">
       <c r="B44" s="8"/>
-      <c r="C44" s="76" t="s">
+      <c r="C44" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="D44" s="76"/>
+      <c r="D44" s="32"/>
       <c r="E44" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F44" s="76" t="s">
+      <c r="F44" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="G44" s="76"/>
+      <c r="G44" s="32"/>
       <c r="H44" s="4" t="s">
         <v>10</v>
       </c>
       <c r="I44" s="7"/>
       <c r="J44" s="7"/>
-      <c r="K44" s="76" t="s">
+      <c r="K44" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="L44" s="76"/>
+      <c r="L44" s="32"/>
       <c r="M44" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="N44" s="76" t="s">
+      <c r="N44" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="O44" s="76"/>
+      <c r="O44" s="32"/>
       <c r="P44" s="4" t="s">
         <v>10</v>
       </c>
       <c r="Q44" s="8"/>
-      <c r="S44" s="76" t="s">
+      <c r="S44" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="T44" s="76"/>
+      <c r="T44" s="32"/>
       <c r="U44" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="V44" s="76" t="s">
+      <c r="V44" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="W44" s="76"/>
+      <c r="W44" s="32"/>
       <c r="X44" s="4" t="s">
         <v>10</v>
       </c>
@@ -7460,6 +7828,40 @@
     </row>
   </sheetData>
   <mergeCells count="50">
+    <mergeCell ref="N44:O44"/>
+    <mergeCell ref="V44:W44"/>
+    <mergeCell ref="S44:T44"/>
+    <mergeCell ref="K44:L44"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="M43:P43"/>
+    <mergeCell ref="U43:X43"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="M23:P23"/>
+    <mergeCell ref="M24:P24"/>
+    <mergeCell ref="U23:X23"/>
+    <mergeCell ref="U24:X24"/>
+    <mergeCell ref="S23:T23"/>
+    <mergeCell ref="S24:T24"/>
+    <mergeCell ref="S25:T25"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="U4:X4"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="K5:L5"/>
     <mergeCell ref="E42:H42"/>
     <mergeCell ref="M42:P42"/>
     <mergeCell ref="U42:X42"/>
@@ -7476,40 +7878,6 @@
     <mergeCell ref="V25:W25"/>
     <mergeCell ref="N25:O25"/>
     <mergeCell ref="U3:X3"/>
-    <mergeCell ref="U4:X4"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="N44:O44"/>
-    <mergeCell ref="V44:W44"/>
-    <mergeCell ref="S44:T44"/>
-    <mergeCell ref="K44:L44"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="M43:P43"/>
-    <mergeCell ref="U43:X43"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="M23:P23"/>
-    <mergeCell ref="M24:P24"/>
-    <mergeCell ref="U23:X23"/>
-    <mergeCell ref="U24:X24"/>
-    <mergeCell ref="S23:T23"/>
-    <mergeCell ref="S24:T24"/>
-    <mergeCell ref="S25:T25"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7557,29 +7925,29 @@
       </c>
     </row>
     <row r="3" spans="2:21">
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="78"/>
-      <c r="D3" s="77" t="s">
+      <c r="C3" s="34"/>
+      <c r="D3" s="33" t="s">
         <v>292</v>
       </c>
-      <c r="E3" s="79"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="78"/>
-      <c r="I3" s="77" t="s">
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="34"/>
+      <c r="I3" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="J3" s="78"/>
-      <c r="K3" s="76" t="s">
+      <c r="J3" s="34"/>
+      <c r="K3" s="32" t="s">
         <v>307</v>
       </c>
-      <c r="L3" s="76"/>
-      <c r="M3" s="76"/>
-      <c r="N3" s="76"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="76"/>
-      <c r="Q3" s="76"/>
+      <c r="L3" s="32"/>
+      <c r="M3" s="32"/>
+      <c r="N3" s="32"/>
+      <c r="O3" s="32"/>
+      <c r="P3" s="32"/>
+      <c r="Q3" s="32"/>
       <c r="S3" s="5">
         <v>0</v>
       </c>
@@ -7589,25 +7957,25 @@
       <c r="U3" s="6"/>
     </row>
     <row r="4" spans="2:21">
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="78"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="79"/>
-      <c r="F4" s="79"/>
-      <c r="G4" s="78"/>
-      <c r="I4" s="77" t="s">
+      <c r="C4" s="34"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="34"/>
+      <c r="I4" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="J4" s="78"/>
-      <c r="K4" s="76"/>
-      <c r="L4" s="76"/>
-      <c r="M4" s="76"/>
-      <c r="N4" s="76"/>
-      <c r="O4" s="76"/>
-      <c r="P4" s="76"/>
-      <c r="Q4" s="76"/>
+      <c r="J4" s="34"/>
+      <c r="K4" s="32"/>
+      <c r="L4" s="32"/>
+      <c r="M4" s="32"/>
+      <c r="N4" s="32"/>
+      <c r="O4" s="32"/>
+      <c r="P4" s="32"/>
+      <c r="Q4" s="32"/>
       <c r="S4" s="5">
         <v>100</v>
       </c>
@@ -7619,38 +7987,38 @@
       </c>
     </row>
     <row r="5" spans="2:21">
-      <c r="B5" s="77" t="s">
+      <c r="B5" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="78"/>
+      <c r="C5" s="34"/>
       <c r="D5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="77" t="s">
+      <c r="E5" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="78"/>
+      <c r="F5" s="34"/>
       <c r="G5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="I5" s="77" t="s">
+      <c r="I5" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="78"/>
+      <c r="J5" s="34"/>
       <c r="K5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L5" s="77" t="s">
+      <c r="L5" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="M5" s="78"/>
+      <c r="M5" s="34"/>
       <c r="N5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="O5" s="77" t="s">
+      <c r="O5" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="P5" s="78"/>
+      <c r="P5" s="34"/>
       <c r="Q5" s="4" t="s">
         <v>10</v>
       </c>
@@ -8345,31 +8713,31 @@
   <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData>
     <row r="6" spans="4:20" ht="17.25" thickBot="1">
-      <c r="D6" s="32" t="s">
+      <c r="D6" s="68" t="s">
         <v>365</v>
       </c>
-      <c r="E6" s="32"/>
-      <c r="F6" s="32"/>
-      <c r="G6" s="32"/>
-      <c r="I6" s="32" t="s">
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
+      <c r="I6" s="68" t="s">
         <v>744</v>
       </c>
-      <c r="J6" s="32"/>
-      <c r="K6" s="32"/>
-      <c r="M6" s="32" t="s">
+      <c r="J6" s="68"/>
+      <c r="K6" s="68"/>
+      <c r="M6" s="68" t="s">
         <v>367</v>
       </c>
-      <c r="N6" s="32"/>
-      <c r="O6" s="32"/>
-      <c r="P6" s="32"/>
-      <c r="R6" s="32" t="s">
+      <c r="N6" s="68"/>
+      <c r="O6" s="68"/>
+      <c r="P6" s="68"/>
+      <c r="R6" s="68" t="s">
         <v>745</v>
       </c>
-      <c r="S6" s="32"/>
-      <c r="T6" s="32"/>
+      <c r="S6" s="68"/>
+      <c r="T6" s="68"/>
     </row>
     <row r="7" spans="4:20" ht="16.5" customHeight="1">
-      <c r="D7" s="63" t="s">
+      <c r="D7" s="36" t="s">
         <v>742</v>
       </c>
       <c r="E7" s="22"/>
@@ -8378,7 +8746,7 @@
       <c r="I7" s="27"/>
       <c r="J7" s="22"/>
       <c r="K7" s="23"/>
-      <c r="M7" s="63" t="s">
+      <c r="M7" s="36" t="s">
         <v>740</v>
       </c>
       <c r="N7" s="22"/>
@@ -8389,195 +8757,195 @@
       <c r="T7" s="23"/>
     </row>
     <row r="8" spans="4:20">
-      <c r="D8" s="64"/>
+      <c r="D8" s="37"/>
       <c r="G8" s="24"/>
       <c r="I8" s="25"/>
       <c r="K8" s="24"/>
-      <c r="M8" s="64"/>
+      <c r="M8" s="37"/>
       <c r="P8" s="24"/>
       <c r="R8" s="25"/>
       <c r="T8" s="24"/>
     </row>
     <row r="9" spans="4:20" ht="16.5" customHeight="1">
-      <c r="D9" s="64"/>
-      <c r="F9" s="41" t="s">
+      <c r="D9" s="37"/>
+      <c r="F9" s="48" t="s">
         <v>739</v>
       </c>
       <c r="G9" s="24"/>
       <c r="I9" s="25"/>
-      <c r="J9" s="41" t="s">
+      <c r="J9" s="48" t="s">
         <v>739</v>
       </c>
       <c r="K9" s="24"/>
-      <c r="M9" s="64"/>
-      <c r="O9" s="41" t="s">
+      <c r="M9" s="37"/>
+      <c r="O9" s="48" t="s">
         <v>739</v>
       </c>
       <c r="P9" s="24"/>
       <c r="R9" s="25"/>
-      <c r="S9" s="41" t="s">
+      <c r="S9" s="48" t="s">
         <v>739</v>
       </c>
       <c r="T9" s="24"/>
     </row>
     <row r="10" spans="4:20">
-      <c r="D10" s="64"/>
-      <c r="F10" s="52"/>
+      <c r="D10" s="37"/>
+      <c r="F10" s="49"/>
       <c r="G10" s="24"/>
       <c r="I10" s="25"/>
-      <c r="J10" s="52"/>
+      <c r="J10" s="49"/>
       <c r="K10" s="24"/>
-      <c r="M10" s="64"/>
-      <c r="O10" s="52"/>
+      <c r="M10" s="37"/>
+      <c r="O10" s="49"/>
       <c r="P10" s="24"/>
       <c r="R10" s="25"/>
-      <c r="S10" s="52"/>
+      <c r="S10" s="49"/>
       <c r="T10" s="24"/>
     </row>
     <row r="11" spans="4:20" ht="16.5" customHeight="1">
-      <c r="D11" s="64"/>
-      <c r="E11" s="39" t="s">
+      <c r="D11" s="37"/>
+      <c r="E11" s="50" t="s">
         <v>738</v>
       </c>
       <c r="G11" s="24"/>
       <c r="I11" s="25"/>
-      <c r="J11" s="39" t="s">
+      <c r="J11" s="50" t="s">
         <v>738</v>
       </c>
       <c r="K11" s="24"/>
-      <c r="M11" s="64"/>
-      <c r="N11" s="39" t="s">
+      <c r="M11" s="37"/>
+      <c r="N11" s="50" t="s">
         <v>738</v>
       </c>
       <c r="P11" s="24"/>
       <c r="R11" s="25"/>
-      <c r="S11" s="39" t="s">
+      <c r="S11" s="50" t="s">
         <v>738</v>
       </c>
       <c r="T11" s="24"/>
     </row>
     <row r="12" spans="4:20">
-      <c r="D12" s="64"/>
-      <c r="E12" s="66"/>
+      <c r="D12" s="37"/>
+      <c r="E12" s="51"/>
       <c r="G12" s="24"/>
       <c r="I12" s="25"/>
-      <c r="J12" s="40"/>
+      <c r="J12" s="61"/>
       <c r="K12" s="24"/>
-      <c r="M12" s="64"/>
-      <c r="N12" s="66"/>
+      <c r="M12" s="37"/>
+      <c r="N12" s="51"/>
       <c r="P12" s="24"/>
       <c r="R12" s="25"/>
-      <c r="S12" s="40"/>
+      <c r="S12" s="61"/>
       <c r="T12" s="24"/>
     </row>
     <row r="13" spans="4:20">
-      <c r="D13" s="65"/>
+      <c r="D13" s="38"/>
       <c r="G13" s="24"/>
       <c r="I13" s="25"/>
       <c r="K13" s="24"/>
-      <c r="M13" s="65"/>
+      <c r="M13" s="38"/>
       <c r="P13" s="24"/>
       <c r="R13" s="25"/>
       <c r="T13" s="24"/>
     </row>
     <row r="14" spans="4:20" ht="16.5" customHeight="1">
       <c r="D14" s="25"/>
-      <c r="E14" s="67" t="s">
+      <c r="E14" s="39" t="s">
         <v>741</v>
       </c>
-      <c r="F14" s="68"/>
-      <c r="G14" s="69"/>
-      <c r="I14" s="53" t="s">
+      <c r="F14" s="40"/>
+      <c r="G14" s="41"/>
+      <c r="I14" s="52" t="s">
         <v>747</v>
       </c>
-      <c r="J14" s="54"/>
-      <c r="K14" s="59"/>
+      <c r="J14" s="53"/>
+      <c r="K14" s="54"/>
       <c r="M14" s="25"/>
-      <c r="N14" s="67" t="s">
+      <c r="N14" s="39" t="s">
         <v>750</v>
       </c>
-      <c r="O14" s="68"/>
-      <c r="P14" s="69"/>
-      <c r="R14" s="53" t="s">
+      <c r="O14" s="40"/>
+      <c r="P14" s="41"/>
+      <c r="R14" s="52" t="s">
         <v>747</v>
       </c>
-      <c r="S14" s="54"/>
-      <c r="T14" s="59"/>
+      <c r="S14" s="53"/>
+      <c r="T14" s="54"/>
     </row>
     <row r="15" spans="4:20">
       <c r="D15" s="25"/>
-      <c r="E15" s="70"/>
-      <c r="F15" s="71"/>
-      <c r="G15" s="72"/>
-      <c r="I15" s="46"/>
-      <c r="J15" s="47"/>
-      <c r="K15" s="48"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="44"/>
+      <c r="I15" s="55"/>
+      <c r="J15" s="56"/>
+      <c r="K15" s="57"/>
       <c r="M15" s="25"/>
-      <c r="N15" s="70"/>
-      <c r="O15" s="71"/>
-      <c r="P15" s="72"/>
-      <c r="R15" s="46"/>
-      <c r="S15" s="47"/>
-      <c r="T15" s="48"/>
+      <c r="N15" s="42"/>
+      <c r="O15" s="43"/>
+      <c r="P15" s="44"/>
+      <c r="R15" s="55"/>
+      <c r="S15" s="56"/>
+      <c r="T15" s="57"/>
     </row>
     <row r="16" spans="4:20">
       <c r="D16" s="25"/>
-      <c r="E16" s="70"/>
-      <c r="F16" s="71"/>
-      <c r="G16" s="72"/>
-      <c r="I16" s="46"/>
-      <c r="J16" s="47"/>
-      <c r="K16" s="48"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="44"/>
+      <c r="I16" s="55"/>
+      <c r="J16" s="56"/>
+      <c r="K16" s="57"/>
       <c r="M16" s="25"/>
-      <c r="N16" s="70"/>
-      <c r="O16" s="71"/>
-      <c r="P16" s="72"/>
-      <c r="R16" s="46"/>
-      <c r="S16" s="47"/>
-      <c r="T16" s="48"/>
+      <c r="N16" s="42"/>
+      <c r="O16" s="43"/>
+      <c r="P16" s="44"/>
+      <c r="R16" s="55"/>
+      <c r="S16" s="56"/>
+      <c r="T16" s="57"/>
     </row>
     <row r="17" spans="4:20" ht="17.25" thickBot="1">
       <c r="D17" s="26"/>
-      <c r="E17" s="73"/>
-      <c r="F17" s="74"/>
-      <c r="G17" s="75"/>
-      <c r="I17" s="60"/>
-      <c r="J17" s="61"/>
-      <c r="K17" s="62"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="46"/>
+      <c r="G17" s="47"/>
+      <c r="I17" s="58"/>
+      <c r="J17" s="59"/>
+      <c r="K17" s="60"/>
       <c r="M17" s="26"/>
-      <c r="N17" s="73"/>
-      <c r="O17" s="74"/>
-      <c r="P17" s="75"/>
-      <c r="R17" s="60"/>
-      <c r="S17" s="61"/>
-      <c r="T17" s="62"/>
+      <c r="N17" s="45"/>
+      <c r="O17" s="46"/>
+      <c r="P17" s="47"/>
+      <c r="R17" s="58"/>
+      <c r="S17" s="59"/>
+      <c r="T17" s="60"/>
     </row>
     <row r="19" spans="4:20" ht="17.25" thickBot="1">
-      <c r="D19" s="32" t="s">
+      <c r="D19" s="68" t="s">
         <v>376</v>
       </c>
-      <c r="E19" s="32"/>
-      <c r="F19" s="32"/>
-      <c r="H19" s="32" t="s">
+      <c r="E19" s="68"/>
+      <c r="F19" s="68"/>
+      <c r="H19" s="68" t="s">
         <v>375</v>
       </c>
-      <c r="I19" s="32"/>
-      <c r="J19" s="32"/>
-      <c r="K19" s="32"/>
-      <c r="R19" s="32" t="s">
+      <c r="I19" s="68"/>
+      <c r="J19" s="68"/>
+      <c r="K19" s="68"/>
+      <c r="R19" s="68" t="s">
         <v>746</v>
       </c>
-      <c r="S19" s="32"/>
-      <c r="T19" s="32"/>
+      <c r="S19" s="68"/>
+      <c r="T19" s="68"/>
     </row>
     <row r="20" spans="4:20">
-      <c r="D20" s="43" t="s">
+      <c r="D20" s="76" t="s">
         <v>743</v>
       </c>
-      <c r="E20" s="44"/>
-      <c r="F20" s="45"/>
+      <c r="E20" s="77"/>
+      <c r="F20" s="78"/>
       <c r="H20" s="27"/>
-      <c r="I20" s="58" t="s">
+      <c r="I20" s="67" t="s">
         <v>739</v>
       </c>
       <c r="J20" s="22"/>
@@ -8586,56 +8954,56 @@
       <c r="N20" s="22"/>
       <c r="O20" s="22"/>
       <c r="P20" s="23"/>
-      <c r="R20" s="43" t="s">
+      <c r="R20" s="76" t="s">
         <v>747</v>
       </c>
-      <c r="S20" s="44"/>
-      <c r="T20" s="45"/>
+      <c r="S20" s="77"/>
+      <c r="T20" s="78"/>
     </row>
     <row r="21" spans="4:20">
-      <c r="D21" s="46"/>
-      <c r="E21" s="47"/>
-      <c r="F21" s="48"/>
+      <c r="D21" s="55"/>
+      <c r="E21" s="56"/>
+      <c r="F21" s="57"/>
       <c r="H21" s="25"/>
-      <c r="I21" s="52"/>
+      <c r="I21" s="49"/>
       <c r="K21" s="24"/>
       <c r="M21" s="25"/>
       <c r="P21" s="24"/>
-      <c r="R21" s="46"/>
-      <c r="S21" s="47"/>
-      <c r="T21" s="48"/>
+      <c r="R21" s="55"/>
+      <c r="S21" s="56"/>
+      <c r="T21" s="57"/>
     </row>
     <row r="22" spans="4:20">
-      <c r="D22" s="46"/>
-      <c r="E22" s="47"/>
-      <c r="F22" s="48"/>
+      <c r="D22" s="55"/>
+      <c r="E22" s="56"/>
+      <c r="F22" s="57"/>
       <c r="H22" s="25"/>
-      <c r="I22" s="39" t="s">
+      <c r="I22" s="50" t="s">
         <v>738</v>
       </c>
-      <c r="J22" s="37" t="s">
+      <c r="J22" s="73" t="s">
         <v>748</v>
       </c>
       <c r="K22" s="24"/>
       <c r="M22" s="25"/>
       <c r="P22" s="24"/>
-      <c r="R22" s="46"/>
-      <c r="S22" s="47"/>
-      <c r="T22" s="48"/>
+      <c r="R22" s="55"/>
+      <c r="S22" s="56"/>
+      <c r="T22" s="57"/>
     </row>
     <row r="23" spans="4:20">
-      <c r="D23" s="49"/>
-      <c r="E23" s="50"/>
-      <c r="F23" s="51"/>
+      <c r="D23" s="64"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="79"/>
       <c r="H23" s="25"/>
-      <c r="I23" s="40"/>
-      <c r="J23" s="38"/>
+      <c r="I23" s="61"/>
+      <c r="J23" s="74"/>
       <c r="K23" s="24"/>
       <c r="M23" s="25"/>
       <c r="P23" s="24"/>
-      <c r="R23" s="49"/>
-      <c r="S23" s="50"/>
-      <c r="T23" s="51"/>
+      <c r="R23" s="64"/>
+      <c r="S23" s="65"/>
+      <c r="T23" s="79"/>
     </row>
     <row r="24" spans="4:20">
       <c r="D24" s="25"/>
@@ -8651,77 +9019,77 @@
     </row>
     <row r="25" spans="4:20" ht="16.5" customHeight="1">
       <c r="D25" s="25"/>
-      <c r="E25" s="39" t="s">
+      <c r="E25" s="50" t="s">
         <v>738</v>
       </c>
       <c r="F25" s="24"/>
-      <c r="H25" s="53" t="s">
+      <c r="H25" s="52" t="s">
         <v>751</v>
       </c>
-      <c r="I25" s="54"/>
-      <c r="J25" s="55"/>
+      <c r="I25" s="53"/>
+      <c r="J25" s="62"/>
       <c r="K25" s="24"/>
       <c r="M25" s="25"/>
       <c r="P25" s="24"/>
       <c r="R25" s="25"/>
-      <c r="S25" s="39" t="s">
+      <c r="S25" s="50" t="s">
         <v>738</v>
       </c>
       <c r="T25" s="24"/>
     </row>
     <row r="26" spans="4:20">
       <c r="D26" s="25"/>
-      <c r="E26" s="40"/>
+      <c r="E26" s="61"/>
       <c r="F26" s="24"/>
-      <c r="H26" s="46"/>
-      <c r="I26" s="47"/>
-      <c r="J26" s="56"/>
+      <c r="H26" s="55"/>
+      <c r="I26" s="56"/>
+      <c r="J26" s="63"/>
       <c r="K26" s="24"/>
       <c r="M26" s="25"/>
       <c r="P26" s="24"/>
       <c r="R26" s="25"/>
-      <c r="S26" s="40"/>
+      <c r="S26" s="61"/>
       <c r="T26" s="24"/>
     </row>
     <row r="27" spans="4:20">
       <c r="D27" s="25"/>
-      <c r="E27" s="41" t="s">
+      <c r="E27" s="48" t="s">
         <v>739</v>
       </c>
       <c r="F27" s="24"/>
-      <c r="H27" s="46"/>
-      <c r="I27" s="47"/>
-      <c r="J27" s="56"/>
-      <c r="K27" s="33" t="s">
+      <c r="H27" s="55"/>
+      <c r="I27" s="56"/>
+      <c r="J27" s="63"/>
+      <c r="K27" s="69" t="s">
         <v>740</v>
       </c>
       <c r="M27" s="25"/>
       <c r="P27" s="24"/>
       <c r="R27" s="25"/>
-      <c r="S27" s="41" t="s">
+      <c r="S27" s="48" t="s">
         <v>739</v>
       </c>
       <c r="T27" s="24"/>
     </row>
     <row r="28" spans="4:20" ht="16.5" customHeight="1">
       <c r="D28" s="25"/>
-      <c r="E28" s="52"/>
+      <c r="E28" s="49"/>
       <c r="F28" s="24"/>
-      <c r="H28" s="49"/>
-      <c r="I28" s="50"/>
-      <c r="J28" s="57"/>
-      <c r="K28" s="34"/>
+      <c r="H28" s="64"/>
+      <c r="I28" s="65"/>
+      <c r="J28" s="66"/>
+      <c r="K28" s="70"/>
       <c r="M28" s="25"/>
       <c r="P28" s="24"/>
       <c r="R28" s="25"/>
-      <c r="S28" s="52"/>
+      <c r="S28" s="49"/>
       <c r="T28" s="24"/>
     </row>
     <row r="29" spans="4:20">
       <c r="D29" s="25"/>
       <c r="F29" s="24"/>
       <c r="H29" s="25"/>
-      <c r="K29" s="35"/>
+      <c r="K29" s="71"/>
       <c r="M29" s="25"/>
       <c r="P29" s="24"/>
       <c r="R29" s="25"/>
@@ -8732,10 +9100,10 @@
       <c r="E30" s="28"/>
       <c r="F30" s="29"/>
       <c r="H30" s="25"/>
-      <c r="I30" s="39" t="s">
+      <c r="I30" s="50" t="s">
         <v>738</v>
       </c>
-      <c r="K30" s="35"/>
+      <c r="K30" s="71"/>
       <c r="M30" s="26"/>
       <c r="N30" s="28"/>
       <c r="O30" s="28"/>
@@ -8746,21 +9114,21 @@
     </row>
     <row r="31" spans="4:20">
       <c r="H31" s="25"/>
-      <c r="I31" s="40"/>
-      <c r="K31" s="35"/>
+      <c r="I31" s="61"/>
+      <c r="K31" s="71"/>
     </row>
     <row r="32" spans="4:20">
       <c r="H32" s="25"/>
-      <c r="I32" s="41" t="s">
+      <c r="I32" s="48" t="s">
         <v>739</v>
       </c>
-      <c r="K32" s="35"/>
+      <c r="K32" s="71"/>
     </row>
     <row r="33" spans="8:24" ht="17.25" thickBot="1">
       <c r="H33" s="26"/>
-      <c r="I33" s="42"/>
+      <c r="I33" s="75"/>
       <c r="J33" s="28"/>
-      <c r="K33" s="36"/>
+      <c r="K33" s="72"/>
     </row>
     <row r="47" spans="8:24">
       <c r="X47" t="s">
@@ -8769,24 +9137,6 @@
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="D7:D13"/>
-    <mergeCell ref="E14:G17"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="I14:K17"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="S11:S12"/>
-    <mergeCell ref="R14:T17"/>
-    <mergeCell ref="M7:M13"/>
-    <mergeCell ref="O9:O10"/>
-    <mergeCell ref="N11:N12"/>
-    <mergeCell ref="N14:P17"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="H25:J28"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="I22:I23"/>
-    <mergeCell ref="J11:J12"/>
     <mergeCell ref="R6:T6"/>
     <mergeCell ref="R19:T19"/>
     <mergeCell ref="D19:F19"/>
@@ -8803,6 +9153,24 @@
     <mergeCell ref="M6:P6"/>
     <mergeCell ref="D20:F23"/>
     <mergeCell ref="E27:E28"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="H25:J28"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="S11:S12"/>
+    <mergeCell ref="R14:T17"/>
+    <mergeCell ref="M7:M13"/>
+    <mergeCell ref="O9:O10"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="N14:P17"/>
+    <mergeCell ref="D7:D13"/>
+    <mergeCell ref="E14:G17"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="I14:K17"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/PLC/IO List.xlsx
+++ b/PLC/IO List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EZENIC\Desktop\Project-Second\PLC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B138645-277F-4831-8CB3-8D4F1F601279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2835CF8F-2E3F-4C19-AB07-89F71B4EF467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3990" yWindow="3555" windowWidth="21600" windowHeight="11295" xr2:uid="{E8A3CD3B-D612-4B37-A180-F6C335096DC9}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{E8A3CD3B-D612-4B37-A180-F6C335096DC9}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="815">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="803">
   <si>
     <t>X10</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -782,10 +782,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>로봇4(제4공정_저항 검사 공정)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>로봇5(제5공정_접착제 충전 공정)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -823,18 +819,9 @@
     <t>Y143</t>
   </si>
   <si>
-    <t>Y144</t>
-  </si>
-  <si>
     <t>Y146</t>
   </si>
   <si>
-    <t>Y147</t>
-  </si>
-  <si>
-    <t>Y148</t>
-  </si>
-  <si>
     <t>Y152</t>
   </si>
   <si>
@@ -1093,10 +1080,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>프레스(제1공정_하우징 공정)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>프레스 비상정지</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1302,23 +1285,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>X123</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>X124</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>X125</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>X126</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>X127</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2169,21 +2140,12 @@
     <t>M1112</t>
   </si>
   <si>
-    <t>M1113</t>
-  </si>
-  <si>
     <t>M1114</t>
   </si>
   <si>
     <t>M1115</t>
   </si>
   <si>
-    <t>M1116</t>
-  </si>
-  <si>
-    <t>M1117</t>
-  </si>
-  <si>
     <t>M1118</t>
   </si>
   <si>
@@ -2414,19 +2376,10 @@
     <t>M2133</t>
   </si>
   <si>
-    <t>M2134</t>
-  </si>
-  <si>
     <t>M2135</t>
   </si>
   <si>
     <t>M2136</t>
-  </si>
-  <si>
-    <t>M2137</t>
-  </si>
-  <si>
-    <t>M2138</t>
   </si>
   <si>
     <t>M2140</t>
@@ -2888,39 +2841,48 @@
     <t>M129</t>
   </si>
   <si>
-    <t>로봇1 타이머</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>로봇2 타이머</t>
-  </si>
-  <si>
-    <t>로봇3 타이머</t>
-  </si>
-  <si>
-    <t>로봇4 타이머</t>
-  </si>
-  <si>
-    <t>로봇5 타이머</t>
-  </si>
-  <si>
-    <t>로봇6 타이머</t>
-  </si>
-  <si>
-    <t>로봇7 타이머</t>
-  </si>
-  <si>
-    <t>로봇8 타이머</t>
-  </si>
-  <si>
-    <t>로봇9 타이머</t>
+    <t>프레스1(제4공정_저항 검사 공정)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>프레스2(제1공정_하우징 공정)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로봇1 작업완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로봇2 작업완료</t>
+  </si>
+  <si>
+    <t>로봇3 작업완료</t>
+  </si>
+  <si>
+    <t>로봇5 작업완료</t>
+  </si>
+  <si>
+    <t>로봇6 작업완료</t>
+  </si>
+  <si>
+    <t>로봇7 작업완료</t>
+  </si>
+  <si>
+    <t>로봇8 작업완료</t>
+  </si>
+  <si>
+    <t>로봇9 작업완료</t>
+  </si>
+  <si>
+    <t>프레스 작업완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2974,15 +2936,6 @@
       <color rgb="FFFF0000"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
@@ -3450,7 +3403,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3514,9 +3467,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -3547,6 +3497,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3559,6 +3512,99 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3566,6 +3612,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3593,105 +3642,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4105,7 +4055,7 @@
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="6" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>31</v>
@@ -4115,16 +4065,16 @@
         <v>49</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
     </row>
     <row r="7" spans="2:11">
@@ -4143,16 +4093,16 @@
         <v>50</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
     </row>
     <row r="8" spans="2:11">
@@ -4161,7 +4111,7 @@
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="6" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>33</v>
@@ -4171,16 +4121,16 @@
         <v>51</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
     </row>
     <row r="9" spans="2:11">
@@ -4189,7 +4139,7 @@
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="6" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>118</v>
@@ -4199,16 +4149,16 @@
         <v>119</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>512</v>
+        <v>504</v>
       </c>
     </row>
     <row r="10" spans="2:11">
@@ -4217,7 +4167,7 @@
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="6" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>34</v>
@@ -4227,16 +4177,16 @@
         <v>120</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>513</v>
+        <v>505</v>
       </c>
     </row>
     <row r="11" spans="2:11">
@@ -4253,16 +4203,16 @@
         <v>121</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
     </row>
     <row r="12" spans="2:11">
@@ -4279,16 +4229,16 @@
         <v>122</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
     </row>
     <row r="13" spans="2:11">
@@ -4305,16 +4255,16 @@
         <v>123</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
     </row>
     <row r="14" spans="2:11">
@@ -4331,10 +4281,10 @@
         <v>124</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="J14" s="5"/>
       <c r="K14" s="6"/>
@@ -4391,16 +4341,16 @@
         <v>127</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
     </row>
     <row r="18" spans="2:11">
@@ -4419,16 +4369,16 @@
         <v>52</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>520</v>
+        <v>512</v>
       </c>
     </row>
     <row r="19" spans="2:11">
@@ -4443,22 +4393,22 @@
         <v>140</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>132</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
     </row>
     <row r="20" spans="2:11">
@@ -4473,16 +4423,16 @@
         <v>141</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>133</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="J20" s="5"/>
       <c r="K20" s="6"/>
@@ -4499,16 +4449,16 @@
         <v>142</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>134</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="J21" s="5"/>
       <c r="K21" s="6"/>
@@ -4525,22 +4475,22 @@
         <v>143</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>135</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
     </row>
     <row r="23" spans="2:11">
@@ -4555,22 +4505,22 @@
         <v>129</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>136</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>786</v>
+        <v>772</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>796</v>
+        <v>782</v>
       </c>
     </row>
     <row r="24" spans="2:11">
@@ -4585,22 +4535,22 @@
         <v>130</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>137</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>787</v>
+        <v>773</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>797</v>
+        <v>783</v>
       </c>
     </row>
     <row r="25" spans="2:11">
@@ -4619,16 +4569,16 @@
         <v>170</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>788</v>
+        <v>774</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>798</v>
+        <v>784</v>
       </c>
     </row>
     <row r="26" spans="2:11">
@@ -4647,16 +4597,16 @@
         <v>171</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>789</v>
+        <v>775</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>799</v>
+        <v>785</v>
       </c>
     </row>
     <row r="27" spans="2:11">
@@ -4677,10 +4627,10 @@
       <c r="H27" s="5"/>
       <c r="I27" s="6"/>
       <c r="J27" s="5" t="s">
-        <v>790</v>
+        <v>776</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>800</v>
+        <v>786</v>
       </c>
     </row>
     <row r="28" spans="2:11">
@@ -4688,7 +4638,7 @@
         <v>6</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>107</v>
@@ -4703,10 +4653,10 @@
       <c r="H28" s="5"/>
       <c r="I28" s="6"/>
       <c r="J28" s="5" t="s">
-        <v>791</v>
+        <v>777</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>801</v>
+        <v>787</v>
       </c>
     </row>
     <row r="29" spans="2:11">
@@ -4714,7 +4664,7 @@
         <v>104</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>108</v>
@@ -4729,10 +4679,10 @@
       <c r="H29" s="5"/>
       <c r="I29" s="6"/>
       <c r="J29" s="5" t="s">
-        <v>792</v>
+        <v>778</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>802</v>
+        <v>788</v>
       </c>
     </row>
     <row r="30" spans="2:11">
@@ -4740,7 +4690,7 @@
         <v>105</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>109</v>
@@ -4755,10 +4705,10 @@
       <c r="H30" s="5"/>
       <c r="I30" s="6"/>
       <c r="J30" s="5" t="s">
-        <v>793</v>
+        <v>779</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>803</v>
+        <v>789</v>
       </c>
     </row>
     <row r="31" spans="2:11">
@@ -4766,7 +4716,7 @@
         <v>106</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>110</v>
@@ -4779,16 +4729,16 @@
         <v>176</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>804</v>
+        <v>790</v>
       </c>
     </row>
     <row r="32" spans="2:11">
@@ -4796,7 +4746,7 @@
         <v>25</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>111</v>
@@ -4809,10 +4759,10 @@
         <v>177</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="J32" s="5"/>
       <c r="K32" s="6"/>
@@ -4822,7 +4772,7 @@
         <v>26</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>112</v>
@@ -4835,10 +4785,10 @@
         <v>178</v>
       </c>
       <c r="H33" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="I33" s="6" t="s">
         <v>465</v>
-      </c>
-      <c r="I33" s="6" t="s">
-        <v>473</v>
       </c>
       <c r="J33" s="5"/>
       <c r="K33" s="6"/>
@@ -4849,7 +4799,7 @@
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="6" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="E34" s="5" t="s">
         <v>151</v>
@@ -4859,10 +4809,10 @@
         <v>179</v>
       </c>
       <c r="H34" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="I34" s="6" t="s">
         <v>466</v>
-      </c>
-      <c r="I34" s="6" t="s">
-        <v>474</v>
       </c>
       <c r="J34" s="5"/>
       <c r="K34" s="6"/>
@@ -4873,7 +4823,7 @@
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="6" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="E35" s="5" t="s">
         <v>152</v>
@@ -4883,10 +4833,10 @@
         <v>180</v>
       </c>
       <c r="H35" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="I35" s="6" t="s">
         <v>467</v>
-      </c>
-      <c r="I35" s="6" t="s">
-        <v>475</v>
       </c>
       <c r="J35" s="5"/>
       <c r="K35" s="6"/>
@@ -4897,7 +4847,7 @@
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="6" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="E36" s="5" t="s">
         <v>153</v>
@@ -4907,10 +4857,10 @@
         <v>181</v>
       </c>
       <c r="H36" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="I36" s="6" t="s">
         <v>468</v>
-      </c>
-      <c r="I36" s="6" t="s">
-        <v>476</v>
       </c>
       <c r="J36" s="5"/>
       <c r="K36" s="6"/>
@@ -4921,7 +4871,7 @@
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="6" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="E37" s="5" t="s">
         <v>154</v>
@@ -4931,10 +4881,10 @@
         <v>182</v>
       </c>
       <c r="H37" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="I37" s="6" t="s">
         <v>469</v>
-      </c>
-      <c r="I37" s="6" t="s">
-        <v>477</v>
       </c>
       <c r="J37" s="5"/>
       <c r="K37" s="6"/>
@@ -4945,7 +4895,7 @@
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="6" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="E38" s="5" t="s">
         <v>155</v>
@@ -4955,10 +4905,10 @@
         <v>183</v>
       </c>
       <c r="H38" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="I38" s="6" t="s">
         <v>470</v>
-      </c>
-      <c r="I38" s="6" t="s">
-        <v>478</v>
       </c>
       <c r="J38" s="5"/>
       <c r="K38" s="6"/>
@@ -4969,7 +4919,7 @@
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="6" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="E39" s="5" t="s">
         <v>156</v>
@@ -4979,10 +4929,10 @@
         <v>184</v>
       </c>
       <c r="H39" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="I39" s="6" t="s">
         <v>471</v>
-      </c>
-      <c r="I39" s="6" t="s">
-        <v>479</v>
       </c>
       <c r="J39" s="5"/>
       <c r="K39" s="6"/>
@@ -4995,7 +4945,7 @@
       <c r="D40" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="E40" s="80" t="s">
+      <c r="E40" s="31" t="s">
         <v>157</v>
       </c>
       <c r="F40" s="5"/>
@@ -5003,10 +4953,10 @@
         <v>185</v>
       </c>
       <c r="H40" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="I40" s="6" t="s">
         <v>472</v>
-      </c>
-      <c r="I40" s="6" t="s">
-        <v>480</v>
       </c>
       <c r="J40" s="5"/>
       <c r="K40" s="6"/>
@@ -5019,7 +4969,7 @@
       <c r="D41" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E41" s="80" t="s">
+      <c r="E41" s="31" t="s">
         <v>158</v>
       </c>
       <c r="F41" s="5"/>
@@ -5039,7 +4989,7 @@
       <c r="D42" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="E42" s="80" t="s">
+      <c r="E42" s="31" t="s">
         <v>159</v>
       </c>
       <c r="F42" s="5"/>
@@ -5047,23 +4997,23 @@
         <v>187</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>775</v>
+        <v>761</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>784</v>
+        <v>770</v>
       </c>
       <c r="J42" s="5"/>
       <c r="K42" s="6"/>
     </row>
     <row r="43" spans="2:11">
       <c r="B43" s="5" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="C43" s="5"/>
       <c r="D43" s="6" t="s">
-        <v>430</v>
-      </c>
-      <c r="E43" s="80" t="s">
+        <v>422</v>
+      </c>
+      <c r="E43" s="31" t="s">
         <v>160</v>
       </c>
       <c r="F43" s="5"/>
@@ -5071,47 +5021,47 @@
         <v>188</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>776</v>
+        <v>762</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>806</v>
+        <v>794</v>
       </c>
       <c r="J43" s="5"/>
       <c r="K43" s="6"/>
     </row>
     <row r="44" spans="2:11">
       <c r="B44" s="5" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="C44" s="5"/>
       <c r="D44" s="6" t="s">
-        <v>429</v>
-      </c>
-      <c r="E44" s="80" t="s">
-        <v>418</v>
+        <v>421</v>
+      </c>
+      <c r="E44" s="31" t="s">
+        <v>410</v>
       </c>
       <c r="F44" s="5"/>
       <c r="G44" s="6" t="s">
         <v>189</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>777</v>
+        <v>763</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>807</v>
+        <v>795</v>
       </c>
       <c r="J44" s="5"/>
       <c r="K44" s="6"/>
     </row>
     <row r="45" spans="2:11">
       <c r="B45" s="5" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="C45" s="5"/>
       <c r="D45" s="6" t="s">
-        <v>428</v>
-      </c>
-      <c r="E45" s="80" t="s">
+        <v>420</v>
+      </c>
+      <c r="E45" s="31" t="s">
         <v>161</v>
       </c>
       <c r="F45" s="5"/>
@@ -5119,23 +5069,23 @@
         <v>190</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>778</v>
+        <v>764</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>808</v>
+        <v>796</v>
       </c>
       <c r="J45" s="5"/>
       <c r="K45" s="6"/>
     </row>
     <row r="46" spans="2:11">
       <c r="B46" s="5" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="C46" s="5"/>
       <c r="D46" s="6" t="s">
-        <v>427</v>
-      </c>
-      <c r="E46" s="80" t="s">
+        <v>419</v>
+      </c>
+      <c r="E46" s="31" t="s">
         <v>162</v>
       </c>
       <c r="F46" s="5"/>
@@ -5143,23 +5093,23 @@
         <v>191</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>779</v>
+        <v>765</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>809</v>
+        <v>802</v>
       </c>
       <c r="J46" s="5"/>
       <c r="K46" s="6"/>
     </row>
     <row r="47" spans="2:11">
       <c r="B47" s="5" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="C47" s="5"/>
       <c r="D47" s="6" t="s">
-        <v>426</v>
-      </c>
-      <c r="E47" s="80" t="s">
+        <v>418</v>
+      </c>
+      <c r="E47" s="31" t="s">
         <v>163</v>
       </c>
       <c r="F47" s="5"/>
@@ -5167,23 +5117,23 @@
         <v>192</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>780</v>
+        <v>766</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>810</v>
+        <v>797</v>
       </c>
       <c r="J47" s="5"/>
       <c r="K47" s="6"/>
     </row>
     <row r="48" spans="2:11">
       <c r="B48" s="5" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="C48" s="5"/>
       <c r="D48" s="6" t="s">
-        <v>425</v>
-      </c>
-      <c r="E48" s="80" t="s">
+        <v>417</v>
+      </c>
+      <c r="E48" s="31" t="s">
         <v>166</v>
       </c>
       <c r="F48" s="5"/>
@@ -5191,10 +5141,10 @@
         <v>193</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>781</v>
+        <v>767</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>811</v>
+        <v>798</v>
       </c>
       <c r="J48" s="5"/>
       <c r="K48" s="6"/>
@@ -5203,7 +5153,7 @@
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
       <c r="D49" s="6"/>
-      <c r="E49" s="80" t="s">
+      <c r="E49" s="31" t="s">
         <v>167</v>
       </c>
       <c r="F49" s="5"/>
@@ -5211,10 +5161,10 @@
         <v>194</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>782</v>
+        <v>768</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>812</v>
+        <v>799</v>
       </c>
       <c r="J49" s="5"/>
       <c r="K49" s="6"/>
@@ -5223,7 +5173,7 @@
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
       <c r="D50" s="6"/>
-      <c r="E50" s="80" t="s">
+      <c r="E50" s="31" t="s">
         <v>168</v>
       </c>
       <c r="F50" s="5"/>
@@ -5231,10 +5181,10 @@
         <v>195</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>783</v>
+        <v>769</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>813</v>
+        <v>800</v>
       </c>
       <c r="J50" s="5"/>
       <c r="K50" s="6"/>
@@ -5243,7 +5193,7 @@
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
       <c r="D51" s="6"/>
-      <c r="E51" s="80" t="s">
+      <c r="E51" s="31" t="s">
         <v>169</v>
       </c>
       <c r="F51" s="5"/>
@@ -5251,10 +5201,10 @@
         <v>196</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>805</v>
+        <v>791</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>814</v>
+        <v>801</v>
       </c>
       <c r="J51" s="5"/>
       <c r="K51" s="6"/>
@@ -5263,14 +5213,14 @@
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
       <c r="D52" s="6"/>
-      <c r="E52" s="80" t="s">
-        <v>379</v>
+      <c r="E52" s="31" t="s">
+        <v>371</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="H52" s="5"/>
       <c r="I52" s="6"/>
@@ -5281,14 +5231,14 @@
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
       <c r="D53" s="6"/>
-      <c r="E53" s="80" t="s">
+      <c r="E53" s="31" t="s">
         <v>164</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="H53" s="5"/>
       <c r="I53" s="6"/>
@@ -5299,14 +5249,14 @@
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
       <c r="D54" s="6"/>
-      <c r="E54" s="80" t="s">
+      <c r="E54" s="31" t="s">
         <v>165</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="H54" s="5"/>
       <c r="I54" s="6"/>
@@ -5317,14 +5267,14 @@
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
       <c r="D55" s="6"/>
-      <c r="E55" s="80" t="s">
-        <v>380</v>
+      <c r="E55" s="31" t="s">
+        <v>372</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="H55" s="5"/>
       <c r="I55" s="6"/>
@@ -5335,14 +5285,14 @@
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
       <c r="D56" s="6"/>
-      <c r="E56" s="80" t="s">
-        <v>381</v>
+      <c r="E56" s="31" t="s">
+        <v>373</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="H56" s="5"/>
       <c r="I56" s="6"/>
@@ -5353,14 +5303,14 @@
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
       <c r="D57" s="6"/>
-      <c r="E57" s="80" t="s">
-        <v>382</v>
+      <c r="E57" s="31" t="s">
+        <v>374</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="G57" s="6" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="H57" s="5"/>
       <c r="I57" s="6"/>
@@ -5411,10 +5361,10 @@
       <c r="F63" s="5"/>
       <c r="G63" s="6"/>
       <c r="H63" s="5" t="s">
+        <v>738</v>
+      </c>
+      <c r="I63" s="6" t="s">
         <v>752</v>
-      </c>
-      <c r="I63" s="6" t="s">
-        <v>766</v>
       </c>
       <c r="J63" s="6"/>
       <c r="K63" s="6"/>
@@ -5423,10 +5373,10 @@
       <c r="F64" s="5"/>
       <c r="G64" s="6"/>
       <c r="H64" s="5" t="s">
+        <v>739</v>
+      </c>
+      <c r="I64" s="6" t="s">
         <v>753</v>
-      </c>
-      <c r="I64" s="6" t="s">
-        <v>767</v>
       </c>
       <c r="J64" s="6"/>
       <c r="K64" s="6"/>
@@ -5435,10 +5385,10 @@
       <c r="F65" s="5"/>
       <c r="G65" s="6"/>
       <c r="H65" s="5" t="s">
+        <v>740</v>
+      </c>
+      <c r="I65" s="6" t="s">
         <v>754</v>
-      </c>
-      <c r="I65" s="6" t="s">
-        <v>768</v>
       </c>
       <c r="J65" s="6"/>
       <c r="K65" s="6"/>
@@ -5447,10 +5397,10 @@
       <c r="F66" s="5"/>
       <c r="G66" s="6"/>
       <c r="H66" s="5" t="s">
+        <v>741</v>
+      </c>
+      <c r="I66" s="6" t="s">
         <v>755</v>
-      </c>
-      <c r="I66" s="6" t="s">
-        <v>769</v>
       </c>
       <c r="J66" s="6"/>
       <c r="K66" s="6"/>
@@ -5459,10 +5409,10 @@
       <c r="F67" s="5"/>
       <c r="G67" s="6"/>
       <c r="H67" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="I67" s="6" t="s">
         <v>756</v>
-      </c>
-      <c r="I67" s="6" t="s">
-        <v>770</v>
       </c>
       <c r="J67" s="6"/>
       <c r="K67" s="6"/>
@@ -5471,10 +5421,10 @@
       <c r="F68" s="5"/>
       <c r="G68" s="6"/>
       <c r="H68" s="5" t="s">
+        <v>743</v>
+      </c>
+      <c r="I68" s="6" t="s">
         <v>757</v>
-      </c>
-      <c r="I68" s="6" t="s">
-        <v>771</v>
       </c>
       <c r="J68" s="6"/>
       <c r="K68" s="6"/>
@@ -5483,10 +5433,10 @@
       <c r="F69" s="5"/>
       <c r="G69" s="6"/>
       <c r="H69" s="5" t="s">
+        <v>744</v>
+      </c>
+      <c r="I69" s="6" t="s">
         <v>758</v>
-      </c>
-      <c r="I69" s="6" t="s">
-        <v>772</v>
       </c>
       <c r="J69" s="6"/>
       <c r="K69" s="6"/>
@@ -5495,10 +5445,10 @@
       <c r="F70" s="5"/>
       <c r="G70" s="6"/>
       <c r="H70" s="5" t="s">
+        <v>745</v>
+      </c>
+      <c r="I70" s="6" t="s">
         <v>759</v>
-      </c>
-      <c r="I70" s="6" t="s">
-        <v>773</v>
       </c>
       <c r="J70" s="6"/>
       <c r="K70" s="6"/>
@@ -5507,10 +5457,10 @@
       <c r="F71" s="5"/>
       <c r="G71" s="6"/>
       <c r="H71" s="5" t="s">
+        <v>746</v>
+      </c>
+      <c r="I71" s="6" t="s">
         <v>760</v>
-      </c>
-      <c r="I71" s="6" t="s">
-        <v>774</v>
       </c>
       <c r="J71" s="6"/>
       <c r="K71" s="6"/>
@@ -5519,10 +5469,10 @@
       <c r="F72" s="5"/>
       <c r="G72" s="6"/>
       <c r="H72" s="5" t="s">
-        <v>761</v>
+        <v>747</v>
       </c>
       <c r="I72" s="6" t="s">
-        <v>766</v>
+        <v>752</v>
       </c>
       <c r="J72" s="6"/>
       <c r="K72" s="6"/>
@@ -5531,10 +5481,10 @@
       <c r="F73" s="5"/>
       <c r="G73" s="6"/>
       <c r="H73" s="5" t="s">
-        <v>762</v>
+        <v>748</v>
       </c>
       <c r="I73" s="6" t="s">
-        <v>767</v>
+        <v>753</v>
       </c>
       <c r="J73" s="6"/>
       <c r="K73" s="6"/>
@@ -5543,10 +5493,10 @@
       <c r="F74" s="5"/>
       <c r="G74" s="6"/>
       <c r="H74" s="5" t="s">
-        <v>763</v>
+        <v>749</v>
       </c>
       <c r="I74" s="6" t="s">
-        <v>768</v>
+        <v>754</v>
       </c>
       <c r="J74" s="6"/>
       <c r="K74" s="6"/>
@@ -5555,10 +5505,10 @@
       <c r="F75" s="5"/>
       <c r="G75" s="6"/>
       <c r="H75" s="5" t="s">
-        <v>764</v>
+        <v>750</v>
       </c>
       <c r="I75" s="6" t="s">
-        <v>766</v>
+        <v>752</v>
       </c>
       <c r="J75" s="6"/>
       <c r="K75" s="6"/>
@@ -5567,10 +5517,10 @@
       <c r="F76" s="5"/>
       <c r="G76" s="6"/>
       <c r="H76" s="5" t="s">
-        <v>765</v>
+        <v>751</v>
       </c>
       <c r="I76" s="6" t="s">
-        <v>767</v>
+        <v>753</v>
       </c>
       <c r="J76" s="6"/>
       <c r="K76" s="6"/>
@@ -5580,7 +5530,7 @@
       <c r="G77" s="6"/>
       <c r="H77" s="5"/>
       <c r="I77" s="6" t="s">
-        <v>768</v>
+        <v>754</v>
       </c>
       <c r="J77" s="6"/>
       <c r="K77" s="6"/>
@@ -5748,30 +5698,30 @@
     </row>
     <row r="6" spans="3:24" s="2" customFormat="1">
       <c r="C6" s="4" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
       <c r="K6" s="4" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
       <c r="O6" s="4"/>
       <c r="P6" s="4"/>
       <c r="S6" s="4" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="U6" s="4"/>
       <c r="V6" s="4"/>
@@ -5783,7 +5733,7 @@
         <v>56</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>7</v>
@@ -5792,7 +5742,7 @@
         <v>57</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>20</v>
@@ -5801,7 +5751,7 @@
         <v>67</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="M7" s="6" t="s">
         <v>7</v>
@@ -5810,7 +5760,7 @@
         <v>74</v>
       </c>
       <c r="O7" s="5" t="s">
-        <v>642</v>
+        <v>631</v>
       </c>
       <c r="P7" s="6" t="s">
         <v>20</v>
@@ -5819,7 +5769,7 @@
         <v>199</v>
       </c>
       <c r="T7" s="5" t="s">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="U7" s="6" t="s">
         <v>7</v>
@@ -5828,7 +5778,7 @@
         <v>205</v>
       </c>
       <c r="W7" s="5" t="s">
-        <v>651</v>
+        <v>640</v>
       </c>
       <c r="X7" s="6" t="s">
         <v>20</v>
@@ -5836,10 +5786,10 @@
     </row>
     <row r="8" spans="3:24">
       <c r="C8" s="5" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>8</v>
@@ -5848,7 +5798,7 @@
         <v>58</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>13</v>
@@ -5857,7 +5807,7 @@
         <v>68</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="M8" s="6" t="s">
         <v>8</v>
@@ -5866,25 +5816,25 @@
         <v>75</v>
       </c>
       <c r="O8" s="5" t="s">
-        <v>643</v>
+        <v>632</v>
       </c>
       <c r="P8" s="6" t="s">
         <v>13</v>
       </c>
       <c r="S8" s="5" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="T8" s="5" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="U8" s="6" t="s">
         <v>8</v>
       </c>
       <c r="V8" s="5" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="W8" s="5" t="s">
-        <v>652</v>
+        <v>641</v>
       </c>
       <c r="X8" s="6" t="s">
         <v>13</v>
@@ -5892,10 +5842,10 @@
     </row>
     <row r="9" spans="3:24">
       <c r="C9" s="9" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>16</v>
@@ -5904,7 +5854,7 @@
         <v>59</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>14</v>
@@ -5913,7 +5863,7 @@
         <v>69</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="M9" s="10" t="s">
         <v>16</v>
@@ -5922,25 +5872,25 @@
         <v>76</v>
       </c>
       <c r="O9" s="5" t="s">
-        <v>644</v>
+        <v>633</v>
       </c>
       <c r="P9" s="6" t="s">
         <v>14</v>
       </c>
       <c r="S9" s="9" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="T9" s="9" t="s">
-        <v>574</v>
+        <v>566</v>
       </c>
       <c r="U9" s="10" t="s">
         <v>16</v>
       </c>
       <c r="V9" s="5" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="W9" s="5" t="s">
-        <v>653</v>
+        <v>642</v>
       </c>
       <c r="X9" s="6" t="s">
         <v>14</v>
@@ -5948,10 +5898,10 @@
     </row>
     <row r="10" spans="3:24">
       <c r="C10" s="9" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>17</v>
@@ -5960,7 +5910,7 @@
         <v>60</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="H10" s="10" t="s">
         <v>12</v>
@@ -5969,7 +5919,7 @@
         <v>70</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="M10" s="10" t="s">
         <v>17</v>
@@ -5978,25 +5928,25 @@
         <v>77</v>
       </c>
       <c r="O10" s="9" t="s">
-        <v>645</v>
+        <v>634</v>
       </c>
       <c r="P10" s="10" t="s">
         <v>12</v>
       </c>
       <c r="S10" s="9" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="T10" s="9" t="s">
-        <v>575</v>
+        <v>567</v>
       </c>
       <c r="U10" s="10" t="s">
         <v>17</v>
       </c>
       <c r="V10" s="9" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="W10" s="9" t="s">
-        <v>654</v>
+        <v>643</v>
       </c>
       <c r="X10" s="10" t="s">
         <v>12</v>
@@ -6004,10 +5954,10 @@
     </row>
     <row r="11" spans="3:24">
       <c r="C11" s="5" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>18</v>
@@ -6016,7 +5966,7 @@
         <v>61</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="H11" s="10" t="s">
         <v>11</v>
@@ -6025,7 +5975,7 @@
         <v>71</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="M11" s="6" t="s">
         <v>18</v>
@@ -6034,25 +5984,25 @@
         <v>78</v>
       </c>
       <c r="O11" s="9" t="s">
-        <v>646</v>
+        <v>635</v>
       </c>
       <c r="P11" s="10" t="s">
         <v>11</v>
       </c>
       <c r="S11" s="5" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="T11" s="5" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="U11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="V11" s="9" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="W11" s="9" t="s">
-        <v>655</v>
+        <v>644</v>
       </c>
       <c r="X11" s="10" t="s">
         <v>11</v>
@@ -6060,48 +6010,48 @@
     </row>
     <row r="12" spans="3:24">
       <c r="C12" s="9" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="E12" s="10"/>
       <c r="F12" s="9"/>
       <c r="G12" s="9" t="s">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="H12" s="10"/>
       <c r="K12" s="9" t="s">
         <v>72</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="M12" s="10"/>
       <c r="N12" s="9"/>
       <c r="O12" s="9" t="s">
-        <v>647</v>
+        <v>636</v>
       </c>
       <c r="P12" s="10"/>
       <c r="S12" s="9" t="s">
         <v>202</v>
       </c>
       <c r="T12" s="9" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="U12" s="10"/>
       <c r="V12" s="9"/>
       <c r="W12" s="9" t="s">
-        <v>656</v>
+        <v>645</v>
       </c>
       <c r="X12" s="10"/>
     </row>
     <row r="13" spans="3:24">
       <c r="C13" s="9" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>22</v>
@@ -6110,7 +6060,7 @@
         <v>62</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="H13" s="10" t="s">
         <v>15</v>
@@ -6119,7 +6069,7 @@
         <v>197</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="M13" s="10" t="s">
         <v>22</v>
@@ -6128,7 +6078,7 @@
         <v>79</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>648</v>
+        <v>637</v>
       </c>
       <c r="P13" s="10" t="s">
         <v>15</v>
@@ -6137,7 +6087,7 @@
         <v>203</v>
       </c>
       <c r="T13" s="9" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="U13" s="10" t="s">
         <v>22</v>
@@ -6146,7 +6096,7 @@
         <v>206</v>
       </c>
       <c r="W13" s="9" t="s">
-        <v>657</v>
+        <v>646</v>
       </c>
       <c r="X13" s="10" t="s">
         <v>15</v>
@@ -6154,10 +6104,10 @@
     </row>
     <row r="14" spans="3:24">
       <c r="C14" s="9" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>21</v>
@@ -6166,16 +6116,16 @@
         <v>63</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="H14" s="10" t="s">
         <v>23</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="M14" s="10" t="s">
         <v>21</v>
@@ -6184,7 +6134,7 @@
         <v>80</v>
       </c>
       <c r="O14" s="9" t="s">
-        <v>649</v>
+        <v>638</v>
       </c>
       <c r="P14" s="10" t="s">
         <v>23</v>
@@ -6193,7 +6143,7 @@
         <v>204</v>
       </c>
       <c r="T14" s="9" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="U14" s="10" t="s">
         <v>21</v>
@@ -6202,7 +6152,7 @@
         <v>207</v>
       </c>
       <c r="W14" s="9" t="s">
-        <v>658</v>
+        <v>647</v>
       </c>
       <c r="X14" s="10" t="s">
         <v>23</v>
@@ -6213,7 +6163,7 @@
         <v>73</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>19</v>
@@ -6222,16 +6172,16 @@
         <v>64</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="H15" s="10" t="s">
         <v>24</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="M15" s="6" t="s">
         <v>19</v>
@@ -6240,16 +6190,16 @@
         <v>198</v>
       </c>
       <c r="O15" s="9" t="s">
-        <v>650</v>
+        <v>639</v>
       </c>
       <c r="P15" s="10" t="s">
         <v>24</v>
       </c>
       <c r="S15" s="5" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="T15" s="5" t="s">
-        <v>580</v>
+        <v>572</v>
       </c>
       <c r="U15" s="6" t="s">
         <v>19</v>
@@ -6258,7 +6208,7 @@
         <v>208</v>
       </c>
       <c r="W15" s="9" t="s">
-        <v>659</v>
+        <v>648</v>
       </c>
       <c r="X15" s="10" t="s">
         <v>24</v>
@@ -6266,43 +6216,43 @@
     </row>
     <row r="16" spans="3:24">
       <c r="C16" s="5" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="F16" s="9"/>
       <c r="G16" s="9"/>
       <c r="H16" s="10"/>
       <c r="K16" s="5" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="L16" s="5" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="N16" s="9"/>
       <c r="O16" s="9"/>
       <c r="P16" s="10"/>
       <c r="S16" s="5" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="T16" s="5" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="U16" s="6" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="V16" s="9"/>
       <c r="W16" s="9"/>
       <c r="X16" s="10"/>
     </row>
-    <row r="17" spans="3:24">
+    <row r="17" spans="2:24">
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="6"/>
@@ -6322,7 +6272,7 @@
       <c r="W17" s="9"/>
       <c r="X17" s="10"/>
     </row>
-    <row r="18" spans="3:24">
+    <row r="18" spans="2:24">
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
       <c r="E18" s="12"/>
@@ -6342,7 +6292,7 @@
       <c r="W18" s="11"/>
       <c r="X18" s="12"/>
     </row>
-    <row r="19" spans="3:24">
+    <row r="19" spans="2:24">
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19"/>
@@ -6350,7 +6300,7 @@
       <c r="O19" s="1"/>
       <c r="P19"/>
     </row>
-    <row r="20" spans="3:24">
+    <row r="20" spans="2:24">
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20"/>
@@ -6358,7 +6308,7 @@
       <c r="O20" s="1"/>
       <c r="P20"/>
     </row>
-    <row r="21" spans="3:24">
+    <row r="21" spans="2:24">
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21"/>
@@ -6366,13 +6316,10 @@
       <c r="O21" s="1"/>
       <c r="P21"/>
     </row>
-    <row r="22" spans="3:24">
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="12"/>
+    <row r="22" spans="2:24">
+      <c r="B22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="H22" s="1"/>
       <c r="K22" s="11"/>
       <c r="L22" s="11"/>
       <c r="M22" s="12"/>
@@ -6386,23 +6333,16 @@
       <c r="W22" s="11"/>
       <c r="X22" s="12"/>
     </row>
-    <row r="23" spans="3:24">
-      <c r="C23" s="32" t="s">
-        <v>40</v>
-      </c>
-      <c r="D23" s="32"/>
-      <c r="E23" s="32" t="s">
-        <v>210</v>
-      </c>
-      <c r="F23" s="32"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="32"/>
+    <row r="23" spans="2:24">
+      <c r="B23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="H23" s="1"/>
       <c r="K23" s="32" t="s">
         <v>40</v>
       </c>
       <c r="L23" s="32"/>
       <c r="M23" s="32" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N23" s="32"/>
       <c r="O23" s="32"/>
@@ -6412,21 +6352,16 @@
       </c>
       <c r="T23" s="32"/>
       <c r="U23" s="32" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="V23" s="32"/>
       <c r="W23" s="32"/>
       <c r="X23" s="32"/>
     </row>
-    <row r="24" spans="3:24">
-      <c r="C24" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="D24" s="32"/>
-      <c r="E24" s="32"/>
-      <c r="F24" s="32"/>
-      <c r="G24" s="32"/>
-      <c r="H24" s="32"/>
+    <row r="24" spans="2:24">
+      <c r="B24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="H24" s="1"/>
       <c r="K24" s="32" t="s">
         <v>39</v>
       </c>
@@ -6444,21 +6379,10 @@
       <c r="W24" s="32"/>
       <c r="X24" s="32"/>
     </row>
-    <row r="25" spans="3:24">
-      <c r="C25" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="32"/>
-      <c r="E25" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="G25" s="32"/>
-      <c r="H25" s="4" t="s">
-        <v>10</v>
-      </c>
+    <row r="25" spans="2:24">
+      <c r="B25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="H25" s="1"/>
       <c r="K25" s="32" t="s">
         <v>9</v>
       </c>
@@ -6488,569 +6412,421 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="3:24">
-      <c r="C26" s="4" t="s">
-        <v>523</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>524</v>
-      </c>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
+    <row r="26" spans="2:24">
+      <c r="B26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="H26" s="1"/>
       <c r="K26" s="4" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="L26" s="4" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="M26" s="4"/>
       <c r="N26" s="4"/>
       <c r="O26" s="4"/>
       <c r="P26" s="4"/>
       <c r="S26" s="4" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="T26" s="4" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="U26" s="4"/>
       <c r="V26" s="4"/>
       <c r="W26" s="4"/>
       <c r="X26" s="4"/>
     </row>
-    <row r="27" spans="3:24">
-      <c r="C27" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>582</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>660</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>20</v>
-      </c>
+    <row r="27" spans="2:24">
+      <c r="B27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="H27" s="1"/>
       <c r="K27" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="L27" s="5" t="s">
-        <v>592</v>
+        <v>581</v>
       </c>
       <c r="M27" s="6" t="s">
         <v>7</v>
       </c>
       <c r="N27" s="5" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="O27" s="5" t="s">
-        <v>669</v>
+        <v>655</v>
       </c>
       <c r="P27" s="6" t="s">
         <v>20</v>
       </c>
       <c r="S27" s="5" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="T27" s="5" t="s">
-        <v>602</v>
+        <v>591</v>
       </c>
       <c r="U27" s="6" t="s">
         <v>7</v>
       </c>
       <c r="V27" s="5" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="W27" s="5" t="s">
-        <v>678</v>
+        <v>664</v>
       </c>
       <c r="X27" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="3:24">
-      <c r="C28" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>583</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>661</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>13</v>
-      </c>
+    <row r="28" spans="2:24">
+      <c r="B28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="H28" s="1"/>
       <c r="K28" s="5" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="L28" s="5" t="s">
-        <v>593</v>
+        <v>582</v>
       </c>
       <c r="M28" s="6" t="s">
         <v>8</v>
       </c>
       <c r="N28" s="5" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="O28" s="5" t="s">
-        <v>670</v>
+        <v>656</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>13</v>
       </c>
       <c r="S28" s="5" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="T28" s="5" t="s">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="U28" s="6" t="s">
         <v>8</v>
       </c>
       <c r="V28" s="5" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="W28" s="5" t="s">
-        <v>679</v>
+        <v>665</v>
       </c>
       <c r="X28" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="3:24">
-      <c r="C29" s="9" t="s">
-        <v>345</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>584</v>
-      </c>
-      <c r="E29" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>662</v>
-      </c>
-      <c r="H29" s="6" t="s">
-        <v>14</v>
-      </c>
+    <row r="29" spans="2:24">
+      <c r="B29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="H29" s="1"/>
       <c r="K29" s="9" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="L29" s="9" t="s">
-        <v>594</v>
+        <v>583</v>
       </c>
       <c r="M29" s="10" t="s">
         <v>16</v>
       </c>
       <c r="N29" s="5" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="O29" s="5" t="s">
-        <v>671</v>
+        <v>657</v>
       </c>
       <c r="P29" s="6" t="s">
         <v>14</v>
       </c>
       <c r="S29" s="9" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="T29" s="9" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="U29" s="10" t="s">
         <v>16</v>
       </c>
       <c r="V29" s="5" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="W29" s="5" t="s">
-        <v>680</v>
+        <v>666</v>
       </c>
       <c r="X29" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="3:24">
-      <c r="C30" s="9" t="s">
-        <v>346</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>585</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="G30" s="9" t="s">
-        <v>663</v>
-      </c>
-      <c r="H30" s="10" t="s">
-        <v>12</v>
-      </c>
+    <row r="30" spans="2:24">
+      <c r="B30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="H30" s="1"/>
       <c r="K30" s="9" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="L30" s="9" t="s">
-        <v>595</v>
+        <v>584</v>
       </c>
       <c r="M30" s="10" t="s">
         <v>17</v>
       </c>
       <c r="N30" s="9" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="O30" s="9" t="s">
-        <v>672</v>
+        <v>658</v>
       </c>
       <c r="P30" s="10" t="s">
         <v>12</v>
       </c>
       <c r="S30" s="9" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="T30" s="9" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="U30" s="10" t="s">
         <v>17</v>
       </c>
       <c r="V30" s="9" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="W30" s="9" t="s">
-        <v>681</v>
+        <v>667</v>
       </c>
       <c r="X30" s="10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="3:24">
-      <c r="C31" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>586</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F31" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="G31" s="9" t="s">
-        <v>664</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>11</v>
-      </c>
+    <row r="31" spans="2:24">
+      <c r="B31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="H31" s="1"/>
       <c r="K31" s="5" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="L31" s="5" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="M31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>673</v>
+        <v>659</v>
       </c>
       <c r="P31" s="10" t="s">
         <v>11</v>
       </c>
       <c r="S31" s="5" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="T31" s="5" t="s">
-        <v>606</v>
+        <v>595</v>
       </c>
       <c r="U31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="V31" s="9" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="W31" s="9" t="s">
-        <v>682</v>
+        <v>668</v>
       </c>
       <c r="X31" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="3:24">
-      <c r="C32" s="9" t="s">
-        <v>348</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>587</v>
-      </c>
-      <c r="E32" s="10"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9" t="s">
-        <v>665</v>
-      </c>
-      <c r="H32" s="10"/>
+    <row r="32" spans="2:24">
+      <c r="B32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="H32" s="1"/>
       <c r="K32" s="9" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="L32" s="9" t="s">
-        <v>597</v>
+        <v>586</v>
       </c>
       <c r="M32" s="10"/>
       <c r="N32" s="9"/>
       <c r="O32" s="9" t="s">
-        <v>674</v>
+        <v>660</v>
       </c>
       <c r="P32" s="10"/>
       <c r="S32" s="9" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="T32" s="9" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="U32" s="10"/>
       <c r="V32" s="9"/>
       <c r="W32" s="9" t="s">
-        <v>683</v>
+        <v>669</v>
       </c>
       <c r="X32" s="10"/>
     </row>
     <row r="33" spans="2:24">
-      <c r="C33" s="9" t="s">
-        <v>349</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>588</v>
-      </c>
-      <c r="E33" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>666</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>15</v>
-      </c>
+      <c r="B33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="H33" s="1"/>
       <c r="K33" s="9" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="L33" s="9" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="M33" s="10" t="s">
         <v>22</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>675</v>
+        <v>661</v>
       </c>
       <c r="P33" s="10" t="s">
         <v>15</v>
       </c>
       <c r="S33" s="9" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="T33" s="9" t="s">
-        <v>608</v>
+        <v>597</v>
       </c>
       <c r="U33" s="10" t="s">
         <v>22</v>
       </c>
       <c r="V33" s="9" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="W33" s="9" t="s">
-        <v>684</v>
+        <v>670</v>
       </c>
       <c r="X33" s="10" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="34" spans="2:24">
-      <c r="C34" s="9" t="s">
-        <v>350</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>589</v>
-      </c>
-      <c r="E34" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>223</v>
-      </c>
-      <c r="G34" s="9" t="s">
-        <v>667</v>
-      </c>
-      <c r="H34" s="10" t="s">
-        <v>23</v>
-      </c>
+      <c r="B34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="H34" s="1"/>
       <c r="K34" s="9" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L34" s="9" t="s">
-        <v>599</v>
+        <v>588</v>
       </c>
       <c r="M34" s="10" t="s">
         <v>21</v>
       </c>
       <c r="N34" s="9" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="O34" s="9" t="s">
-        <v>676</v>
+        <v>662</v>
       </c>
       <c r="P34" s="10" t="s">
         <v>23</v>
       </c>
       <c r="S34" s="9" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="T34" s="9" t="s">
-        <v>609</v>
+        <v>598</v>
       </c>
       <c r="U34" s="10" t="s">
         <v>21</v>
       </c>
       <c r="V34" s="9" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="W34" s="9" t="s">
-        <v>685</v>
+        <v>671</v>
       </c>
       <c r="X34" s="10" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="35" spans="2:24">
-      <c r="C35" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>590</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F35" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="G35" s="9" t="s">
-        <v>668</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>24</v>
-      </c>
+      <c r="B35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="H35" s="1"/>
       <c r="K35" s="5" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="L35" s="5" t="s">
-        <v>600</v>
+        <v>589</v>
       </c>
       <c r="M35" s="6" t="s">
         <v>19</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>677</v>
+        <v>663</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>24</v>
       </c>
       <c r="S35" s="5" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="T35" s="5" t="s">
-        <v>610</v>
+        <v>599</v>
       </c>
       <c r="U35" s="6" t="s">
         <v>19</v>
       </c>
       <c r="V35" s="9" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="W35" s="9" t="s">
-        <v>686</v>
+        <v>672</v>
       </c>
       <c r="X35" s="10" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="36" spans="2:24">
-      <c r="C36" s="5" t="s">
-        <v>398</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>591</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>395</v>
-      </c>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="10"/>
+      <c r="B36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="H36" s="1"/>
       <c r="K36" s="5" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="L36" s="5" t="s">
-        <v>601</v>
+        <v>590</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="N36" s="9"/>
       <c r="O36" s="9"/>
       <c r="P36" s="10"/>
       <c r="S36" s="5" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="T36" s="5" t="s">
-        <v>611</v>
+        <v>600</v>
       </c>
       <c r="U36" s="6" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="V36" s="9"/>
       <c r="W36" s="9"/>
       <c r="X36" s="10"/>
     </row>
     <row r="37" spans="2:24">
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="12"/>
+      <c r="B37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="H37" s="1"/>
       <c r="K37" s="11"/>
       <c r="L37" s="11"/>
       <c r="M37" s="12"/>
@@ -7063,6 +6839,11 @@
       <c r="V37" s="11"/>
       <c r="W37" s="11"/>
       <c r="X37" s="12"/>
+    </row>
+    <row r="38" spans="2:24">
+      <c r="B38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="H38" s="1"/>
     </row>
     <row r="41" spans="2:24">
       <c r="B41" s="8"/>
@@ -7095,7 +6876,7 @@
       </c>
       <c r="D42" s="32"/>
       <c r="E42" s="32" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F42" s="32"/>
       <c r="G42" s="32"/>
@@ -7107,7 +6888,7 @@
       </c>
       <c r="L42" s="4"/>
       <c r="M42" s="32" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="N42" s="32"/>
       <c r="O42" s="32"/>
@@ -7118,7 +6899,7 @@
       </c>
       <c r="T42" s="4"/>
       <c r="U42" s="32" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="V42" s="32"/>
       <c r="W42" s="32"/>
@@ -7205,10 +6986,10 @@
     <row r="45" spans="2:24">
       <c r="B45" s="8"/>
       <c r="C45" s="4" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
@@ -7217,10 +6998,10 @@
       <c r="I45" s="7"/>
       <c r="J45" s="7"/>
       <c r="K45" s="4" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="M45" s="4"/>
       <c r="N45" s="4"/>
@@ -7228,10 +7009,10 @@
       <c r="P45" s="4"/>
       <c r="Q45" s="8"/>
       <c r="S45" s="4" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="T45" s="4" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="U45" s="4"/>
       <c r="V45" s="4"/>
@@ -7241,19 +7022,19 @@
     <row r="46" spans="2:24">
       <c r="B46" s="8"/>
       <c r="C46" s="5" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>612</v>
+        <v>601</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>687</v>
+        <v>673</v>
       </c>
       <c r="H46" s="6" t="s">
         <v>20</v>
@@ -7261,38 +7042,38 @@
       <c r="I46" s="7"/>
       <c r="J46" s="7"/>
       <c r="K46" s="5" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="L46" s="5" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="M46" s="6" t="s">
         <v>7</v>
       </c>
       <c r="N46" s="5" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="O46" s="5" t="s">
-        <v>696</v>
+        <v>682</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>20</v>
       </c>
       <c r="Q46" s="8"/>
       <c r="S46" s="5" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="T46" s="5" t="s">
-        <v>632</v>
+        <v>621</v>
       </c>
       <c r="U46" s="6" t="s">
         <v>7</v>
       </c>
       <c r="V46" s="5" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="W46" s="5" t="s">
-        <v>705</v>
+        <v>691</v>
       </c>
       <c r="X46" s="6" t="s">
         <v>20</v>
@@ -7301,19 +7082,19 @@
     <row r="47" spans="2:24">
       <c r="B47" s="8"/>
       <c r="C47" s="5" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>613</v>
+        <v>602</v>
       </c>
       <c r="E47" s="6" t="s">
         <v>8</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>688</v>
+        <v>674</v>
       </c>
       <c r="H47" s="6" t="s">
         <v>13</v>
@@ -7321,38 +7102,38 @@
       <c r="I47" s="7"/>
       <c r="J47" s="7"/>
       <c r="K47" s="5" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="L47" s="5" t="s">
-        <v>623</v>
+        <v>612</v>
       </c>
       <c r="M47" s="6" t="s">
         <v>8</v>
       </c>
       <c r="N47" s="5" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="O47" s="5" t="s">
-        <v>697</v>
+        <v>683</v>
       </c>
       <c r="P47" s="6" t="s">
         <v>13</v>
       </c>
       <c r="Q47" s="8"/>
       <c r="S47" s="5" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="T47" s="5" t="s">
-        <v>633</v>
+        <v>622</v>
       </c>
       <c r="U47" s="6" t="s">
         <v>8</v>
       </c>
       <c r="V47" s="5" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="W47" s="5" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="X47" s="6" t="s">
         <v>13</v>
@@ -7361,19 +7142,19 @@
     <row r="48" spans="2:24">
       <c r="B48" s="8"/>
       <c r="C48" s="9" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>614</v>
+        <v>603</v>
       </c>
       <c r="E48" s="10" t="s">
         <v>16</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>689</v>
+        <v>675</v>
       </c>
       <c r="H48" s="6" t="s">
         <v>14</v>
@@ -7381,38 +7162,38 @@
       <c r="I48" s="7"/>
       <c r="J48" s="7"/>
       <c r="K48" s="9" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="L48" s="9" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="M48" s="10" t="s">
         <v>16</v>
       </c>
       <c r="N48" s="5" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="O48" s="5" t="s">
-        <v>698</v>
+        <v>684</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>14</v>
       </c>
       <c r="Q48" s="8"/>
       <c r="S48" s="9" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="T48" s="9" t="s">
-        <v>634</v>
+        <v>623</v>
       </c>
       <c r="U48" s="10" t="s">
         <v>16</v>
       </c>
       <c r="V48" s="5" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="W48" s="5" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="X48" s="6" t="s">
         <v>14</v>
@@ -7421,19 +7202,19 @@
     <row r="49" spans="2:24">
       <c r="B49" s="8"/>
       <c r="C49" s="9" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>615</v>
+        <v>604</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>17</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="H49" s="10" t="s">
         <v>12</v>
@@ -7441,38 +7222,38 @@
       <c r="I49" s="7"/>
       <c r="J49" s="7"/>
       <c r="K49" s="9" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="L49" s="9" t="s">
-        <v>625</v>
+        <v>614</v>
       </c>
       <c r="M49" s="10" t="s">
         <v>17</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>12</v>
       </c>
       <c r="Q49" s="8"/>
       <c r="S49" s="9" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="T49" s="9" t="s">
-        <v>635</v>
+        <v>624</v>
       </c>
       <c r="U49" s="10" t="s">
         <v>17</v>
       </c>
       <c r="V49" s="9" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="W49" s="9" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
       <c r="X49" s="10" t="s">
         <v>12</v>
@@ -7481,19 +7262,19 @@
     <row r="50" spans="2:24">
       <c r="B50" s="8"/>
       <c r="C50" s="5" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>616</v>
+        <v>605</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>691</v>
+        <v>677</v>
       </c>
       <c r="H50" s="10" t="s">
         <v>11</v>
@@ -7501,38 +7282,38 @@
       <c r="I50" s="7"/>
       <c r="J50" s="7"/>
       <c r="K50" s="5" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="L50" s="5" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="M50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="N50" s="9" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="O50" s="9" t="s">
-        <v>700</v>
+        <v>686</v>
       </c>
       <c r="P50" s="10" t="s">
         <v>11</v>
       </c>
       <c r="Q50" s="8"/>
       <c r="S50" s="5" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="T50" s="5" t="s">
-        <v>636</v>
+        <v>625</v>
       </c>
       <c r="U50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="V50" s="9" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="W50" s="9" t="s">
-        <v>709</v>
+        <v>695</v>
       </c>
       <c r="X50" s="10" t="s">
         <v>11</v>
@@ -7541,61 +7322,61 @@
     <row r="51" spans="2:24">
       <c r="B51" s="8"/>
       <c r="C51" s="9" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>617</v>
+        <v>606</v>
       </c>
       <c r="E51" s="10"/>
       <c r="F51" s="9"/>
       <c r="G51" s="9" t="s">
-        <v>692</v>
+        <v>678</v>
       </c>
       <c r="H51" s="10"/>
       <c r="I51" s="7"/>
       <c r="J51" s="7"/>
       <c r="K51" s="9" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="L51" s="9" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="M51" s="10"/>
       <c r="N51" s="9"/>
       <c r="O51" s="9" t="s">
-        <v>701</v>
+        <v>687</v>
       </c>
       <c r="P51" s="10"/>
       <c r="Q51" s="8"/>
       <c r="S51" s="9" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="T51" s="9" t="s">
-        <v>637</v>
+        <v>626</v>
       </c>
       <c r="U51" s="10"/>
       <c r="V51" s="9"/>
       <c r="W51" s="9" t="s">
-        <v>710</v>
+        <v>696</v>
       </c>
       <c r="X51" s="10"/>
     </row>
     <row r="52" spans="2:24">
       <c r="B52" s="8"/>
       <c r="C52" s="9" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="E52" s="10" t="s">
         <v>22</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>693</v>
+        <v>679</v>
       </c>
       <c r="H52" s="10" t="s">
         <v>15</v>
@@ -7603,38 +7384,38 @@
       <c r="I52" s="7"/>
       <c r="J52" s="7"/>
       <c r="K52" s="9" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="L52" s="9" t="s">
-        <v>628</v>
+        <v>617</v>
       </c>
       <c r="M52" s="10" t="s">
         <v>22</v>
       </c>
       <c r="N52" s="9" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="O52" s="9" t="s">
-        <v>702</v>
+        <v>688</v>
       </c>
       <c r="P52" s="10" t="s">
         <v>15</v>
       </c>
       <c r="Q52" s="8"/>
       <c r="S52" s="9" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="T52" s="9" t="s">
-        <v>638</v>
+        <v>627</v>
       </c>
       <c r="U52" s="10" t="s">
         <v>22</v>
       </c>
       <c r="V52" s="9" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="W52" s="9" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="X52" s="10" t="s">
         <v>15</v>
@@ -7643,19 +7424,19 @@
     <row r="53" spans="2:24">
       <c r="B53" s="8"/>
       <c r="C53" s="9" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>619</v>
+        <v>608</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>21</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>694</v>
+        <v>680</v>
       </c>
       <c r="H53" s="10" t="s">
         <v>23</v>
@@ -7663,38 +7444,38 @@
       <c r="I53" s="7"/>
       <c r="J53" s="7"/>
       <c r="K53" s="9" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="L53" s="9" t="s">
-        <v>629</v>
+        <v>618</v>
       </c>
       <c r="M53" s="10" t="s">
         <v>21</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>703</v>
+        <v>689</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>23</v>
       </c>
       <c r="Q53" s="8"/>
       <c r="S53" s="9" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="T53" s="9" t="s">
-        <v>639</v>
+        <v>628</v>
       </c>
       <c r="U53" s="10" t="s">
         <v>21</v>
       </c>
       <c r="V53" s="9" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="W53" s="9" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="X53" s="10" t="s">
         <v>23</v>
@@ -7703,19 +7484,19 @@
     <row r="54" spans="2:24">
       <c r="B54" s="8"/>
       <c r="C54" s="5" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>695</v>
+        <v>681</v>
       </c>
       <c r="H54" s="10" t="s">
         <v>24</v>
@@ -7723,38 +7504,38 @@
       <c r="I54" s="7"/>
       <c r="J54" s="7"/>
       <c r="K54" s="5" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="L54" s="5" t="s">
-        <v>630</v>
+        <v>619</v>
       </c>
       <c r="M54" s="6" t="s">
         <v>19</v>
       </c>
       <c r="N54" s="9" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="O54" s="9" t="s">
-        <v>704</v>
+        <v>690</v>
       </c>
       <c r="P54" s="10" t="s">
         <v>24</v>
       </c>
       <c r="Q54" s="8"/>
       <c r="S54" s="5" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="T54" s="5" t="s">
-        <v>640</v>
+        <v>629</v>
       </c>
       <c r="U54" s="6" t="s">
         <v>19</v>
       </c>
       <c r="V54" s="9" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="W54" s="9" t="s">
-        <v>713</v>
+        <v>699</v>
       </c>
       <c r="X54" s="10" t="s">
         <v>24</v>
@@ -7763,13 +7544,13 @@
     <row r="55" spans="2:24">
       <c r="B55" s="8"/>
       <c r="C55" s="5" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="F55" s="9"/>
       <c r="G55" s="9"/>
@@ -7777,26 +7558,26 @@
       <c r="I55" s="7"/>
       <c r="J55" s="7"/>
       <c r="K55" s="5" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="L55" s="5" t="s">
-        <v>631</v>
+        <v>620</v>
       </c>
       <c r="M55" s="6" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="N55" s="9"/>
       <c r="O55" s="9"/>
       <c r="P55" s="10"/>
       <c r="Q55" s="8"/>
       <c r="S55" s="5" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="T55" s="5" t="s">
-        <v>641</v>
+        <v>630</v>
       </c>
       <c r="U55" s="6" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="V55" s="9"/>
       <c r="W55" s="9"/>
@@ -7827,42 +7608,7 @@
       <c r="X56" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="50">
-    <mergeCell ref="N44:O44"/>
-    <mergeCell ref="V44:W44"/>
-    <mergeCell ref="S44:T44"/>
-    <mergeCell ref="K44:L44"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="M43:P43"/>
-    <mergeCell ref="U43:X43"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="M23:P23"/>
-    <mergeCell ref="M24:P24"/>
-    <mergeCell ref="U23:X23"/>
-    <mergeCell ref="U24:X24"/>
-    <mergeCell ref="S23:T23"/>
-    <mergeCell ref="S24:T24"/>
-    <mergeCell ref="S25:T25"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="U4:X4"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="E42:H42"/>
+  <mergeCells count="44">
     <mergeCell ref="M42:P42"/>
     <mergeCell ref="U42:X42"/>
     <mergeCell ref="E3:H3"/>
@@ -7878,6 +7624,35 @@
     <mergeCell ref="V25:W25"/>
     <mergeCell ref="N25:O25"/>
     <mergeCell ref="U3:X3"/>
+    <mergeCell ref="U4:X4"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="N44:O44"/>
+    <mergeCell ref="V44:W44"/>
+    <mergeCell ref="S44:T44"/>
+    <mergeCell ref="K44:L44"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="M43:P43"/>
+    <mergeCell ref="U43:X43"/>
+    <mergeCell ref="M23:P23"/>
+    <mergeCell ref="M24:P24"/>
+    <mergeCell ref="U23:X23"/>
+    <mergeCell ref="U24:X24"/>
+    <mergeCell ref="S23:T23"/>
+    <mergeCell ref="S24:T24"/>
+    <mergeCell ref="S25:T25"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7886,7 +7661,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EA47EA4-7B31-40FE-9AED-CE45ED8264B2}">
-  <dimension ref="B2:U28"/>
+  <dimension ref="B2:U34"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="4" max="4" width="20.625" customWidth="1"/>
@@ -7915,13 +7690,13 @@
       <c r="P2" s="14"/>
       <c r="Q2" s="14"/>
       <c r="S2" s="17" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="T2" s="18" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="U2" s="18" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
     </row>
     <row r="3" spans="2:21">
@@ -7930,7 +7705,7 @@
       </c>
       <c r="C3" s="34"/>
       <c r="D3" s="33" t="s">
-        <v>292</v>
+        <v>793</v>
       </c>
       <c r="E3" s="35"/>
       <c r="F3" s="35"/>
@@ -7940,7 +7715,7 @@
       </c>
       <c r="J3" s="34"/>
       <c r="K3" s="32" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="L3" s="32"/>
       <c r="M3" s="32"/>
@@ -7952,7 +7727,7 @@
         <v>0</v>
       </c>
       <c r="T3" s="6" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="U3" s="6"/>
     </row>
@@ -7980,10 +7755,10 @@
         <v>100</v>
       </c>
       <c r="T4" s="6" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="U4" s="6" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
     </row>
     <row r="5" spans="2:21">
@@ -8026,145 +7801,145 @@
         <v>200</v>
       </c>
       <c r="T5" s="6" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="U5" s="6" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
     </row>
     <row r="6" spans="2:21">
       <c r="B6" s="4" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="G6" s="4"/>
       <c r="I6" s="4" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="N6" s="4"/>
       <c r="O6" s="4" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="Q6" s="4"/>
       <c r="S6" s="5">
         <v>300</v>
       </c>
       <c r="T6" s="6" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="U6" s="6" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
     </row>
     <row r="7" spans="2:21">
       <c r="B7" s="5" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>719</v>
+        <v>705</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>7</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>714</v>
+        <v>700</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>20</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>725</v>
+        <v>711</v>
       </c>
       <c r="K7" s="6" t="s">
         <v>7</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>733</v>
+        <v>719</v>
       </c>
       <c r="N7" s="6" t="s">
         <v>20</v>
       </c>
       <c r="O7" s="16" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="P7" s="16"/>
       <c r="Q7" s="6" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="S7" s="5">
         <v>400</v>
       </c>
       <c r="T7" s="6" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="U7" s="6" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
     </row>
     <row r="8" spans="2:21">
       <c r="B8" s="5" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>720</v>
+        <v>706</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>715</v>
+        <v>701</v>
       </c>
       <c r="G8" s="10" t="s">
         <v>13</v>
       </c>
       <c r="I8" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>712</v>
+      </c>
+      <c r="K8" s="10" t="s">
         <v>317</v>
       </c>
-      <c r="J8" s="9" t="s">
-        <v>726</v>
-      </c>
-      <c r="K8" s="10" t="s">
-        <v>322</v>
-      </c>
       <c r="L8" s="9" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="M8" s="9" t="s">
-        <v>734</v>
+        <v>720</v>
       </c>
       <c r="N8" s="10" t="s">
         <v>13</v>
@@ -8176,45 +7951,45 @@
         <v>500</v>
       </c>
       <c r="T8" s="6" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="U8" s="6" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
     </row>
     <row r="9" spans="2:21">
       <c r="B9" s="9" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="G9" s="10" t="s">
         <v>14</v>
       </c>
       <c r="I9" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>713</v>
+      </c>
+      <c r="K9" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="J9" s="9" t="s">
-        <v>727</v>
-      </c>
-      <c r="K9" s="10" t="s">
-        <v>323</v>
-      </c>
       <c r="L9" s="9" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="M9" s="9" t="s">
-        <v>735</v>
+        <v>721</v>
       </c>
       <c r="N9" s="10" t="s">
         <v>14</v>
@@ -8226,48 +8001,48 @@
         <v>600</v>
       </c>
       <c r="T9" s="6" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="U9" s="6" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
     </row>
     <row r="10" spans="2:21">
       <c r="B10" s="5" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>722</v>
+        <v>708</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="K10" s="10" t="s">
         <v>17</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="M10" s="9" t="s">
-        <v>736</v>
+        <v>722</v>
       </c>
       <c r="N10" s="10" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="O10" s="6"/>
       <c r="P10" s="6"/>
@@ -8276,45 +8051,45 @@
         <v>601</v>
       </c>
       <c r="T10" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="U10" s="20" t="s">
         <v>437</v>
-      </c>
-      <c r="U10" s="20" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="11" spans="2:21">
       <c r="B11" s="5" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>723</v>
+        <v>709</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>718</v>
+        <v>704</v>
       </c>
       <c r="G11" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>729</v>
+        <v>715</v>
       </c>
       <c r="K11" s="10" t="s">
         <v>18</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="M11" s="9" t="s">
-        <v>737</v>
+        <v>723</v>
       </c>
       <c r="N11" s="10" t="s">
         <v>15</v>
@@ -8326,18 +8101,18 @@
         <v>610</v>
       </c>
       <c r="T11" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="U11" s="6" t="s">
         <v>438</v>
-      </c>
-      <c r="U11" s="6" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="12" spans="2:21">
       <c r="B12" s="5" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>724</v>
+        <v>710</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>19</v>
@@ -8346,10 +8121,10 @@
       <c r="F12" s="5"/>
       <c r="G12" s="6"/>
       <c r="I12" s="5" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>730</v>
+        <v>716</v>
       </c>
       <c r="K12" s="6"/>
       <c r="L12" s="5"/>
@@ -8362,10 +8137,10 @@
         <v>611</v>
       </c>
       <c r="T12" s="6" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="U12" s="20" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
     </row>
     <row r="13" spans="2:21">
@@ -8376,10 +8151,10 @@
       <c r="F13" s="5"/>
       <c r="G13" s="6"/>
       <c r="I13" s="5" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>731</v>
+        <v>717</v>
       </c>
       <c r="K13" s="6" t="s">
         <v>19</v>
@@ -8394,10 +8169,10 @@
         <v>620</v>
       </c>
       <c r="T13" s="6" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="U13" s="6" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
     </row>
     <row r="14" spans="2:21">
@@ -8408,13 +8183,13 @@
       <c r="F14" s="5"/>
       <c r="G14" s="6"/>
       <c r="I14" s="5" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>732</v>
+        <v>718</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
@@ -8426,10 +8201,10 @@
         <v>621</v>
       </c>
       <c r="T14" s="6" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="U14" s="20" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
     </row>
     <row r="15" spans="2:21">
@@ -8452,10 +8227,10 @@
         <v>630</v>
       </c>
       <c r="T15" s="6" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
     </row>
     <row r="16" spans="2:21">
@@ -8478,13 +8253,13 @@
         <v>631</v>
       </c>
       <c r="T16" s="6" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="U16" s="20" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="17" spans="9:21">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="17" spans="2:21">
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
       <c r="K17" s="6"/>
@@ -8498,13 +8273,13 @@
         <v>640</v>
       </c>
       <c r="T17" s="6" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="U17" s="6" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="18" spans="9:21">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="18" spans="2:21">
       <c r="I18" s="5"/>
       <c r="J18" s="5"/>
       <c r="K18" s="6"/>
@@ -8518,13 +8293,19 @@
         <v>641</v>
       </c>
       <c r="T18" s="6" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="U18" s="20" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="19" spans="9:21">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="19" spans="2:21">
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="12"/>
       <c r="I19" s="5"/>
       <c r="J19" s="5"/>
       <c r="K19" s="6"/>
@@ -8538,13 +8319,23 @@
         <v>650</v>
       </c>
       <c r="T19" s="6" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="U19" s="6" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="20" spans="9:21">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="20" spans="2:21">
+      <c r="B20" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32" t="s">
+        <v>792</v>
+      </c>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
       <c r="I20" s="5"/>
       <c r="J20" s="5"/>
       <c r="K20" s="6"/>
@@ -8558,13 +8349,21 @@
         <v>651</v>
       </c>
       <c r="T20" s="6" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="U20" s="20" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="21" spans="9:21">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="21" spans="2:21">
+      <c r="B21" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
       <c r="I21" s="5"/>
       <c r="J21" s="5"/>
       <c r="K21" s="6"/>
@@ -8578,13 +8377,27 @@
         <v>700</v>
       </c>
       <c r="T21" s="6" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="U21" s="6" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="22" spans="9:21">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="22" spans="2:21">
+      <c r="B22" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="32"/>
+      <c r="D22" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="32"/>
+      <c r="G22" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="I22" s="5"/>
       <c r="J22" s="5"/>
       <c r="K22" s="6"/>
@@ -8598,13 +8411,23 @@
         <v>800</v>
       </c>
       <c r="T22" s="6" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="U22" s="6" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="23" spans="9:21">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="23" spans="2:21">
+      <c r="B23" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
       <c r="I23" s="5"/>
       <c r="J23" s="5"/>
       <c r="K23" s="6"/>
@@ -8618,13 +8441,31 @@
         <v>900</v>
       </c>
       <c r="T23" s="6" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="U23" s="6" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="24" spans="9:21">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="24" spans="2:21">
+      <c r="B24" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>574</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>649</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="I24" s="15"/>
       <c r="J24" s="15"/>
       <c r="K24" s="12"/>
@@ -8638,56 +8479,194 @@
         <v>1000</v>
       </c>
       <c r="T24" s="6" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="U24" s="6" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="25" spans="9:21">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="25" spans="2:21">
+      <c r="B25" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>575</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>13</v>
+      </c>
       <c r="S25" s="5">
         <v>1100</v>
       </c>
       <c r="T25" s="6" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="U25" s="6" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="26" spans="9:21">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="26" spans="2:21">
+      <c r="B26" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>576</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>651</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>14</v>
+      </c>
       <c r="S26" s="5">
         <v>1200</v>
       </c>
       <c r="T26" s="6" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="U26" s="6" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="27" spans="9:21">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="27" spans="2:21">
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>652</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>288</v>
+      </c>
       <c r="S27" s="5">
         <v>1300</v>
       </c>
       <c r="T27" s="6" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="U27" s="6" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="28" spans="9:21">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="28" spans="2:21">
+      <c r="B28" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>577</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="10"/>
       <c r="S28" s="5">
         <v>1400</v>
       </c>
       <c r="T28" s="6" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="U28" s="6"/>
     </row>
+    <row r="29" spans="2:21">
+      <c r="B29" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>578</v>
+      </c>
+      <c r="D29" s="10"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="G29" s="10"/>
+    </row>
+    <row r="30" spans="2:21">
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="G30" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="2:21">
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="10"/>
+    </row>
+    <row r="32" spans="2:21">
+      <c r="B32" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>579</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="10"/>
+    </row>
+    <row r="33" spans="2:7">
+      <c r="B33" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="10"/>
+    </row>
+    <row r="34" spans="2:7">
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="12"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="19">
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:G20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="E22:F22"/>
     <mergeCell ref="O5:P5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="B5:C5"/>
@@ -8713,430 +8692,448 @@
   <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData>
     <row r="6" spans="4:20" ht="17.25" thickBot="1">
-      <c r="D6" s="68" t="s">
-        <v>365</v>
-      </c>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
-      <c r="I6" s="68" t="s">
-        <v>744</v>
-      </c>
-      <c r="J6" s="68"/>
-      <c r="K6" s="68"/>
-      <c r="M6" s="68" t="s">
+      <c r="D6" s="36" t="s">
+        <v>357</v>
+      </c>
+      <c r="E6" s="36"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="36"/>
+      <c r="I6" s="36" t="s">
+        <v>730</v>
+      </c>
+      <c r="J6" s="36"/>
+      <c r="K6" s="36"/>
+      <c r="M6" s="36" t="s">
+        <v>359</v>
+      </c>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
+      <c r="P6" s="36"/>
+      <c r="R6" s="36" t="s">
+        <v>731</v>
+      </c>
+      <c r="S6" s="36"/>
+      <c r="T6" s="36"/>
+    </row>
+    <row r="7" spans="4:20" ht="16.5" customHeight="1">
+      <c r="D7" s="67" t="s">
+        <v>728</v>
+      </c>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="22"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="22"/>
+      <c r="M7" s="67" t="s">
+        <v>726</v>
+      </c>
+      <c r="N7" s="21"/>
+      <c r="O7" s="21"/>
+      <c r="P7" s="22"/>
+      <c r="R7" s="26"/>
+      <c r="S7" s="21"/>
+      <c r="T7" s="22"/>
+    </row>
+    <row r="8" spans="4:20">
+      <c r="D8" s="68"/>
+      <c r="G8" s="23"/>
+      <c r="I8" s="24"/>
+      <c r="K8" s="23"/>
+      <c r="M8" s="68"/>
+      <c r="P8" s="23"/>
+      <c r="R8" s="24"/>
+      <c r="T8" s="23"/>
+    </row>
+    <row r="9" spans="4:20" ht="16.5" customHeight="1">
+      <c r="D9" s="68"/>
+      <c r="F9" s="45" t="s">
+        <v>725</v>
+      </c>
+      <c r="G9" s="23"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="45" t="s">
+        <v>725</v>
+      </c>
+      <c r="K9" s="23"/>
+      <c r="M9" s="68"/>
+      <c r="O9" s="45" t="s">
+        <v>725</v>
+      </c>
+      <c r="P9" s="23"/>
+      <c r="R9" s="24"/>
+      <c r="S9" s="45" t="s">
+        <v>725</v>
+      </c>
+      <c r="T9" s="23"/>
+    </row>
+    <row r="10" spans="4:20">
+      <c r="D10" s="68"/>
+      <c r="F10" s="56"/>
+      <c r="G10" s="23"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="56"/>
+      <c r="K10" s="23"/>
+      <c r="M10" s="68"/>
+      <c r="O10" s="56"/>
+      <c r="P10" s="23"/>
+      <c r="R10" s="24"/>
+      <c r="S10" s="56"/>
+      <c r="T10" s="23"/>
+    </row>
+    <row r="11" spans="4:20" ht="16.5" customHeight="1">
+      <c r="D11" s="68"/>
+      <c r="E11" s="43" t="s">
+        <v>724</v>
+      </c>
+      <c r="G11" s="23"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="43" t="s">
+        <v>724</v>
+      </c>
+      <c r="K11" s="23"/>
+      <c r="M11" s="68"/>
+      <c r="N11" s="43" t="s">
+        <v>724</v>
+      </c>
+      <c r="P11" s="23"/>
+      <c r="R11" s="24"/>
+      <c r="S11" s="43" t="s">
+        <v>724</v>
+      </c>
+      <c r="T11" s="23"/>
+    </row>
+    <row r="12" spans="4:20">
+      <c r="D12" s="68"/>
+      <c r="E12" s="70"/>
+      <c r="G12" s="23"/>
+      <c r="I12" s="24"/>
+      <c r="J12" s="44"/>
+      <c r="K12" s="23"/>
+      <c r="M12" s="68"/>
+      <c r="N12" s="70"/>
+      <c r="P12" s="23"/>
+      <c r="R12" s="24"/>
+      <c r="S12" s="44"/>
+      <c r="T12" s="23"/>
+    </row>
+    <row r="13" spans="4:20">
+      <c r="D13" s="69"/>
+      <c r="G13" s="23"/>
+      <c r="I13" s="24"/>
+      <c r="K13" s="23"/>
+      <c r="M13" s="69"/>
+      <c r="P13" s="23"/>
+      <c r="R13" s="24"/>
+      <c r="T13" s="23"/>
+    </row>
+    <row r="14" spans="4:20" ht="16.5" customHeight="1">
+      <c r="D14" s="24"/>
+      <c r="E14" s="71" t="s">
+        <v>727</v>
+      </c>
+      <c r="F14" s="72"/>
+      <c r="G14" s="73"/>
+      <c r="I14" s="57" t="s">
+        <v>733</v>
+      </c>
+      <c r="J14" s="58"/>
+      <c r="K14" s="63"/>
+      <c r="M14" s="24"/>
+      <c r="N14" s="71" t="s">
+        <v>736</v>
+      </c>
+      <c r="O14" s="72"/>
+      <c r="P14" s="73"/>
+      <c r="R14" s="57" t="s">
+        <v>733</v>
+      </c>
+      <c r="S14" s="58"/>
+      <c r="T14" s="63"/>
+    </row>
+    <row r="15" spans="4:20">
+      <c r="D15" s="24"/>
+      <c r="E15" s="74"/>
+      <c r="F15" s="75"/>
+      <c r="G15" s="76"/>
+      <c r="I15" s="50"/>
+      <c r="J15" s="51"/>
+      <c r="K15" s="52"/>
+      <c r="M15" s="24"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="75"/>
+      <c r="P15" s="76"/>
+      <c r="R15" s="50"/>
+      <c r="S15" s="51"/>
+      <c r="T15" s="52"/>
+    </row>
+    <row r="16" spans="4:20">
+      <c r="D16" s="24"/>
+      <c r="E16" s="74"/>
+      <c r="F16" s="75"/>
+      <c r="G16" s="76"/>
+      <c r="I16" s="50"/>
+      <c r="J16" s="51"/>
+      <c r="K16" s="52"/>
+      <c r="M16" s="24"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="75"/>
+      <c r="P16" s="76"/>
+      <c r="R16" s="50"/>
+      <c r="S16" s="51"/>
+      <c r="T16" s="52"/>
+    </row>
+    <row r="17" spans="4:20" ht="17.25" thickBot="1">
+      <c r="D17" s="25"/>
+      <c r="E17" s="77"/>
+      <c r="F17" s="78"/>
+      <c r="G17" s="79"/>
+      <c r="I17" s="64"/>
+      <c r="J17" s="65"/>
+      <c r="K17" s="66"/>
+      <c r="M17" s="25"/>
+      <c r="N17" s="77"/>
+      <c r="O17" s="78"/>
+      <c r="P17" s="79"/>
+      <c r="R17" s="64"/>
+      <c r="S17" s="65"/>
+      <c r="T17" s="66"/>
+    </row>
+    <row r="19" spans="4:20" ht="17.25" thickBot="1">
+      <c r="D19" s="36" t="s">
+        <v>368</v>
+      </c>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
+      <c r="H19" s="36" t="s">
         <v>367</v>
       </c>
-      <c r="N6" s="68"/>
-      <c r="O6" s="68"/>
-      <c r="P6" s="68"/>
-      <c r="R6" s="68" t="s">
-        <v>745</v>
-      </c>
-      <c r="S6" s="68"/>
-      <c r="T6" s="68"/>
-    </row>
-    <row r="7" spans="4:20" ht="16.5" customHeight="1">
-      <c r="D7" s="36" t="s">
-        <v>742</v>
-      </c>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="23"/>
-      <c r="I7" s="27"/>
-      <c r="J7" s="22"/>
-      <c r="K7" s="23"/>
-      <c r="M7" s="36" t="s">
-        <v>740</v>
-      </c>
-      <c r="N7" s="22"/>
-      <c r="O7" s="22"/>
-      <c r="P7" s="23"/>
-      <c r="R7" s="27"/>
-      <c r="S7" s="22"/>
-      <c r="T7" s="23"/>
-    </row>
-    <row r="8" spans="4:20">
-      <c r="D8" s="37"/>
-      <c r="G8" s="24"/>
-      <c r="I8" s="25"/>
-      <c r="K8" s="24"/>
-      <c r="M8" s="37"/>
-      <c r="P8" s="24"/>
-      <c r="R8" s="25"/>
-      <c r="T8" s="24"/>
-    </row>
-    <row r="9" spans="4:20" ht="16.5" customHeight="1">
-      <c r="D9" s="37"/>
-      <c r="F9" s="48" t="s">
-        <v>739</v>
-      </c>
-      <c r="G9" s="24"/>
-      <c r="I9" s="25"/>
-      <c r="J9" s="48" t="s">
-        <v>739</v>
-      </c>
-      <c r="K9" s="24"/>
-      <c r="M9" s="37"/>
-      <c r="O9" s="48" t="s">
-        <v>739</v>
-      </c>
-      <c r="P9" s="24"/>
-      <c r="R9" s="25"/>
-      <c r="S9" s="48" t="s">
-        <v>739</v>
-      </c>
-      <c r="T9" s="24"/>
-    </row>
-    <row r="10" spans="4:20">
-      <c r="D10" s="37"/>
-      <c r="F10" s="49"/>
-      <c r="G10" s="24"/>
-      <c r="I10" s="25"/>
-      <c r="J10" s="49"/>
-      <c r="K10" s="24"/>
-      <c r="M10" s="37"/>
-      <c r="O10" s="49"/>
-      <c r="P10" s="24"/>
-      <c r="R10" s="25"/>
-      <c r="S10" s="49"/>
-      <c r="T10" s="24"/>
-    </row>
-    <row r="11" spans="4:20" ht="16.5" customHeight="1">
-      <c r="D11" s="37"/>
-      <c r="E11" s="50" t="s">
-        <v>738</v>
-      </c>
-      <c r="G11" s="24"/>
-      <c r="I11" s="25"/>
-      <c r="J11" s="50" t="s">
-        <v>738</v>
-      </c>
-      <c r="K11" s="24"/>
-      <c r="M11" s="37"/>
-      <c r="N11" s="50" t="s">
-        <v>738</v>
-      </c>
-      <c r="P11" s="24"/>
-      <c r="R11" s="25"/>
-      <c r="S11" s="50" t="s">
-        <v>738</v>
-      </c>
-      <c r="T11" s="24"/>
-    </row>
-    <row r="12" spans="4:20">
-      <c r="D12" s="37"/>
-      <c r="E12" s="51"/>
-      <c r="G12" s="24"/>
-      <c r="I12" s="25"/>
-      <c r="J12" s="61"/>
-      <c r="K12" s="24"/>
-      <c r="M12" s="37"/>
-      <c r="N12" s="51"/>
-      <c r="P12" s="24"/>
-      <c r="R12" s="25"/>
-      <c r="S12" s="61"/>
-      <c r="T12" s="24"/>
-    </row>
-    <row r="13" spans="4:20">
-      <c r="D13" s="38"/>
-      <c r="G13" s="24"/>
-      <c r="I13" s="25"/>
-      <c r="K13" s="24"/>
-      <c r="M13" s="38"/>
-      <c r="P13" s="24"/>
-      <c r="R13" s="25"/>
-      <c r="T13" s="24"/>
-    </row>
-    <row r="14" spans="4:20" ht="16.5" customHeight="1">
-      <c r="D14" s="25"/>
-      <c r="E14" s="39" t="s">
-        <v>741</v>
-      </c>
-      <c r="F14" s="40"/>
-      <c r="G14" s="41"/>
-      <c r="I14" s="52" t="s">
-        <v>747</v>
-      </c>
-      <c r="J14" s="53"/>
-      <c r="K14" s="54"/>
-      <c r="M14" s="25"/>
-      <c r="N14" s="39" t="s">
-        <v>750</v>
-      </c>
-      <c r="O14" s="40"/>
-      <c r="P14" s="41"/>
-      <c r="R14" s="52" t="s">
-        <v>747</v>
-      </c>
-      <c r="S14" s="53"/>
-      <c r="T14" s="54"/>
-    </row>
-    <row r="15" spans="4:20">
-      <c r="D15" s="25"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="44"/>
-      <c r="I15" s="55"/>
-      <c r="J15" s="56"/>
-      <c r="K15" s="57"/>
-      <c r="M15" s="25"/>
-      <c r="N15" s="42"/>
-      <c r="O15" s="43"/>
-      <c r="P15" s="44"/>
-      <c r="R15" s="55"/>
-      <c r="S15" s="56"/>
-      <c r="T15" s="57"/>
-    </row>
-    <row r="16" spans="4:20">
-      <c r="D16" s="25"/>
-      <c r="E16" s="42"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="44"/>
-      <c r="I16" s="55"/>
-      <c r="J16" s="56"/>
-      <c r="K16" s="57"/>
-      <c r="M16" s="25"/>
-      <c r="N16" s="42"/>
-      <c r="O16" s="43"/>
-      <c r="P16" s="44"/>
-      <c r="R16" s="55"/>
-      <c r="S16" s="56"/>
-      <c r="T16" s="57"/>
-    </row>
-    <row r="17" spans="4:20" ht="17.25" thickBot="1">
-      <c r="D17" s="26"/>
-      <c r="E17" s="45"/>
-      <c r="F17" s="46"/>
-      <c r="G17" s="47"/>
-      <c r="I17" s="58"/>
-      <c r="J17" s="59"/>
-      <c r="K17" s="60"/>
-      <c r="M17" s="26"/>
-      <c r="N17" s="45"/>
-      <c r="O17" s="46"/>
-      <c r="P17" s="47"/>
-      <c r="R17" s="58"/>
-      <c r="S17" s="59"/>
-      <c r="T17" s="60"/>
-    </row>
-    <row r="19" spans="4:20" ht="17.25" thickBot="1">
-      <c r="D19" s="68" t="s">
-        <v>376</v>
-      </c>
-      <c r="E19" s="68"/>
-      <c r="F19" s="68"/>
-      <c r="H19" s="68" t="s">
-        <v>375</v>
-      </c>
-      <c r="I19" s="68"/>
-      <c r="J19" s="68"/>
-      <c r="K19" s="68"/>
-      <c r="R19" s="68" t="s">
-        <v>746</v>
-      </c>
-      <c r="S19" s="68"/>
-      <c r="T19" s="68"/>
+      <c r="I19" s="36"/>
+      <c r="J19" s="36"/>
+      <c r="K19" s="36"/>
+      <c r="R19" s="36" t="s">
+        <v>732</v>
+      </c>
+      <c r="S19" s="36"/>
+      <c r="T19" s="36"/>
     </row>
     <row r="20" spans="4:20">
-      <c r="D20" s="76" t="s">
-        <v>743</v>
-      </c>
-      <c r="E20" s="77"/>
-      <c r="F20" s="78"/>
-      <c r="H20" s="27"/>
-      <c r="I20" s="67" t="s">
-        <v>739</v>
-      </c>
-      <c r="J20" s="22"/>
-      <c r="K20" s="23"/>
-      <c r="M20" s="27"/>
-      <c r="N20" s="22"/>
-      <c r="O20" s="22"/>
-      <c r="P20" s="23"/>
-      <c r="R20" s="76" t="s">
-        <v>747</v>
-      </c>
-      <c r="S20" s="77"/>
-      <c r="T20" s="78"/>
+      <c r="D20" s="47" t="s">
+        <v>729</v>
+      </c>
+      <c r="E20" s="48"/>
+      <c r="F20" s="49"/>
+      <c r="H20" s="26"/>
+      <c r="I20" s="62" t="s">
+        <v>725</v>
+      </c>
+      <c r="J20" s="21"/>
+      <c r="K20" s="22"/>
+      <c r="M20" s="26"/>
+      <c r="N20" s="21"/>
+      <c r="O20" s="21"/>
+      <c r="P20" s="22"/>
+      <c r="R20" s="47" t="s">
+        <v>733</v>
+      </c>
+      <c r="S20" s="48"/>
+      <c r="T20" s="49"/>
     </row>
     <row r="21" spans="4:20">
-      <c r="D21" s="55"/>
-      <c r="E21" s="56"/>
-      <c r="F21" s="57"/>
-      <c r="H21" s="25"/>
-      <c r="I21" s="49"/>
-      <c r="K21" s="24"/>
-      <c r="M21" s="25"/>
-      <c r="P21" s="24"/>
-      <c r="R21" s="55"/>
-      <c r="S21" s="56"/>
-      <c r="T21" s="57"/>
+      <c r="D21" s="50"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="52"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="56"/>
+      <c r="K21" s="23"/>
+      <c r="M21" s="24"/>
+      <c r="P21" s="23"/>
+      <c r="R21" s="50"/>
+      <c r="S21" s="51"/>
+      <c r="T21" s="52"/>
     </row>
     <row r="22" spans="4:20">
-      <c r="D22" s="55"/>
-      <c r="E22" s="56"/>
-      <c r="F22" s="57"/>
-      <c r="H22" s="25"/>
-      <c r="I22" s="50" t="s">
-        <v>738</v>
-      </c>
-      <c r="J22" s="73" t="s">
-        <v>748</v>
-      </c>
-      <c r="K22" s="24"/>
-      <c r="M22" s="25"/>
-      <c r="P22" s="24"/>
-      <c r="R22" s="55"/>
-      <c r="S22" s="56"/>
-      <c r="T22" s="57"/>
+      <c r="D22" s="50"/>
+      <c r="E22" s="51"/>
+      <c r="F22" s="52"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="43" t="s">
+        <v>724</v>
+      </c>
+      <c r="J22" s="41" t="s">
+        <v>734</v>
+      </c>
+      <c r="K22" s="23"/>
+      <c r="M22" s="24"/>
+      <c r="P22" s="23"/>
+      <c r="R22" s="50"/>
+      <c r="S22" s="51"/>
+      <c r="T22" s="52"/>
     </row>
     <row r="23" spans="4:20">
-      <c r="D23" s="64"/>
-      <c r="E23" s="65"/>
-      <c r="F23" s="79"/>
-      <c r="H23" s="25"/>
-      <c r="I23" s="61"/>
-      <c r="J23" s="74"/>
-      <c r="K23" s="24"/>
-      <c r="M23" s="25"/>
-      <c r="P23" s="24"/>
-      <c r="R23" s="64"/>
-      <c r="S23" s="65"/>
-      <c r="T23" s="79"/>
+      <c r="D23" s="53"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="55"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="44"/>
+      <c r="J23" s="42"/>
+      <c r="K23" s="23"/>
+      <c r="M23" s="24"/>
+      <c r="P23" s="23"/>
+      <c r="R23" s="53"/>
+      <c r="S23" s="54"/>
+      <c r="T23" s="55"/>
     </row>
     <row r="24" spans="4:20">
-      <c r="D24" s="25"/>
-      <c r="F24" s="24"/>
-      <c r="H24" s="30"/>
-      <c r="I24" s="31"/>
-      <c r="J24" s="31"/>
-      <c r="K24" s="24"/>
-      <c r="M24" s="25"/>
-      <c r="P24" s="24"/>
-      <c r="R24" s="25"/>
-      <c r="T24" s="24"/>
+      <c r="D24" s="24"/>
+      <c r="F24" s="23"/>
+      <c r="H24" s="29"/>
+      <c r="I24" s="30"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="23"/>
+      <c r="M24" s="24"/>
+      <c r="P24" s="23"/>
+      <c r="R24" s="24"/>
+      <c r="T24" s="23"/>
     </row>
     <row r="25" spans="4:20" ht="16.5" customHeight="1">
-      <c r="D25" s="25"/>
-      <c r="E25" s="50" t="s">
-        <v>738</v>
-      </c>
-      <c r="F25" s="24"/>
-      <c r="H25" s="52" t="s">
-        <v>751</v>
-      </c>
-      <c r="I25" s="53"/>
-      <c r="J25" s="62"/>
-      <c r="K25" s="24"/>
-      <c r="M25" s="25"/>
-      <c r="P25" s="24"/>
-      <c r="R25" s="25"/>
-      <c r="S25" s="50" t="s">
-        <v>738</v>
-      </c>
-      <c r="T25" s="24"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="43" t="s">
+        <v>724</v>
+      </c>
+      <c r="F25" s="23"/>
+      <c r="H25" s="57" t="s">
+        <v>737</v>
+      </c>
+      <c r="I25" s="58"/>
+      <c r="J25" s="59"/>
+      <c r="K25" s="23"/>
+      <c r="M25" s="24"/>
+      <c r="P25" s="23"/>
+      <c r="R25" s="24"/>
+      <c r="S25" s="43" t="s">
+        <v>724</v>
+      </c>
+      <c r="T25" s="23"/>
     </row>
     <row r="26" spans="4:20">
-      <c r="D26" s="25"/>
-      <c r="E26" s="61"/>
-      <c r="F26" s="24"/>
-      <c r="H26" s="55"/>
-      <c r="I26" s="56"/>
-      <c r="J26" s="63"/>
-      <c r="K26" s="24"/>
-      <c r="M26" s="25"/>
-      <c r="P26" s="24"/>
-      <c r="R26" s="25"/>
-      <c r="S26" s="61"/>
-      <c r="T26" s="24"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="44"/>
+      <c r="F26" s="23"/>
+      <c r="H26" s="50"/>
+      <c r="I26" s="51"/>
+      <c r="J26" s="60"/>
+      <c r="K26" s="23"/>
+      <c r="M26" s="24"/>
+      <c r="P26" s="23"/>
+      <c r="R26" s="24"/>
+      <c r="S26" s="44"/>
+      <c r="T26" s="23"/>
     </row>
     <row r="27" spans="4:20">
-      <c r="D27" s="25"/>
-      <c r="E27" s="48" t="s">
-        <v>739</v>
-      </c>
-      <c r="F27" s="24"/>
-      <c r="H27" s="55"/>
-      <c r="I27" s="56"/>
-      <c r="J27" s="63"/>
-      <c r="K27" s="69" t="s">
-        <v>740</v>
-      </c>
-      <c r="M27" s="25"/>
-      <c r="P27" s="24"/>
-      <c r="R27" s="25"/>
-      <c r="S27" s="48" t="s">
-        <v>739</v>
-      </c>
-      <c r="T27" s="24"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="45" t="s">
+        <v>725</v>
+      </c>
+      <c r="F27" s="23"/>
+      <c r="H27" s="50"/>
+      <c r="I27" s="51"/>
+      <c r="J27" s="60"/>
+      <c r="K27" s="37" t="s">
+        <v>726</v>
+      </c>
+      <c r="M27" s="24"/>
+      <c r="P27" s="23"/>
+      <c r="R27" s="24"/>
+      <c r="S27" s="45" t="s">
+        <v>725</v>
+      </c>
+      <c r="T27" s="23"/>
     </row>
     <row r="28" spans="4:20" ht="16.5" customHeight="1">
-      <c r="D28" s="25"/>
-      <c r="E28" s="49"/>
-      <c r="F28" s="24"/>
-      <c r="H28" s="64"/>
-      <c r="I28" s="65"/>
-      <c r="J28" s="66"/>
-      <c r="K28" s="70"/>
-      <c r="M28" s="25"/>
-      <c r="P28" s="24"/>
-      <c r="R28" s="25"/>
-      <c r="S28" s="49"/>
-      <c r="T28" s="24"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="56"/>
+      <c r="F28" s="23"/>
+      <c r="H28" s="53"/>
+      <c r="I28" s="54"/>
+      <c r="J28" s="61"/>
+      <c r="K28" s="38"/>
+      <c r="M28" s="24"/>
+      <c r="P28" s="23"/>
+      <c r="R28" s="24"/>
+      <c r="S28" s="56"/>
+      <c r="T28" s="23"/>
     </row>
     <row r="29" spans="4:20">
-      <c r="D29" s="25"/>
-      <c r="F29" s="24"/>
-      <c r="H29" s="25"/>
-      <c r="K29" s="71"/>
-      <c r="M29" s="25"/>
-      <c r="P29" s="24"/>
-      <c r="R29" s="25"/>
-      <c r="T29" s="24"/>
+      <c r="D29" s="24"/>
+      <c r="F29" s="23"/>
+      <c r="H29" s="24"/>
+      <c r="K29" s="39"/>
+      <c r="M29" s="24"/>
+      <c r="P29" s="23"/>
+      <c r="R29" s="24"/>
+      <c r="T29" s="23"/>
     </row>
     <row r="30" spans="4:20" ht="17.25" thickBot="1">
-      <c r="D30" s="26"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="29"/>
-      <c r="H30" s="25"/>
-      <c r="I30" s="50" t="s">
-        <v>738</v>
-      </c>
-      <c r="K30" s="71"/>
-      <c r="M30" s="26"/>
-      <c r="N30" s="28"/>
-      <c r="O30" s="28"/>
-      <c r="P30" s="29"/>
-      <c r="R30" s="26"/>
-      <c r="S30" s="28"/>
-      <c r="T30" s="29"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="28"/>
+      <c r="H30" s="24"/>
+      <c r="I30" s="43" t="s">
+        <v>724</v>
+      </c>
+      <c r="K30" s="39"/>
+      <c r="M30" s="25"/>
+      <c r="N30" s="27"/>
+      <c r="O30" s="27"/>
+      <c r="P30" s="28"/>
+      <c r="R30" s="25"/>
+      <c r="S30" s="27"/>
+      <c r="T30" s="28"/>
     </row>
     <row r="31" spans="4:20">
-      <c r="H31" s="25"/>
-      <c r="I31" s="61"/>
-      <c r="K31" s="71"/>
+      <c r="H31" s="24"/>
+      <c r="I31" s="44"/>
+      <c r="K31" s="39"/>
     </row>
     <row r="32" spans="4:20">
-      <c r="H32" s="25"/>
-      <c r="I32" s="48" t="s">
-        <v>739</v>
-      </c>
-      <c r="K32" s="71"/>
+      <c r="H32" s="24"/>
+      <c r="I32" s="45" t="s">
+        <v>725</v>
+      </c>
+      <c r="K32" s="39"/>
     </row>
     <row r="33" spans="8:24" ht="17.25" thickBot="1">
-      <c r="H33" s="26"/>
-      <c r="I33" s="75"/>
-      <c r="J33" s="28"/>
-      <c r="K33" s="72"/>
+      <c r="H33" s="25"/>
+      <c r="I33" s="46"/>
+      <c r="J33" s="27"/>
+      <c r="K33" s="40"/>
     </row>
     <row r="47" spans="8:24">
       <c r="X47" t="s">
-        <v>749</v>
+        <v>735</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="D7:D13"/>
+    <mergeCell ref="E14:G17"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="I14:K17"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="S11:S12"/>
+    <mergeCell ref="R14:T17"/>
+    <mergeCell ref="M7:M13"/>
+    <mergeCell ref="O9:O10"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="N14:P17"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="H25:J28"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="J11:J12"/>
     <mergeCell ref="R6:T6"/>
     <mergeCell ref="R19:T19"/>
     <mergeCell ref="D19:F19"/>
@@ -9153,24 +9150,6 @@
     <mergeCell ref="M6:P6"/>
     <mergeCell ref="D20:F23"/>
     <mergeCell ref="E27:E28"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="H25:J28"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="I22:I23"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="S11:S12"/>
-    <mergeCell ref="R14:T17"/>
-    <mergeCell ref="M7:M13"/>
-    <mergeCell ref="O9:O10"/>
-    <mergeCell ref="N11:N12"/>
-    <mergeCell ref="N14:P17"/>
-    <mergeCell ref="D7:D13"/>
-    <mergeCell ref="E14:G17"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="I14:K17"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/PLC/IO List.xlsx
+++ b/PLC/IO List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EZENIC\Desktop\Project-Second\PLC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2835CF8F-2E3F-4C19-AB07-89F71B4EF467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{269B18CA-B154-4D02-8D2B-D6A949600900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{E8A3CD3B-D612-4B37-A180-F6C335096DC9}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{E8A3CD3B-D612-4B37-A180-F6C335096DC9}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="803">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="823">
   <si>
     <t>X10</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2876,6 +2876,74 @@
   <si>
     <t>프레스 작업완료</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>챔버1 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M11</t>
+  </si>
+  <si>
+    <t>M12</t>
+  </si>
+  <si>
+    <t>M13</t>
+  </si>
+  <si>
+    <t>챔버2 상태</t>
+  </si>
+  <si>
+    <t>챔버3 상태</t>
+  </si>
+  <si>
+    <t>챔버4 상태</t>
+  </si>
+  <si>
+    <t>T30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>챔버1 완료 후 딜레이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>T31</t>
+  </si>
+  <si>
+    <t>T32</t>
+  </si>
+  <si>
+    <t>T33</t>
+  </si>
+  <si>
+    <t>챔버2 완료 후 딜레이</t>
+  </si>
+  <si>
+    <t>챔버3 완료 후 딜레이</t>
+  </si>
+  <si>
+    <t>챔버4 완료 후 딜레이</t>
   </si>
 </sst>
 </file>
@@ -3512,99 +3580,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3612,9 +3587,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3643,6 +3615,102 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4203,7 +4271,7 @@
         <v>121</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>447</v>
+        <v>803</v>
       </c>
       <c r="I11" s="6" t="s">
         <v>448</v>
@@ -4229,7 +4297,7 @@
         <v>122</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>449</v>
+        <v>804</v>
       </c>
       <c r="I12" s="6" t="s">
         <v>450</v>
@@ -4255,7 +4323,7 @@
         <v>123</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>447</v>
+        <v>805</v>
       </c>
       <c r="I13" s="6" t="s">
         <v>448</v>
@@ -4281,7 +4349,7 @@
         <v>124</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>449</v>
+        <v>806</v>
       </c>
       <c r="I14" s="6" t="s">
         <v>450</v>
@@ -4320,8 +4388,12 @@
       <c r="G16" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="H16" s="5"/>
-      <c r="I16" s="6"/>
+      <c r="H16" s="5" t="s">
+        <v>807</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>808</v>
+      </c>
       <c r="J16" s="5"/>
       <c r="K16" s="6"/>
     </row>
@@ -4341,10 +4413,10 @@
         <v>127</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>473</v>
+        <v>809</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>474</v>
+        <v>812</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>509</v>
@@ -4369,10 +4441,10 @@
         <v>52</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>483</v>
+        <v>810</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>475</v>
+        <v>813</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>510</v>
@@ -4399,10 +4471,10 @@
         <v>132</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>484</v>
+        <v>811</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>476</v>
+        <v>814</v>
       </c>
       <c r="J19" s="5" t="s">
         <v>511</v>
@@ -4428,12 +4500,6 @@
       <c r="G20" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="H20" s="5" t="s">
-        <v>485</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>477</v>
-      </c>
       <c r="J20" s="5"/>
       <c r="K20" s="6"/>
     </row>
@@ -4454,12 +4520,6 @@
       <c r="G21" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="H21" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>478</v>
-      </c>
       <c r="J21" s="5"/>
       <c r="K21" s="6"/>
     </row>
@@ -4480,12 +4540,6 @@
       <c r="G22" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="H22" s="5" t="s">
-        <v>487</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>479</v>
-      </c>
       <c r="J22" s="5" t="s">
         <v>771</v>
       </c>
@@ -4510,12 +4564,6 @@
       <c r="G23" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="H23" s="5" t="s">
-        <v>488</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>480</v>
-      </c>
       <c r="J23" s="5" t="s">
         <v>772</v>
       </c>
@@ -4541,10 +4589,10 @@
         <v>137</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>489</v>
+        <v>473</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="J24" s="5" t="s">
         <v>773</v>
@@ -4569,10 +4617,10 @@
         <v>170</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="J25" s="5" t="s">
         <v>774</v>
@@ -4597,10 +4645,10 @@
         <v>171</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>492</v>
+        <v>476</v>
       </c>
       <c r="J26" s="5" t="s">
         <v>775</v>
@@ -4624,8 +4672,12 @@
       <c r="G27" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="H27" s="5"/>
-      <c r="I27" s="6"/>
+      <c r="H27" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>477</v>
+      </c>
       <c r="J27" s="5" t="s">
         <v>776</v>
       </c>
@@ -4650,8 +4702,12 @@
       <c r="G28" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="H28" s="5"/>
-      <c r="I28" s="6"/>
+      <c r="H28" s="5" t="s">
+        <v>486</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>478</v>
+      </c>
       <c r="J28" s="5" t="s">
         <v>777</v>
       </c>
@@ -4676,8 +4732,12 @@
       <c r="G29" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="H29" s="5"/>
-      <c r="I29" s="6"/>
+      <c r="H29" s="5" t="s">
+        <v>487</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>479</v>
+      </c>
       <c r="J29" s="5" t="s">
         <v>778</v>
       </c>
@@ -4702,8 +4762,12 @@
       <c r="G30" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="H30" s="5"/>
-      <c r="I30" s="6"/>
+      <c r="H30" s="5" t="s">
+        <v>488</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>480</v>
+      </c>
       <c r="J30" s="5" t="s">
         <v>779</v>
       </c>
@@ -4729,10 +4793,10 @@
         <v>176</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>453</v>
+        <v>489</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>456</v>
+        <v>481</v>
       </c>
       <c r="J31" s="5" t="s">
         <v>780</v>
@@ -4759,10 +4823,10 @@
         <v>177</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>454</v>
+        <v>490</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>455</v>
+        <v>482</v>
       </c>
       <c r="J32" s="5"/>
       <c r="K32" s="6"/>
@@ -4785,13 +4849,17 @@
         <v>178</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>457</v>
+        <v>491</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>465</v>
-      </c>
-      <c r="J33" s="5"/>
-      <c r="K33" s="6"/>
+        <v>492</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>815</v>
+      </c>
+      <c r="K33" s="6" t="s">
+        <v>816</v>
+      </c>
     </row>
     <row r="34" spans="2:11">
       <c r="B34" s="5" t="s">
@@ -4808,14 +4876,14 @@
       <c r="G34" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="H34" s="5" t="s">
-        <v>458</v>
-      </c>
-      <c r="I34" s="6" t="s">
-        <v>466</v>
-      </c>
-      <c r="J34" s="5"/>
-      <c r="K34" s="6"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="5" t="s">
+        <v>817</v>
+      </c>
+      <c r="K34" s="6" t="s">
+        <v>820</v>
+      </c>
     </row>
     <row r="35" spans="2:11">
       <c r="B35" s="5" t="s">
@@ -4832,14 +4900,14 @@
       <c r="G35" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="H35" s="5" t="s">
-        <v>459</v>
-      </c>
-      <c r="I35" s="6" t="s">
-        <v>467</v>
-      </c>
-      <c r="J35" s="5"/>
-      <c r="K35" s="6"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="5" t="s">
+        <v>818</v>
+      </c>
+      <c r="K35" s="6" t="s">
+        <v>821</v>
+      </c>
     </row>
     <row r="36" spans="2:11">
       <c r="B36" s="5" t="s">
@@ -4856,14 +4924,14 @@
       <c r="G36" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="H36" s="5" t="s">
-        <v>460</v>
-      </c>
-      <c r="I36" s="6" t="s">
-        <v>468</v>
-      </c>
-      <c r="J36" s="5"/>
-      <c r="K36" s="6"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="5" t="s">
+        <v>819</v>
+      </c>
+      <c r="K36" s="6" t="s">
+        <v>822</v>
+      </c>
     </row>
     <row r="37" spans="2:11">
       <c r="B37" s="5" t="s">
@@ -4880,12 +4948,8 @@
       <c r="G37" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="H37" s="5" t="s">
-        <v>461</v>
-      </c>
-      <c r="I37" s="6" t="s">
-        <v>469</v>
-      </c>
+      <c r="H37" s="5"/>
+      <c r="I37" s="6"/>
       <c r="J37" s="5"/>
       <c r="K37" s="6"/>
     </row>
@@ -4905,10 +4969,10 @@
         <v>183</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>470</v>
+        <v>456</v>
       </c>
       <c r="J38" s="5"/>
       <c r="K38" s="6"/>
@@ -4929,10 +4993,10 @@
         <v>184</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>471</v>
+        <v>455</v>
       </c>
       <c r="J39" s="5"/>
       <c r="K39" s="6"/>
@@ -4953,10 +5017,10 @@
         <v>185</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="J40" s="5"/>
       <c r="K40" s="6"/>
@@ -4976,8 +5040,12 @@
       <c r="G41" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="H41" s="5"/>
-      <c r="I41" s="6"/>
+      <c r="H41" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>466</v>
+      </c>
       <c r="J41" s="5"/>
       <c r="K41" s="6"/>
     </row>
@@ -4997,10 +5065,10 @@
         <v>187</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>761</v>
+        <v>459</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>770</v>
+        <v>467</v>
       </c>
       <c r="J42" s="5"/>
       <c r="K42" s="6"/>
@@ -5021,10 +5089,10 @@
         <v>188</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>762</v>
+        <v>460</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>794</v>
+        <v>468</v>
       </c>
       <c r="J43" s="5"/>
       <c r="K43" s="6"/>
@@ -5045,10 +5113,10 @@
         <v>189</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>763</v>
+        <v>461</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>795</v>
+        <v>469</v>
       </c>
       <c r="J44" s="5"/>
       <c r="K44" s="6"/>
@@ -5069,10 +5137,10 @@
         <v>190</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>764</v>
+        <v>462</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>796</v>
+        <v>470</v>
       </c>
       <c r="J45" s="5"/>
       <c r="K45" s="6"/>
@@ -5093,10 +5161,10 @@
         <v>191</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>765</v>
+        <v>463</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>802</v>
+        <v>471</v>
       </c>
       <c r="J46" s="5"/>
       <c r="K46" s="6"/>
@@ -5117,10 +5185,10 @@
         <v>192</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>766</v>
+        <v>464</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>797</v>
+        <v>472</v>
       </c>
       <c r="J47" s="5"/>
       <c r="K47" s="6"/>
@@ -5140,12 +5208,8 @@
       <c r="G48" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="H48" s="5" t="s">
-        <v>767</v>
-      </c>
-      <c r="I48" s="6" t="s">
-        <v>798</v>
-      </c>
+      <c r="H48" s="5"/>
+      <c r="I48" s="6"/>
       <c r="J48" s="5"/>
       <c r="K48" s="6"/>
     </row>
@@ -5161,10 +5225,10 @@
         <v>194</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>768</v>
+        <v>761</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>799</v>
+        <v>770</v>
       </c>
       <c r="J49" s="5"/>
       <c r="K49" s="6"/>
@@ -5181,10 +5245,10 @@
         <v>195</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>800</v>
+        <v>794</v>
       </c>
       <c r="J50" s="5"/>
       <c r="K50" s="6"/>
@@ -5201,10 +5265,10 @@
         <v>196</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>791</v>
+        <v>763</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>801</v>
+        <v>795</v>
       </c>
       <c r="J51" s="5"/>
       <c r="K51" s="6"/>
@@ -5222,8 +5286,12 @@
       <c r="G52" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="H52" s="5"/>
-      <c r="I52" s="6"/>
+      <c r="H52" s="5" t="s">
+        <v>764</v>
+      </c>
+      <c r="I52" s="6" t="s">
+        <v>796</v>
+      </c>
       <c r="J52" s="5"/>
       <c r="K52" s="6"/>
     </row>
@@ -5240,8 +5308,12 @@
       <c r="G53" s="6" t="s">
         <v>376</v>
       </c>
-      <c r="H53" s="5"/>
-      <c r="I53" s="6"/>
+      <c r="H53" s="5" t="s">
+        <v>765</v>
+      </c>
+      <c r="I53" s="6" t="s">
+        <v>802</v>
+      </c>
       <c r="J53" s="5"/>
       <c r="K53" s="6"/>
     </row>
@@ -5258,8 +5330,12 @@
       <c r="G54" s="6" t="s">
         <v>377</v>
       </c>
-      <c r="H54" s="5"/>
-      <c r="I54" s="6"/>
+      <c r="H54" s="5" t="s">
+        <v>766</v>
+      </c>
+      <c r="I54" s="6" t="s">
+        <v>797</v>
+      </c>
       <c r="J54" s="5"/>
       <c r="K54" s="6"/>
     </row>
@@ -5276,8 +5352,12 @@
       <c r="G55" s="6" t="s">
         <v>378</v>
       </c>
-      <c r="H55" s="5"/>
-      <c r="I55" s="6"/>
+      <c r="H55" s="5" t="s">
+        <v>767</v>
+      </c>
+      <c r="I55" s="6" t="s">
+        <v>798</v>
+      </c>
       <c r="J55" s="5"/>
       <c r="K55" s="6"/>
     </row>
@@ -5294,8 +5374,12 @@
       <c r="G56" s="6" t="s">
         <v>379</v>
       </c>
-      <c r="H56" s="5"/>
-      <c r="I56" s="6"/>
+      <c r="H56" s="5" t="s">
+        <v>768</v>
+      </c>
+      <c r="I56" s="6" t="s">
+        <v>799</v>
+      </c>
       <c r="J56" s="5"/>
       <c r="K56" s="6"/>
     </row>
@@ -5312,16 +5396,24 @@
       <c r="G57" s="6" t="s">
         <v>380</v>
       </c>
-      <c r="H57" s="5"/>
-      <c r="I57" s="6"/>
+      <c r="H57" s="5" t="s">
+        <v>769</v>
+      </c>
+      <c r="I57" s="6" t="s">
+        <v>800</v>
+      </c>
       <c r="J57" s="5"/>
       <c r="K57" s="6"/>
     </row>
     <row r="58" spans="2:11">
       <c r="F58" s="5"/>
       <c r="G58" s="6"/>
-      <c r="H58" s="5"/>
-      <c r="I58" s="6"/>
+      <c r="H58" s="5" t="s">
+        <v>791</v>
+      </c>
+      <c r="I58" s="6" t="s">
+        <v>801</v>
+      </c>
       <c r="J58" s="6"/>
       <c r="K58" s="6"/>
     </row>
@@ -7609,6 +7701,34 @@
     </row>
   </sheetData>
   <mergeCells count="44">
+    <mergeCell ref="N44:O44"/>
+    <mergeCell ref="V44:W44"/>
+    <mergeCell ref="S44:T44"/>
+    <mergeCell ref="K44:L44"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="M43:P43"/>
+    <mergeCell ref="U43:X43"/>
+    <mergeCell ref="M23:P23"/>
+    <mergeCell ref="M24:P24"/>
+    <mergeCell ref="U23:X23"/>
+    <mergeCell ref="U24:X24"/>
+    <mergeCell ref="S23:T23"/>
+    <mergeCell ref="S24:T24"/>
+    <mergeCell ref="S25:T25"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="E42:H42"/>
     <mergeCell ref="M42:P42"/>
     <mergeCell ref="U42:X42"/>
     <mergeCell ref="E3:H3"/>
@@ -7625,34 +7745,6 @@
     <mergeCell ref="N25:O25"/>
     <mergeCell ref="U3:X3"/>
     <mergeCell ref="U4:X4"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="E42:H42"/>
-    <mergeCell ref="N44:O44"/>
-    <mergeCell ref="V44:W44"/>
-    <mergeCell ref="S44:T44"/>
-    <mergeCell ref="K44:L44"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="M43:P43"/>
-    <mergeCell ref="U43:X43"/>
-    <mergeCell ref="M23:P23"/>
-    <mergeCell ref="M24:P24"/>
-    <mergeCell ref="U23:X23"/>
-    <mergeCell ref="U24:X24"/>
-    <mergeCell ref="S23:T23"/>
-    <mergeCell ref="S24:T24"/>
-    <mergeCell ref="S25:T25"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8661,12 +8753,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:G20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="E22:F22"/>
     <mergeCell ref="O5:P5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="B5:C5"/>
@@ -8680,6 +8766,12 @@
     <mergeCell ref="K4:Q4"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:G20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="E22:F22"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8692,31 +8784,31 @@
   <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData>
     <row r="6" spans="4:20" ht="17.25" thickBot="1">
-      <c r="D6" s="36" t="s">
+      <c r="D6" s="68" t="s">
         <v>357</v>
       </c>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
-      <c r="I6" s="36" t="s">
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
+      <c r="I6" s="68" t="s">
         <v>730</v>
       </c>
-      <c r="J6" s="36"/>
-      <c r="K6" s="36"/>
-      <c r="M6" s="36" t="s">
+      <c r="J6" s="68"/>
+      <c r="K6" s="68"/>
+      <c r="M6" s="68" t="s">
         <v>359</v>
       </c>
-      <c r="N6" s="36"/>
-      <c r="O6" s="36"/>
-      <c r="P6" s="36"/>
-      <c r="R6" s="36" t="s">
+      <c r="N6" s="68"/>
+      <c r="O6" s="68"/>
+      <c r="P6" s="68"/>
+      <c r="R6" s="68" t="s">
         <v>731</v>
       </c>
-      <c r="S6" s="36"/>
-      <c r="T6" s="36"/>
+      <c r="S6" s="68"/>
+      <c r="T6" s="68"/>
     </row>
     <row r="7" spans="4:20" ht="16.5" customHeight="1">
-      <c r="D7" s="67" t="s">
+      <c r="D7" s="36" t="s">
         <v>728</v>
       </c>
       <c r="E7" s="21"/>
@@ -8725,7 +8817,7 @@
       <c r="I7" s="26"/>
       <c r="J7" s="21"/>
       <c r="K7" s="22"/>
-      <c r="M7" s="67" t="s">
+      <c r="M7" s="36" t="s">
         <v>726</v>
       </c>
       <c r="N7" s="21"/>
@@ -8736,195 +8828,195 @@
       <c r="T7" s="22"/>
     </row>
     <row r="8" spans="4:20">
-      <c r="D8" s="68"/>
+      <c r="D8" s="37"/>
       <c r="G8" s="23"/>
       <c r="I8" s="24"/>
       <c r="K8" s="23"/>
-      <c r="M8" s="68"/>
+      <c r="M8" s="37"/>
       <c r="P8" s="23"/>
       <c r="R8" s="24"/>
       <c r="T8" s="23"/>
     </row>
     <row r="9" spans="4:20" ht="16.5" customHeight="1">
-      <c r="D9" s="68"/>
-      <c r="F9" s="45" t="s">
+      <c r="D9" s="37"/>
+      <c r="F9" s="48" t="s">
         <v>725</v>
       </c>
       <c r="G9" s="23"/>
       <c r="I9" s="24"/>
-      <c r="J9" s="45" t="s">
+      <c r="J9" s="48" t="s">
         <v>725</v>
       </c>
       <c r="K9" s="23"/>
-      <c r="M9" s="68"/>
-      <c r="O9" s="45" t="s">
+      <c r="M9" s="37"/>
+      <c r="O9" s="48" t="s">
         <v>725</v>
       </c>
       <c r="P9" s="23"/>
       <c r="R9" s="24"/>
-      <c r="S9" s="45" t="s">
+      <c r="S9" s="48" t="s">
         <v>725</v>
       </c>
       <c r="T9" s="23"/>
     </row>
     <row r="10" spans="4:20">
-      <c r="D10" s="68"/>
-      <c r="F10" s="56"/>
+      <c r="D10" s="37"/>
+      <c r="F10" s="49"/>
       <c r="G10" s="23"/>
       <c r="I10" s="24"/>
-      <c r="J10" s="56"/>
+      <c r="J10" s="49"/>
       <c r="K10" s="23"/>
-      <c r="M10" s="68"/>
-      <c r="O10" s="56"/>
+      <c r="M10" s="37"/>
+      <c r="O10" s="49"/>
       <c r="P10" s="23"/>
       <c r="R10" s="24"/>
-      <c r="S10" s="56"/>
+      <c r="S10" s="49"/>
       <c r="T10" s="23"/>
     </row>
     <row r="11" spans="4:20" ht="16.5" customHeight="1">
-      <c r="D11" s="68"/>
-      <c r="E11" s="43" t="s">
+      <c r="D11" s="37"/>
+      <c r="E11" s="50" t="s">
         <v>724</v>
       </c>
       <c r="G11" s="23"/>
       <c r="I11" s="24"/>
-      <c r="J11" s="43" t="s">
+      <c r="J11" s="50" t="s">
         <v>724</v>
       </c>
       <c r="K11" s="23"/>
-      <c r="M11" s="68"/>
-      <c r="N11" s="43" t="s">
+      <c r="M11" s="37"/>
+      <c r="N11" s="50" t="s">
         <v>724</v>
       </c>
       <c r="P11" s="23"/>
       <c r="R11" s="24"/>
-      <c r="S11" s="43" t="s">
+      <c r="S11" s="50" t="s">
         <v>724</v>
       </c>
       <c r="T11" s="23"/>
     </row>
     <row r="12" spans="4:20">
-      <c r="D12" s="68"/>
-      <c r="E12" s="70"/>
+      <c r="D12" s="37"/>
+      <c r="E12" s="51"/>
       <c r="G12" s="23"/>
       <c r="I12" s="24"/>
-      <c r="J12" s="44"/>
+      <c r="J12" s="61"/>
       <c r="K12" s="23"/>
-      <c r="M12" s="68"/>
-      <c r="N12" s="70"/>
+      <c r="M12" s="37"/>
+      <c r="N12" s="51"/>
       <c r="P12" s="23"/>
       <c r="R12" s="24"/>
-      <c r="S12" s="44"/>
+      <c r="S12" s="61"/>
       <c r="T12" s="23"/>
     </row>
     <row r="13" spans="4:20">
-      <c r="D13" s="69"/>
+      <c r="D13" s="38"/>
       <c r="G13" s="23"/>
       <c r="I13" s="24"/>
       <c r="K13" s="23"/>
-      <c r="M13" s="69"/>
+      <c r="M13" s="38"/>
       <c r="P13" s="23"/>
       <c r="R13" s="24"/>
       <c r="T13" s="23"/>
     </row>
     <row r="14" spans="4:20" ht="16.5" customHeight="1">
       <c r="D14" s="24"/>
-      <c r="E14" s="71" t="s">
+      <c r="E14" s="39" t="s">
         <v>727</v>
       </c>
-      <c r="F14" s="72"/>
-      <c r="G14" s="73"/>
-      <c r="I14" s="57" t="s">
+      <c r="F14" s="40"/>
+      <c r="G14" s="41"/>
+      <c r="I14" s="52" t="s">
         <v>733</v>
       </c>
-      <c r="J14" s="58"/>
-      <c r="K14" s="63"/>
+      <c r="J14" s="53"/>
+      <c r="K14" s="54"/>
       <c r="M14" s="24"/>
-      <c r="N14" s="71" t="s">
+      <c r="N14" s="39" t="s">
         <v>736</v>
       </c>
-      <c r="O14" s="72"/>
-      <c r="P14" s="73"/>
-      <c r="R14" s="57" t="s">
+      <c r="O14" s="40"/>
+      <c r="P14" s="41"/>
+      <c r="R14" s="52" t="s">
         <v>733</v>
       </c>
-      <c r="S14" s="58"/>
-      <c r="T14" s="63"/>
+      <c r="S14" s="53"/>
+      <c r="T14" s="54"/>
     </row>
     <row r="15" spans="4:20">
       <c r="D15" s="24"/>
-      <c r="E15" s="74"/>
-      <c r="F15" s="75"/>
-      <c r="G15" s="76"/>
-      <c r="I15" s="50"/>
-      <c r="J15" s="51"/>
-      <c r="K15" s="52"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="44"/>
+      <c r="I15" s="55"/>
+      <c r="J15" s="56"/>
+      <c r="K15" s="57"/>
       <c r="M15" s="24"/>
-      <c r="N15" s="74"/>
-      <c r="O15" s="75"/>
-      <c r="P15" s="76"/>
-      <c r="R15" s="50"/>
-      <c r="S15" s="51"/>
-      <c r="T15" s="52"/>
+      <c r="N15" s="42"/>
+      <c r="O15" s="43"/>
+      <c r="P15" s="44"/>
+      <c r="R15" s="55"/>
+      <c r="S15" s="56"/>
+      <c r="T15" s="57"/>
     </row>
     <row r="16" spans="4:20">
       <c r="D16" s="24"/>
-      <c r="E16" s="74"/>
-      <c r="F16" s="75"/>
-      <c r="G16" s="76"/>
-      <c r="I16" s="50"/>
-      <c r="J16" s="51"/>
-      <c r="K16" s="52"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="44"/>
+      <c r="I16" s="55"/>
+      <c r="J16" s="56"/>
+      <c r="K16" s="57"/>
       <c r="M16" s="24"/>
-      <c r="N16" s="74"/>
-      <c r="O16" s="75"/>
-      <c r="P16" s="76"/>
-      <c r="R16" s="50"/>
-      <c r="S16" s="51"/>
-      <c r="T16" s="52"/>
+      <c r="N16" s="42"/>
+      <c r="O16" s="43"/>
+      <c r="P16" s="44"/>
+      <c r="R16" s="55"/>
+      <c r="S16" s="56"/>
+      <c r="T16" s="57"/>
     </row>
     <row r="17" spans="4:20" ht="17.25" thickBot="1">
       <c r="D17" s="25"/>
-      <c r="E17" s="77"/>
-      <c r="F17" s="78"/>
-      <c r="G17" s="79"/>
-      <c r="I17" s="64"/>
-      <c r="J17" s="65"/>
-      <c r="K17" s="66"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="46"/>
+      <c r="G17" s="47"/>
+      <c r="I17" s="58"/>
+      <c r="J17" s="59"/>
+      <c r="K17" s="60"/>
       <c r="M17" s="25"/>
-      <c r="N17" s="77"/>
-      <c r="O17" s="78"/>
-      <c r="P17" s="79"/>
-      <c r="R17" s="64"/>
-      <c r="S17" s="65"/>
-      <c r="T17" s="66"/>
+      <c r="N17" s="45"/>
+      <c r="O17" s="46"/>
+      <c r="P17" s="47"/>
+      <c r="R17" s="58"/>
+      <c r="S17" s="59"/>
+      <c r="T17" s="60"/>
     </row>
     <row r="19" spans="4:20" ht="17.25" thickBot="1">
-      <c r="D19" s="36" t="s">
+      <c r="D19" s="68" t="s">
         <v>368</v>
       </c>
-      <c r="E19" s="36"/>
-      <c r="F19" s="36"/>
-      <c r="H19" s="36" t="s">
+      <c r="E19" s="68"/>
+      <c r="F19" s="68"/>
+      <c r="H19" s="68" t="s">
         <v>367</v>
       </c>
-      <c r="I19" s="36"/>
-      <c r="J19" s="36"/>
-      <c r="K19" s="36"/>
-      <c r="R19" s="36" t="s">
+      <c r="I19" s="68"/>
+      <c r="J19" s="68"/>
+      <c r="K19" s="68"/>
+      <c r="R19" s="68" t="s">
         <v>732</v>
       </c>
-      <c r="S19" s="36"/>
-      <c r="T19" s="36"/>
+      <c r="S19" s="68"/>
+      <c r="T19" s="68"/>
     </row>
     <row r="20" spans="4:20">
-      <c r="D20" s="47" t="s">
+      <c r="D20" s="76" t="s">
         <v>729</v>
       </c>
-      <c r="E20" s="48"/>
-      <c r="F20" s="49"/>
+      <c r="E20" s="77"/>
+      <c r="F20" s="78"/>
       <c r="H20" s="26"/>
-      <c r="I20" s="62" t="s">
+      <c r="I20" s="67" t="s">
         <v>725</v>
       </c>
       <c r="J20" s="21"/>
@@ -8933,56 +9025,56 @@
       <c r="N20" s="21"/>
       <c r="O20" s="21"/>
       <c r="P20" s="22"/>
-      <c r="R20" s="47" t="s">
+      <c r="R20" s="76" t="s">
         <v>733</v>
       </c>
-      <c r="S20" s="48"/>
-      <c r="T20" s="49"/>
+      <c r="S20" s="77"/>
+      <c r="T20" s="78"/>
     </row>
     <row r="21" spans="4:20">
-      <c r="D21" s="50"/>
-      <c r="E21" s="51"/>
-      <c r="F21" s="52"/>
+      <c r="D21" s="55"/>
+      <c r="E21" s="56"/>
+      <c r="F21" s="57"/>
       <c r="H21" s="24"/>
-      <c r="I21" s="56"/>
+      <c r="I21" s="49"/>
       <c r="K21" s="23"/>
       <c r="M21" s="24"/>
       <c r="P21" s="23"/>
-      <c r="R21" s="50"/>
-      <c r="S21" s="51"/>
-      <c r="T21" s="52"/>
+      <c r="R21" s="55"/>
+      <c r="S21" s="56"/>
+      <c r="T21" s="57"/>
     </row>
     <row r="22" spans="4:20">
-      <c r="D22" s="50"/>
-      <c r="E22" s="51"/>
-      <c r="F22" s="52"/>
+      <c r="D22" s="55"/>
+      <c r="E22" s="56"/>
+      <c r="F22" s="57"/>
       <c r="H22" s="24"/>
-      <c r="I22" s="43" t="s">
+      <c r="I22" s="50" t="s">
         <v>724</v>
       </c>
-      <c r="J22" s="41" t="s">
+      <c r="J22" s="73" t="s">
         <v>734</v>
       </c>
       <c r="K22" s="23"/>
       <c r="M22" s="24"/>
       <c r="P22" s="23"/>
-      <c r="R22" s="50"/>
-      <c r="S22" s="51"/>
-      <c r="T22" s="52"/>
+      <c r="R22" s="55"/>
+      <c r="S22" s="56"/>
+      <c r="T22" s="57"/>
     </row>
     <row r="23" spans="4:20">
-      <c r="D23" s="53"/>
-      <c r="E23" s="54"/>
-      <c r="F23" s="55"/>
+      <c r="D23" s="64"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="79"/>
       <c r="H23" s="24"/>
-      <c r="I23" s="44"/>
-      <c r="J23" s="42"/>
+      <c r="I23" s="61"/>
+      <c r="J23" s="74"/>
       <c r="K23" s="23"/>
       <c r="M23" s="24"/>
       <c r="P23" s="23"/>
-      <c r="R23" s="53"/>
-      <c r="S23" s="54"/>
-      <c r="T23" s="55"/>
+      <c r="R23" s="64"/>
+      <c r="S23" s="65"/>
+      <c r="T23" s="79"/>
     </row>
     <row r="24" spans="4:20">
       <c r="D24" s="24"/>
@@ -8998,77 +9090,77 @@
     </row>
     <row r="25" spans="4:20" ht="16.5" customHeight="1">
       <c r="D25" s="24"/>
-      <c r="E25" s="43" t="s">
+      <c r="E25" s="50" t="s">
         <v>724</v>
       </c>
       <c r="F25" s="23"/>
-      <c r="H25" s="57" t="s">
+      <c r="H25" s="52" t="s">
         <v>737</v>
       </c>
-      <c r="I25" s="58"/>
-      <c r="J25" s="59"/>
+      <c r="I25" s="53"/>
+      <c r="J25" s="62"/>
       <c r="K25" s="23"/>
       <c r="M25" s="24"/>
       <c r="P25" s="23"/>
       <c r="R25" s="24"/>
-      <c r="S25" s="43" t="s">
+      <c r="S25" s="50" t="s">
         <v>724</v>
       </c>
       <c r="T25" s="23"/>
     </row>
     <row r="26" spans="4:20">
       <c r="D26" s="24"/>
-      <c r="E26" s="44"/>
+      <c r="E26" s="61"/>
       <c r="F26" s="23"/>
-      <c r="H26" s="50"/>
-      <c r="I26" s="51"/>
-      <c r="J26" s="60"/>
+      <c r="H26" s="55"/>
+      <c r="I26" s="56"/>
+      <c r="J26" s="63"/>
       <c r="K26" s="23"/>
       <c r="M26" s="24"/>
       <c r="P26" s="23"/>
       <c r="R26" s="24"/>
-      <c r="S26" s="44"/>
+      <c r="S26" s="61"/>
       <c r="T26" s="23"/>
     </row>
     <row r="27" spans="4:20">
       <c r="D27" s="24"/>
-      <c r="E27" s="45" t="s">
+      <c r="E27" s="48" t="s">
         <v>725</v>
       </c>
       <c r="F27" s="23"/>
-      <c r="H27" s="50"/>
-      <c r="I27" s="51"/>
-      <c r="J27" s="60"/>
-      <c r="K27" s="37" t="s">
+      <c r="H27" s="55"/>
+      <c r="I27" s="56"/>
+      <c r="J27" s="63"/>
+      <c r="K27" s="69" t="s">
         <v>726</v>
       </c>
       <c r="M27" s="24"/>
       <c r="P27" s="23"/>
       <c r="R27" s="24"/>
-      <c r="S27" s="45" t="s">
+      <c r="S27" s="48" t="s">
         <v>725</v>
       </c>
       <c r="T27" s="23"/>
     </row>
     <row r="28" spans="4:20" ht="16.5" customHeight="1">
       <c r="D28" s="24"/>
-      <c r="E28" s="56"/>
+      <c r="E28" s="49"/>
       <c r="F28" s="23"/>
-      <c r="H28" s="53"/>
-      <c r="I28" s="54"/>
-      <c r="J28" s="61"/>
-      <c r="K28" s="38"/>
+      <c r="H28" s="64"/>
+      <c r="I28" s="65"/>
+      <c r="J28" s="66"/>
+      <c r="K28" s="70"/>
       <c r="M28" s="24"/>
       <c r="P28" s="23"/>
       <c r="R28" s="24"/>
-      <c r="S28" s="56"/>
+      <c r="S28" s="49"/>
       <c r="T28" s="23"/>
     </row>
     <row r="29" spans="4:20">
       <c r="D29" s="24"/>
       <c r="F29" s="23"/>
       <c r="H29" s="24"/>
-      <c r="K29" s="39"/>
+      <c r="K29" s="71"/>
       <c r="M29" s="24"/>
       <c r="P29" s="23"/>
       <c r="R29" s="24"/>
@@ -9079,10 +9171,10 @@
       <c r="E30" s="27"/>
       <c r="F30" s="28"/>
       <c r="H30" s="24"/>
-      <c r="I30" s="43" t="s">
+      <c r="I30" s="50" t="s">
         <v>724</v>
       </c>
-      <c r="K30" s="39"/>
+      <c r="K30" s="71"/>
       <c r="M30" s="25"/>
       <c r="N30" s="27"/>
       <c r="O30" s="27"/>
@@ -9093,21 +9185,21 @@
     </row>
     <row r="31" spans="4:20">
       <c r="H31" s="24"/>
-      <c r="I31" s="44"/>
-      <c r="K31" s="39"/>
+      <c r="I31" s="61"/>
+      <c r="K31" s="71"/>
     </row>
     <row r="32" spans="4:20">
       <c r="H32" s="24"/>
-      <c r="I32" s="45" t="s">
+      <c r="I32" s="48" t="s">
         <v>725</v>
       </c>
-      <c r="K32" s="39"/>
+      <c r="K32" s="71"/>
     </row>
     <row r="33" spans="8:24" ht="17.25" thickBot="1">
       <c r="H33" s="25"/>
-      <c r="I33" s="46"/>
+      <c r="I33" s="75"/>
       <c r="J33" s="27"/>
-      <c r="K33" s="40"/>
+      <c r="K33" s="72"/>
     </row>
     <row r="47" spans="8:24">
       <c r="X47" t="s">
@@ -9116,24 +9208,6 @@
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="D7:D13"/>
-    <mergeCell ref="E14:G17"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="I14:K17"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="S11:S12"/>
-    <mergeCell ref="R14:T17"/>
-    <mergeCell ref="M7:M13"/>
-    <mergeCell ref="O9:O10"/>
-    <mergeCell ref="N11:N12"/>
-    <mergeCell ref="N14:P17"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="H25:J28"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="I22:I23"/>
-    <mergeCell ref="J11:J12"/>
     <mergeCell ref="R6:T6"/>
     <mergeCell ref="R19:T19"/>
     <mergeCell ref="D19:F19"/>
@@ -9150,6 +9224,24 @@
     <mergeCell ref="M6:P6"/>
     <mergeCell ref="D20:F23"/>
     <mergeCell ref="E27:E28"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="H25:J28"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="S11:S12"/>
+    <mergeCell ref="R14:T17"/>
+    <mergeCell ref="M7:M13"/>
+    <mergeCell ref="O9:O10"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="N14:P17"/>
+    <mergeCell ref="D7:D13"/>
+    <mergeCell ref="E14:G17"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="I14:K17"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/PLC/IO List.xlsx
+++ b/PLC/IO List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EZENIC\Desktop\Project-Second\PLC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{269B18CA-B154-4D02-8D2B-D6A949600900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A14F4D4F-D5C1-4E7F-AFCC-E03C21C9C9D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{E8A3CD3B-D612-4B37-A180-F6C335096DC9}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="2" xr2:uid="{E8A3CD3B-D612-4B37-A180-F6C335096DC9}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="2" r:id="rId1"/>
@@ -2037,9 +2037,6 @@
     <t>M1088</t>
   </si>
   <si>
-    <t>M1089</t>
-  </si>
-  <si>
     <t>M2100</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2096,9 +2093,6 @@
     <t>M1098</t>
   </si>
   <si>
-    <t>M1099</t>
-  </si>
-  <si>
     <t>M1100</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2127,9 +2121,6 @@
     <t>M1108</t>
   </si>
   <si>
-    <t>M1109</t>
-  </si>
-  <si>
     <t>M1110</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2180,9 +2171,6 @@
     <t>M1128</t>
   </si>
   <si>
-    <t>M1129</t>
-  </si>
-  <si>
     <t>M1130</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2211,9 +2199,6 @@
     <t>M1138</t>
   </si>
   <si>
-    <t>M1139</t>
-  </si>
-  <si>
     <t>M1140</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2242,9 +2227,6 @@
     <t>M1148</t>
   </si>
   <si>
-    <t>M1149</t>
-  </si>
-  <si>
     <t>M1150</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2273,9 +2255,6 @@
     <t>M1158</t>
   </si>
   <si>
-    <t>M1159</t>
-  </si>
-  <si>
     <t>M1160</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2302,9 +2281,6 @@
   </si>
   <si>
     <t>M1168</t>
-  </si>
-  <si>
-    <t>M1169</t>
   </si>
   <si>
     <t>M2110</t>
@@ -2944,6 +2920,32 @@
   </si>
   <si>
     <t>챔버4 완료 후 딜레이</t>
+  </si>
+  <si>
+    <t>M15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M16</t>
+  </si>
+  <si>
+    <t>M17</t>
+  </si>
+  <si>
+    <t>M18</t>
+  </si>
+  <si>
+    <t>챔버1 로봇 경유위치 이동 완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>챔버2 로봇 경유위치 이동 완료</t>
+  </si>
+  <si>
+    <t>챔버3 로봇 경유위치 이동 완료</t>
+  </si>
+  <si>
+    <t>챔버4 로봇 경유위치 이동 완료</t>
   </si>
 </sst>
 </file>
@@ -3471,7 +3473,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3580,6 +3582,99 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3587,6 +3682,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3616,101 +3714,8 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4046,7 +4051,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{228BF0B7-E586-4CC1-BF31-0F024BABECA2}">
-  <dimension ref="B3:K77"/>
+  <dimension ref="B3:K88"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="3" width="9" style="1"/>
@@ -4271,7 +4276,7 @@
         <v>121</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>803</v>
+        <v>795</v>
       </c>
       <c r="I11" s="6" t="s">
         <v>448</v>
@@ -4297,7 +4302,7 @@
         <v>122</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>804</v>
+        <v>796</v>
       </c>
       <c r="I12" s="6" t="s">
         <v>450</v>
@@ -4323,7 +4328,7 @@
         <v>123</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>805</v>
+        <v>797</v>
       </c>
       <c r="I13" s="6" t="s">
         <v>448</v>
@@ -4349,7 +4354,7 @@
         <v>124</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>806</v>
+        <v>798</v>
       </c>
       <c r="I14" s="6" t="s">
         <v>450</v>
@@ -4389,10 +4394,10 @@
         <v>126</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>807</v>
+        <v>799</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>808</v>
+        <v>800</v>
       </c>
       <c r="J16" s="5"/>
       <c r="K16" s="6"/>
@@ -4413,10 +4418,10 @@
         <v>127</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>809</v>
+        <v>801</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>812</v>
+        <v>804</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>509</v>
@@ -4441,10 +4446,10 @@
         <v>52</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>810</v>
+        <v>802</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>813</v>
+        <v>805</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>510</v>
@@ -4471,10 +4476,10 @@
         <v>132</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>811</v>
+        <v>803</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>814</v>
+        <v>806</v>
       </c>
       <c r="J19" s="5" t="s">
         <v>511</v>
@@ -4500,6 +4505,8 @@
       <c r="G20" s="6" t="s">
         <v>133</v>
       </c>
+      <c r="H20" s="5"/>
+      <c r="I20" s="6"/>
       <c r="J20" s="5"/>
       <c r="K20" s="6"/>
     </row>
@@ -4520,6 +4527,8 @@
       <c r="G21" s="6" t="s">
         <v>134</v>
       </c>
+      <c r="H21" s="5"/>
+      <c r="I21" s="6"/>
       <c r="J21" s="5"/>
       <c r="K21" s="6"/>
     </row>
@@ -4540,11 +4549,17 @@
       <c r="G22" s="6" t="s">
         <v>135</v>
       </c>
+      <c r="H22" s="5" t="s">
+        <v>815</v>
+      </c>
+      <c r="I22" s="80" t="s">
+        <v>819</v>
+      </c>
       <c r="J22" s="5" t="s">
-        <v>771</v>
+        <v>763</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>781</v>
+        <v>773</v>
       </c>
     </row>
     <row r="23" spans="2:11">
@@ -4564,11 +4579,17 @@
       <c r="G23" s="6" t="s">
         <v>136</v>
       </c>
+      <c r="H23" s="5" t="s">
+        <v>816</v>
+      </c>
+      <c r="I23" s="80" t="s">
+        <v>820</v>
+      </c>
       <c r="J23" s="5" t="s">
-        <v>772</v>
+        <v>764</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>782</v>
+        <v>774</v>
       </c>
     </row>
     <row r="24" spans="2:11">
@@ -4589,16 +4610,16 @@
         <v>137</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>473</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>474</v>
+        <v>817</v>
+      </c>
+      <c r="I24" s="80" t="s">
+        <v>821</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>773</v>
+        <v>765</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>783</v>
+        <v>775</v>
       </c>
     </row>
     <row r="25" spans="2:11">
@@ -4617,16 +4638,16 @@
         <v>170</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>483</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>475</v>
+        <v>818</v>
+      </c>
+      <c r="I25" s="80" t="s">
+        <v>822</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>774</v>
+        <v>766</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
     </row>
     <row r="26" spans="2:11">
@@ -4644,17 +4665,13 @@
       <c r="G26" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="H26" s="5" t="s">
-        <v>484</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>476</v>
-      </c>
+      <c r="H26" s="5"/>
+      <c r="I26" s="6"/>
       <c r="J26" s="5" t="s">
-        <v>775</v>
+        <v>767</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>785</v>
+        <v>777</v>
       </c>
     </row>
     <row r="27" spans="2:11">
@@ -4672,17 +4689,13 @@
       <c r="G27" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="H27" s="5" t="s">
-        <v>485</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>477</v>
-      </c>
+      <c r="H27" s="5"/>
+      <c r="I27" s="6"/>
       <c r="J27" s="5" t="s">
-        <v>776</v>
+        <v>768</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>786</v>
+        <v>778</v>
       </c>
     </row>
     <row r="28" spans="2:11">
@@ -4702,17 +4715,13 @@
       <c r="G28" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="H28" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>478</v>
-      </c>
+      <c r="H28" s="5"/>
+      <c r="I28" s="6"/>
       <c r="J28" s="5" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>787</v>
+        <v>779</v>
       </c>
     </row>
     <row r="29" spans="2:11">
@@ -4732,17 +4741,13 @@
       <c r="G29" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="H29" s="5" t="s">
-        <v>487</v>
-      </c>
-      <c r="I29" s="6" t="s">
-        <v>479</v>
-      </c>
+      <c r="H29" s="5"/>
+      <c r="I29" s="6"/>
       <c r="J29" s="5" t="s">
-        <v>778</v>
+        <v>770</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>788</v>
+        <v>780</v>
       </c>
     </row>
     <row r="30" spans="2:11">
@@ -4762,17 +4767,13 @@
       <c r="G30" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="H30" s="5" t="s">
-        <v>488</v>
-      </c>
-      <c r="I30" s="6" t="s">
-        <v>480</v>
-      </c>
+      <c r="H30" s="5"/>
+      <c r="I30" s="6"/>
       <c r="J30" s="5" t="s">
-        <v>779</v>
+        <v>771</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>789</v>
+        <v>781</v>
       </c>
     </row>
     <row r="31" spans="2:11">
@@ -4792,17 +4793,13 @@
       <c r="G31" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="H31" s="5" t="s">
-        <v>489</v>
-      </c>
-      <c r="I31" s="6" t="s">
-        <v>481</v>
-      </c>
+      <c r="H31" s="5"/>
+      <c r="I31" s="6"/>
       <c r="J31" s="5" t="s">
-        <v>780</v>
+        <v>772</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>790</v>
+        <v>782</v>
       </c>
     </row>
     <row r="32" spans="2:11">
@@ -4822,12 +4819,8 @@
       <c r="G32" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="H32" s="5" t="s">
-        <v>490</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>482</v>
-      </c>
+      <c r="H32" s="5"/>
+      <c r="I32" s="6"/>
       <c r="J32" s="5"/>
       <c r="K32" s="6"/>
     </row>
@@ -4848,17 +4841,13 @@
       <c r="G33" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="H33" s="5" t="s">
-        <v>491</v>
-      </c>
-      <c r="I33" s="6" t="s">
-        <v>492</v>
-      </c>
+      <c r="H33" s="5"/>
+      <c r="I33" s="6"/>
       <c r="J33" s="5" t="s">
-        <v>815</v>
+        <v>807</v>
       </c>
       <c r="K33" s="6" t="s">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="34" spans="2:11">
@@ -4879,10 +4868,10 @@
       <c r="H34" s="5"/>
       <c r="I34" s="6"/>
       <c r="J34" s="5" t="s">
-        <v>817</v>
+        <v>809</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>820</v>
+        <v>812</v>
       </c>
     </row>
     <row r="35" spans="2:11">
@@ -4900,13 +4889,17 @@
       <c r="G35" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="H35" s="5"/>
-      <c r="I35" s="6"/>
+      <c r="H35" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>474</v>
+      </c>
       <c r="J35" s="5" t="s">
-        <v>818</v>
+        <v>810</v>
       </c>
       <c r="K35" s="6" t="s">
-        <v>821</v>
+        <v>813</v>
       </c>
     </row>
     <row r="36" spans="2:11">
@@ -4924,13 +4917,17 @@
       <c r="G36" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="H36" s="5"/>
-      <c r="I36" s="6"/>
+      <c r="H36" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>475</v>
+      </c>
       <c r="J36" s="5" t="s">
-        <v>819</v>
+        <v>811</v>
       </c>
       <c r="K36" s="6" t="s">
-        <v>822</v>
+        <v>814</v>
       </c>
     </row>
     <row r="37" spans="2:11">
@@ -4948,8 +4945,12 @@
       <c r="G37" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="H37" s="5"/>
-      <c r="I37" s="6"/>
+      <c r="H37" s="5" t="s">
+        <v>484</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>476</v>
+      </c>
       <c r="J37" s="5"/>
       <c r="K37" s="6"/>
     </row>
@@ -4969,10 +4970,10 @@
         <v>183</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>453</v>
+        <v>485</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>456</v>
+        <v>477</v>
       </c>
       <c r="J38" s="5"/>
       <c r="K38" s="6"/>
@@ -4993,10 +4994,10 @@
         <v>184</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>454</v>
+        <v>486</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>455</v>
+        <v>478</v>
       </c>
       <c r="J39" s="5"/>
       <c r="K39" s="6"/>
@@ -5017,10 +5018,10 @@
         <v>185</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>457</v>
+        <v>487</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>465</v>
+        <v>479</v>
       </c>
       <c r="J40" s="5"/>
       <c r="K40" s="6"/>
@@ -5041,10 +5042,10 @@
         <v>186</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>458</v>
+        <v>488</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>466</v>
+        <v>480</v>
       </c>
       <c r="J41" s="5"/>
       <c r="K41" s="6"/>
@@ -5065,10 +5066,10 @@
         <v>187</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>459</v>
+        <v>489</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>467</v>
+        <v>481</v>
       </c>
       <c r="J42" s="5"/>
       <c r="K42" s="6"/>
@@ -5089,10 +5090,10 @@
         <v>188</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>460</v>
+        <v>490</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>468</v>
+        <v>482</v>
       </c>
       <c r="J43" s="5"/>
       <c r="K43" s="6"/>
@@ -5113,10 +5114,10 @@
         <v>189</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>461</v>
+        <v>491</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>469</v>
+        <v>492</v>
       </c>
       <c r="J44" s="5"/>
       <c r="K44" s="6"/>
@@ -5136,12 +5137,8 @@
       <c r="G45" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="H45" s="5" t="s">
-        <v>462</v>
-      </c>
-      <c r="I45" s="6" t="s">
-        <v>470</v>
-      </c>
+      <c r="H45" s="5"/>
+      <c r="I45" s="6"/>
       <c r="J45" s="5"/>
       <c r="K45" s="6"/>
     </row>
@@ -5160,12 +5157,8 @@
       <c r="G46" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="H46" s="5" t="s">
-        <v>463</v>
-      </c>
-      <c r="I46" s="6" t="s">
-        <v>471</v>
-      </c>
+      <c r="H46" s="5"/>
+      <c r="I46" s="6"/>
       <c r="J46" s="5"/>
       <c r="K46" s="6"/>
     </row>
@@ -5184,12 +5177,8 @@
       <c r="G47" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="H47" s="5" t="s">
-        <v>464</v>
-      </c>
-      <c r="I47" s="6" t="s">
-        <v>472</v>
-      </c>
+      <c r="H47" s="5"/>
+      <c r="I47" s="6"/>
       <c r="J47" s="5"/>
       <c r="K47" s="6"/>
     </row>
@@ -5225,10 +5214,10 @@
         <v>194</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>761</v>
+        <v>453</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>770</v>
+        <v>456</v>
       </c>
       <c r="J49" s="5"/>
       <c r="K49" s="6"/>
@@ -5245,10 +5234,10 @@
         <v>195</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>762</v>
+        <v>454</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>794</v>
+        <v>455</v>
       </c>
       <c r="J50" s="5"/>
       <c r="K50" s="6"/>
@@ -5265,10 +5254,10 @@
         <v>196</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>763</v>
+        <v>457</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>795</v>
+        <v>465</v>
       </c>
       <c r="J51" s="5"/>
       <c r="K51" s="6"/>
@@ -5287,10 +5276,10 @@
         <v>375</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>764</v>
+        <v>458</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>796</v>
+        <v>466</v>
       </c>
       <c r="J52" s="5"/>
       <c r="K52" s="6"/>
@@ -5309,10 +5298,10 @@
         <v>376</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>765</v>
+        <v>459</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>802</v>
+        <v>467</v>
       </c>
       <c r="J53" s="5"/>
       <c r="K53" s="6"/>
@@ -5331,10 +5320,10 @@
         <v>377</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>766</v>
+        <v>460</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>797</v>
+        <v>468</v>
       </c>
       <c r="J54" s="5"/>
       <c r="K54" s="6"/>
@@ -5353,10 +5342,10 @@
         <v>378</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>767</v>
+        <v>461</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>798</v>
+        <v>469</v>
       </c>
       <c r="J55" s="5"/>
       <c r="K55" s="6"/>
@@ -5375,10 +5364,10 @@
         <v>379</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>768</v>
+        <v>462</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>799</v>
+        <v>470</v>
       </c>
       <c r="J56" s="5"/>
       <c r="K56" s="6"/>
@@ -5397,10 +5386,10 @@
         <v>380</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>769</v>
+        <v>463</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>800</v>
+        <v>471</v>
       </c>
       <c r="J57" s="5"/>
       <c r="K57" s="6"/>
@@ -5409,10 +5398,10 @@
       <c r="F58" s="5"/>
       <c r="G58" s="6"/>
       <c r="H58" s="5" t="s">
-        <v>791</v>
+        <v>464</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>801</v>
+        <v>472</v>
       </c>
       <c r="J58" s="6"/>
       <c r="K58" s="6"/>
@@ -5428,24 +5417,36 @@
     <row r="60" spans="2:11">
       <c r="F60" s="5"/>
       <c r="G60" s="6"/>
-      <c r="H60" s="5"/>
-      <c r="I60" s="6"/>
+      <c r="H60" s="5" t="s">
+        <v>753</v>
+      </c>
+      <c r="I60" s="6" t="s">
+        <v>762</v>
+      </c>
       <c r="J60" s="6"/>
       <c r="K60" s="6"/>
     </row>
     <row r="61" spans="2:11">
       <c r="F61" s="5"/>
       <c r="G61" s="6"/>
-      <c r="H61" s="5"/>
-      <c r="I61" s="6"/>
+      <c r="H61" s="5" t="s">
+        <v>754</v>
+      </c>
+      <c r="I61" s="6" t="s">
+        <v>786</v>
+      </c>
       <c r="J61" s="6"/>
       <c r="K61" s="6"/>
     </row>
     <row r="62" spans="2:11">
       <c r="F62" s="5"/>
       <c r="G62" s="6"/>
-      <c r="H62" s="5"/>
-      <c r="I62" s="6"/>
+      <c r="H62" s="5" t="s">
+        <v>755</v>
+      </c>
+      <c r="I62" s="6" t="s">
+        <v>787</v>
+      </c>
       <c r="J62" s="6"/>
       <c r="K62" s="6"/>
     </row>
@@ -5453,10 +5454,10 @@
       <c r="F63" s="5"/>
       <c r="G63" s="6"/>
       <c r="H63" s="5" t="s">
-        <v>738</v>
+        <v>756</v>
       </c>
       <c r="I63" s="6" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="J63" s="6"/>
       <c r="K63" s="6"/>
@@ -5465,10 +5466,10 @@
       <c r="F64" s="5"/>
       <c r="G64" s="6"/>
       <c r="H64" s="5" t="s">
-        <v>739</v>
+        <v>757</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>753</v>
+        <v>794</v>
       </c>
       <c r="J64" s="6"/>
       <c r="K64" s="6"/>
@@ -5477,10 +5478,10 @@
       <c r="F65" s="5"/>
       <c r="G65" s="6"/>
       <c r="H65" s="5" t="s">
-        <v>740</v>
+        <v>758</v>
       </c>
       <c r="I65" s="6" t="s">
-        <v>754</v>
+        <v>789</v>
       </c>
       <c r="J65" s="6"/>
       <c r="K65" s="6"/>
@@ -5489,10 +5490,10 @@
       <c r="F66" s="5"/>
       <c r="G66" s="6"/>
       <c r="H66" s="5" t="s">
-        <v>741</v>
+        <v>759</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>755</v>
+        <v>790</v>
       </c>
       <c r="J66" s="6"/>
       <c r="K66" s="6"/>
@@ -5501,10 +5502,10 @@
       <c r="F67" s="5"/>
       <c r="G67" s="6"/>
       <c r="H67" s="5" t="s">
-        <v>742</v>
+        <v>760</v>
       </c>
       <c r="I67" s="6" t="s">
-        <v>756</v>
+        <v>791</v>
       </c>
       <c r="J67" s="6"/>
       <c r="K67" s="6"/>
@@ -5513,10 +5514,10 @@
       <c r="F68" s="5"/>
       <c r="G68" s="6"/>
       <c r="H68" s="5" t="s">
-        <v>743</v>
+        <v>761</v>
       </c>
       <c r="I68" s="6" t="s">
-        <v>757</v>
+        <v>792</v>
       </c>
       <c r="J68" s="6"/>
       <c r="K68" s="6"/>
@@ -5525,10 +5526,10 @@
       <c r="F69" s="5"/>
       <c r="G69" s="6"/>
       <c r="H69" s="5" t="s">
-        <v>744</v>
+        <v>783</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>758</v>
+        <v>793</v>
       </c>
       <c r="J69" s="6"/>
       <c r="K69" s="6"/>
@@ -5536,48 +5537,32 @@
     <row r="70" spans="6:11">
       <c r="F70" s="5"/>
       <c r="G70" s="6"/>
-      <c r="H70" s="5" t="s">
-        <v>745</v>
-      </c>
-      <c r="I70" s="6" t="s">
-        <v>759</v>
-      </c>
+      <c r="H70" s="5"/>
+      <c r="I70" s="6"/>
       <c r="J70" s="6"/>
       <c r="K70" s="6"/>
     </row>
     <row r="71" spans="6:11">
       <c r="F71" s="5"/>
       <c r="G71" s="6"/>
-      <c r="H71" s="5" t="s">
-        <v>746</v>
-      </c>
-      <c r="I71" s="6" t="s">
-        <v>760</v>
-      </c>
+      <c r="H71" s="5"/>
+      <c r="I71" s="6"/>
       <c r="J71" s="6"/>
       <c r="K71" s="6"/>
     </row>
     <row r="72" spans="6:11">
       <c r="F72" s="5"/>
       <c r="G72" s="6"/>
-      <c r="H72" s="5" t="s">
-        <v>747</v>
-      </c>
-      <c r="I72" s="6" t="s">
-        <v>752</v>
-      </c>
+      <c r="H72" s="5"/>
+      <c r="I72" s="6"/>
       <c r="J72" s="6"/>
       <c r="K72" s="6"/>
     </row>
     <row r="73" spans="6:11">
       <c r="F73" s="5"/>
       <c r="G73" s="6"/>
-      <c r="H73" s="5" t="s">
-        <v>748</v>
-      </c>
-      <c r="I73" s="6" t="s">
-        <v>753</v>
-      </c>
+      <c r="H73" s="5"/>
+      <c r="I73" s="6"/>
       <c r="J73" s="6"/>
       <c r="K73" s="6"/>
     </row>
@@ -5585,10 +5570,10 @@
       <c r="F74" s="5"/>
       <c r="G74" s="6"/>
       <c r="H74" s="5" t="s">
-        <v>749</v>
+        <v>730</v>
       </c>
       <c r="I74" s="6" t="s">
-        <v>754</v>
+        <v>744</v>
       </c>
       <c r="J74" s="6"/>
       <c r="K74" s="6"/>
@@ -5597,10 +5582,10 @@
       <c r="F75" s="5"/>
       <c r="G75" s="6"/>
       <c r="H75" s="5" t="s">
-        <v>750</v>
+        <v>731</v>
       </c>
       <c r="I75" s="6" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="J75" s="6"/>
       <c r="K75" s="6"/>
@@ -5609,10 +5594,10 @@
       <c r="F76" s="5"/>
       <c r="G76" s="6"/>
       <c r="H76" s="5" t="s">
-        <v>751</v>
+        <v>732</v>
       </c>
       <c r="I76" s="6" t="s">
-        <v>753</v>
+        <v>746</v>
       </c>
       <c r="J76" s="6"/>
       <c r="K76" s="6"/>
@@ -5620,12 +5605,100 @@
     <row r="77" spans="6:11">
       <c r="F77" s="5"/>
       <c r="G77" s="6"/>
-      <c r="H77" s="5"/>
+      <c r="H77" s="5" t="s">
+        <v>733</v>
+      </c>
       <c r="I77" s="6" t="s">
-        <v>754</v>
+        <v>747</v>
       </c>
       <c r="J77" s="6"/>
       <c r="K77" s="6"/>
+    </row>
+    <row r="78" spans="6:11">
+      <c r="H78" s="5" t="s">
+        <v>734</v>
+      </c>
+      <c r="I78" s="6" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="79" spans="6:11">
+      <c r="H79" s="5" t="s">
+        <v>735</v>
+      </c>
+      <c r="I79" s="6" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="80" spans="6:11">
+      <c r="H80" s="5" t="s">
+        <v>736</v>
+      </c>
+      <c r="I80" s="6" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="81" spans="8:9">
+      <c r="H81" s="5" t="s">
+        <v>737</v>
+      </c>
+      <c r="I81" s="6" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="82" spans="8:9">
+      <c r="H82" s="5" t="s">
+        <v>738</v>
+      </c>
+      <c r="I82" s="6" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="83" spans="8:9">
+      <c r="H83" s="5" t="s">
+        <v>739</v>
+      </c>
+      <c r="I83" s="6" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="84" spans="8:9">
+      <c r="H84" s="5" t="s">
+        <v>740</v>
+      </c>
+      <c r="I84" s="6" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="85" spans="8:9">
+      <c r="H85" s="5" t="s">
+        <v>741</v>
+      </c>
+      <c r="I85" s="6" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="86" spans="8:9">
+      <c r="H86" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="I86" s="6" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="87" spans="8:9">
+      <c r="H87" s="5" t="s">
+        <v>743</v>
+      </c>
+      <c r="I87" s="6" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="88" spans="8:9">
+      <c r="H88" s="5"/>
+      <c r="I88" s="6" t="s">
+        <v>746</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -5834,7 +5907,7 @@
         <v>57</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>20</v>
@@ -5843,7 +5916,7 @@
         <v>67</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="M7" s="6" t="s">
         <v>7</v>
@@ -5852,7 +5925,7 @@
         <v>74</v>
       </c>
       <c r="O7" s="5" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="P7" s="6" t="s">
         <v>20</v>
@@ -5861,7 +5934,7 @@
         <v>199</v>
       </c>
       <c r="T7" s="5" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="U7" s="6" t="s">
         <v>7</v>
@@ -5870,7 +5943,7 @@
         <v>205</v>
       </c>
       <c r="W7" s="5" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="X7" s="6" t="s">
         <v>20</v>
@@ -5890,7 +5963,7 @@
         <v>58</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>13</v>
@@ -5899,7 +5972,7 @@
         <v>68</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="M8" s="6" t="s">
         <v>8</v>
@@ -5908,7 +5981,7 @@
         <v>75</v>
       </c>
       <c r="O8" s="5" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="P8" s="6" t="s">
         <v>13</v>
@@ -5917,7 +5990,7 @@
         <v>347</v>
       </c>
       <c r="T8" s="5" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="U8" s="6" t="s">
         <v>8</v>
@@ -5926,7 +5999,7 @@
         <v>236</v>
       </c>
       <c r="W8" s="5" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="X8" s="6" t="s">
         <v>13</v>
@@ -5946,7 +6019,7 @@
         <v>59</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>14</v>
@@ -5955,7 +6028,7 @@
         <v>69</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="M9" s="10" t="s">
         <v>16</v>
@@ -5964,7 +6037,7 @@
         <v>76</v>
       </c>
       <c r="O9" s="5" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="P9" s="6" t="s">
         <v>14</v>
@@ -5973,7 +6046,7 @@
         <v>238</v>
       </c>
       <c r="T9" s="9" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="U9" s="10" t="s">
         <v>16</v>
@@ -5982,7 +6055,7 @@
         <v>237</v>
       </c>
       <c r="W9" s="5" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="X9" s="6" t="s">
         <v>14</v>
@@ -6002,7 +6075,7 @@
         <v>60</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H10" s="10" t="s">
         <v>12</v>
@@ -6011,7 +6084,7 @@
         <v>70</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="M10" s="10" t="s">
         <v>17</v>
@@ -6020,7 +6093,7 @@
         <v>77</v>
       </c>
       <c r="O10" s="9" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="P10" s="10" t="s">
         <v>12</v>
@@ -6029,7 +6102,7 @@
         <v>232</v>
       </c>
       <c r="T10" s="9" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="U10" s="10" t="s">
         <v>17</v>
@@ -6038,7 +6111,7 @@
         <v>233</v>
       </c>
       <c r="W10" s="9" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="X10" s="10" t="s">
         <v>12</v>
@@ -6058,7 +6131,7 @@
         <v>61</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H11" s="10" t="s">
         <v>11</v>
@@ -6067,7 +6140,7 @@
         <v>71</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="M11" s="6" t="s">
         <v>18</v>
@@ -6076,7 +6149,7 @@
         <v>78</v>
       </c>
       <c r="O11" s="9" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="P11" s="10" t="s">
         <v>11</v>
@@ -6085,7 +6158,7 @@
         <v>234</v>
       </c>
       <c r="T11" s="5" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="U11" s="6" t="s">
         <v>18</v>
@@ -6094,7 +6167,7 @@
         <v>235</v>
       </c>
       <c r="W11" s="9" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="X11" s="10" t="s">
         <v>11</v>
@@ -6110,31 +6183,31 @@
       <c r="E12" s="10"/>
       <c r="F12" s="9"/>
       <c r="G12" s="9" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H12" s="10"/>
       <c r="K12" s="9" t="s">
         <v>72</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="M12" s="10"/>
       <c r="N12" s="9"/>
       <c r="O12" s="9" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="P12" s="10"/>
       <c r="S12" s="9" t="s">
         <v>202</v>
       </c>
       <c r="T12" s="9" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="U12" s="10"/>
       <c r="V12" s="9"/>
       <c r="W12" s="9" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="X12" s="10"/>
     </row>
@@ -6152,7 +6225,7 @@
         <v>62</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H13" s="10" t="s">
         <v>15</v>
@@ -6161,7 +6234,7 @@
         <v>197</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="M13" s="10" t="s">
         <v>22</v>
@@ -6170,7 +6243,7 @@
         <v>79</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="P13" s="10" t="s">
         <v>15</v>
@@ -6179,7 +6252,7 @@
         <v>203</v>
       </c>
       <c r="T13" s="9" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="U13" s="10" t="s">
         <v>22</v>
@@ -6188,7 +6261,7 @@
         <v>206</v>
       </c>
       <c r="W13" s="9" t="s">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="X13" s="10" t="s">
         <v>15</v>
@@ -6208,7 +6281,7 @@
         <v>63</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H14" s="10" t="s">
         <v>23</v>
@@ -6217,7 +6290,7 @@
         <v>346</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="M14" s="10" t="s">
         <v>21</v>
@@ -6226,7 +6299,7 @@
         <v>80</v>
       </c>
       <c r="O14" s="9" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="P14" s="10" t="s">
         <v>23</v>
@@ -6235,7 +6308,7 @@
         <v>204</v>
       </c>
       <c r="T14" s="9" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="U14" s="10" t="s">
         <v>21</v>
@@ -6244,7 +6317,7 @@
         <v>207</v>
       </c>
       <c r="W14" s="9" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="X14" s="10" t="s">
         <v>23</v>
@@ -6264,7 +6337,7 @@
         <v>64</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H15" s="10" t="s">
         <v>24</v>
@@ -6273,7 +6346,7 @@
         <v>349</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="M15" s="6" t="s">
         <v>19</v>
@@ -6282,7 +6355,7 @@
         <v>198</v>
       </c>
       <c r="O15" s="9" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="P15" s="10" t="s">
         <v>24</v>
@@ -6291,7 +6364,7 @@
         <v>350</v>
       </c>
       <c r="T15" s="5" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="U15" s="6" t="s">
         <v>19</v>
@@ -6300,7 +6373,7 @@
         <v>208</v>
       </c>
       <c r="W15" s="9" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
       <c r="X15" s="10" t="s">
         <v>24</v>
@@ -6310,9 +6383,7 @@
       <c r="C16" s="5" t="s">
         <v>386</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>544</v>
-      </c>
+      <c r="D16" s="5"/>
       <c r="E16" s="6" t="s">
         <v>387</v>
       </c>
@@ -6322,9 +6393,7 @@
       <c r="K16" s="5" t="s">
         <v>388</v>
       </c>
-      <c r="L16" s="5" t="s">
-        <v>563</v>
-      </c>
+      <c r="L16" s="5"/>
       <c r="M16" s="6" t="s">
         <v>387</v>
       </c>
@@ -6334,9 +6403,7 @@
       <c r="S16" s="5" t="s">
         <v>389</v>
       </c>
-      <c r="T16" s="5" t="s">
-        <v>573</v>
-      </c>
+      <c r="T16" s="5"/>
       <c r="U16" s="6" t="s">
         <v>387</v>
       </c>
@@ -6537,7 +6604,7 @@
         <v>215</v>
       </c>
       <c r="L27" s="5" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="M27" s="6" t="s">
         <v>7</v>
@@ -6546,7 +6613,7 @@
         <v>222</v>
       </c>
       <c r="O27" s="5" t="s">
-        <v>655</v>
+        <v>647</v>
       </c>
       <c r="P27" s="6" t="s">
         <v>20</v>
@@ -6555,7 +6622,7 @@
         <v>268</v>
       </c>
       <c r="T27" s="5" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="U27" s="6" t="s">
         <v>7</v>
@@ -6564,7 +6631,7 @@
         <v>228</v>
       </c>
       <c r="W27" s="5" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
       <c r="X27" s="6" t="s">
         <v>20</v>
@@ -6578,7 +6645,7 @@
         <v>261</v>
       </c>
       <c r="L28" s="5" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="M28" s="6" t="s">
         <v>8</v>
@@ -6587,7 +6654,7 @@
         <v>223</v>
       </c>
       <c r="O28" s="5" t="s">
-        <v>656</v>
+        <v>648</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>13</v>
@@ -6596,7 +6663,7 @@
         <v>333</v>
       </c>
       <c r="T28" s="5" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="U28" s="6" t="s">
         <v>8</v>
@@ -6605,7 +6672,7 @@
         <v>321</v>
       </c>
       <c r="W28" s="5" t="s">
-        <v>665</v>
+        <v>657</v>
       </c>
       <c r="X28" s="6" t="s">
         <v>13</v>
@@ -6619,7 +6686,7 @@
         <v>262</v>
       </c>
       <c r="L29" s="9" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="M29" s="10" t="s">
         <v>16</v>
@@ -6628,7 +6695,7 @@
         <v>224</v>
       </c>
       <c r="O29" s="5" t="s">
-        <v>657</v>
+        <v>649</v>
       </c>
       <c r="P29" s="6" t="s">
         <v>14</v>
@@ -6637,7 +6704,7 @@
         <v>334</v>
       </c>
       <c r="T29" s="9" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="U29" s="10" t="s">
         <v>16</v>
@@ -6646,7 +6713,7 @@
         <v>240</v>
       </c>
       <c r="W29" s="5" t="s">
-        <v>666</v>
+        <v>658</v>
       </c>
       <c r="X29" s="6" t="s">
         <v>14</v>
@@ -6660,7 +6727,7 @@
         <v>263</v>
       </c>
       <c r="L30" s="9" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="M30" s="10" t="s">
         <v>17</v>
@@ -6669,7 +6736,7 @@
         <v>225</v>
       </c>
       <c r="O30" s="9" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="P30" s="10" t="s">
         <v>12</v>
@@ -6678,7 +6745,7 @@
         <v>335</v>
       </c>
       <c r="T30" s="9" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="U30" s="10" t="s">
         <v>17</v>
@@ -6687,7 +6754,7 @@
         <v>241</v>
       </c>
       <c r="W30" s="9" t="s">
-        <v>667</v>
+        <v>659</v>
       </c>
       <c r="X30" s="10" t="s">
         <v>12</v>
@@ -6701,7 +6768,7 @@
         <v>264</v>
       </c>
       <c r="L31" s="5" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="M31" s="6" t="s">
         <v>18</v>
@@ -6710,7 +6777,7 @@
         <v>226</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="P31" s="10" t="s">
         <v>11</v>
@@ -6719,7 +6786,7 @@
         <v>336</v>
       </c>
       <c r="T31" s="5" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="U31" s="6" t="s">
         <v>18</v>
@@ -6728,7 +6795,7 @@
         <v>242</v>
       </c>
       <c r="W31" s="9" t="s">
-        <v>668</v>
+        <v>660</v>
       </c>
       <c r="X31" s="10" t="s">
         <v>11</v>
@@ -6742,24 +6809,24 @@
         <v>265</v>
       </c>
       <c r="L32" s="9" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="M32" s="10"/>
       <c r="N32" s="9"/>
       <c r="O32" s="9" t="s">
-        <v>660</v>
+        <v>652</v>
       </c>
       <c r="P32" s="10"/>
       <c r="S32" s="9" t="s">
         <v>337</v>
       </c>
       <c r="T32" s="9" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="U32" s="10"/>
       <c r="V32" s="9"/>
       <c r="W32" s="9" t="s">
-        <v>669</v>
+        <v>661</v>
       </c>
       <c r="X32" s="10"/>
     </row>
@@ -6771,7 +6838,7 @@
         <v>266</v>
       </c>
       <c r="L33" s="9" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="M33" s="10" t="s">
         <v>22</v>
@@ -6780,7 +6847,7 @@
         <v>227</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>661</v>
+        <v>653</v>
       </c>
       <c r="P33" s="10" t="s">
         <v>15</v>
@@ -6789,7 +6856,7 @@
         <v>338</v>
       </c>
       <c r="T33" s="9" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="U33" s="10" t="s">
         <v>22</v>
@@ -6798,7 +6865,7 @@
         <v>229</v>
       </c>
       <c r="W33" s="9" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="X33" s="10" t="s">
         <v>15</v>
@@ -6812,7 +6879,7 @@
         <v>267</v>
       </c>
       <c r="L34" s="9" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="M34" s="10" t="s">
         <v>21</v>
@@ -6821,7 +6888,7 @@
         <v>239</v>
       </c>
       <c r="O34" s="9" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
       <c r="P34" s="10" t="s">
         <v>23</v>
@@ -6830,7 +6897,7 @@
         <v>339</v>
       </c>
       <c r="T34" s="9" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="U34" s="10" t="s">
         <v>21</v>
@@ -6839,7 +6906,7 @@
         <v>230</v>
       </c>
       <c r="W34" s="9" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="X34" s="10" t="s">
         <v>23</v>
@@ -6853,7 +6920,7 @@
         <v>268</v>
       </c>
       <c r="L35" s="5" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="M35" s="6" t="s">
         <v>19</v>
@@ -6862,7 +6929,7 @@
         <v>221</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>663</v>
+        <v>655</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>24</v>
@@ -6871,7 +6938,7 @@
         <v>352</v>
       </c>
       <c r="T35" s="5" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="U35" s="6" t="s">
         <v>19</v>
@@ -6880,7 +6947,7 @@
         <v>231</v>
       </c>
       <c r="W35" s="9" t="s">
-        <v>672</v>
+        <v>664</v>
       </c>
       <c r="X35" s="10" t="s">
         <v>24</v>
@@ -6893,9 +6960,7 @@
       <c r="K36" s="5" t="s">
         <v>333</v>
       </c>
-      <c r="L36" s="5" t="s">
-        <v>590</v>
-      </c>
+      <c r="L36" s="5"/>
       <c r="M36" s="6" t="s">
         <v>387</v>
       </c>
@@ -6905,9 +6970,7 @@
       <c r="S36" s="5" t="s">
         <v>391</v>
       </c>
-      <c r="T36" s="5" t="s">
-        <v>600</v>
-      </c>
+      <c r="T36" s="5"/>
       <c r="U36" s="6" t="s">
         <v>387</v>
       </c>
@@ -7117,7 +7180,7 @@
         <v>269</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>7</v>
@@ -7126,7 +7189,7 @@
         <v>243</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>673</v>
+        <v>665</v>
       </c>
       <c r="H46" s="6" t="s">
         <v>20</v>
@@ -7137,7 +7200,7 @@
         <v>277</v>
       </c>
       <c r="L46" s="5" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="M46" s="6" t="s">
         <v>7</v>
@@ -7146,7 +7209,7 @@
         <v>251</v>
       </c>
       <c r="O46" s="5" t="s">
-        <v>682</v>
+        <v>674</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>20</v>
@@ -7156,7 +7219,7 @@
         <v>280</v>
       </c>
       <c r="T46" s="5" t="s">
-        <v>621</v>
+        <v>614</v>
       </c>
       <c r="U46" s="6" t="s">
         <v>7</v>
@@ -7165,7 +7228,7 @@
         <v>258</v>
       </c>
       <c r="W46" s="5" t="s">
-        <v>691</v>
+        <v>683</v>
       </c>
       <c r="X46" s="6" t="s">
         <v>20</v>
@@ -7177,7 +7240,7 @@
         <v>270</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="E47" s="6" t="s">
         <v>8</v>
@@ -7186,7 +7249,7 @@
         <v>244</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="H47" s="6" t="s">
         <v>13</v>
@@ -7197,7 +7260,7 @@
         <v>328</v>
       </c>
       <c r="L47" s="5" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="M47" s="6" t="s">
         <v>8</v>
@@ -7206,7 +7269,7 @@
         <v>252</v>
       </c>
       <c r="O47" s="5" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="P47" s="6" t="s">
         <v>13</v>
@@ -7216,7 +7279,7 @@
         <v>281</v>
       </c>
       <c r="T47" s="5" t="s">
-        <v>622</v>
+        <v>615</v>
       </c>
       <c r="U47" s="6" t="s">
         <v>8</v>
@@ -7225,7 +7288,7 @@
         <v>323</v>
       </c>
       <c r="W47" s="5" t="s">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="X47" s="6" t="s">
         <v>13</v>
@@ -7237,7 +7300,7 @@
         <v>271</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="E48" s="10" t="s">
         <v>16</v>
@@ -7246,7 +7309,7 @@
         <v>245</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>675</v>
+        <v>667</v>
       </c>
       <c r="H48" s="6" t="s">
         <v>14</v>
@@ -7257,7 +7320,7 @@
         <v>329</v>
       </c>
       <c r="L48" s="9" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="M48" s="10" t="s">
         <v>16</v>
@@ -7266,7 +7329,7 @@
         <v>253</v>
       </c>
       <c r="O48" s="5" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>14</v>
@@ -7276,7 +7339,7 @@
         <v>282</v>
       </c>
       <c r="T48" s="9" t="s">
-        <v>623</v>
+        <v>616</v>
       </c>
       <c r="U48" s="10" t="s">
         <v>16</v>
@@ -7285,7 +7348,7 @@
         <v>324</v>
       </c>
       <c r="W48" s="5" t="s">
-        <v>693</v>
+        <v>685</v>
       </c>
       <c r="X48" s="6" t="s">
         <v>14</v>
@@ -7297,7 +7360,7 @@
         <v>272</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>17</v>
@@ -7306,7 +7369,7 @@
         <v>246</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="H49" s="10" t="s">
         <v>12</v>
@@ -7317,7 +7380,7 @@
         <v>330</v>
       </c>
       <c r="L49" s="9" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="M49" s="10" t="s">
         <v>17</v>
@@ -7326,7 +7389,7 @@
         <v>254</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>685</v>
+        <v>677</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>12</v>
@@ -7336,7 +7399,7 @@
         <v>283</v>
       </c>
       <c r="T49" s="9" t="s">
-        <v>624</v>
+        <v>617</v>
       </c>
       <c r="U49" s="10" t="s">
         <v>17</v>
@@ -7345,7 +7408,7 @@
         <v>325</v>
       </c>
       <c r="W49" s="9" t="s">
-        <v>694</v>
+        <v>686</v>
       </c>
       <c r="X49" s="10" t="s">
         <v>12</v>
@@ -7357,7 +7420,7 @@
         <v>273</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>18</v>
@@ -7366,7 +7429,7 @@
         <v>247</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
       <c r="H50" s="10" t="s">
         <v>11</v>
@@ -7377,7 +7440,7 @@
         <v>331</v>
       </c>
       <c r="L50" s="5" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="M50" s="6" t="s">
         <v>18</v>
@@ -7386,7 +7449,7 @@
         <v>255</v>
       </c>
       <c r="O50" s="9" t="s">
-        <v>686</v>
+        <v>678</v>
       </c>
       <c r="P50" s="10" t="s">
         <v>11</v>
@@ -7396,7 +7459,7 @@
         <v>284</v>
       </c>
       <c r="T50" s="5" t="s">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="U50" s="6" t="s">
         <v>18</v>
@@ -7405,7 +7468,7 @@
         <v>326</v>
       </c>
       <c r="W50" s="9" t="s">
-        <v>695</v>
+        <v>687</v>
       </c>
       <c r="X50" s="10" t="s">
         <v>11</v>
@@ -7417,12 +7480,12 @@
         <v>274</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="E51" s="10"/>
       <c r="F51" s="9"/>
       <c r="G51" s="9" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="H51" s="10"/>
       <c r="I51" s="7"/>
@@ -7431,12 +7494,12 @@
         <v>332</v>
       </c>
       <c r="L51" s="9" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="M51" s="10"/>
       <c r="N51" s="9"/>
       <c r="O51" s="9" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="P51" s="10"/>
       <c r="Q51" s="8"/>
@@ -7444,12 +7507,12 @@
         <v>285</v>
       </c>
       <c r="T51" s="9" t="s">
-        <v>626</v>
+        <v>619</v>
       </c>
       <c r="U51" s="10"/>
       <c r="V51" s="9"/>
       <c r="W51" s="9" t="s">
-        <v>696</v>
+        <v>688</v>
       </c>
       <c r="X51" s="10"/>
     </row>
@@ -7459,7 +7522,7 @@
         <v>275</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="E52" s="10" t="s">
         <v>22</v>
@@ -7468,7 +7531,7 @@
         <v>248</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>679</v>
+        <v>671</v>
       </c>
       <c r="H52" s="10" t="s">
         <v>15</v>
@@ -7479,7 +7542,7 @@
         <v>278</v>
       </c>
       <c r="L52" s="9" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="M52" s="10" t="s">
         <v>22</v>
@@ -7488,7 +7551,7 @@
         <v>256</v>
       </c>
       <c r="O52" s="9" t="s">
-        <v>688</v>
+        <v>680</v>
       </c>
       <c r="P52" s="10" t="s">
         <v>15</v>
@@ -7498,7 +7561,7 @@
         <v>286</v>
       </c>
       <c r="T52" s="9" t="s">
-        <v>627</v>
+        <v>620</v>
       </c>
       <c r="U52" s="10" t="s">
         <v>22</v>
@@ -7507,7 +7570,7 @@
         <v>327</v>
       </c>
       <c r="W52" s="9" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="X52" s="10" t="s">
         <v>15</v>
@@ -7519,7 +7582,7 @@
         <v>276</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>21</v>
@@ -7528,7 +7591,7 @@
         <v>249</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>680</v>
+        <v>672</v>
       </c>
       <c r="H53" s="10" t="s">
         <v>23</v>
@@ -7539,7 +7602,7 @@
         <v>279</v>
       </c>
       <c r="L53" s="9" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="M53" s="10" t="s">
         <v>21</v>
@@ -7548,7 +7611,7 @@
         <v>322</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>689</v>
+        <v>681</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>23</v>
@@ -7558,7 +7621,7 @@
         <v>287</v>
       </c>
       <c r="T53" s="9" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="U53" s="10" t="s">
         <v>21</v>
@@ -7567,7 +7630,7 @@
         <v>259</v>
       </c>
       <c r="W53" s="9" t="s">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="X53" s="10" t="s">
         <v>23</v>
@@ -7579,7 +7642,7 @@
         <v>277</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>19</v>
@@ -7588,7 +7651,7 @@
         <v>250</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
       <c r="H54" s="10" t="s">
         <v>24</v>
@@ -7599,7 +7662,7 @@
         <v>280</v>
       </c>
       <c r="L54" s="5" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="M54" s="6" t="s">
         <v>19</v>
@@ -7608,7 +7671,7 @@
         <v>257</v>
       </c>
       <c r="O54" s="9" t="s">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="P54" s="10" t="s">
         <v>24</v>
@@ -7618,7 +7681,7 @@
         <v>348</v>
       </c>
       <c r="T54" s="5" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
       <c r="U54" s="6" t="s">
         <v>19</v>
@@ -7627,7 +7690,7 @@
         <v>260</v>
       </c>
       <c r="W54" s="9" t="s">
-        <v>699</v>
+        <v>691</v>
       </c>
       <c r="X54" s="10" t="s">
         <v>24</v>
@@ -7638,9 +7701,7 @@
       <c r="C55" s="5" t="s">
         <v>328</v>
       </c>
-      <c r="D55" s="5" t="s">
-        <v>610</v>
-      </c>
+      <c r="D55" s="5"/>
       <c r="E55" s="6" t="s">
         <v>387</v>
       </c>
@@ -7652,9 +7713,7 @@
       <c r="K55" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="L55" s="5" t="s">
-        <v>620</v>
-      </c>
+      <c r="L55" s="5"/>
       <c r="M55" s="6" t="s">
         <v>387</v>
       </c>
@@ -7665,9 +7724,7 @@
       <c r="S55" s="5" t="s">
         <v>392</v>
       </c>
-      <c r="T55" s="5" t="s">
-        <v>630</v>
-      </c>
+      <c r="T55" s="5"/>
       <c r="U55" s="6" t="s">
         <v>387</v>
       </c>
@@ -7701,6 +7758,34 @@
     </row>
   </sheetData>
   <mergeCells count="44">
+    <mergeCell ref="V5:W5"/>
+    <mergeCell ref="V25:W25"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="U3:X3"/>
+    <mergeCell ref="U4:X4"/>
+    <mergeCell ref="M3:P3"/>
+    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="S5:T5"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="M4:P4"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="E4:H4"/>
     <mergeCell ref="N44:O44"/>
     <mergeCell ref="V44:W44"/>
     <mergeCell ref="S44:T44"/>
@@ -7715,36 +7800,8 @@
     <mergeCell ref="S23:T23"/>
     <mergeCell ref="S24:T24"/>
     <mergeCell ref="S25:T25"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="E42:H42"/>
     <mergeCell ref="M42:P42"/>
     <mergeCell ref="U42:X42"/>
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="M3:P3"/>
-    <mergeCell ref="S3:T3"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="S5:T5"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="M4:P4"/>
-    <mergeCell ref="V5:W5"/>
-    <mergeCell ref="V25:W25"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="U3:X3"/>
-    <mergeCell ref="U4:X4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7797,7 +7854,7 @@
       </c>
       <c r="C3" s="34"/>
       <c r="D3" s="33" t="s">
-        <v>793</v>
+        <v>785</v>
       </c>
       <c r="E3" s="35"/>
       <c r="F3" s="35"/>
@@ -7950,7 +8007,7 @@
         <v>295</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>705</v>
+        <v>697</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>7</v>
@@ -7959,7 +8016,7 @@
         <v>304</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>700</v>
+        <v>692</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>20</v>
@@ -7968,7 +8025,7 @@
         <v>303</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>711</v>
+        <v>703</v>
       </c>
       <c r="K7" s="6" t="s">
         <v>7</v>
@@ -7977,7 +8034,7 @@
         <v>308</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>719</v>
+        <v>711</v>
       </c>
       <c r="N7" s="6" t="s">
         <v>20</v>
@@ -8004,7 +8061,7 @@
         <v>296</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>706</v>
+        <v>698</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>290</v>
@@ -8013,7 +8070,7 @@
         <v>305</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="G8" s="10" t="s">
         <v>13</v>
@@ -8022,7 +8079,7 @@
         <v>312</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>712</v>
+        <v>704</v>
       </c>
       <c r="K8" s="10" t="s">
         <v>317</v>
@@ -8031,7 +8088,7 @@
         <v>301</v>
       </c>
       <c r="M8" s="9" t="s">
-        <v>720</v>
+        <v>712</v>
       </c>
       <c r="N8" s="10" t="s">
         <v>13</v>
@@ -8054,7 +8111,7 @@
         <v>297</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>707</v>
+        <v>699</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>289</v>
@@ -8063,7 +8120,7 @@
         <v>306</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>702</v>
+        <v>694</v>
       </c>
       <c r="G9" s="10" t="s">
         <v>14</v>
@@ -8072,7 +8129,7 @@
         <v>313</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
       <c r="K9" s="10" t="s">
         <v>318</v>
@@ -8081,7 +8138,7 @@
         <v>309</v>
       </c>
       <c r="M9" s="9" t="s">
-        <v>721</v>
+        <v>713</v>
       </c>
       <c r="N9" s="10" t="s">
         <v>14</v>
@@ -8104,7 +8161,7 @@
         <v>298</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>708</v>
+        <v>700</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>387</v>
@@ -8113,7 +8170,7 @@
         <v>300</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>703</v>
+        <v>695</v>
       </c>
       <c r="G10" s="10" t="s">
         <v>288</v>
@@ -8122,7 +8179,7 @@
         <v>314</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>714</v>
+        <v>706</v>
       </c>
       <c r="K10" s="10" t="s">
         <v>17</v>
@@ -8131,7 +8188,7 @@
         <v>310</v>
       </c>
       <c r="M10" s="9" t="s">
-        <v>722</v>
+        <v>714</v>
       </c>
       <c r="N10" s="10" t="s">
         <v>316</v>
@@ -8154,7 +8211,7 @@
         <v>299</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>709</v>
+        <v>701</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>18</v>
@@ -8163,7 +8220,7 @@
         <v>307</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>704</v>
+        <v>696</v>
       </c>
       <c r="G11" s="10" t="s">
         <v>15</v>
@@ -8172,7 +8229,7 @@
         <v>315</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>715</v>
+        <v>707</v>
       </c>
       <c r="K11" s="10" t="s">
         <v>18</v>
@@ -8181,7 +8238,7 @@
         <v>311</v>
       </c>
       <c r="M11" s="9" t="s">
-        <v>723</v>
+        <v>715</v>
       </c>
       <c r="N11" s="10" t="s">
         <v>15</v>
@@ -8204,7 +8261,7 @@
         <v>353</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>19</v>
@@ -8216,7 +8273,7 @@
         <v>319</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>716</v>
+        <v>708</v>
       </c>
       <c r="K12" s="6"/>
       <c r="L12" s="5"/>
@@ -8246,7 +8303,7 @@
         <v>320</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>717</v>
+        <v>709</v>
       </c>
       <c r="K13" s="6" t="s">
         <v>19</v>
@@ -8278,7 +8335,7 @@
         <v>384</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
       <c r="K14" s="6" t="s">
         <v>385</v>
@@ -8423,7 +8480,7 @@
       </c>
       <c r="C20" s="32"/>
       <c r="D20" s="32" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="E20" s="32"/>
       <c r="F20" s="32"/>
@@ -8544,7 +8601,7 @@
         <v>200</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>7</v>
@@ -8553,7 +8610,7 @@
         <v>216</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>649</v>
+        <v>641</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>20</v>
@@ -8582,7 +8639,7 @@
         <v>201</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>290</v>
@@ -8591,7 +8648,7 @@
         <v>217</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>650</v>
+        <v>642</v>
       </c>
       <c r="G25" s="10" t="s">
         <v>13</v>
@@ -8611,7 +8668,7 @@
         <v>340</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="D26" s="10" t="s">
         <v>289</v>
@@ -8620,7 +8677,7 @@
         <v>218</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>651</v>
+        <v>643</v>
       </c>
       <c r="G26" s="10" t="s">
         <v>14</v>
@@ -8643,7 +8700,7 @@
         <v>219</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>652</v>
+        <v>644</v>
       </c>
       <c r="G27" s="10" t="s">
         <v>288</v>
@@ -8663,7 +8720,7 @@
         <v>341</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>18</v>
@@ -8684,12 +8741,12 @@
         <v>342</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="D29" s="10"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9" t="s">
-        <v>653</v>
+        <v>645</v>
       </c>
       <c r="G29" s="10"/>
     </row>
@@ -8701,7 +8758,7 @@
         <v>220</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>654</v>
+        <v>646</v>
       </c>
       <c r="G30" s="10" t="s">
         <v>15</v>
@@ -8720,7 +8777,7 @@
         <v>351</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>19</v>
@@ -8734,7 +8791,7 @@
         <v>390</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>387</v>
@@ -8753,6 +8810,12 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:G20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="E22:F22"/>
     <mergeCell ref="O5:P5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="B5:C5"/>
@@ -8766,12 +8829,6 @@
     <mergeCell ref="K4:Q4"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:G20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="E22:F22"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8784,32 +8841,32 @@
   <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData>
     <row r="6" spans="4:20" ht="17.25" thickBot="1">
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="36" t="s">
         <v>357</v>
       </c>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
-      <c r="I6" s="68" t="s">
-        <v>730</v>
-      </c>
-      <c r="J6" s="68"/>
-      <c r="K6" s="68"/>
-      <c r="M6" s="68" t="s">
+      <c r="E6" s="36"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="36"/>
+      <c r="I6" s="36" t="s">
+        <v>722</v>
+      </c>
+      <c r="J6" s="36"/>
+      <c r="K6" s="36"/>
+      <c r="M6" s="36" t="s">
         <v>359</v>
       </c>
-      <c r="N6" s="68"/>
-      <c r="O6" s="68"/>
-      <c r="P6" s="68"/>
-      <c r="R6" s="68" t="s">
-        <v>731</v>
-      </c>
-      <c r="S6" s="68"/>
-      <c r="T6" s="68"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
+      <c r="P6" s="36"/>
+      <c r="R6" s="36" t="s">
+        <v>723</v>
+      </c>
+      <c r="S6" s="36"/>
+      <c r="T6" s="36"/>
     </row>
     <row r="7" spans="4:20" ht="16.5" customHeight="1">
-      <c r="D7" s="36" t="s">
-        <v>728</v>
+      <c r="D7" s="67" t="s">
+        <v>720</v>
       </c>
       <c r="E7" s="21"/>
       <c r="F7" s="21"/>
@@ -8817,8 +8874,8 @@
       <c r="I7" s="26"/>
       <c r="J7" s="21"/>
       <c r="K7" s="22"/>
-      <c r="M7" s="36" t="s">
-        <v>726</v>
+      <c r="M7" s="67" t="s">
+        <v>718</v>
       </c>
       <c r="N7" s="21"/>
       <c r="O7" s="21"/>
@@ -8828,196 +8885,196 @@
       <c r="T7" s="22"/>
     </row>
     <row r="8" spans="4:20">
-      <c r="D8" s="37"/>
+      <c r="D8" s="68"/>
       <c r="G8" s="23"/>
       <c r="I8" s="24"/>
       <c r="K8" s="23"/>
-      <c r="M8" s="37"/>
+      <c r="M8" s="68"/>
       <c r="P8" s="23"/>
       <c r="R8" s="24"/>
       <c r="T8" s="23"/>
     </row>
     <row r="9" spans="4:20" ht="16.5" customHeight="1">
-      <c r="D9" s="37"/>
-      <c r="F9" s="48" t="s">
-        <v>725</v>
+      <c r="D9" s="68"/>
+      <c r="F9" s="45" t="s">
+        <v>717</v>
       </c>
       <c r="G9" s="23"/>
       <c r="I9" s="24"/>
-      <c r="J9" s="48" t="s">
-        <v>725</v>
+      <c r="J9" s="45" t="s">
+        <v>717</v>
       </c>
       <c r="K9" s="23"/>
-      <c r="M9" s="37"/>
-      <c r="O9" s="48" t="s">
-        <v>725</v>
+      <c r="M9" s="68"/>
+      <c r="O9" s="45" t="s">
+        <v>717</v>
       </c>
       <c r="P9" s="23"/>
       <c r="R9" s="24"/>
-      <c r="S9" s="48" t="s">
-        <v>725</v>
+      <c r="S9" s="45" t="s">
+        <v>717</v>
       </c>
       <c r="T9" s="23"/>
     </row>
     <row r="10" spans="4:20">
-      <c r="D10" s="37"/>
-      <c r="F10" s="49"/>
+      <c r="D10" s="68"/>
+      <c r="F10" s="56"/>
       <c r="G10" s="23"/>
       <c r="I10" s="24"/>
-      <c r="J10" s="49"/>
+      <c r="J10" s="56"/>
       <c r="K10" s="23"/>
-      <c r="M10" s="37"/>
-      <c r="O10" s="49"/>
+      <c r="M10" s="68"/>
+      <c r="O10" s="56"/>
       <c r="P10" s="23"/>
       <c r="R10" s="24"/>
-      <c r="S10" s="49"/>
+      <c r="S10" s="56"/>
       <c r="T10" s="23"/>
     </row>
     <row r="11" spans="4:20" ht="16.5" customHeight="1">
-      <c r="D11" s="37"/>
-      <c r="E11" s="50" t="s">
-        <v>724</v>
+      <c r="D11" s="68"/>
+      <c r="E11" s="43" t="s">
+        <v>716</v>
       </c>
       <c r="G11" s="23"/>
       <c r="I11" s="24"/>
-      <c r="J11" s="50" t="s">
-        <v>724</v>
+      <c r="J11" s="43" t="s">
+        <v>716</v>
       </c>
       <c r="K11" s="23"/>
-      <c r="M11" s="37"/>
-      <c r="N11" s="50" t="s">
-        <v>724</v>
+      <c r="M11" s="68"/>
+      <c r="N11" s="43" t="s">
+        <v>716</v>
       </c>
       <c r="P11" s="23"/>
       <c r="R11" s="24"/>
-      <c r="S11" s="50" t="s">
-        <v>724</v>
+      <c r="S11" s="43" t="s">
+        <v>716</v>
       </c>
       <c r="T11" s="23"/>
     </row>
     <row r="12" spans="4:20">
-      <c r="D12" s="37"/>
-      <c r="E12" s="51"/>
+      <c r="D12" s="68"/>
+      <c r="E12" s="70"/>
       <c r="G12" s="23"/>
       <c r="I12" s="24"/>
-      <c r="J12" s="61"/>
+      <c r="J12" s="44"/>
       <c r="K12" s="23"/>
-      <c r="M12" s="37"/>
-      <c r="N12" s="51"/>
+      <c r="M12" s="68"/>
+      <c r="N12" s="70"/>
       <c r="P12" s="23"/>
       <c r="R12" s="24"/>
-      <c r="S12" s="61"/>
+      <c r="S12" s="44"/>
       <c r="T12" s="23"/>
     </row>
     <row r="13" spans="4:20">
-      <c r="D13" s="38"/>
+      <c r="D13" s="69"/>
       <c r="G13" s="23"/>
       <c r="I13" s="24"/>
       <c r="K13" s="23"/>
-      <c r="M13" s="38"/>
+      <c r="M13" s="69"/>
       <c r="P13" s="23"/>
       <c r="R13" s="24"/>
       <c r="T13" s="23"/>
     </row>
     <row r="14" spans="4:20" ht="16.5" customHeight="1">
       <c r="D14" s="24"/>
-      <c r="E14" s="39" t="s">
-        <v>727</v>
-      </c>
-      <c r="F14" s="40"/>
-      <c r="G14" s="41"/>
-      <c r="I14" s="52" t="s">
-        <v>733</v>
-      </c>
-      <c r="J14" s="53"/>
-      <c r="K14" s="54"/>
+      <c r="E14" s="71" t="s">
+        <v>719</v>
+      </c>
+      <c r="F14" s="72"/>
+      <c r="G14" s="73"/>
+      <c r="I14" s="57" t="s">
+        <v>725</v>
+      </c>
+      <c r="J14" s="58"/>
+      <c r="K14" s="63"/>
       <c r="M14" s="24"/>
-      <c r="N14" s="39" t="s">
-        <v>736</v>
-      </c>
-      <c r="O14" s="40"/>
-      <c r="P14" s="41"/>
-      <c r="R14" s="52" t="s">
-        <v>733</v>
-      </c>
-      <c r="S14" s="53"/>
-      <c r="T14" s="54"/>
+      <c r="N14" s="71" t="s">
+        <v>728</v>
+      </c>
+      <c r="O14" s="72"/>
+      <c r="P14" s="73"/>
+      <c r="R14" s="57" t="s">
+        <v>725</v>
+      </c>
+      <c r="S14" s="58"/>
+      <c r="T14" s="63"/>
     </row>
     <row r="15" spans="4:20">
       <c r="D15" s="24"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="44"/>
-      <c r="I15" s="55"/>
-      <c r="J15" s="56"/>
-      <c r="K15" s="57"/>
+      <c r="E15" s="74"/>
+      <c r="F15" s="75"/>
+      <c r="G15" s="76"/>
+      <c r="I15" s="50"/>
+      <c r="J15" s="51"/>
+      <c r="K15" s="52"/>
       <c r="M15" s="24"/>
-      <c r="N15" s="42"/>
-      <c r="O15" s="43"/>
-      <c r="P15" s="44"/>
-      <c r="R15" s="55"/>
-      <c r="S15" s="56"/>
-      <c r="T15" s="57"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="75"/>
+      <c r="P15" s="76"/>
+      <c r="R15" s="50"/>
+      <c r="S15" s="51"/>
+      <c r="T15" s="52"/>
     </row>
     <row r="16" spans="4:20">
       <c r="D16" s="24"/>
-      <c r="E16" s="42"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="44"/>
-      <c r="I16" s="55"/>
-      <c r="J16" s="56"/>
-      <c r="K16" s="57"/>
+      <c r="E16" s="74"/>
+      <c r="F16" s="75"/>
+      <c r="G16" s="76"/>
+      <c r="I16" s="50"/>
+      <c r="J16" s="51"/>
+      <c r="K16" s="52"/>
       <c r="M16" s="24"/>
-      <c r="N16" s="42"/>
-      <c r="O16" s="43"/>
-      <c r="P16" s="44"/>
-      <c r="R16" s="55"/>
-      <c r="S16" s="56"/>
-      <c r="T16" s="57"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="75"/>
+      <c r="P16" s="76"/>
+      <c r="R16" s="50"/>
+      <c r="S16" s="51"/>
+      <c r="T16" s="52"/>
     </row>
     <row r="17" spans="4:20" ht="17.25" thickBot="1">
       <c r="D17" s="25"/>
-      <c r="E17" s="45"/>
-      <c r="F17" s="46"/>
-      <c r="G17" s="47"/>
-      <c r="I17" s="58"/>
-      <c r="J17" s="59"/>
-      <c r="K17" s="60"/>
+      <c r="E17" s="77"/>
+      <c r="F17" s="78"/>
+      <c r="G17" s="79"/>
+      <c r="I17" s="64"/>
+      <c r="J17" s="65"/>
+      <c r="K17" s="66"/>
       <c r="M17" s="25"/>
-      <c r="N17" s="45"/>
-      <c r="O17" s="46"/>
-      <c r="P17" s="47"/>
-      <c r="R17" s="58"/>
-      <c r="S17" s="59"/>
-      <c r="T17" s="60"/>
+      <c r="N17" s="77"/>
+      <c r="O17" s="78"/>
+      <c r="P17" s="79"/>
+      <c r="R17" s="64"/>
+      <c r="S17" s="65"/>
+      <c r="T17" s="66"/>
     </row>
     <row r="19" spans="4:20" ht="17.25" thickBot="1">
-      <c r="D19" s="68" t="s">
+      <c r="D19" s="36" t="s">
         <v>368</v>
       </c>
-      <c r="E19" s="68"/>
-      <c r="F19" s="68"/>
-      <c r="H19" s="68" t="s">
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
+      <c r="H19" s="36" t="s">
         <v>367</v>
       </c>
-      <c r="I19" s="68"/>
-      <c r="J19" s="68"/>
-      <c r="K19" s="68"/>
-      <c r="R19" s="68" t="s">
-        <v>732</v>
-      </c>
-      <c r="S19" s="68"/>
-      <c r="T19" s="68"/>
+      <c r="I19" s="36"/>
+      <c r="J19" s="36"/>
+      <c r="K19" s="36"/>
+      <c r="R19" s="36" t="s">
+        <v>724</v>
+      </c>
+      <c r="S19" s="36"/>
+      <c r="T19" s="36"/>
     </row>
     <row r="20" spans="4:20">
-      <c r="D20" s="76" t="s">
-        <v>729</v>
-      </c>
-      <c r="E20" s="77"/>
-      <c r="F20" s="78"/>
+      <c r="D20" s="47" t="s">
+        <v>721</v>
+      </c>
+      <c r="E20" s="48"/>
+      <c r="F20" s="49"/>
       <c r="H20" s="26"/>
-      <c r="I20" s="67" t="s">
-        <v>725</v>
+      <c r="I20" s="62" t="s">
+        <v>717</v>
       </c>
       <c r="J20" s="21"/>
       <c r="K20" s="22"/>
@@ -9025,56 +9082,56 @@
       <c r="N20" s="21"/>
       <c r="O20" s="21"/>
       <c r="P20" s="22"/>
-      <c r="R20" s="76" t="s">
-        <v>733</v>
-      </c>
-      <c r="S20" s="77"/>
-      <c r="T20" s="78"/>
+      <c r="R20" s="47" t="s">
+        <v>725</v>
+      </c>
+      <c r="S20" s="48"/>
+      <c r="T20" s="49"/>
     </row>
     <row r="21" spans="4:20">
-      <c r="D21" s="55"/>
-      <c r="E21" s="56"/>
-      <c r="F21" s="57"/>
+      <c r="D21" s="50"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="52"/>
       <c r="H21" s="24"/>
-      <c r="I21" s="49"/>
+      <c r="I21" s="56"/>
       <c r="K21" s="23"/>
       <c r="M21" s="24"/>
       <c r="P21" s="23"/>
-      <c r="R21" s="55"/>
-      <c r="S21" s="56"/>
-      <c r="T21" s="57"/>
+      <c r="R21" s="50"/>
+      <c r="S21" s="51"/>
+      <c r="T21" s="52"/>
     </row>
     <row r="22" spans="4:20">
-      <c r="D22" s="55"/>
-      <c r="E22" s="56"/>
-      <c r="F22" s="57"/>
+      <c r="D22" s="50"/>
+      <c r="E22" s="51"/>
+      <c r="F22" s="52"/>
       <c r="H22" s="24"/>
-      <c r="I22" s="50" t="s">
-        <v>724</v>
-      </c>
-      <c r="J22" s="73" t="s">
-        <v>734</v>
+      <c r="I22" s="43" t="s">
+        <v>716</v>
+      </c>
+      <c r="J22" s="41" t="s">
+        <v>726</v>
       </c>
       <c r="K22" s="23"/>
       <c r="M22" s="24"/>
       <c r="P22" s="23"/>
-      <c r="R22" s="55"/>
-      <c r="S22" s="56"/>
-      <c r="T22" s="57"/>
+      <c r="R22" s="50"/>
+      <c r="S22" s="51"/>
+      <c r="T22" s="52"/>
     </row>
     <row r="23" spans="4:20">
-      <c r="D23" s="64"/>
-      <c r="E23" s="65"/>
-      <c r="F23" s="79"/>
+      <c r="D23" s="53"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="55"/>
       <c r="H23" s="24"/>
-      <c r="I23" s="61"/>
-      <c r="J23" s="74"/>
+      <c r="I23" s="44"/>
+      <c r="J23" s="42"/>
       <c r="K23" s="23"/>
       <c r="M23" s="24"/>
       <c r="P23" s="23"/>
-      <c r="R23" s="64"/>
-      <c r="S23" s="65"/>
-      <c r="T23" s="79"/>
+      <c r="R23" s="53"/>
+      <c r="S23" s="54"/>
+      <c r="T23" s="55"/>
     </row>
     <row r="24" spans="4:20">
       <c r="D24" s="24"/>
@@ -9090,77 +9147,77 @@
     </row>
     <row r="25" spans="4:20" ht="16.5" customHeight="1">
       <c r="D25" s="24"/>
-      <c r="E25" s="50" t="s">
-        <v>724</v>
+      <c r="E25" s="43" t="s">
+        <v>716</v>
       </c>
       <c r="F25" s="23"/>
-      <c r="H25" s="52" t="s">
-        <v>737</v>
-      </c>
-      <c r="I25" s="53"/>
-      <c r="J25" s="62"/>
+      <c r="H25" s="57" t="s">
+        <v>729</v>
+      </c>
+      <c r="I25" s="58"/>
+      <c r="J25" s="59"/>
       <c r="K25" s="23"/>
       <c r="M25" s="24"/>
       <c r="P25" s="23"/>
       <c r="R25" s="24"/>
-      <c r="S25" s="50" t="s">
-        <v>724</v>
+      <c r="S25" s="43" t="s">
+        <v>716</v>
       </c>
       <c r="T25" s="23"/>
     </row>
     <row r="26" spans="4:20">
       <c r="D26" s="24"/>
-      <c r="E26" s="61"/>
+      <c r="E26" s="44"/>
       <c r="F26" s="23"/>
-      <c r="H26" s="55"/>
-      <c r="I26" s="56"/>
-      <c r="J26" s="63"/>
+      <c r="H26" s="50"/>
+      <c r="I26" s="51"/>
+      <c r="J26" s="60"/>
       <c r="K26" s="23"/>
       <c r="M26" s="24"/>
       <c r="P26" s="23"/>
       <c r="R26" s="24"/>
-      <c r="S26" s="61"/>
+      <c r="S26" s="44"/>
       <c r="T26" s="23"/>
     </row>
     <row r="27" spans="4:20">
       <c r="D27" s="24"/>
-      <c r="E27" s="48" t="s">
-        <v>725</v>
+      <c r="E27" s="45" t="s">
+        <v>717</v>
       </c>
       <c r="F27" s="23"/>
-      <c r="H27" s="55"/>
-      <c r="I27" s="56"/>
-      <c r="J27" s="63"/>
-      <c r="K27" s="69" t="s">
-        <v>726</v>
+      <c r="H27" s="50"/>
+      <c r="I27" s="51"/>
+      <c r="J27" s="60"/>
+      <c r="K27" s="37" t="s">
+        <v>718</v>
       </c>
       <c r="M27" s="24"/>
       <c r="P27" s="23"/>
       <c r="R27" s="24"/>
-      <c r="S27" s="48" t="s">
-        <v>725</v>
+      <c r="S27" s="45" t="s">
+        <v>717</v>
       </c>
       <c r="T27" s="23"/>
     </row>
     <row r="28" spans="4:20" ht="16.5" customHeight="1">
       <c r="D28" s="24"/>
-      <c r="E28" s="49"/>
+      <c r="E28" s="56"/>
       <c r="F28" s="23"/>
-      <c r="H28" s="64"/>
-      <c r="I28" s="65"/>
-      <c r="J28" s="66"/>
-      <c r="K28" s="70"/>
+      <c r="H28" s="53"/>
+      <c r="I28" s="54"/>
+      <c r="J28" s="61"/>
+      <c r="K28" s="38"/>
       <c r="M28" s="24"/>
       <c r="P28" s="23"/>
       <c r="R28" s="24"/>
-      <c r="S28" s="49"/>
+      <c r="S28" s="56"/>
       <c r="T28" s="23"/>
     </row>
     <row r="29" spans="4:20">
       <c r="D29" s="24"/>
       <c r="F29" s="23"/>
       <c r="H29" s="24"/>
-      <c r="K29" s="71"/>
+      <c r="K29" s="39"/>
       <c r="M29" s="24"/>
       <c r="P29" s="23"/>
       <c r="R29" s="24"/>
@@ -9171,10 +9228,10 @@
       <c r="E30" s="27"/>
       <c r="F30" s="28"/>
       <c r="H30" s="24"/>
-      <c r="I30" s="50" t="s">
-        <v>724</v>
-      </c>
-      <c r="K30" s="71"/>
+      <c r="I30" s="43" t="s">
+        <v>716</v>
+      </c>
+      <c r="K30" s="39"/>
       <c r="M30" s="25"/>
       <c r="N30" s="27"/>
       <c r="O30" s="27"/>
@@ -9185,29 +9242,47 @@
     </row>
     <row r="31" spans="4:20">
       <c r="H31" s="24"/>
-      <c r="I31" s="61"/>
-      <c r="K31" s="71"/>
+      <c r="I31" s="44"/>
+      <c r="K31" s="39"/>
     </row>
     <row r="32" spans="4:20">
       <c r="H32" s="24"/>
-      <c r="I32" s="48" t="s">
-        <v>725</v>
-      </c>
-      <c r="K32" s="71"/>
+      <c r="I32" s="45" t="s">
+        <v>717</v>
+      </c>
+      <c r="K32" s="39"/>
     </row>
     <row r="33" spans="8:24" ht="17.25" thickBot="1">
       <c r="H33" s="25"/>
-      <c r="I33" s="75"/>
+      <c r="I33" s="46"/>
       <c r="J33" s="27"/>
-      <c r="K33" s="72"/>
+      <c r="K33" s="40"/>
     </row>
     <row r="47" spans="8:24">
       <c r="X47" t="s">
-        <v>735</v>
+        <v>727</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="D7:D13"/>
+    <mergeCell ref="E14:G17"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="I14:K17"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="S11:S12"/>
+    <mergeCell ref="R14:T17"/>
+    <mergeCell ref="M7:M13"/>
+    <mergeCell ref="O9:O10"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="N14:P17"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="H25:J28"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="J11:J12"/>
     <mergeCell ref="R6:T6"/>
     <mergeCell ref="R19:T19"/>
     <mergeCell ref="D19:F19"/>
@@ -9224,24 +9299,6 @@
     <mergeCell ref="M6:P6"/>
     <mergeCell ref="D20:F23"/>
     <mergeCell ref="E27:E28"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="H25:J28"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="I22:I23"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="S11:S12"/>
-    <mergeCell ref="R14:T17"/>
-    <mergeCell ref="M7:M13"/>
-    <mergeCell ref="O9:O10"/>
-    <mergeCell ref="N11:N12"/>
-    <mergeCell ref="N14:P17"/>
-    <mergeCell ref="D7:D13"/>
-    <mergeCell ref="E14:G17"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="I14:K17"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/PLC/IO List.xlsx
+++ b/PLC/IO List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EZENIC\Desktop\Project-Second\PLC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A14F4D4F-D5C1-4E7F-AFCC-E03C21C9C9D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B51D53EB-C2E6-4AC8-811A-E779848FBC14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="2" xr2:uid="{E8A3CD3B-D612-4B37-A180-F6C335096DC9}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{E8A3CD3B-D612-4B37-A180-F6C335096DC9}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="823">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="829">
   <si>
     <t>X10</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2946,6 +2946,26 @@
   </si>
   <si>
     <t>챔버4 로봇 경유위치 이동 완료</t>
+  </si>
+  <si>
+    <t>M20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수작업7 START</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M21</t>
+  </si>
+  <si>
+    <t>M22</t>
+  </si>
+  <si>
+    <t>수작업8 START</t>
+  </si>
+  <si>
+    <t>수작업9 START</t>
   </si>
 </sst>
 </file>
@@ -3570,6 +3590,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3582,99 +3605,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3682,9 +3612,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3714,8 +3641,101 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4065,47 +4085,47 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:11">
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="34"/>
-      <c r="D3" s="32" t="s">
+      <c r="C3" s="35"/>
+      <c r="D3" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
-      <c r="J3" s="32"/>
-      <c r="K3" s="32"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
+      <c r="J3" s="33"/>
+      <c r="K3" s="33"/>
     </row>
     <row r="4" spans="2:11">
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="34"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="32"/>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="33"/>
+      <c r="K4" s="33"/>
     </row>
     <row r="5" spans="2:11">
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="34"/>
+      <c r="C5" s="35"/>
       <c r="D5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="33" t="s">
+      <c r="E5" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="34"/>
+      <c r="F5" s="35"/>
       <c r="G5" s="4" t="s">
         <v>10</v>
       </c>
@@ -4552,7 +4572,7 @@
       <c r="H22" s="5" t="s">
         <v>815</v>
       </c>
-      <c r="I22" s="80" t="s">
+      <c r="I22" s="32" t="s">
         <v>819</v>
       </c>
       <c r="J22" s="5" t="s">
@@ -4582,7 +4602,7 @@
       <c r="H23" s="5" t="s">
         <v>816</v>
       </c>
-      <c r="I23" s="80" t="s">
+      <c r="I23" s="32" t="s">
         <v>820</v>
       </c>
       <c r="J23" s="5" t="s">
@@ -4612,7 +4632,7 @@
       <c r="H24" s="5" t="s">
         <v>817</v>
       </c>
-      <c r="I24" s="80" t="s">
+      <c r="I24" s="32" t="s">
         <v>821</v>
       </c>
       <c r="J24" s="5" t="s">
@@ -4640,7 +4660,7 @@
       <c r="H25" s="5" t="s">
         <v>818</v>
       </c>
-      <c r="I25" s="80" t="s">
+      <c r="I25" s="32" t="s">
         <v>822</v>
       </c>
       <c r="J25" s="5" t="s">
@@ -4715,8 +4735,12 @@
       <c r="G28" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="H28" s="5"/>
-      <c r="I28" s="6"/>
+      <c r="H28" s="5" t="s">
+        <v>823</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>824</v>
+      </c>
       <c r="J28" s="5" t="s">
         <v>769</v>
       </c>
@@ -4741,8 +4765,12 @@
       <c r="G29" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="H29" s="5"/>
-      <c r="I29" s="6"/>
+      <c r="H29" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>827</v>
+      </c>
       <c r="J29" s="5" t="s">
         <v>770</v>
       </c>
@@ -4767,8 +4795,12 @@
       <c r="G30" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="H30" s="5"/>
-      <c r="I30" s="6"/>
+      <c r="H30" s="5" t="s">
+        <v>826</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>828</v>
+      </c>
       <c r="J30" s="5" t="s">
         <v>771</v>
       </c>
@@ -5758,105 +5790,105 @@
       <c r="X2" s="12"/>
     </row>
     <row r="3" spans="3:24" s="3" customFormat="1">
-      <c r="C3" s="32" t="s">
+      <c r="C3" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32" t="s">
+      <c r="D3" s="33"/>
+      <c r="E3" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="K3" s="32" t="s">
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+      <c r="K3" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="L3" s="32"/>
-      <c r="M3" s="32" t="s">
+      <c r="L3" s="33"/>
+      <c r="M3" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="N3" s="32"/>
-      <c r="O3" s="32"/>
-      <c r="P3" s="32"/>
-      <c r="S3" s="32" t="s">
+      <c r="N3" s="33"/>
+      <c r="O3" s="33"/>
+      <c r="P3" s="33"/>
+      <c r="S3" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="T3" s="32"/>
-      <c r="U3" s="32" t="s">
+      <c r="T3" s="33"/>
+      <c r="U3" s="33" t="s">
         <v>209</v>
       </c>
-      <c r="V3" s="32"/>
-      <c r="W3" s="32"/>
-      <c r="X3" s="32"/>
+      <c r="V3" s="33"/>
+      <c r="W3" s="33"/>
+      <c r="X3" s="33"/>
     </row>
     <row r="4" spans="3:24" s="3" customFormat="1">
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="33"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
-      <c r="K4" s="32" t="s">
+      <c r="K4" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
-      <c r="O4" s="32"/>
-      <c r="P4" s="32"/>
-      <c r="S4" s="32" t="s">
+      <c r="L4" s="33"/>
+      <c r="M4" s="33"/>
+      <c r="N4" s="33"/>
+      <c r="O4" s="33"/>
+      <c r="P4" s="33"/>
+      <c r="S4" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="T4" s="32"/>
-      <c r="U4" s="32"/>
-      <c r="V4" s="32"/>
-      <c r="W4" s="32"/>
-      <c r="X4" s="32"/>
+      <c r="T4" s="33"/>
+      <c r="U4" s="33"/>
+      <c r="V4" s="33"/>
+      <c r="W4" s="33"/>
+      <c r="X4" s="33"/>
     </row>
     <row r="5" spans="3:24" s="2" customFormat="1">
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="32"/>
+      <c r="D5" s="33"/>
       <c r="E5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="32" t="s">
+      <c r="F5" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="32"/>
+      <c r="G5" s="33"/>
       <c r="H5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K5" s="32" t="s">
+      <c r="K5" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="L5" s="32"/>
+      <c r="L5" s="33"/>
       <c r="M5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="N5" s="32" t="s">
+      <c r="N5" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="O5" s="32"/>
+      <c r="O5" s="33"/>
       <c r="P5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="S5" s="32" t="s">
+      <c r="S5" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="T5" s="32"/>
+      <c r="T5" s="33"/>
       <c r="U5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="V5" s="32" t="s">
+      <c r="V5" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="W5" s="32"/>
+      <c r="W5" s="33"/>
       <c r="X5" s="4" t="s">
         <v>10</v>
       </c>
@@ -6496,77 +6528,77 @@
       <c r="B23" s="1"/>
       <c r="E23" s="1"/>
       <c r="H23" s="1"/>
-      <c r="K23" s="32" t="s">
+      <c r="K23" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="L23" s="32"/>
-      <c r="M23" s="32" t="s">
+      <c r="L23" s="33"/>
+      <c r="M23" s="33" t="s">
         <v>210</v>
       </c>
-      <c r="N23" s="32"/>
-      <c r="O23" s="32"/>
-      <c r="P23" s="32"/>
-      <c r="S23" s="32" t="s">
+      <c r="N23" s="33"/>
+      <c r="O23" s="33"/>
+      <c r="P23" s="33"/>
+      <c r="S23" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="T23" s="32"/>
-      <c r="U23" s="32" t="s">
+      <c r="T23" s="33"/>
+      <c r="U23" s="33" t="s">
         <v>211</v>
       </c>
-      <c r="V23" s="32"/>
-      <c r="W23" s="32"/>
-      <c r="X23" s="32"/>
+      <c r="V23" s="33"/>
+      <c r="W23" s="33"/>
+      <c r="X23" s="33"/>
     </row>
     <row r="24" spans="2:24">
       <c r="B24" s="1"/>
       <c r="E24" s="1"/>
       <c r="H24" s="1"/>
-      <c r="K24" s="32" t="s">
+      <c r="K24" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="L24" s="32"/>
-      <c r="M24" s="32"/>
-      <c r="N24" s="32"/>
-      <c r="O24" s="32"/>
-      <c r="P24" s="32"/>
-      <c r="S24" s="32" t="s">
+      <c r="L24" s="33"/>
+      <c r="M24" s="33"/>
+      <c r="N24" s="33"/>
+      <c r="O24" s="33"/>
+      <c r="P24" s="33"/>
+      <c r="S24" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="T24" s="32"/>
-      <c r="U24" s="32"/>
-      <c r="V24" s="32"/>
-      <c r="W24" s="32"/>
-      <c r="X24" s="32"/>
+      <c r="T24" s="33"/>
+      <c r="U24" s="33"/>
+      <c r="V24" s="33"/>
+      <c r="W24" s="33"/>
+      <c r="X24" s="33"/>
     </row>
     <row r="25" spans="2:24">
       <c r="B25" s="1"/>
       <c r="E25" s="1"/>
       <c r="H25" s="1"/>
-      <c r="K25" s="32" t="s">
+      <c r="K25" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="L25" s="32"/>
+      <c r="L25" s="33"/>
       <c r="M25" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="N25" s="32" t="s">
+      <c r="N25" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="O25" s="32"/>
+      <c r="O25" s="33"/>
       <c r="P25" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="S25" s="32" t="s">
+      <c r="S25" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="T25" s="32"/>
+      <c r="T25" s="33"/>
       <c r="U25" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="V25" s="32" t="s">
+      <c r="V25" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="W25" s="32"/>
+      <c r="W25" s="33"/>
       <c r="X25" s="4" t="s">
         <v>10</v>
       </c>
@@ -7026,114 +7058,114 @@
     </row>
     <row r="42" spans="2:24">
       <c r="B42" s="8"/>
-      <c r="C42" s="32" t="s">
+      <c r="C42" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="D42" s="32"/>
-      <c r="E42" s="32" t="s">
+      <c r="D42" s="33"/>
+      <c r="E42" s="33" t="s">
         <v>212</v>
       </c>
-      <c r="F42" s="32"/>
-      <c r="G42" s="32"/>
-      <c r="H42" s="32"/>
+      <c r="F42" s="33"/>
+      <c r="G42" s="33"/>
+      <c r="H42" s="33"/>
       <c r="I42" s="7"/>
       <c r="J42" s="7"/>
       <c r="K42" s="4" t="s">
         <v>40</v>
       </c>
       <c r="L42" s="4"/>
-      <c r="M42" s="32" t="s">
+      <c r="M42" s="33" t="s">
         <v>213</v>
       </c>
-      <c r="N42" s="32"/>
-      <c r="O42" s="32"/>
-      <c r="P42" s="32"/>
+      <c r="N42" s="33"/>
+      <c r="O42" s="33"/>
+      <c r="P42" s="33"/>
       <c r="Q42" s="8"/>
       <c r="S42" s="4" t="s">
         <v>40</v>
       </c>
       <c r="T42" s="4"/>
-      <c r="U42" s="32" t="s">
+      <c r="U42" s="33" t="s">
         <v>214</v>
       </c>
-      <c r="V42" s="32"/>
-      <c r="W42" s="32"/>
-      <c r="X42" s="32"/>
+      <c r="V42" s="33"/>
+      <c r="W42" s="33"/>
+      <c r="X42" s="33"/>
     </row>
     <row r="43" spans="2:24">
       <c r="B43" s="8"/>
-      <c r="C43" s="32" t="s">
+      <c r="C43" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="D43" s="32"/>
-      <c r="E43" s="32"/>
-      <c r="F43" s="32"/>
-      <c r="G43" s="32"/>
-      <c r="H43" s="32"/>
+      <c r="D43" s="33"/>
+      <c r="E43" s="33"/>
+      <c r="F43" s="33"/>
+      <c r="G43" s="33"/>
+      <c r="H43" s="33"/>
       <c r="I43" s="7"/>
       <c r="J43" s="7"/>
       <c r="K43" s="4" t="s">
         <v>39</v>
       </c>
       <c r="L43" s="4"/>
-      <c r="M43" s="32"/>
-      <c r="N43" s="32"/>
-      <c r="O43" s="32"/>
-      <c r="P43" s="32"/>
+      <c r="M43" s="33"/>
+      <c r="N43" s="33"/>
+      <c r="O43" s="33"/>
+      <c r="P43" s="33"/>
       <c r="Q43" s="8"/>
       <c r="S43" s="4" t="s">
         <v>39</v>
       </c>
       <c r="T43" s="4"/>
-      <c r="U43" s="32"/>
-      <c r="V43" s="32"/>
-      <c r="W43" s="32"/>
-      <c r="X43" s="32"/>
+      <c r="U43" s="33"/>
+      <c r="V43" s="33"/>
+      <c r="W43" s="33"/>
+      <c r="X43" s="33"/>
     </row>
     <row r="44" spans="2:24">
       <c r="B44" s="8"/>
-      <c r="C44" s="32" t="s">
+      <c r="C44" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="D44" s="32"/>
+      <c r="D44" s="33"/>
       <c r="E44" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F44" s="32" t="s">
+      <c r="F44" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="G44" s="32"/>
+      <c r="G44" s="33"/>
       <c r="H44" s="4" t="s">
         <v>10</v>
       </c>
       <c r="I44" s="7"/>
       <c r="J44" s="7"/>
-      <c r="K44" s="32" t="s">
+      <c r="K44" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="L44" s="32"/>
+      <c r="L44" s="33"/>
       <c r="M44" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="N44" s="32" t="s">
+      <c r="N44" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="O44" s="32"/>
+      <c r="O44" s="33"/>
       <c r="P44" s="4" t="s">
         <v>10</v>
       </c>
       <c r="Q44" s="8"/>
-      <c r="S44" s="32" t="s">
+      <c r="S44" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="T44" s="32"/>
+      <c r="T44" s="33"/>
       <c r="U44" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="V44" s="32" t="s">
+      <c r="V44" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="W44" s="32"/>
+      <c r="W44" s="33"/>
       <c r="X44" s="4" t="s">
         <v>10</v>
       </c>
@@ -7758,18 +7790,22 @@
     </row>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="V5:W5"/>
-    <mergeCell ref="V25:W25"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="U3:X3"/>
-    <mergeCell ref="U4:X4"/>
-    <mergeCell ref="M3:P3"/>
-    <mergeCell ref="S3:T3"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="S5:T5"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="M4:P4"/>
+    <mergeCell ref="N44:O44"/>
+    <mergeCell ref="V44:W44"/>
+    <mergeCell ref="S44:T44"/>
+    <mergeCell ref="K44:L44"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="M43:P43"/>
+    <mergeCell ref="U43:X43"/>
+    <mergeCell ref="M23:P23"/>
+    <mergeCell ref="M24:P24"/>
+    <mergeCell ref="U23:X23"/>
+    <mergeCell ref="U24:X24"/>
+    <mergeCell ref="S23:T23"/>
+    <mergeCell ref="S24:T24"/>
+    <mergeCell ref="S25:T25"/>
+    <mergeCell ref="M42:P42"/>
+    <mergeCell ref="U42:X42"/>
     <mergeCell ref="K3:L3"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C3:D3"/>
@@ -7786,22 +7822,18 @@
     <mergeCell ref="E42:H42"/>
     <mergeCell ref="E3:H3"/>
     <mergeCell ref="E4:H4"/>
-    <mergeCell ref="N44:O44"/>
-    <mergeCell ref="V44:W44"/>
-    <mergeCell ref="S44:T44"/>
-    <mergeCell ref="K44:L44"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="M43:P43"/>
-    <mergeCell ref="U43:X43"/>
-    <mergeCell ref="M23:P23"/>
-    <mergeCell ref="M24:P24"/>
-    <mergeCell ref="U23:X23"/>
-    <mergeCell ref="U24:X24"/>
-    <mergeCell ref="S23:T23"/>
-    <mergeCell ref="S24:T24"/>
-    <mergeCell ref="S25:T25"/>
-    <mergeCell ref="M42:P42"/>
-    <mergeCell ref="U42:X42"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="S5:T5"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="M4:P4"/>
+    <mergeCell ref="V5:W5"/>
+    <mergeCell ref="V25:W25"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="U3:X3"/>
+    <mergeCell ref="U4:X4"/>
+    <mergeCell ref="M3:P3"/>
+    <mergeCell ref="S3:T3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7849,29 +7881,29 @@
       </c>
     </row>
     <row r="3" spans="2:21">
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="34"/>
-      <c r="D3" s="33" t="s">
+      <c r="C3" s="35"/>
+      <c r="D3" s="34" t="s">
         <v>785</v>
       </c>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="34"/>
-      <c r="I3" s="33" t="s">
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="35"/>
+      <c r="I3" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="J3" s="34"/>
-      <c r="K3" s="32" t="s">
+      <c r="J3" s="35"/>
+      <c r="K3" s="33" t="s">
         <v>302</v>
       </c>
-      <c r="L3" s="32"/>
-      <c r="M3" s="32"/>
-      <c r="N3" s="32"/>
-      <c r="O3" s="32"/>
-      <c r="P3" s="32"/>
-      <c r="Q3" s="32"/>
+      <c r="L3" s="33"/>
+      <c r="M3" s="33"/>
+      <c r="N3" s="33"/>
+      <c r="O3" s="33"/>
+      <c r="P3" s="33"/>
+      <c r="Q3" s="33"/>
       <c r="S3" s="5">
         <v>0</v>
       </c>
@@ -7881,25 +7913,25 @@
       <c r="U3" s="6"/>
     </row>
     <row r="4" spans="2:21">
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="34"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="34"/>
-      <c r="I4" s="33" t="s">
+      <c r="C4" s="35"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="35"/>
+      <c r="I4" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="J4" s="34"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
-      <c r="O4" s="32"/>
-      <c r="P4" s="32"/>
-      <c r="Q4" s="32"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="33"/>
+      <c r="L4" s="33"/>
+      <c r="M4" s="33"/>
+      <c r="N4" s="33"/>
+      <c r="O4" s="33"/>
+      <c r="P4" s="33"/>
+      <c r="Q4" s="33"/>
       <c r="S4" s="5">
         <v>100</v>
       </c>
@@ -7911,38 +7943,38 @@
       </c>
     </row>
     <row r="5" spans="2:21">
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="34"/>
+      <c r="C5" s="35"/>
       <c r="D5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="33" t="s">
+      <c r="E5" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="34"/>
+      <c r="F5" s="35"/>
       <c r="G5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="I5" s="33" t="s">
+      <c r="I5" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="34"/>
+      <c r="J5" s="35"/>
       <c r="K5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L5" s="33" t="s">
+      <c r="L5" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="M5" s="34"/>
+      <c r="M5" s="35"/>
       <c r="N5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="O5" s="33" t="s">
+      <c r="O5" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="P5" s="34"/>
+      <c r="P5" s="35"/>
       <c r="Q5" s="4" t="s">
         <v>10</v>
       </c>
@@ -8475,16 +8507,16 @@
       </c>
     </row>
     <row r="20" spans="2:21">
-      <c r="B20" s="32" t="s">
+      <c r="B20" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="32"/>
-      <c r="D20" s="32" t="s">
+      <c r="C20" s="33"/>
+      <c r="D20" s="33" t="s">
         <v>784</v>
       </c>
-      <c r="E20" s="32"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="33"/>
       <c r="I20" s="5"/>
       <c r="J20" s="5"/>
       <c r="K20" s="6"/>
@@ -8505,14 +8537,14 @@
       </c>
     </row>
     <row r="21" spans="2:21">
-      <c r="B21" s="32" t="s">
+      <c r="B21" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
+      <c r="C21" s="33"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="33"/>
       <c r="I21" s="5"/>
       <c r="J21" s="5"/>
       <c r="K21" s="6"/>
@@ -8533,17 +8565,17 @@
       </c>
     </row>
     <row r="22" spans="2:21">
-      <c r="B22" s="32" t="s">
+      <c r="B22" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="32"/>
+      <c r="C22" s="33"/>
       <c r="D22" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E22" s="32" t="s">
+      <c r="E22" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="F22" s="32"/>
+      <c r="F22" s="33"/>
       <c r="G22" s="4" t="s">
         <v>10</v>
       </c>
@@ -8810,12 +8842,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:G20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="E22:F22"/>
     <mergeCell ref="O5:P5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="B5:C5"/>
@@ -8829,6 +8855,12 @@
     <mergeCell ref="K4:Q4"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:G20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="E22:F22"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8841,31 +8873,31 @@
   <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData>
     <row r="6" spans="4:20" ht="17.25" thickBot="1">
-      <c r="D6" s="36" t="s">
+      <c r="D6" s="69" t="s">
         <v>357</v>
       </c>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
-      <c r="I6" s="36" t="s">
+      <c r="E6" s="69"/>
+      <c r="F6" s="69"/>
+      <c r="G6" s="69"/>
+      <c r="I6" s="69" t="s">
         <v>722</v>
       </c>
-      <c r="J6" s="36"/>
-      <c r="K6" s="36"/>
-      <c r="M6" s="36" t="s">
+      <c r="J6" s="69"/>
+      <c r="K6" s="69"/>
+      <c r="M6" s="69" t="s">
         <v>359</v>
       </c>
-      <c r="N6" s="36"/>
-      <c r="O6" s="36"/>
-      <c r="P6" s="36"/>
-      <c r="R6" s="36" t="s">
+      <c r="N6" s="69"/>
+      <c r="O6" s="69"/>
+      <c r="P6" s="69"/>
+      <c r="R6" s="69" t="s">
         <v>723</v>
       </c>
-      <c r="S6" s="36"/>
-      <c r="T6" s="36"/>
+      <c r="S6" s="69"/>
+      <c r="T6" s="69"/>
     </row>
     <row r="7" spans="4:20" ht="16.5" customHeight="1">
-      <c r="D7" s="67" t="s">
+      <c r="D7" s="37" t="s">
         <v>720</v>
       </c>
       <c r="E7" s="21"/>
@@ -8874,7 +8906,7 @@
       <c r="I7" s="26"/>
       <c r="J7" s="21"/>
       <c r="K7" s="22"/>
-      <c r="M7" s="67" t="s">
+      <c r="M7" s="37" t="s">
         <v>718</v>
       </c>
       <c r="N7" s="21"/>
@@ -8885,195 +8917,195 @@
       <c r="T7" s="22"/>
     </row>
     <row r="8" spans="4:20">
-      <c r="D8" s="68"/>
+      <c r="D8" s="38"/>
       <c r="G8" s="23"/>
       <c r="I8" s="24"/>
       <c r="K8" s="23"/>
-      <c r="M8" s="68"/>
+      <c r="M8" s="38"/>
       <c r="P8" s="23"/>
       <c r="R8" s="24"/>
       <c r="T8" s="23"/>
     </row>
     <row r="9" spans="4:20" ht="16.5" customHeight="1">
-      <c r="D9" s="68"/>
-      <c r="F9" s="45" t="s">
+      <c r="D9" s="38"/>
+      <c r="F9" s="49" t="s">
         <v>717</v>
       </c>
       <c r="G9" s="23"/>
       <c r="I9" s="24"/>
-      <c r="J9" s="45" t="s">
+      <c r="J9" s="49" t="s">
         <v>717</v>
       </c>
       <c r="K9" s="23"/>
-      <c r="M9" s="68"/>
-      <c r="O9" s="45" t="s">
+      <c r="M9" s="38"/>
+      <c r="O9" s="49" t="s">
         <v>717</v>
       </c>
       <c r="P9" s="23"/>
       <c r="R9" s="24"/>
-      <c r="S9" s="45" t="s">
+      <c r="S9" s="49" t="s">
         <v>717</v>
       </c>
       <c r="T9" s="23"/>
     </row>
     <row r="10" spans="4:20">
-      <c r="D10" s="68"/>
-      <c r="F10" s="56"/>
+      <c r="D10" s="38"/>
+      <c r="F10" s="50"/>
       <c r="G10" s="23"/>
       <c r="I10" s="24"/>
-      <c r="J10" s="56"/>
+      <c r="J10" s="50"/>
       <c r="K10" s="23"/>
-      <c r="M10" s="68"/>
-      <c r="O10" s="56"/>
+      <c r="M10" s="38"/>
+      <c r="O10" s="50"/>
       <c r="P10" s="23"/>
       <c r="R10" s="24"/>
-      <c r="S10" s="56"/>
+      <c r="S10" s="50"/>
       <c r="T10" s="23"/>
     </row>
     <row r="11" spans="4:20" ht="16.5" customHeight="1">
-      <c r="D11" s="68"/>
-      <c r="E11" s="43" t="s">
+      <c r="D11" s="38"/>
+      <c r="E11" s="51" t="s">
         <v>716</v>
       </c>
       <c r="G11" s="23"/>
       <c r="I11" s="24"/>
-      <c r="J11" s="43" t="s">
+      <c r="J11" s="51" t="s">
         <v>716</v>
       </c>
       <c r="K11" s="23"/>
-      <c r="M11" s="68"/>
-      <c r="N11" s="43" t="s">
+      <c r="M11" s="38"/>
+      <c r="N11" s="51" t="s">
         <v>716</v>
       </c>
       <c r="P11" s="23"/>
       <c r="R11" s="24"/>
-      <c r="S11" s="43" t="s">
+      <c r="S11" s="51" t="s">
         <v>716</v>
       </c>
       <c r="T11" s="23"/>
     </row>
     <row r="12" spans="4:20">
-      <c r="D12" s="68"/>
-      <c r="E12" s="70"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="52"/>
       <c r="G12" s="23"/>
       <c r="I12" s="24"/>
-      <c r="J12" s="44"/>
+      <c r="J12" s="62"/>
       <c r="K12" s="23"/>
-      <c r="M12" s="68"/>
-      <c r="N12" s="70"/>
+      <c r="M12" s="38"/>
+      <c r="N12" s="52"/>
       <c r="P12" s="23"/>
       <c r="R12" s="24"/>
-      <c r="S12" s="44"/>
+      <c r="S12" s="62"/>
       <c r="T12" s="23"/>
     </row>
     <row r="13" spans="4:20">
-      <c r="D13" s="69"/>
+      <c r="D13" s="39"/>
       <c r="G13" s="23"/>
       <c r="I13" s="24"/>
       <c r="K13" s="23"/>
-      <c r="M13" s="69"/>
+      <c r="M13" s="39"/>
       <c r="P13" s="23"/>
       <c r="R13" s="24"/>
       <c r="T13" s="23"/>
     </row>
     <row r="14" spans="4:20" ht="16.5" customHeight="1">
       <c r="D14" s="24"/>
-      <c r="E14" s="71" t="s">
+      <c r="E14" s="40" t="s">
         <v>719</v>
       </c>
-      <c r="F14" s="72"/>
-      <c r="G14" s="73"/>
-      <c r="I14" s="57" t="s">
+      <c r="F14" s="41"/>
+      <c r="G14" s="42"/>
+      <c r="I14" s="53" t="s">
         <v>725</v>
       </c>
-      <c r="J14" s="58"/>
-      <c r="K14" s="63"/>
+      <c r="J14" s="54"/>
+      <c r="K14" s="55"/>
       <c r="M14" s="24"/>
-      <c r="N14" s="71" t="s">
+      <c r="N14" s="40" t="s">
         <v>728</v>
       </c>
-      <c r="O14" s="72"/>
-      <c r="P14" s="73"/>
-      <c r="R14" s="57" t="s">
+      <c r="O14" s="41"/>
+      <c r="P14" s="42"/>
+      <c r="R14" s="53" t="s">
         <v>725</v>
       </c>
-      <c r="S14" s="58"/>
-      <c r="T14" s="63"/>
+      <c r="S14" s="54"/>
+      <c r="T14" s="55"/>
     </row>
     <row r="15" spans="4:20">
       <c r="D15" s="24"/>
-      <c r="E15" s="74"/>
-      <c r="F15" s="75"/>
-      <c r="G15" s="76"/>
-      <c r="I15" s="50"/>
-      <c r="J15" s="51"/>
-      <c r="K15" s="52"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="45"/>
+      <c r="I15" s="56"/>
+      <c r="J15" s="57"/>
+      <c r="K15" s="58"/>
       <c r="M15" s="24"/>
-      <c r="N15" s="74"/>
-      <c r="O15" s="75"/>
-      <c r="P15" s="76"/>
-      <c r="R15" s="50"/>
-      <c r="S15" s="51"/>
-      <c r="T15" s="52"/>
+      <c r="N15" s="43"/>
+      <c r="O15" s="44"/>
+      <c r="P15" s="45"/>
+      <c r="R15" s="56"/>
+      <c r="S15" s="57"/>
+      <c r="T15" s="58"/>
     </row>
     <row r="16" spans="4:20">
       <c r="D16" s="24"/>
-      <c r="E16" s="74"/>
-      <c r="F16" s="75"/>
-      <c r="G16" s="76"/>
-      <c r="I16" s="50"/>
-      <c r="J16" s="51"/>
-      <c r="K16" s="52"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="45"/>
+      <c r="I16" s="56"/>
+      <c r="J16" s="57"/>
+      <c r="K16" s="58"/>
       <c r="M16" s="24"/>
-      <c r="N16" s="74"/>
-      <c r="O16" s="75"/>
-      <c r="P16" s="76"/>
-      <c r="R16" s="50"/>
-      <c r="S16" s="51"/>
-      <c r="T16" s="52"/>
+      <c r="N16" s="43"/>
+      <c r="O16" s="44"/>
+      <c r="P16" s="45"/>
+      <c r="R16" s="56"/>
+      <c r="S16" s="57"/>
+      <c r="T16" s="58"/>
     </row>
     <row r="17" spans="4:20" ht="17.25" thickBot="1">
       <c r="D17" s="25"/>
-      <c r="E17" s="77"/>
-      <c r="F17" s="78"/>
-      <c r="G17" s="79"/>
-      <c r="I17" s="64"/>
-      <c r="J17" s="65"/>
-      <c r="K17" s="66"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="47"/>
+      <c r="G17" s="48"/>
+      <c r="I17" s="59"/>
+      <c r="J17" s="60"/>
+      <c r="K17" s="61"/>
       <c r="M17" s="25"/>
-      <c r="N17" s="77"/>
-      <c r="O17" s="78"/>
-      <c r="P17" s="79"/>
-      <c r="R17" s="64"/>
-      <c r="S17" s="65"/>
-      <c r="T17" s="66"/>
+      <c r="N17" s="46"/>
+      <c r="O17" s="47"/>
+      <c r="P17" s="48"/>
+      <c r="R17" s="59"/>
+      <c r="S17" s="60"/>
+      <c r="T17" s="61"/>
     </row>
     <row r="19" spans="4:20" ht="17.25" thickBot="1">
-      <c r="D19" s="36" t="s">
+      <c r="D19" s="69" t="s">
         <v>368</v>
       </c>
-      <c r="E19" s="36"/>
-      <c r="F19" s="36"/>
-      <c r="H19" s="36" t="s">
+      <c r="E19" s="69"/>
+      <c r="F19" s="69"/>
+      <c r="H19" s="69" t="s">
         <v>367</v>
       </c>
-      <c r="I19" s="36"/>
-      <c r="J19" s="36"/>
-      <c r="K19" s="36"/>
-      <c r="R19" s="36" t="s">
+      <c r="I19" s="69"/>
+      <c r="J19" s="69"/>
+      <c r="K19" s="69"/>
+      <c r="R19" s="69" t="s">
         <v>724</v>
       </c>
-      <c r="S19" s="36"/>
-      <c r="T19" s="36"/>
+      <c r="S19" s="69"/>
+      <c r="T19" s="69"/>
     </row>
     <row r="20" spans="4:20">
-      <c r="D20" s="47" t="s">
+      <c r="D20" s="77" t="s">
         <v>721</v>
       </c>
-      <c r="E20" s="48"/>
-      <c r="F20" s="49"/>
+      <c r="E20" s="78"/>
+      <c r="F20" s="79"/>
       <c r="H20" s="26"/>
-      <c r="I20" s="62" t="s">
+      <c r="I20" s="68" t="s">
         <v>717</v>
       </c>
       <c r="J20" s="21"/>
@@ -9082,56 +9114,56 @@
       <c r="N20" s="21"/>
       <c r="O20" s="21"/>
       <c r="P20" s="22"/>
-      <c r="R20" s="47" t="s">
+      <c r="R20" s="77" t="s">
         <v>725</v>
       </c>
-      <c r="S20" s="48"/>
-      <c r="T20" s="49"/>
+      <c r="S20" s="78"/>
+      <c r="T20" s="79"/>
     </row>
     <row r="21" spans="4:20">
-      <c r="D21" s="50"/>
-      <c r="E21" s="51"/>
-      <c r="F21" s="52"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="57"/>
+      <c r="F21" s="58"/>
       <c r="H21" s="24"/>
-      <c r="I21" s="56"/>
+      <c r="I21" s="50"/>
       <c r="K21" s="23"/>
       <c r="M21" s="24"/>
       <c r="P21" s="23"/>
-      <c r="R21" s="50"/>
-      <c r="S21" s="51"/>
-      <c r="T21" s="52"/>
+      <c r="R21" s="56"/>
+      <c r="S21" s="57"/>
+      <c r="T21" s="58"/>
     </row>
     <row r="22" spans="4:20">
-      <c r="D22" s="50"/>
-      <c r="E22" s="51"/>
-      <c r="F22" s="52"/>
+      <c r="D22" s="56"/>
+      <c r="E22" s="57"/>
+      <c r="F22" s="58"/>
       <c r="H22" s="24"/>
-      <c r="I22" s="43" t="s">
+      <c r="I22" s="51" t="s">
         <v>716</v>
       </c>
-      <c r="J22" s="41" t="s">
+      <c r="J22" s="74" t="s">
         <v>726</v>
       </c>
       <c r="K22" s="23"/>
       <c r="M22" s="24"/>
       <c r="P22" s="23"/>
-      <c r="R22" s="50"/>
-      <c r="S22" s="51"/>
-      <c r="T22" s="52"/>
+      <c r="R22" s="56"/>
+      <c r="S22" s="57"/>
+      <c r="T22" s="58"/>
     </row>
     <row r="23" spans="4:20">
-      <c r="D23" s="53"/>
-      <c r="E23" s="54"/>
-      <c r="F23" s="55"/>
+      <c r="D23" s="65"/>
+      <c r="E23" s="66"/>
+      <c r="F23" s="80"/>
       <c r="H23" s="24"/>
-      <c r="I23" s="44"/>
-      <c r="J23" s="42"/>
+      <c r="I23" s="62"/>
+      <c r="J23" s="75"/>
       <c r="K23" s="23"/>
       <c r="M23" s="24"/>
       <c r="P23" s="23"/>
-      <c r="R23" s="53"/>
-      <c r="S23" s="54"/>
-      <c r="T23" s="55"/>
+      <c r="R23" s="65"/>
+      <c r="S23" s="66"/>
+      <c r="T23" s="80"/>
     </row>
     <row r="24" spans="4:20">
       <c r="D24" s="24"/>
@@ -9147,77 +9179,77 @@
     </row>
     <row r="25" spans="4:20" ht="16.5" customHeight="1">
       <c r="D25" s="24"/>
-      <c r="E25" s="43" t="s">
+      <c r="E25" s="51" t="s">
         <v>716</v>
       </c>
       <c r="F25" s="23"/>
-      <c r="H25" s="57" t="s">
+      <c r="H25" s="53" t="s">
         <v>729</v>
       </c>
-      <c r="I25" s="58"/>
-      <c r="J25" s="59"/>
+      <c r="I25" s="54"/>
+      <c r="J25" s="63"/>
       <c r="K25" s="23"/>
       <c r="M25" s="24"/>
       <c r="P25" s="23"/>
       <c r="R25" s="24"/>
-      <c r="S25" s="43" t="s">
+      <c r="S25" s="51" t="s">
         <v>716</v>
       </c>
       <c r="T25" s="23"/>
     </row>
     <row r="26" spans="4:20">
       <c r="D26" s="24"/>
-      <c r="E26" s="44"/>
+      <c r="E26" s="62"/>
       <c r="F26" s="23"/>
-      <c r="H26" s="50"/>
-      <c r="I26" s="51"/>
-      <c r="J26" s="60"/>
+      <c r="H26" s="56"/>
+      <c r="I26" s="57"/>
+      <c r="J26" s="64"/>
       <c r="K26" s="23"/>
       <c r="M26" s="24"/>
       <c r="P26" s="23"/>
       <c r="R26" s="24"/>
-      <c r="S26" s="44"/>
+      <c r="S26" s="62"/>
       <c r="T26" s="23"/>
     </row>
     <row r="27" spans="4:20">
       <c r="D27" s="24"/>
-      <c r="E27" s="45" t="s">
+      <c r="E27" s="49" t="s">
         <v>717</v>
       </c>
       <c r="F27" s="23"/>
-      <c r="H27" s="50"/>
-      <c r="I27" s="51"/>
-      <c r="J27" s="60"/>
-      <c r="K27" s="37" t="s">
+      <c r="H27" s="56"/>
+      <c r="I27" s="57"/>
+      <c r="J27" s="64"/>
+      <c r="K27" s="70" t="s">
         <v>718</v>
       </c>
       <c r="M27" s="24"/>
       <c r="P27" s="23"/>
       <c r="R27" s="24"/>
-      <c r="S27" s="45" t="s">
+      <c r="S27" s="49" t="s">
         <v>717</v>
       </c>
       <c r="T27" s="23"/>
     </row>
     <row r="28" spans="4:20" ht="16.5" customHeight="1">
       <c r="D28" s="24"/>
-      <c r="E28" s="56"/>
+      <c r="E28" s="50"/>
       <c r="F28" s="23"/>
-      <c r="H28" s="53"/>
-      <c r="I28" s="54"/>
-      <c r="J28" s="61"/>
-      <c r="K28" s="38"/>
+      <c r="H28" s="65"/>
+      <c r="I28" s="66"/>
+      <c r="J28" s="67"/>
+      <c r="K28" s="71"/>
       <c r="M28" s="24"/>
       <c r="P28" s="23"/>
       <c r="R28" s="24"/>
-      <c r="S28" s="56"/>
+      <c r="S28" s="50"/>
       <c r="T28" s="23"/>
     </row>
     <row r="29" spans="4:20">
       <c r="D29" s="24"/>
       <c r="F29" s="23"/>
       <c r="H29" s="24"/>
-      <c r="K29" s="39"/>
+      <c r="K29" s="72"/>
       <c r="M29" s="24"/>
       <c r="P29" s="23"/>
       <c r="R29" s="24"/>
@@ -9228,10 +9260,10 @@
       <c r="E30" s="27"/>
       <c r="F30" s="28"/>
       <c r="H30" s="24"/>
-      <c r="I30" s="43" t="s">
+      <c r="I30" s="51" t="s">
         <v>716</v>
       </c>
-      <c r="K30" s="39"/>
+      <c r="K30" s="72"/>
       <c r="M30" s="25"/>
       <c r="N30" s="27"/>
       <c r="O30" s="27"/>
@@ -9242,21 +9274,21 @@
     </row>
     <row r="31" spans="4:20">
       <c r="H31" s="24"/>
-      <c r="I31" s="44"/>
-      <c r="K31" s="39"/>
+      <c r="I31" s="62"/>
+      <c r="K31" s="72"/>
     </row>
     <row r="32" spans="4:20">
       <c r="H32" s="24"/>
-      <c r="I32" s="45" t="s">
+      <c r="I32" s="49" t="s">
         <v>717</v>
       </c>
-      <c r="K32" s="39"/>
+      <c r="K32" s="72"/>
     </row>
     <row r="33" spans="8:24" ht="17.25" thickBot="1">
       <c r="H33" s="25"/>
-      <c r="I33" s="46"/>
+      <c r="I33" s="76"/>
       <c r="J33" s="27"/>
-      <c r="K33" s="40"/>
+      <c r="K33" s="73"/>
     </row>
     <row r="47" spans="8:24">
       <c r="X47" t="s">
@@ -9265,24 +9297,6 @@
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="D7:D13"/>
-    <mergeCell ref="E14:G17"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="I14:K17"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="S11:S12"/>
-    <mergeCell ref="R14:T17"/>
-    <mergeCell ref="M7:M13"/>
-    <mergeCell ref="O9:O10"/>
-    <mergeCell ref="N11:N12"/>
-    <mergeCell ref="N14:P17"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="H25:J28"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="I22:I23"/>
-    <mergeCell ref="J11:J12"/>
     <mergeCell ref="R6:T6"/>
     <mergeCell ref="R19:T19"/>
     <mergeCell ref="D19:F19"/>
@@ -9299,6 +9313,24 @@
     <mergeCell ref="M6:P6"/>
     <mergeCell ref="D20:F23"/>
     <mergeCell ref="E27:E28"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="H25:J28"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="S11:S12"/>
+    <mergeCell ref="R14:T17"/>
+    <mergeCell ref="M7:M13"/>
+    <mergeCell ref="O9:O10"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="N14:P17"/>
+    <mergeCell ref="D7:D13"/>
+    <mergeCell ref="E14:G17"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="I14:K17"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/PLC/IO List.xlsx
+++ b/PLC/IO List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EZENIC\Desktop\Project-Second\PLC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B51D53EB-C2E6-4AC8-811A-E779848FBC14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9A51A6B-5AAA-4444-86A2-0AB88C7199FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{E8A3CD3B-D612-4B37-A180-F6C335096DC9}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="11280" windowHeight="15585" xr2:uid="{E8A3CD3B-D612-4B37-A180-F6C335096DC9}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="829">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1192" uniqueCount="874">
   <si>
     <t>X10</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2966,6 +2966,153 @@
   </si>
   <si>
     <t>수작업9 START</t>
+  </si>
+  <si>
+    <t>출하장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PASS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M90</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGV1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M91</t>
+  </si>
+  <si>
+    <t>M92</t>
+  </si>
+  <si>
+    <t>M93</t>
+  </si>
+  <si>
+    <t>M94</t>
+  </si>
+  <si>
+    <t>M95</t>
+  </si>
+  <si>
+    <t>AGV2</t>
+  </si>
+  <si>
+    <t>AGV3</t>
+  </si>
+  <si>
+    <t>AGV4</t>
+  </si>
+  <si>
+    <t>AGV5</t>
+  </si>
+  <si>
+    <t>AGV6</t>
+  </si>
+  <si>
+    <t>M1190</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M1191</t>
+  </si>
+  <si>
+    <t>M1192</t>
+  </si>
+  <si>
+    <t>M1193</t>
+  </si>
+  <si>
+    <t>M1194</t>
+  </si>
+  <si>
+    <t>M1195</t>
+  </si>
+  <si>
+    <t>M1196</t>
+  </si>
+  <si>
+    <t>M1197</t>
+  </si>
+  <si>
+    <t>M2228</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M2229</t>
+  </si>
+  <si>
+    <t>M2230</t>
+  </si>
+  <si>
+    <t>M2231</t>
+  </si>
+  <si>
+    <t>M2232</t>
+  </si>
+  <si>
+    <t>D01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGV1 기동 MAIN 신호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGV2 기동 MAIN 신호</t>
+  </si>
+  <si>
+    <t>AGV3 기동 MAIN 신호</t>
+  </si>
+  <si>
+    <t>AGV4 기동 MAIN 신호</t>
+  </si>
+  <si>
+    <t>AGV5 기동 MAIN 신호</t>
+  </si>
+  <si>
+    <t>AGV6 기동 MAIN 신호</t>
+  </si>
+  <si>
+    <t>AGV7 기동 MAIN 신호</t>
+  </si>
+  <si>
+    <t>T40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGV1 기동 MAIN 딜레이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M150</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M151</t>
+  </si>
+  <si>
+    <t>M152</t>
+  </si>
+  <si>
+    <t>M153</t>
+  </si>
+  <si>
+    <t>M154</t>
+  </si>
+  <si>
+    <t>M155</t>
+  </si>
+  <si>
+    <t>M156</t>
   </si>
 </sst>
 </file>
@@ -4071,7 +4218,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{228BF0B7-E586-4CC1-BF31-0F024BABECA2}">
-  <dimension ref="B3:K88"/>
+  <dimension ref="B3:K105"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="3" width="9" style="1"/>
@@ -5031,8 +5178,12 @@
       <c r="I39" s="6" t="s">
         <v>478</v>
       </c>
-      <c r="J39" s="5"/>
-      <c r="K39" s="6"/>
+      <c r="J39" s="5" t="s">
+        <v>865</v>
+      </c>
+      <c r="K39" s="6" t="s">
+        <v>866</v>
+      </c>
     </row>
     <row r="40" spans="2:11">
       <c r="B40" s="5" t="s">
@@ -5189,8 +5340,12 @@
       <c r="G46" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="H46" s="5"/>
-      <c r="I46" s="6"/>
+      <c r="H46" s="5" t="s">
+        <v>832</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>833</v>
+      </c>
       <c r="J46" s="5"/>
       <c r="K46" s="6"/>
     </row>
@@ -5209,8 +5364,12 @@
       <c r="G47" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="H47" s="5"/>
-      <c r="I47" s="6"/>
+      <c r="H47" s="5" t="s">
+        <v>834</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>839</v>
+      </c>
       <c r="J47" s="5"/>
       <c r="K47" s="6"/>
     </row>
@@ -5229,8 +5388,12 @@
       <c r="G48" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="H48" s="5"/>
-      <c r="I48" s="6"/>
+      <c r="H48" s="5" t="s">
+        <v>835</v>
+      </c>
+      <c r="I48" s="6" t="s">
+        <v>840</v>
+      </c>
       <c r="J48" s="5"/>
       <c r="K48" s="6"/>
     </row>
@@ -5246,10 +5409,10 @@
         <v>194</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>453</v>
+        <v>836</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>456</v>
+        <v>841</v>
       </c>
       <c r="J49" s="5"/>
       <c r="K49" s="6"/>
@@ -5266,10 +5429,10 @@
         <v>195</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>454</v>
+        <v>837</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>455</v>
+        <v>842</v>
       </c>
       <c r="J50" s="5"/>
       <c r="K50" s="6"/>
@@ -5286,10 +5449,10 @@
         <v>196</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>457</v>
+        <v>838</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>465</v>
+        <v>843</v>
       </c>
       <c r="J51" s="5"/>
       <c r="K51" s="6"/>
@@ -5307,12 +5470,8 @@
       <c r="G52" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="H52" s="5" t="s">
-        <v>458</v>
-      </c>
-      <c r="I52" s="6" t="s">
-        <v>466</v>
-      </c>
+      <c r="H52" s="5"/>
+      <c r="I52" s="6"/>
       <c r="J52" s="5"/>
       <c r="K52" s="6"/>
     </row>
@@ -5330,10 +5489,10 @@
         <v>376</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>459</v>
+        <v>867</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>467</v>
+        <v>858</v>
       </c>
       <c r="J53" s="5"/>
       <c r="K53" s="6"/>
@@ -5352,10 +5511,10 @@
         <v>377</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>460</v>
+        <v>868</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>468</v>
+        <v>859</v>
       </c>
       <c r="J54" s="5"/>
       <c r="K54" s="6"/>
@@ -5374,10 +5533,10 @@
         <v>378</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>461</v>
+        <v>869</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>469</v>
+        <v>860</v>
       </c>
       <c r="J55" s="5"/>
       <c r="K55" s="6"/>
@@ -5396,10 +5555,10 @@
         <v>379</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>462</v>
+        <v>870</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>470</v>
+        <v>861</v>
       </c>
       <c r="J56" s="5"/>
       <c r="K56" s="6"/>
@@ -5418,10 +5577,10 @@
         <v>380</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>463</v>
+        <v>871</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>471</v>
+        <v>862</v>
       </c>
       <c r="J57" s="5"/>
       <c r="K57" s="6"/>
@@ -5430,10 +5589,10 @@
       <c r="F58" s="5"/>
       <c r="G58" s="6"/>
       <c r="H58" s="5" t="s">
-        <v>464</v>
+        <v>872</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>472</v>
+        <v>863</v>
       </c>
       <c r="J58" s="6"/>
       <c r="K58" s="6"/>
@@ -5441,80 +5600,48 @@
     <row r="59" spans="2:11">
       <c r="F59" s="5"/>
       <c r="G59" s="6"/>
-      <c r="H59" s="5"/>
-      <c r="I59" s="6"/>
+      <c r="H59" s="5" t="s">
+        <v>873</v>
+      </c>
+      <c r="I59" s="6" t="s">
+        <v>864</v>
+      </c>
       <c r="J59" s="6"/>
       <c r="K59" s="6"/>
     </row>
     <row r="60" spans="2:11">
       <c r="F60" s="5"/>
       <c r="G60" s="6"/>
-      <c r="H60" s="5" t="s">
-        <v>753</v>
-      </c>
-      <c r="I60" s="6" t="s">
-        <v>762</v>
-      </c>
       <c r="J60" s="6"/>
       <c r="K60" s="6"/>
     </row>
     <row r="61" spans="2:11">
       <c r="F61" s="5"/>
       <c r="G61" s="6"/>
-      <c r="H61" s="5" t="s">
-        <v>754</v>
-      </c>
-      <c r="I61" s="6" t="s">
-        <v>786</v>
-      </c>
       <c r="J61" s="6"/>
       <c r="K61" s="6"/>
     </row>
     <row r="62" spans="2:11">
       <c r="F62" s="5"/>
       <c r="G62" s="6"/>
-      <c r="H62" s="5" t="s">
-        <v>755</v>
-      </c>
-      <c r="I62" s="6" t="s">
-        <v>787</v>
-      </c>
       <c r="J62" s="6"/>
       <c r="K62" s="6"/>
     </row>
     <row r="63" spans="2:11">
       <c r="F63" s="5"/>
       <c r="G63" s="6"/>
-      <c r="H63" s="5" t="s">
-        <v>756</v>
-      </c>
-      <c r="I63" s="6" t="s">
-        <v>788</v>
-      </c>
       <c r="J63" s="6"/>
       <c r="K63" s="6"/>
     </row>
     <row r="64" spans="2:11">
       <c r="F64" s="5"/>
       <c r="G64" s="6"/>
-      <c r="H64" s="5" t="s">
-        <v>757</v>
-      </c>
-      <c r="I64" s="6" t="s">
-        <v>794</v>
-      </c>
       <c r="J64" s="6"/>
       <c r="K64" s="6"/>
     </row>
     <row r="65" spans="6:11">
       <c r="F65" s="5"/>
       <c r="G65" s="6"/>
-      <c r="H65" s="5" t="s">
-        <v>758</v>
-      </c>
-      <c r="I65" s="6" t="s">
-        <v>789</v>
-      </c>
       <c r="J65" s="6"/>
       <c r="K65" s="6"/>
     </row>
@@ -5522,10 +5649,10 @@
       <c r="F66" s="5"/>
       <c r="G66" s="6"/>
       <c r="H66" s="5" t="s">
-        <v>759</v>
+        <v>453</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>790</v>
+        <v>456</v>
       </c>
       <c r="J66" s="6"/>
       <c r="K66" s="6"/>
@@ -5534,10 +5661,10 @@
       <c r="F67" s="5"/>
       <c r="G67" s="6"/>
       <c r="H67" s="5" t="s">
-        <v>760</v>
+        <v>454</v>
       </c>
       <c r="I67" s="6" t="s">
-        <v>791</v>
+        <v>455</v>
       </c>
       <c r="J67" s="6"/>
       <c r="K67" s="6"/>
@@ -5546,10 +5673,10 @@
       <c r="F68" s="5"/>
       <c r="G68" s="6"/>
       <c r="H68" s="5" t="s">
-        <v>761</v>
+        <v>457</v>
       </c>
       <c r="I68" s="6" t="s">
-        <v>792</v>
+        <v>465</v>
       </c>
       <c r="J68" s="6"/>
       <c r="K68" s="6"/>
@@ -5558,10 +5685,10 @@
       <c r="F69" s="5"/>
       <c r="G69" s="6"/>
       <c r="H69" s="5" t="s">
-        <v>783</v>
+        <v>458</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>793</v>
+        <v>466</v>
       </c>
       <c r="J69" s="6"/>
       <c r="K69" s="6"/>
@@ -5569,32 +5696,48 @@
     <row r="70" spans="6:11">
       <c r="F70" s="5"/>
       <c r="G70" s="6"/>
-      <c r="H70" s="5"/>
-      <c r="I70" s="6"/>
+      <c r="H70" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="I70" s="6" t="s">
+        <v>467</v>
+      </c>
       <c r="J70" s="6"/>
       <c r="K70" s="6"/>
     </row>
     <row r="71" spans="6:11">
       <c r="F71" s="5"/>
       <c r="G71" s="6"/>
-      <c r="H71" s="5"/>
-      <c r="I71" s="6"/>
+      <c r="H71" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="I71" s="6" t="s">
+        <v>468</v>
+      </c>
       <c r="J71" s="6"/>
       <c r="K71" s="6"/>
     </row>
     <row r="72" spans="6:11">
       <c r="F72" s="5"/>
       <c r="G72" s="6"/>
-      <c r="H72" s="5"/>
-      <c r="I72" s="6"/>
+      <c r="H72" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="I72" s="6" t="s">
+        <v>469</v>
+      </c>
       <c r="J72" s="6"/>
       <c r="K72" s="6"/>
     </row>
     <row r="73" spans="6:11">
       <c r="F73" s="5"/>
       <c r="G73" s="6"/>
-      <c r="H73" s="5"/>
-      <c r="I73" s="6"/>
+      <c r="H73" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="I73" s="6" t="s">
+        <v>470</v>
+      </c>
       <c r="J73" s="6"/>
       <c r="K73" s="6"/>
     </row>
@@ -5602,10 +5745,10 @@
       <c r="F74" s="5"/>
       <c r="G74" s="6"/>
       <c r="H74" s="5" t="s">
-        <v>730</v>
+        <v>463</v>
       </c>
       <c r="I74" s="6" t="s">
-        <v>744</v>
+        <v>471</v>
       </c>
       <c r="J74" s="6"/>
       <c r="K74" s="6"/>
@@ -5614,10 +5757,10 @@
       <c r="F75" s="5"/>
       <c r="G75" s="6"/>
       <c r="H75" s="5" t="s">
-        <v>731</v>
+        <v>464</v>
       </c>
       <c r="I75" s="6" t="s">
-        <v>745</v>
+        <v>472</v>
       </c>
       <c r="J75" s="6"/>
       <c r="K75" s="6"/>
@@ -5625,12 +5768,8 @@
     <row r="76" spans="6:11">
       <c r="F76" s="5"/>
       <c r="G76" s="6"/>
-      <c r="H76" s="5" t="s">
-        <v>732</v>
-      </c>
-      <c r="I76" s="6" t="s">
-        <v>746</v>
-      </c>
+      <c r="H76" s="5"/>
+      <c r="I76" s="6"/>
       <c r="J76" s="6"/>
       <c r="K76" s="6"/>
     </row>
@@ -5638,97 +5777,217 @@
       <c r="F77" s="5"/>
       <c r="G77" s="6"/>
       <c r="H77" s="5" t="s">
-        <v>733</v>
+        <v>753</v>
       </c>
       <c r="I77" s="6" t="s">
-        <v>747</v>
+        <v>762</v>
       </c>
       <c r="J77" s="6"/>
       <c r="K77" s="6"/>
     </row>
     <row r="78" spans="6:11">
       <c r="H78" s="5" t="s">
-        <v>734</v>
+        <v>754</v>
       </c>
       <c r="I78" s="6" t="s">
-        <v>748</v>
+        <v>786</v>
       </c>
     </row>
     <row r="79" spans="6:11">
       <c r="H79" s="5" t="s">
-        <v>735</v>
+        <v>755</v>
       </c>
       <c r="I79" s="6" t="s">
-        <v>749</v>
+        <v>787</v>
       </c>
     </row>
     <row r="80" spans="6:11">
       <c r="H80" s="5" t="s">
-        <v>736</v>
+        <v>756</v>
       </c>
       <c r="I80" s="6" t="s">
-        <v>750</v>
+        <v>788</v>
       </c>
     </row>
     <row r="81" spans="8:9">
       <c r="H81" s="5" t="s">
-        <v>737</v>
+        <v>757</v>
       </c>
       <c r="I81" s="6" t="s">
-        <v>751</v>
+        <v>794</v>
       </c>
     </row>
     <row r="82" spans="8:9">
       <c r="H82" s="5" t="s">
-        <v>738</v>
+        <v>758</v>
       </c>
       <c r="I82" s="6" t="s">
-        <v>752</v>
+        <v>789</v>
       </c>
     </row>
     <row r="83" spans="8:9">
       <c r="H83" s="5" t="s">
-        <v>739</v>
+        <v>759</v>
       </c>
       <c r="I83" s="6" t="s">
-        <v>744</v>
+        <v>790</v>
       </c>
     </row>
     <row r="84" spans="8:9">
       <c r="H84" s="5" t="s">
-        <v>740</v>
+        <v>760</v>
       </c>
       <c r="I84" s="6" t="s">
-        <v>745</v>
+        <v>791</v>
       </c>
     </row>
     <row r="85" spans="8:9">
       <c r="H85" s="5" t="s">
-        <v>741</v>
+        <v>761</v>
       </c>
       <c r="I85" s="6" t="s">
-        <v>746</v>
+        <v>792</v>
       </c>
     </row>
     <row r="86" spans="8:9">
       <c r="H86" s="5" t="s">
-        <v>742</v>
+        <v>783</v>
       </c>
       <c r="I86" s="6" t="s">
-        <v>744</v>
+        <v>793</v>
       </c>
     </row>
     <row r="87" spans="8:9">
-      <c r="H87" s="5" t="s">
-        <v>743</v>
-      </c>
-      <c r="I87" s="6" t="s">
-        <v>745</v>
-      </c>
+      <c r="H87" s="5"/>
+      <c r="I87" s="6"/>
     </row>
     <row r="88" spans="8:9">
       <c r="H88" s="5"/>
-      <c r="I88" s="6" t="s">
+      <c r="I88" s="6"/>
+    </row>
+    <row r="89" spans="8:9">
+      <c r="H89" s="5"/>
+      <c r="I89" s="6"/>
+    </row>
+    <row r="90" spans="8:9">
+      <c r="H90" s="5"/>
+      <c r="I90" s="6"/>
+    </row>
+    <row r="91" spans="8:9">
+      <c r="H91" s="5" t="s">
+        <v>730</v>
+      </c>
+      <c r="I91" s="6" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="92" spans="8:9">
+      <c r="H92" s="5" t="s">
+        <v>731</v>
+      </c>
+      <c r="I92" s="6" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="93" spans="8:9">
+      <c r="H93" s="5" t="s">
+        <v>732</v>
+      </c>
+      <c r="I93" s="6" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="94" spans="8:9">
+      <c r="H94" s="5" t="s">
+        <v>733</v>
+      </c>
+      <c r="I94" s="6" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="95" spans="8:9">
+      <c r="H95" s="5" t="s">
+        <v>734</v>
+      </c>
+      <c r="I95" s="6" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="96" spans="8:9">
+      <c r="H96" s="5" t="s">
+        <v>735</v>
+      </c>
+      <c r="I96" s="6" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="97" spans="8:9">
+      <c r="H97" s="5" t="s">
+        <v>736</v>
+      </c>
+      <c r="I97" s="6" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="98" spans="8:9">
+      <c r="H98" s="5" t="s">
+        <v>737</v>
+      </c>
+      <c r="I98" s="6" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="99" spans="8:9">
+      <c r="H99" s="5" t="s">
+        <v>738</v>
+      </c>
+      <c r="I99" s="6" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="100" spans="8:9">
+      <c r="H100" s="5" t="s">
+        <v>739</v>
+      </c>
+      <c r="I100" s="6" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="101" spans="8:9">
+      <c r="H101" s="5" t="s">
+        <v>740</v>
+      </c>
+      <c r="I101" s="6" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="102" spans="8:9">
+      <c r="H102" s="5" t="s">
+        <v>741</v>
+      </c>
+      <c r="I102" s="6" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="103" spans="8:9">
+      <c r="H103" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="I103" s="6" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="104" spans="8:9">
+      <c r="H104" s="5" t="s">
+        <v>743</v>
+      </c>
+      <c r="I104" s="6" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="105" spans="8:9">
+      <c r="H105" s="5"/>
+      <c r="I105" s="6" t="s">
         <v>746</v>
       </c>
     </row>
@@ -7374,7 +7633,7 @@
         <v>616</v>
       </c>
       <c r="U48" s="10" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="V48" s="5" t="s">
         <v>324</v>
@@ -7434,7 +7693,7 @@
         <v>617</v>
       </c>
       <c r="U49" s="10" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="V49" s="9" t="s">
         <v>325</v>
@@ -7541,7 +7800,9 @@
       <c r="T51" s="9" t="s">
         <v>619</v>
       </c>
-      <c r="U51" s="10"/>
+      <c r="U51" s="10" t="s">
+        <v>16</v>
+      </c>
       <c r="V51" s="9"/>
       <c r="W51" s="9" t="s">
         <v>688</v>
@@ -7596,7 +7857,7 @@
         <v>620</v>
       </c>
       <c r="U52" s="10" t="s">
-        <v>22</v>
+        <v>830</v>
       </c>
       <c r="V52" s="9" t="s">
         <v>327</v>
@@ -7656,7 +7917,7 @@
         <v>621</v>
       </c>
       <c r="U53" s="10" t="s">
-        <v>21</v>
+        <v>831</v>
       </c>
       <c r="V53" s="9" t="s">
         <v>259</v>
@@ -7842,7 +8103,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EA47EA4-7B31-40FE-9AED-CE45ED8264B2}">
-  <dimension ref="B2:U34"/>
+  <dimension ref="B2:U49"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="4" max="4" width="20.625" customWidth="1"/>
@@ -8314,13 +8575,13 @@
       <c r="O12" s="6"/>
       <c r="P12" s="6"/>
       <c r="Q12" s="6"/>
-      <c r="S12" s="19">
+      <c r="S12" s="5">
         <v>611</v>
       </c>
       <c r="T12" s="6" t="s">
         <v>430</v>
       </c>
-      <c r="U12" s="20" t="s">
+      <c r="U12" s="6" t="s">
         <v>436</v>
       </c>
     </row>
@@ -8378,13 +8639,13 @@
       <c r="O14" s="6"/>
       <c r="P14" s="6"/>
       <c r="Q14" s="6"/>
-      <c r="S14" s="19">
+      <c r="S14" s="5">
         <v>621</v>
       </c>
       <c r="T14" s="6" t="s">
         <v>431</v>
       </c>
-      <c r="U14" s="20" t="s">
+      <c r="U14" s="6" t="s">
         <v>442</v>
       </c>
     </row>
@@ -8430,13 +8691,13 @@
       <c r="O16" s="6"/>
       <c r="P16" s="6"/>
       <c r="Q16" s="6"/>
-      <c r="S16" s="19">
+      <c r="S16" s="5">
         <v>631</v>
       </c>
       <c r="T16" s="6" t="s">
         <v>432</v>
       </c>
-      <c r="U16" s="20" t="s">
+      <c r="U16" s="6" t="s">
         <v>441</v>
       </c>
     </row>
@@ -8470,13 +8731,13 @@
       <c r="O18" s="6"/>
       <c r="P18" s="6"/>
       <c r="Q18" s="6"/>
-      <c r="S18" s="19">
+      <c r="S18" s="5">
         <v>641</v>
       </c>
       <c r="T18" s="6" t="s">
         <v>433</v>
       </c>
-      <c r="U18" s="20" t="s">
+      <c r="U18" s="6" t="s">
         <v>440</v>
       </c>
     </row>
@@ -8526,13 +8787,13 @@
       <c r="O20" s="6"/>
       <c r="P20" s="6"/>
       <c r="Q20" s="6"/>
-      <c r="S20" s="19">
+      <c r="S20" s="5">
         <v>651</v>
       </c>
       <c r="T20" s="6" t="s">
         <v>434</v>
       </c>
-      <c r="U20" s="20" t="s">
+      <c r="U20" s="6" t="s">
         <v>439</v>
       </c>
     </row>
@@ -8737,6 +8998,15 @@
       <c r="G27" s="10" t="s">
         <v>288</v>
       </c>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="12"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="13"/>
+      <c r="O27" s="14"/>
+      <c r="P27" s="14"/>
+      <c r="Q27" s="14"/>
       <c r="S27" s="5">
         <v>1300</v>
       </c>
@@ -8760,6 +9030,19 @@
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
       <c r="G28" s="10"/>
+      <c r="I28" s="34" t="s">
+        <v>40</v>
+      </c>
+      <c r="J28" s="35"/>
+      <c r="K28" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="L28" s="33"/>
+      <c r="M28" s="33"/>
+      <c r="N28" s="33"/>
+      <c r="O28" s="33"/>
+      <c r="P28" s="33"/>
+      <c r="Q28" s="33"/>
       <c r="S28" s="5">
         <v>1400</v>
       </c>
@@ -8781,6 +9064,24 @@
         <v>645</v>
       </c>
       <c r="G29" s="10"/>
+      <c r="I29" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="J29" s="35"/>
+      <c r="K29" s="33"/>
+      <c r="L29" s="33"/>
+      <c r="M29" s="33"/>
+      <c r="N29" s="33"/>
+      <c r="O29" s="33"/>
+      <c r="P29" s="33"/>
+      <c r="Q29" s="33"/>
+      <c r="S29" s="5">
+        <v>1500</v>
+      </c>
+      <c r="T29" s="6" t="s">
+        <v>829</v>
+      </c>
+      <c r="U29" s="6"/>
     </row>
     <row r="30" spans="2:21">
       <c r="B30" s="9"/>
@@ -8794,6 +9095,27 @@
       </c>
       <c r="G30" s="10" t="s">
         <v>15</v>
+      </c>
+      <c r="I30" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="J30" s="35"/>
+      <c r="K30" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L30" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="M30" s="35"/>
+      <c r="N30" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="O30" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="P30" s="35"/>
+      <c r="Q30" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="2:21">
@@ -8803,6 +9125,27 @@
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
       <c r="G31" s="10"/>
+      <c r="I31" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="K31" s="4"/>
+      <c r="L31" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="M31" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="N31" s="4"/>
+      <c r="O31" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="P31" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="Q31" s="4"/>
     </row>
     <row r="32" spans="2:21">
       <c r="B32" s="5" t="s">
@@ -8817,8 +9160,29 @@
       <c r="E32" s="9"/>
       <c r="F32" s="9"/>
       <c r="G32" s="10"/>
-    </row>
-    <row r="33" spans="2:7">
+      <c r="I32" s="5"/>
+      <c r="J32" s="5" t="s">
+        <v>844</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="L32" s="5"/>
+      <c r="M32" s="5" t="s">
+        <v>852</v>
+      </c>
+      <c r="N32" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="O32" s="16" t="s">
+        <v>857</v>
+      </c>
+      <c r="P32" s="16"/>
+      <c r="Q32" s="6" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17">
       <c r="B33" s="5" t="s">
         <v>390</v>
       </c>
@@ -8831,17 +9195,249 @@
       <c r="E33" s="9"/>
       <c r="F33" s="9"/>
       <c r="G33" s="10"/>
-    </row>
-    <row r="34" spans="2:7">
+      <c r="I33" s="9"/>
+      <c r="J33" s="9" t="s">
+        <v>845</v>
+      </c>
+      <c r="K33" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="L33" s="9"/>
+      <c r="M33" s="9" t="s">
+        <v>853</v>
+      </c>
+      <c r="N33" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="O33" s="6"/>
+      <c r="P33" s="6"/>
+      <c r="Q33" s="6"/>
+    </row>
+    <row r="34" spans="2:17">
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
       <c r="D34" s="12"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="12"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="9" t="s">
+        <v>846</v>
+      </c>
+      <c r="K34" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="L34" s="9"/>
+      <c r="M34" s="9" t="s">
+        <v>854</v>
+      </c>
+      <c r="N34" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="O34" s="6"/>
+      <c r="P34" s="6"/>
+      <c r="Q34" s="6"/>
+    </row>
+    <row r="35" spans="2:17">
+      <c r="I35" s="9"/>
+      <c r="J35" s="9" t="s">
+        <v>847</v>
+      </c>
+      <c r="K35" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="L35" s="9"/>
+      <c r="M35" s="9" t="s">
+        <v>855</v>
+      </c>
+      <c r="N35" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="O35" s="6"/>
+      <c r="P35" s="6"/>
+      <c r="Q35" s="6"/>
+    </row>
+    <row r="36" spans="2:17">
+      <c r="I36" s="9"/>
+      <c r="J36" s="9" t="s">
+        <v>848</v>
+      </c>
+      <c r="K36" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="L36" s="9"/>
+      <c r="M36" s="9" t="s">
+        <v>856</v>
+      </c>
+      <c r="N36" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="O36" s="6"/>
+      <c r="P36" s="6"/>
+      <c r="Q36" s="6"/>
+    </row>
+    <row r="37" spans="2:17">
+      <c r="I37" s="5"/>
+      <c r="J37" s="5" t="s">
+        <v>849</v>
+      </c>
+      <c r="K37" s="6"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="5"/>
+      <c r="N37" s="6"/>
+      <c r="O37" s="6"/>
+      <c r="P37" s="6"/>
+      <c r="Q37" s="6"/>
+    </row>
+    <row r="38" spans="2:17">
+      <c r="I38" s="5"/>
+      <c r="J38" s="5" t="s">
+        <v>850</v>
+      </c>
+      <c r="K38" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L38" s="5"/>
+      <c r="M38" s="5"/>
+      <c r="N38" s="6"/>
+      <c r="O38" s="6"/>
+      <c r="P38" s="6"/>
+      <c r="Q38" s="6"/>
+    </row>
+    <row r="39" spans="2:17">
+      <c r="I39" s="5"/>
+      <c r="J39" s="5" t="s">
+        <v>851</v>
+      </c>
+      <c r="K39" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="L39" s="5"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="6"/>
+      <c r="O39" s="6"/>
+      <c r="P39" s="6"/>
+      <c r="Q39" s="6"/>
+    </row>
+    <row r="40" spans="2:17">
+      <c r="I40" s="5"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="6"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="5"/>
+      <c r="N40" s="6"/>
+      <c r="O40" s="6"/>
+      <c r="P40" s="6"/>
+      <c r="Q40" s="6"/>
+    </row>
+    <row r="41" spans="2:17">
+      <c r="I41" s="5"/>
+      <c r="J41" s="5"/>
+      <c r="K41" s="6"/>
+      <c r="L41" s="5"/>
+      <c r="M41" s="5"/>
+      <c r="N41" s="6"/>
+      <c r="O41" s="6"/>
+      <c r="P41" s="6"/>
+      <c r="Q41" s="6"/>
+    </row>
+    <row r="42" spans="2:17">
+      <c r="I42" s="5"/>
+      <c r="J42" s="5"/>
+      <c r="K42" s="6"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="5"/>
+      <c r="N42" s="6"/>
+      <c r="O42" s="6"/>
+      <c r="P42" s="6"/>
+      <c r="Q42" s="6"/>
+    </row>
+    <row r="43" spans="2:17">
+      <c r="I43" s="5"/>
+      <c r="J43" s="5"/>
+      <c r="K43" s="6"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="5"/>
+      <c r="N43" s="6"/>
+      <c r="O43" s="6"/>
+      <c r="P43" s="6"/>
+      <c r="Q43" s="6"/>
+    </row>
+    <row r="44" spans="2:17">
+      <c r="I44" s="5"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="6"/>
+      <c r="L44" s="5"/>
+      <c r="M44" s="5"/>
+      <c r="N44" s="6"/>
+      <c r="O44" s="6"/>
+      <c r="P44" s="6"/>
+      <c r="Q44" s="6"/>
+    </row>
+    <row r="45" spans="2:17">
+      <c r="I45" s="5"/>
+      <c r="J45" s="5"/>
+      <c r="K45" s="6"/>
+      <c r="L45" s="5"/>
+      <c r="M45" s="5"/>
+      <c r="N45" s="6"/>
+      <c r="O45" s="6"/>
+      <c r="P45" s="6"/>
+      <c r="Q45" s="6"/>
+    </row>
+    <row r="46" spans="2:17">
+      <c r="I46" s="5"/>
+      <c r="J46" s="5"/>
+      <c r="K46" s="6"/>
+      <c r="L46" s="5"/>
+      <c r="M46" s="5"/>
+      <c r="N46" s="6"/>
+      <c r="O46" s="6"/>
+      <c r="P46" s="6"/>
+      <c r="Q46" s="6"/>
+    </row>
+    <row r="47" spans="2:17">
+      <c r="I47" s="5"/>
+      <c r="J47" s="5"/>
+      <c r="K47" s="6"/>
+      <c r="L47" s="5"/>
+      <c r="M47" s="5"/>
+      <c r="N47" s="6"/>
+      <c r="O47" s="6"/>
+      <c r="P47" s="6"/>
+      <c r="Q47" s="6"/>
+    </row>
+    <row r="48" spans="2:17">
+      <c r="I48" s="5"/>
+      <c r="J48" s="5"/>
+      <c r="K48" s="6"/>
+      <c r="L48" s="5"/>
+      <c r="M48" s="5"/>
+      <c r="N48" s="6"/>
+      <c r="O48" s="6"/>
+      <c r="P48" s="6"/>
+      <c r="Q48" s="6"/>
+    </row>
+    <row r="49" spans="9:17">
+      <c r="I49" s="15"/>
+      <c r="J49" s="15"/>
+      <c r="K49" s="12"/>
+      <c r="L49" s="11"/>
+      <c r="M49" s="11"/>
+      <c r="N49" s="12"/>
+      <c r="O49" s="12"/>
+      <c r="P49" s="12"/>
+      <c r="Q49" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="26">
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="K28:Q28"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="K29:Q29"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="O30:P30"/>
     <mergeCell ref="O5:P5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="B5:C5"/>

--- a/PLC/IO List.xlsx
+++ b/PLC/IO List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EZENIC\Desktop\Project-Second\PLC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9A51A6B-5AAA-4444-86A2-0AB88C7199FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1A01ADF-AA34-42D2-9837-C6D0970E05D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="11280" windowHeight="15585" xr2:uid="{E8A3CD3B-D612-4B37-A180-F6C335096DC9}"/>
+    <workbookView xWindow="1050" yWindow="2025" windowWidth="21600" windowHeight="11295" xr2:uid="{E8A3CD3B-D612-4B37-A180-F6C335096DC9}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="2" r:id="rId1"/>
@@ -3752,6 +3752,99 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3759,6 +3852,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3787,102 +3883,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5612,36 +5612,48 @@
     <row r="60" spans="2:11">
       <c r="F60" s="5"/>
       <c r="G60" s="6"/>
+      <c r="H60" s="5"/>
+      <c r="I60" s="6"/>
       <c r="J60" s="6"/>
       <c r="K60" s="6"/>
     </row>
     <row r="61" spans="2:11">
       <c r="F61" s="5"/>
       <c r="G61" s="6"/>
+      <c r="H61" s="5"/>
+      <c r="I61" s="6"/>
       <c r="J61" s="6"/>
       <c r="K61" s="6"/>
     </row>
     <row r="62" spans="2:11">
       <c r="F62" s="5"/>
       <c r="G62" s="6"/>
+      <c r="H62" s="5"/>
+      <c r="I62" s="6"/>
       <c r="J62" s="6"/>
       <c r="K62" s="6"/>
     </row>
     <row r="63" spans="2:11">
       <c r="F63" s="5"/>
       <c r="G63" s="6"/>
+      <c r="H63" s="5"/>
+      <c r="I63" s="6"/>
       <c r="J63" s="6"/>
       <c r="K63" s="6"/>
     </row>
     <row r="64" spans="2:11">
       <c r="F64" s="5"/>
       <c r="G64" s="6"/>
+      <c r="H64" s="5"/>
+      <c r="I64" s="6"/>
       <c r="J64" s="6"/>
       <c r="K64" s="6"/>
     </row>
     <row r="65" spans="6:11">
       <c r="F65" s="5"/>
       <c r="G65" s="6"/>
+      <c r="H65" s="5"/>
+      <c r="I65" s="6"/>
       <c r="J65" s="6"/>
       <c r="K65" s="6"/>
     </row>
@@ -8051,6 +8063,34 @@
     </row>
   </sheetData>
   <mergeCells count="44">
+    <mergeCell ref="V5:W5"/>
+    <mergeCell ref="V25:W25"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="U3:X3"/>
+    <mergeCell ref="U4:X4"/>
+    <mergeCell ref="M3:P3"/>
+    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="S5:T5"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="M4:P4"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="E4:H4"/>
     <mergeCell ref="N44:O44"/>
     <mergeCell ref="V44:W44"/>
     <mergeCell ref="S44:T44"/>
@@ -8067,34 +8107,6 @@
     <mergeCell ref="S25:T25"/>
     <mergeCell ref="M42:P42"/>
     <mergeCell ref="U42:X42"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="E42:H42"/>
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="S5:T5"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="M4:P4"/>
-    <mergeCell ref="V5:W5"/>
-    <mergeCell ref="V25:W25"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="U3:X3"/>
-    <mergeCell ref="U4:X4"/>
-    <mergeCell ref="M3:P3"/>
-    <mergeCell ref="S3:T3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9431,13 +9443,12 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="K28:Q28"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="K29:Q29"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="L30:M30"/>
-    <mergeCell ref="O30:P30"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:G20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="E22:F22"/>
     <mergeCell ref="O5:P5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="B5:C5"/>
@@ -9451,12 +9462,13 @@
     <mergeCell ref="K4:Q4"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:G20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="K28:Q28"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="K29:Q29"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="O30:P30"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9469,31 +9481,31 @@
   <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData>
     <row r="6" spans="4:20" ht="17.25" thickBot="1">
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="37" t="s">
         <v>357</v>
       </c>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
-      <c r="I6" s="69" t="s">
+      <c r="E6" s="37"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="37"/>
+      <c r="I6" s="37" t="s">
         <v>722</v>
       </c>
-      <c r="J6" s="69"/>
-      <c r="K6" s="69"/>
-      <c r="M6" s="69" t="s">
+      <c r="J6" s="37"/>
+      <c r="K6" s="37"/>
+      <c r="M6" s="37" t="s">
         <v>359</v>
       </c>
-      <c r="N6" s="69"/>
-      <c r="O6" s="69"/>
-      <c r="P6" s="69"/>
-      <c r="R6" s="69" t="s">
+      <c r="N6" s="37"/>
+      <c r="O6" s="37"/>
+      <c r="P6" s="37"/>
+      <c r="R6" s="37" t="s">
         <v>723</v>
       </c>
-      <c r="S6" s="69"/>
-      <c r="T6" s="69"/>
+      <c r="S6" s="37"/>
+      <c r="T6" s="37"/>
     </row>
     <row r="7" spans="4:20" ht="16.5" customHeight="1">
-      <c r="D7" s="37" t="s">
+      <c r="D7" s="68" t="s">
         <v>720</v>
       </c>
       <c r="E7" s="21"/>
@@ -9502,7 +9514,7 @@
       <c r="I7" s="26"/>
       <c r="J7" s="21"/>
       <c r="K7" s="22"/>
-      <c r="M7" s="37" t="s">
+      <c r="M7" s="68" t="s">
         <v>718</v>
       </c>
       <c r="N7" s="21"/>
@@ -9513,195 +9525,195 @@
       <c r="T7" s="22"/>
     </row>
     <row r="8" spans="4:20">
-      <c r="D8" s="38"/>
+      <c r="D8" s="69"/>
       <c r="G8" s="23"/>
       <c r="I8" s="24"/>
       <c r="K8" s="23"/>
-      <c r="M8" s="38"/>
+      <c r="M8" s="69"/>
       <c r="P8" s="23"/>
       <c r="R8" s="24"/>
       <c r="T8" s="23"/>
     </row>
     <row r="9" spans="4:20" ht="16.5" customHeight="1">
-      <c r="D9" s="38"/>
-      <c r="F9" s="49" t="s">
+      <c r="D9" s="69"/>
+      <c r="F9" s="46" t="s">
         <v>717</v>
       </c>
       <c r="G9" s="23"/>
       <c r="I9" s="24"/>
-      <c r="J9" s="49" t="s">
+      <c r="J9" s="46" t="s">
         <v>717</v>
       </c>
       <c r="K9" s="23"/>
-      <c r="M9" s="38"/>
-      <c r="O9" s="49" t="s">
+      <c r="M9" s="69"/>
+      <c r="O9" s="46" t="s">
         <v>717</v>
       </c>
       <c r="P9" s="23"/>
       <c r="R9" s="24"/>
-      <c r="S9" s="49" t="s">
+      <c r="S9" s="46" t="s">
         <v>717</v>
       </c>
       <c r="T9" s="23"/>
     </row>
     <row r="10" spans="4:20">
-      <c r="D10" s="38"/>
-      <c r="F10" s="50"/>
+      <c r="D10" s="69"/>
+      <c r="F10" s="57"/>
       <c r="G10" s="23"/>
       <c r="I10" s="24"/>
-      <c r="J10" s="50"/>
+      <c r="J10" s="57"/>
       <c r="K10" s="23"/>
-      <c r="M10" s="38"/>
-      <c r="O10" s="50"/>
+      <c r="M10" s="69"/>
+      <c r="O10" s="57"/>
       <c r="P10" s="23"/>
       <c r="R10" s="24"/>
-      <c r="S10" s="50"/>
+      <c r="S10" s="57"/>
       <c r="T10" s="23"/>
     </row>
     <row r="11" spans="4:20" ht="16.5" customHeight="1">
-      <c r="D11" s="38"/>
-      <c r="E11" s="51" t="s">
+      <c r="D11" s="69"/>
+      <c r="E11" s="44" t="s">
         <v>716</v>
       </c>
       <c r="G11" s="23"/>
       <c r="I11" s="24"/>
-      <c r="J11" s="51" t="s">
+      <c r="J11" s="44" t="s">
         <v>716</v>
       </c>
       <c r="K11" s="23"/>
-      <c r="M11" s="38"/>
-      <c r="N11" s="51" t="s">
+      <c r="M11" s="69"/>
+      <c r="N11" s="44" t="s">
         <v>716</v>
       </c>
       <c r="P11" s="23"/>
       <c r="R11" s="24"/>
-      <c r="S11" s="51" t="s">
+      <c r="S11" s="44" t="s">
         <v>716</v>
       </c>
       <c r="T11" s="23"/>
     </row>
     <row r="12" spans="4:20">
-      <c r="D12" s="38"/>
-      <c r="E12" s="52"/>
+      <c r="D12" s="69"/>
+      <c r="E12" s="71"/>
       <c r="G12" s="23"/>
       <c r="I12" s="24"/>
-      <c r="J12" s="62"/>
+      <c r="J12" s="45"/>
       <c r="K12" s="23"/>
-      <c r="M12" s="38"/>
-      <c r="N12" s="52"/>
+      <c r="M12" s="69"/>
+      <c r="N12" s="71"/>
       <c r="P12" s="23"/>
       <c r="R12" s="24"/>
-      <c r="S12" s="62"/>
+      <c r="S12" s="45"/>
       <c r="T12" s="23"/>
     </row>
     <row r="13" spans="4:20">
-      <c r="D13" s="39"/>
+      <c r="D13" s="70"/>
       <c r="G13" s="23"/>
       <c r="I13" s="24"/>
       <c r="K13" s="23"/>
-      <c r="M13" s="39"/>
+      <c r="M13" s="70"/>
       <c r="P13" s="23"/>
       <c r="R13" s="24"/>
       <c r="T13" s="23"/>
     </row>
     <row r="14" spans="4:20" ht="16.5" customHeight="1">
       <c r="D14" s="24"/>
-      <c r="E14" s="40" t="s">
+      <c r="E14" s="72" t="s">
         <v>719</v>
       </c>
-      <c r="F14" s="41"/>
-      <c r="G14" s="42"/>
-      <c r="I14" s="53" t="s">
+      <c r="F14" s="73"/>
+      <c r="G14" s="74"/>
+      <c r="I14" s="58" t="s">
         <v>725</v>
       </c>
-      <c r="J14" s="54"/>
-      <c r="K14" s="55"/>
+      <c r="J14" s="59"/>
+      <c r="K14" s="64"/>
       <c r="M14" s="24"/>
-      <c r="N14" s="40" t="s">
+      <c r="N14" s="72" t="s">
         <v>728</v>
       </c>
-      <c r="O14" s="41"/>
-      <c r="P14" s="42"/>
-      <c r="R14" s="53" t="s">
+      <c r="O14" s="73"/>
+      <c r="P14" s="74"/>
+      <c r="R14" s="58" t="s">
         <v>725</v>
       </c>
-      <c r="S14" s="54"/>
-      <c r="T14" s="55"/>
+      <c r="S14" s="59"/>
+      <c r="T14" s="64"/>
     </row>
     <row r="15" spans="4:20">
       <c r="D15" s="24"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="45"/>
-      <c r="I15" s="56"/>
-      <c r="J15" s="57"/>
-      <c r="K15" s="58"/>
+      <c r="E15" s="75"/>
+      <c r="F15" s="76"/>
+      <c r="G15" s="77"/>
+      <c r="I15" s="51"/>
+      <c r="J15" s="52"/>
+      <c r="K15" s="53"/>
       <c r="M15" s="24"/>
-      <c r="N15" s="43"/>
-      <c r="O15" s="44"/>
-      <c r="P15" s="45"/>
-      <c r="R15" s="56"/>
-      <c r="S15" s="57"/>
-      <c r="T15" s="58"/>
+      <c r="N15" s="75"/>
+      <c r="O15" s="76"/>
+      <c r="P15" s="77"/>
+      <c r="R15" s="51"/>
+      <c r="S15" s="52"/>
+      <c r="T15" s="53"/>
     </row>
     <row r="16" spans="4:20">
       <c r="D16" s="24"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="45"/>
-      <c r="I16" s="56"/>
-      <c r="J16" s="57"/>
-      <c r="K16" s="58"/>
+      <c r="E16" s="75"/>
+      <c r="F16" s="76"/>
+      <c r="G16" s="77"/>
+      <c r="I16" s="51"/>
+      <c r="J16" s="52"/>
+      <c r="K16" s="53"/>
       <c r="M16" s="24"/>
-      <c r="N16" s="43"/>
-      <c r="O16" s="44"/>
-      <c r="P16" s="45"/>
-      <c r="R16" s="56"/>
-      <c r="S16" s="57"/>
-      <c r="T16" s="58"/>
+      <c r="N16" s="75"/>
+      <c r="O16" s="76"/>
+      <c r="P16" s="77"/>
+      <c r="R16" s="51"/>
+      <c r="S16" s="52"/>
+      <c r="T16" s="53"/>
     </row>
     <row r="17" spans="4:20" ht="17.25" thickBot="1">
       <c r="D17" s="25"/>
-      <c r="E17" s="46"/>
-      <c r="F17" s="47"/>
-      <c r="G17" s="48"/>
-      <c r="I17" s="59"/>
-      <c r="J17" s="60"/>
-      <c r="K17" s="61"/>
+      <c r="E17" s="78"/>
+      <c r="F17" s="79"/>
+      <c r="G17" s="80"/>
+      <c r="I17" s="65"/>
+      <c r="J17" s="66"/>
+      <c r="K17" s="67"/>
       <c r="M17" s="25"/>
-      <c r="N17" s="46"/>
-      <c r="O17" s="47"/>
-      <c r="P17" s="48"/>
-      <c r="R17" s="59"/>
-      <c r="S17" s="60"/>
-      <c r="T17" s="61"/>
+      <c r="N17" s="78"/>
+      <c r="O17" s="79"/>
+      <c r="P17" s="80"/>
+      <c r="R17" s="65"/>
+      <c r="S17" s="66"/>
+      <c r="T17" s="67"/>
     </row>
     <row r="19" spans="4:20" ht="17.25" thickBot="1">
-      <c r="D19" s="69" t="s">
+      <c r="D19" s="37" t="s">
         <v>368</v>
       </c>
-      <c r="E19" s="69"/>
-      <c r="F19" s="69"/>
-      <c r="H19" s="69" t="s">
+      <c r="E19" s="37"/>
+      <c r="F19" s="37"/>
+      <c r="H19" s="37" t="s">
         <v>367</v>
       </c>
-      <c r="I19" s="69"/>
-      <c r="J19" s="69"/>
-      <c r="K19" s="69"/>
-      <c r="R19" s="69" t="s">
+      <c r="I19" s="37"/>
+      <c r="J19" s="37"/>
+      <c r="K19" s="37"/>
+      <c r="R19" s="37" t="s">
         <v>724</v>
       </c>
-      <c r="S19" s="69"/>
-      <c r="T19" s="69"/>
+      <c r="S19" s="37"/>
+      <c r="T19" s="37"/>
     </row>
     <row r="20" spans="4:20">
-      <c r="D20" s="77" t="s">
+      <c r="D20" s="48" t="s">
         <v>721</v>
       </c>
-      <c r="E20" s="78"/>
-      <c r="F20" s="79"/>
+      <c r="E20" s="49"/>
+      <c r="F20" s="50"/>
       <c r="H20" s="26"/>
-      <c r="I20" s="68" t="s">
+      <c r="I20" s="63" t="s">
         <v>717</v>
       </c>
       <c r="J20" s="21"/>
@@ -9710,56 +9722,56 @@
       <c r="N20" s="21"/>
       <c r="O20" s="21"/>
       <c r="P20" s="22"/>
-      <c r="R20" s="77" t="s">
+      <c r="R20" s="48" t="s">
         <v>725</v>
       </c>
-      <c r="S20" s="78"/>
-      <c r="T20" s="79"/>
+      <c r="S20" s="49"/>
+      <c r="T20" s="50"/>
     </row>
     <row r="21" spans="4:20">
-      <c r="D21" s="56"/>
-      <c r="E21" s="57"/>
-      <c r="F21" s="58"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="52"/>
+      <c r="F21" s="53"/>
       <c r="H21" s="24"/>
-      <c r="I21" s="50"/>
+      <c r="I21" s="57"/>
       <c r="K21" s="23"/>
       <c r="M21" s="24"/>
       <c r="P21" s="23"/>
-      <c r="R21" s="56"/>
-      <c r="S21" s="57"/>
-      <c r="T21" s="58"/>
+      <c r="R21" s="51"/>
+      <c r="S21" s="52"/>
+      <c r="T21" s="53"/>
     </row>
     <row r="22" spans="4:20">
-      <c r="D22" s="56"/>
-      <c r="E22" s="57"/>
-      <c r="F22" s="58"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="52"/>
+      <c r="F22" s="53"/>
       <c r="H22" s="24"/>
-      <c r="I22" s="51" t="s">
+      <c r="I22" s="44" t="s">
         <v>716</v>
       </c>
-      <c r="J22" s="74" t="s">
+      <c r="J22" s="42" t="s">
         <v>726</v>
       </c>
       <c r="K22" s="23"/>
       <c r="M22" s="24"/>
       <c r="P22" s="23"/>
-      <c r="R22" s="56"/>
-      <c r="S22" s="57"/>
-      <c r="T22" s="58"/>
+      <c r="R22" s="51"/>
+      <c r="S22" s="52"/>
+      <c r="T22" s="53"/>
     </row>
     <row r="23" spans="4:20">
-      <c r="D23" s="65"/>
-      <c r="E23" s="66"/>
-      <c r="F23" s="80"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="55"/>
+      <c r="F23" s="56"/>
       <c r="H23" s="24"/>
-      <c r="I23" s="62"/>
-      <c r="J23" s="75"/>
+      <c r="I23" s="45"/>
+      <c r="J23" s="43"/>
       <c r="K23" s="23"/>
       <c r="M23" s="24"/>
       <c r="P23" s="23"/>
-      <c r="R23" s="65"/>
-      <c r="S23" s="66"/>
-      <c r="T23" s="80"/>
+      <c r="R23" s="54"/>
+      <c r="S23" s="55"/>
+      <c r="T23" s="56"/>
     </row>
     <row r="24" spans="4:20">
       <c r="D24" s="24"/>
@@ -9775,77 +9787,77 @@
     </row>
     <row r="25" spans="4:20" ht="16.5" customHeight="1">
       <c r="D25" s="24"/>
-      <c r="E25" s="51" t="s">
+      <c r="E25" s="44" t="s">
         <v>716</v>
       </c>
       <c r="F25" s="23"/>
-      <c r="H25" s="53" t="s">
+      <c r="H25" s="58" t="s">
         <v>729</v>
       </c>
-      <c r="I25" s="54"/>
-      <c r="J25" s="63"/>
+      <c r="I25" s="59"/>
+      <c r="J25" s="60"/>
       <c r="K25" s="23"/>
       <c r="M25" s="24"/>
       <c r="P25" s="23"/>
       <c r="R25" s="24"/>
-      <c r="S25" s="51" t="s">
+      <c r="S25" s="44" t="s">
         <v>716</v>
       </c>
       <c r="T25" s="23"/>
     </row>
     <row r="26" spans="4:20">
       <c r="D26" s="24"/>
-      <c r="E26" s="62"/>
+      <c r="E26" s="45"/>
       <c r="F26" s="23"/>
-      <c r="H26" s="56"/>
-      <c r="I26" s="57"/>
-      <c r="J26" s="64"/>
+      <c r="H26" s="51"/>
+      <c r="I26" s="52"/>
+      <c r="J26" s="61"/>
       <c r="K26" s="23"/>
       <c r="M26" s="24"/>
       <c r="P26" s="23"/>
       <c r="R26" s="24"/>
-      <c r="S26" s="62"/>
+      <c r="S26" s="45"/>
       <c r="T26" s="23"/>
     </row>
     <row r="27" spans="4:20">
       <c r="D27" s="24"/>
-      <c r="E27" s="49" t="s">
+      <c r="E27" s="46" t="s">
         <v>717</v>
       </c>
       <c r="F27" s="23"/>
-      <c r="H27" s="56"/>
-      <c r="I27" s="57"/>
-      <c r="J27" s="64"/>
-      <c r="K27" s="70" t="s">
+      <c r="H27" s="51"/>
+      <c r="I27" s="52"/>
+      <c r="J27" s="61"/>
+      <c r="K27" s="38" t="s">
         <v>718</v>
       </c>
       <c r="M27" s="24"/>
       <c r="P27" s="23"/>
       <c r="R27" s="24"/>
-      <c r="S27" s="49" t="s">
+      <c r="S27" s="46" t="s">
         <v>717</v>
       </c>
       <c r="T27" s="23"/>
     </row>
     <row r="28" spans="4:20" ht="16.5" customHeight="1">
       <c r="D28" s="24"/>
-      <c r="E28" s="50"/>
+      <c r="E28" s="57"/>
       <c r="F28" s="23"/>
-      <c r="H28" s="65"/>
-      <c r="I28" s="66"/>
-      <c r="J28" s="67"/>
-      <c r="K28" s="71"/>
+      <c r="H28" s="54"/>
+      <c r="I28" s="55"/>
+      <c r="J28" s="62"/>
+      <c r="K28" s="39"/>
       <c r="M28" s="24"/>
       <c r="P28" s="23"/>
       <c r="R28" s="24"/>
-      <c r="S28" s="50"/>
+      <c r="S28" s="57"/>
       <c r="T28" s="23"/>
     </row>
     <row r="29" spans="4:20">
       <c r="D29" s="24"/>
       <c r="F29" s="23"/>
       <c r="H29" s="24"/>
-      <c r="K29" s="72"/>
+      <c r="K29" s="40"/>
       <c r="M29" s="24"/>
       <c r="P29" s="23"/>
       <c r="R29" s="24"/>
@@ -9856,10 +9868,10 @@
       <c r="E30" s="27"/>
       <c r="F30" s="28"/>
       <c r="H30" s="24"/>
-      <c r="I30" s="51" t="s">
+      <c r="I30" s="44" t="s">
         <v>716</v>
       </c>
-      <c r="K30" s="72"/>
+      <c r="K30" s="40"/>
       <c r="M30" s="25"/>
       <c r="N30" s="27"/>
       <c r="O30" s="27"/>
@@ -9870,21 +9882,21 @@
     </row>
     <row r="31" spans="4:20">
       <c r="H31" s="24"/>
-      <c r="I31" s="62"/>
-      <c r="K31" s="72"/>
+      <c r="I31" s="45"/>
+      <c r="K31" s="40"/>
     </row>
     <row r="32" spans="4:20">
       <c r="H32" s="24"/>
-      <c r="I32" s="49" t="s">
+      <c r="I32" s="46" t="s">
         <v>717</v>
       </c>
-      <c r="K32" s="72"/>
+      <c r="K32" s="40"/>
     </row>
     <row r="33" spans="8:24" ht="17.25" thickBot="1">
       <c r="H33" s="25"/>
-      <c r="I33" s="76"/>
+      <c r="I33" s="47"/>
       <c r="J33" s="27"/>
-      <c r="K33" s="73"/>
+      <c r="K33" s="41"/>
     </row>
     <row r="47" spans="8:24">
       <c r="X47" t="s">
@@ -9893,6 +9905,24 @@
     </row>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="D7:D13"/>
+    <mergeCell ref="E14:G17"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="I14:K17"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="S11:S12"/>
+    <mergeCell ref="R14:T17"/>
+    <mergeCell ref="M7:M13"/>
+    <mergeCell ref="O9:O10"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="N14:P17"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="H25:J28"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="J11:J12"/>
     <mergeCell ref="R6:T6"/>
     <mergeCell ref="R19:T19"/>
     <mergeCell ref="D19:F19"/>
@@ -9909,24 +9939,6 @@
     <mergeCell ref="M6:P6"/>
     <mergeCell ref="D20:F23"/>
     <mergeCell ref="E27:E28"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="H25:J28"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="I22:I23"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="S11:S12"/>
-    <mergeCell ref="R14:T17"/>
-    <mergeCell ref="M7:M13"/>
-    <mergeCell ref="O9:O10"/>
-    <mergeCell ref="N11:N12"/>
-    <mergeCell ref="N14:P17"/>
-    <mergeCell ref="D7:D13"/>
-    <mergeCell ref="E14:G17"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="I14:K17"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/PLC/IO List.xlsx
+++ b/PLC/IO List.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EZENIC\Desktop\Project-Second\PLC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ezen-01\Desktop\Project\PLC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1A01ADF-AA34-42D2-9837-C6D0970E05D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19097A28-10A3-4342-936B-5164D9DC6526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1050" yWindow="2025" windowWidth="21600" windowHeight="11295" xr2:uid="{E8A3CD3B-D612-4B37-A180-F6C335096DC9}"/>
+    <workbookView xWindow="4920" yWindow="3825" windowWidth="21600" windowHeight="11385" activeTab="3" xr2:uid="{E8A3CD3B-D612-4B37-A180-F6C335096DC9}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1192" uniqueCount="874">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1206" uniqueCount="890">
   <si>
     <t>X10</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2584,11 +2584,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>셀 대차
-P[2]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>AGV
 P[3]</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2631,488 +2626,560 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>M300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M301</t>
+  </si>
+  <si>
+    <t>M302</t>
+  </si>
+  <si>
+    <t>M303</t>
+  </si>
+  <si>
+    <t>M304</t>
+  </si>
+  <si>
+    <t>M305</t>
+  </si>
+  <si>
+    <t>M306</t>
+  </si>
+  <si>
+    <t>M307</t>
+  </si>
+  <si>
+    <t>M308</t>
+  </si>
+  <si>
+    <t>M309</t>
+  </si>
+  <si>
+    <t>M310</t>
+  </si>
+  <si>
+    <t>M311</t>
+  </si>
+  <si>
+    <t>M312</t>
+  </si>
+  <si>
+    <t>M313</t>
+  </si>
+  <si>
+    <t>경화1 공정 완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경화공정1 AGV 배출 신호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경화공정1 완료 후 문닫힘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경화2 공정 완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경화공정2 AGV 배출 신호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경화공정2 완료 후 문닫힘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경화3 공정 완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경화공정3 AGV 배출 신호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경화공정3 완료 후 문닫힘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M120</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M121</t>
+  </si>
+  <si>
+    <t>M122</t>
+  </si>
+  <si>
+    <t>M123</t>
+  </si>
+  <si>
+    <t>M124</t>
+  </si>
+  <si>
+    <t>M125</t>
+  </si>
+  <si>
+    <t>M126</t>
+  </si>
+  <si>
+    <t>M127</t>
+  </si>
+  <si>
+    <t>M128</t>
+  </si>
+  <si>
+    <t>AGV 내부 펄스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>T20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>T21</t>
+  </si>
+  <si>
+    <t>T22</t>
+  </si>
+  <si>
+    <t>T23</t>
+  </si>
+  <si>
+    <t>T24</t>
+  </si>
+  <si>
+    <t>T25</t>
+  </si>
+  <si>
+    <t>T26</t>
+  </si>
+  <si>
+    <t>T27</t>
+  </si>
+  <si>
+    <t>T28</t>
+  </si>
+  <si>
+    <t>T29</t>
+  </si>
+  <si>
+    <t>1공정 agv 신호 딜레이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2공정 agv 신호 딜레이</t>
+  </si>
+  <si>
+    <t>3공정 agv 신호 딜레이</t>
+  </si>
+  <si>
+    <t>4공정 agv 신호 딜레이</t>
+  </si>
+  <si>
+    <t>5공정 agv 신호 딜레이</t>
+  </si>
+  <si>
+    <t>6공정 agv 신호 딜레이</t>
+  </si>
+  <si>
+    <t>7공정 agv 신호 딜레이</t>
+  </si>
+  <si>
+    <t>8공정 agv 신호 딜레이</t>
+  </si>
+  <si>
+    <t>9공정 agv 신호 딜레이</t>
+  </si>
+  <si>
+    <t>10공정 agv 신호 딜레이</t>
+  </si>
+  <si>
+    <t>M129</t>
+  </si>
+  <si>
+    <t>프레스1(제4공정_저항 검사 공정)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>프레스2(제1공정_하우징 공정)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로봇1 작업완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로봇2 작업완료</t>
+  </si>
+  <si>
+    <t>로봇3 작업완료</t>
+  </si>
+  <si>
+    <t>로봇5 작업완료</t>
+  </si>
+  <si>
+    <t>로봇6 작업완료</t>
+  </si>
+  <si>
+    <t>로봇7 작업완료</t>
+  </si>
+  <si>
+    <t>로봇8 작업완료</t>
+  </si>
+  <si>
+    <t>로봇9 작업완료</t>
+  </si>
+  <si>
+    <t>프레스 작업완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>챔버1 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M11</t>
+  </si>
+  <si>
+    <t>M12</t>
+  </si>
+  <si>
+    <t>M13</t>
+  </si>
+  <si>
+    <t>챔버2 상태</t>
+  </si>
+  <si>
+    <t>챔버3 상태</t>
+  </si>
+  <si>
+    <t>챔버4 상태</t>
+  </si>
+  <si>
+    <t>T30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>챔버1 완료 후 딜레이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>T31</t>
+  </si>
+  <si>
+    <t>T32</t>
+  </si>
+  <si>
+    <t>T33</t>
+  </si>
+  <si>
+    <t>챔버2 완료 후 딜레이</t>
+  </si>
+  <si>
+    <t>챔버3 완료 후 딜레이</t>
+  </si>
+  <si>
+    <t>챔버4 완료 후 딜레이</t>
+  </si>
+  <si>
+    <t>M15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M16</t>
+  </si>
+  <si>
+    <t>M17</t>
+  </si>
+  <si>
+    <t>M18</t>
+  </si>
+  <si>
+    <t>챔버1 로봇 경유위치 이동 완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>챔버2 로봇 경유위치 이동 완료</t>
+  </si>
+  <si>
+    <t>챔버3 로봇 경유위치 이동 완료</t>
+  </si>
+  <si>
+    <t>챔버4 로봇 경유위치 이동 완료</t>
+  </si>
+  <si>
+    <t>M20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수작업7 START</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M21</t>
+  </si>
+  <si>
+    <t>M22</t>
+  </si>
+  <si>
+    <t>수작업8 START</t>
+  </si>
+  <si>
+    <t>수작업9 START</t>
+  </si>
+  <si>
+    <t>출하장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PASS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M90</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGV1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M91</t>
+  </si>
+  <si>
+    <t>M92</t>
+  </si>
+  <si>
+    <t>M93</t>
+  </si>
+  <si>
+    <t>M94</t>
+  </si>
+  <si>
+    <t>M95</t>
+  </si>
+  <si>
+    <t>AGV2</t>
+  </si>
+  <si>
+    <t>AGV3</t>
+  </si>
+  <si>
+    <t>AGV4</t>
+  </si>
+  <si>
+    <t>AGV5</t>
+  </si>
+  <si>
+    <t>AGV6</t>
+  </si>
+  <si>
+    <t>M1190</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M1191</t>
+  </si>
+  <si>
+    <t>M1192</t>
+  </si>
+  <si>
+    <t>M1193</t>
+  </si>
+  <si>
+    <t>M1194</t>
+  </si>
+  <si>
+    <t>M1195</t>
+  </si>
+  <si>
+    <t>M1196</t>
+  </si>
+  <si>
+    <t>M1197</t>
+  </si>
+  <si>
+    <t>M2228</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M2229</t>
+  </si>
+  <si>
+    <t>M2230</t>
+  </si>
+  <si>
+    <t>M2231</t>
+  </si>
+  <si>
+    <t>M2232</t>
+  </si>
+  <si>
+    <t>D01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGV1 기동 MAIN 신호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGV2 기동 MAIN 신호</t>
+  </si>
+  <si>
+    <t>AGV3 기동 MAIN 신호</t>
+  </si>
+  <si>
+    <t>AGV4 기동 MAIN 신호</t>
+  </si>
+  <si>
+    <t>AGV5 기동 MAIN 신호</t>
+  </si>
+  <si>
+    <t>AGV6 기동 MAIN 신호</t>
+  </si>
+  <si>
+    <t>AGV7 기동 MAIN 신호</t>
+  </si>
+  <si>
+    <t>T40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGV1 기동 MAIN 딜레이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M150</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M151</t>
+  </si>
+  <si>
+    <t>M152</t>
+  </si>
+  <si>
+    <t>M153</t>
+  </si>
+  <si>
+    <t>M154</t>
+  </si>
+  <si>
+    <t>M155</t>
+  </si>
+  <si>
+    <t>M156</t>
+  </si>
+  <si>
+    <t>경유지점
+P[1~2]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1번 배터리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2번 배터리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3번 배터리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4번 배터리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>셀 대차
+P[3~6]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>AGV
+P[7~8]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-&gt;3-&gt;7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2-&gt;4-&gt;8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2-&gt;6-&gt;8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-&gt;5-&gt;7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1번 커버</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2번 커버</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>셀 대차
 P[3~4]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>1-&gt;3-.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2-&gt;4-&gt;6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>AGV
-P[3~8]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M300</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M301</t>
-  </si>
-  <si>
-    <t>M302</t>
-  </si>
-  <si>
-    <t>M303</t>
-  </si>
-  <si>
-    <t>M304</t>
-  </si>
-  <si>
-    <t>M305</t>
-  </si>
-  <si>
-    <t>M306</t>
-  </si>
-  <si>
-    <t>M307</t>
-  </si>
-  <si>
-    <t>M308</t>
-  </si>
-  <si>
-    <t>M309</t>
-  </si>
-  <si>
-    <t>M310</t>
-  </si>
-  <si>
-    <t>M311</t>
-  </si>
-  <si>
-    <t>M312</t>
-  </si>
-  <si>
-    <t>M313</t>
-  </si>
-  <si>
-    <t>경화1 공정 완료</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>경화공정1 AGV 배출 신호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>경화공정1 완료 후 문닫힘</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>경화2 공정 완료</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>경화공정2 AGV 배출 신호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>경화공정2 완료 후 문닫힘</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>경화3 공정 완료</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>경화공정3 AGV 배출 신호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>경화공정3 완료 후 문닫힘</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M120</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M121</t>
-  </si>
-  <si>
-    <t>M122</t>
-  </si>
-  <si>
-    <t>M123</t>
-  </si>
-  <si>
-    <t>M124</t>
-  </si>
-  <si>
-    <t>M125</t>
-  </si>
-  <si>
-    <t>M126</t>
-  </si>
-  <si>
-    <t>M127</t>
-  </si>
-  <si>
-    <t>M128</t>
-  </si>
-  <si>
-    <t>AGV 내부 펄스</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>T20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>T21</t>
-  </si>
-  <si>
-    <t>T22</t>
-  </si>
-  <si>
-    <t>T23</t>
-  </si>
-  <si>
-    <t>T24</t>
-  </si>
-  <si>
-    <t>T25</t>
-  </si>
-  <si>
-    <t>T26</t>
-  </si>
-  <si>
-    <t>T27</t>
-  </si>
-  <si>
-    <t>T28</t>
-  </si>
-  <si>
-    <t>T29</t>
-  </si>
-  <si>
-    <t>1공정 agv 신호 딜레이</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2공정 agv 신호 딜레이</t>
-  </si>
-  <si>
-    <t>3공정 agv 신호 딜레이</t>
-  </si>
-  <si>
-    <t>4공정 agv 신호 딜레이</t>
-  </si>
-  <si>
-    <t>5공정 agv 신호 딜레이</t>
-  </si>
-  <si>
-    <t>6공정 agv 신호 딜레이</t>
-  </si>
-  <si>
-    <t>7공정 agv 신호 딜레이</t>
-  </si>
-  <si>
-    <t>8공정 agv 신호 딜레이</t>
-  </si>
-  <si>
-    <t>9공정 agv 신호 딜레이</t>
-  </si>
-  <si>
-    <t>10공정 agv 신호 딜레이</t>
-  </si>
-  <si>
-    <t>M129</t>
-  </si>
-  <si>
-    <t>프레스1(제4공정_저항 검사 공정)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>프레스2(제1공정_하우징 공정)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>로봇1 작업완료</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>로봇2 작업완료</t>
-  </si>
-  <si>
-    <t>로봇3 작업완료</t>
-  </si>
-  <si>
-    <t>로봇5 작업완료</t>
-  </si>
-  <si>
-    <t>로봇6 작업완료</t>
-  </si>
-  <si>
-    <t>로봇7 작업완료</t>
-  </si>
-  <si>
-    <t>로봇8 작업완료</t>
-  </si>
-  <si>
-    <t>로봇9 작업완료</t>
-  </si>
-  <si>
-    <t>프레스 작업완료</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>챔버1 상태</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M11</t>
-  </si>
-  <si>
-    <t>M12</t>
-  </si>
-  <si>
-    <t>M13</t>
-  </si>
-  <si>
-    <t>챔버2 상태</t>
-  </si>
-  <si>
-    <t>챔버3 상태</t>
-  </si>
-  <si>
-    <t>챔버4 상태</t>
-  </si>
-  <si>
-    <t>T30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>챔버1 완료 후 딜레이</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>T31</t>
-  </si>
-  <si>
-    <t>T32</t>
-  </si>
-  <si>
-    <t>T33</t>
-  </si>
-  <si>
-    <t>챔버2 완료 후 딜레이</t>
-  </si>
-  <si>
-    <t>챔버3 완료 후 딜레이</t>
-  </si>
-  <si>
-    <t>챔버4 완료 후 딜레이</t>
-  </si>
-  <si>
-    <t>M15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M16</t>
-  </si>
-  <si>
-    <t>M17</t>
-  </si>
-  <si>
-    <t>M18</t>
-  </si>
-  <si>
-    <t>챔버1 로봇 경유위치 이동 완료</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>챔버2 로봇 경유위치 이동 완료</t>
-  </si>
-  <si>
-    <t>챔버3 로봇 경유위치 이동 완료</t>
-  </si>
-  <si>
-    <t>챔버4 로봇 경유위치 이동 완료</t>
-  </si>
-  <si>
-    <t>M20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>수작업7 START</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M21</t>
-  </si>
-  <si>
-    <t>M22</t>
-  </si>
-  <si>
-    <t>수작업8 START</t>
-  </si>
-  <si>
-    <t>수작업9 START</t>
-  </si>
-  <si>
-    <t>출하장</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PASS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M90</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AGV1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M91</t>
-  </si>
-  <si>
-    <t>M92</t>
-  </si>
-  <si>
-    <t>M93</t>
-  </si>
-  <si>
-    <t>M94</t>
-  </si>
-  <si>
-    <t>M95</t>
-  </si>
-  <si>
-    <t>AGV2</t>
-  </si>
-  <si>
-    <t>AGV3</t>
-  </si>
-  <si>
-    <t>AGV4</t>
-  </si>
-  <si>
-    <t>AGV5</t>
-  </si>
-  <si>
-    <t>AGV6</t>
-  </si>
-  <si>
-    <t>M1190</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M1191</t>
-  </si>
-  <si>
-    <t>M1192</t>
-  </si>
-  <si>
-    <t>M1193</t>
-  </si>
-  <si>
-    <t>M1194</t>
-  </si>
-  <si>
-    <t>M1195</t>
-  </si>
-  <si>
-    <t>M1196</t>
-  </si>
-  <si>
-    <t>M1197</t>
-  </si>
-  <si>
-    <t>M2228</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M2229</t>
-  </si>
-  <si>
-    <t>M2230</t>
-  </si>
-  <si>
-    <t>M2231</t>
-  </si>
-  <si>
-    <t>M2232</t>
-  </si>
-  <si>
-    <t>D01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AGV1 기동 MAIN 신호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AGV2 기동 MAIN 신호</t>
-  </si>
-  <si>
-    <t>AGV3 기동 MAIN 신호</t>
-  </si>
-  <si>
-    <t>AGV4 기동 MAIN 신호</t>
-  </si>
-  <si>
-    <t>AGV5 기동 MAIN 신호</t>
-  </si>
-  <si>
-    <t>AGV6 기동 MAIN 신호</t>
-  </si>
-  <si>
-    <t>AGV7 기동 MAIN 신호</t>
-  </si>
-  <si>
-    <t>T40</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AGV1 기동 MAIN 딜레이</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M150</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M151</t>
-  </si>
-  <si>
-    <t>M152</t>
-  </si>
-  <si>
-    <t>M153</t>
-  </si>
-  <si>
-    <t>M154</t>
-  </si>
-  <si>
-    <t>M155</t>
-  </si>
-  <si>
-    <t>M156</t>
+P[3~6]
+P[5~6]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>볼트 체결</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-&gt;2-&gt;3~6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3640,7 +3707,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3752,99 +3819,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3852,9 +3826,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3883,6 +3854,105 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4443,7 +4513,7 @@
         <v>121</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="I11" s="6" t="s">
         <v>448</v>
@@ -4469,7 +4539,7 @@
         <v>122</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="I12" s="6" t="s">
         <v>450</v>
@@ -4495,7 +4565,7 @@
         <v>123</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="I13" s="6" t="s">
         <v>448</v>
@@ -4521,7 +4591,7 @@
         <v>124</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="I14" s="6" t="s">
         <v>450</v>
@@ -4561,10 +4631,10 @@
         <v>126</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="J16" s="5"/>
       <c r="K16" s="6"/>
@@ -4585,10 +4655,10 @@
         <v>127</v>
       </c>
       <c r="H17" s="5" t="s">
+        <v>798</v>
+      </c>
+      <c r="I17" s="6" t="s">
         <v>801</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>804</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>509</v>
@@ -4613,10 +4683,10 @@
         <v>52</v>
       </c>
       <c r="H18" s="5" t="s">
+        <v>799</v>
+      </c>
+      <c r="I18" s="6" t="s">
         <v>802</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>805</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>510</v>
@@ -4643,10 +4713,10 @@
         <v>132</v>
       </c>
       <c r="H19" s="5" t="s">
+        <v>800</v>
+      </c>
+      <c r="I19" s="6" t="s">
         <v>803</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>806</v>
       </c>
       <c r="J19" s="5" t="s">
         <v>511</v>
@@ -4717,16 +4787,16 @@
         <v>135</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="I22" s="32" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
     </row>
     <row r="23" spans="2:11">
@@ -4747,16 +4817,16 @@
         <v>136</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="I23" s="32" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
     </row>
     <row r="24" spans="2:11">
@@ -4777,16 +4847,16 @@
         <v>137</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="I24" s="32" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
     </row>
     <row r="25" spans="2:11">
@@ -4805,16 +4875,16 @@
         <v>170</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="I25" s="32" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
     </row>
     <row r="26" spans="2:11">
@@ -4835,10 +4905,10 @@
       <c r="H26" s="5"/>
       <c r="I26" s="6"/>
       <c r="J26" s="5" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
     </row>
     <row r="27" spans="2:11">
@@ -4859,10 +4929,10 @@
       <c r="H27" s="5"/>
       <c r="I27" s="6"/>
       <c r="J27" s="5" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
     </row>
     <row r="28" spans="2:11">
@@ -4883,16 +4953,16 @@
         <v>173</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
     </row>
     <row r="29" spans="2:11">
@@ -4913,16 +4983,16 @@
         <v>174</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
     </row>
     <row r="30" spans="2:11">
@@ -4943,16 +5013,16 @@
         <v>175</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
     </row>
     <row r="31" spans="2:11">
@@ -4975,10 +5045,10 @@
       <c r="H31" s="5"/>
       <c r="I31" s="6"/>
       <c r="J31" s="5" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
     </row>
     <row r="32" spans="2:11">
@@ -5023,10 +5093,10 @@
       <c r="H33" s="5"/>
       <c r="I33" s="6"/>
       <c r="J33" s="5" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="K33" s="6" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
     </row>
     <row r="34" spans="2:11">
@@ -5047,10 +5117,10 @@
       <c r="H34" s="5"/>
       <c r="I34" s="6"/>
       <c r="J34" s="5" t="s">
+        <v>806</v>
+      </c>
+      <c r="K34" s="6" t="s">
         <v>809</v>
-      </c>
-      <c r="K34" s="6" t="s">
-        <v>812</v>
       </c>
     </row>
     <row r="35" spans="2:11">
@@ -5075,10 +5145,10 @@
         <v>474</v>
       </c>
       <c r="J35" s="5" t="s">
+        <v>807</v>
+      </c>
+      <c r="K35" s="6" t="s">
         <v>810</v>
-      </c>
-      <c r="K35" s="6" t="s">
-        <v>813</v>
       </c>
     </row>
     <row r="36" spans="2:11">
@@ -5103,10 +5173,10 @@
         <v>475</v>
       </c>
       <c r="J36" s="5" t="s">
+        <v>808</v>
+      </c>
+      <c r="K36" s="6" t="s">
         <v>811</v>
-      </c>
-      <c r="K36" s="6" t="s">
-        <v>814</v>
       </c>
     </row>
     <row r="37" spans="2:11">
@@ -5179,10 +5249,10 @@
         <v>478</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="K39" s="6" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
     </row>
     <row r="40" spans="2:11">
@@ -5341,10 +5411,10 @@
         <v>191</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="J46" s="5"/>
       <c r="K46" s="6"/>
@@ -5365,10 +5435,10 @@
         <v>192</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="J47" s="5"/>
       <c r="K47" s="6"/>
@@ -5389,10 +5459,10 @@
         <v>193</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="J48" s="5"/>
       <c r="K48" s="6"/>
@@ -5409,10 +5479,10 @@
         <v>194</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="J49" s="5"/>
       <c r="K49" s="6"/>
@@ -5429,10 +5499,10 @@
         <v>195</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="J50" s="5"/>
       <c r="K50" s="6"/>
@@ -5449,10 +5519,10 @@
         <v>196</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="J51" s="5"/>
       <c r="K51" s="6"/>
@@ -5489,10 +5559,10 @@
         <v>376</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="J53" s="5"/>
       <c r="K53" s="6"/>
@@ -5511,10 +5581,10 @@
         <v>377</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="J54" s="5"/>
       <c r="K54" s="6"/>
@@ -5533,10 +5603,10 @@
         <v>378</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="J55" s="5"/>
       <c r="K55" s="6"/>
@@ -5555,10 +5625,10 @@
         <v>379</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="J56" s="5"/>
       <c r="K56" s="6"/>
@@ -5577,10 +5647,10 @@
         <v>380</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="J57" s="5"/>
       <c r="K57" s="6"/>
@@ -5589,10 +5659,10 @@
       <c r="F58" s="5"/>
       <c r="G58" s="6"/>
       <c r="H58" s="5" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="J58" s="6"/>
       <c r="K58" s="6"/>
@@ -5601,10 +5671,10 @@
       <c r="F59" s="5"/>
       <c r="G59" s="6"/>
       <c r="H59" s="5" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="J59" s="6"/>
       <c r="K59" s="6"/>
@@ -5789,84 +5859,84 @@
       <c r="F77" s="5"/>
       <c r="G77" s="6"/>
       <c r="H77" s="5" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="I77" s="6" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="J77" s="6"/>
       <c r="K77" s="6"/>
     </row>
     <row r="78" spans="6:11">
       <c r="H78" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="I78" s="6" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
     </row>
     <row r="79" spans="6:11">
       <c r="H79" s="5" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="I79" s="6" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
     </row>
     <row r="80" spans="6:11">
       <c r="H80" s="5" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="I80" s="6" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
     </row>
     <row r="81" spans="8:9">
       <c r="H81" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="I81" s="6" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
     </row>
     <row r="82" spans="8:9">
       <c r="H82" s="5" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="I82" s="6" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
     </row>
     <row r="83" spans="8:9">
       <c r="H83" s="5" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="I83" s="6" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
     </row>
     <row r="84" spans="8:9">
       <c r="H84" s="5" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="I84" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="85" spans="8:9">
       <c r="H85" s="5" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="I85" s="6" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
     </row>
     <row r="86" spans="8:9">
       <c r="H86" s="5" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="I86" s="6" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
     </row>
     <row r="87" spans="8:9">
@@ -5887,120 +5957,120 @@
     </row>
     <row r="91" spans="8:9">
       <c r="H91" s="5" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="I91" s="6" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
     </row>
     <row r="92" spans="8:9">
       <c r="H92" s="5" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="I92" s="6" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
     </row>
     <row r="93" spans="8:9">
       <c r="H93" s="5" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="I93" s="6" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
     </row>
     <row r="94" spans="8:9">
       <c r="H94" s="5" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="I94" s="6" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
     </row>
     <row r="95" spans="8:9">
       <c r="H95" s="5" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="I95" s="6" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
     </row>
     <row r="96" spans="8:9">
       <c r="H96" s="5" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="I96" s="6" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
     </row>
     <row r="97" spans="8:9">
       <c r="H97" s="5" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="I97" s="6" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
     </row>
     <row r="98" spans="8:9">
       <c r="H98" s="5" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="I98" s="6" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
     </row>
     <row r="99" spans="8:9">
       <c r="H99" s="5" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="I99" s="6" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
     </row>
     <row r="100" spans="8:9">
       <c r="H100" s="5" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="I100" s="6" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
     </row>
     <row r="101" spans="8:9">
       <c r="H101" s="5" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="I101" s="6" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
     </row>
     <row r="102" spans="8:9">
       <c r="H102" s="5" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="I102" s="6" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
     </row>
     <row r="103" spans="8:9">
       <c r="H103" s="5" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="I103" s="6" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
     </row>
     <row r="104" spans="8:9">
       <c r="H104" s="5" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="I104" s="6" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
     </row>
     <row r="105" spans="8:9">
       <c r="H105" s="5"/>
       <c r="I105" s="6" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
     </row>
   </sheetData>
@@ -7869,7 +7939,7 @@
         <v>620</v>
       </c>
       <c r="U52" s="10" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="V52" s="9" t="s">
         <v>327</v>
@@ -7929,7 +7999,7 @@
         <v>621</v>
       </c>
       <c r="U53" s="10" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="V53" s="9" t="s">
         <v>259</v>
@@ -8063,18 +8133,22 @@
     </row>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="V5:W5"/>
-    <mergeCell ref="V25:W25"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="U3:X3"/>
-    <mergeCell ref="U4:X4"/>
-    <mergeCell ref="M3:P3"/>
-    <mergeCell ref="S3:T3"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="S5:T5"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="M4:P4"/>
+    <mergeCell ref="N44:O44"/>
+    <mergeCell ref="V44:W44"/>
+    <mergeCell ref="S44:T44"/>
+    <mergeCell ref="K44:L44"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="M43:P43"/>
+    <mergeCell ref="U43:X43"/>
+    <mergeCell ref="M23:P23"/>
+    <mergeCell ref="M24:P24"/>
+    <mergeCell ref="U23:X23"/>
+    <mergeCell ref="U24:X24"/>
+    <mergeCell ref="S23:T23"/>
+    <mergeCell ref="S24:T24"/>
+    <mergeCell ref="S25:T25"/>
+    <mergeCell ref="M42:P42"/>
+    <mergeCell ref="U42:X42"/>
     <mergeCell ref="K3:L3"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C3:D3"/>
@@ -8091,22 +8165,18 @@
     <mergeCell ref="E42:H42"/>
     <mergeCell ref="E3:H3"/>
     <mergeCell ref="E4:H4"/>
-    <mergeCell ref="N44:O44"/>
-    <mergeCell ref="V44:W44"/>
-    <mergeCell ref="S44:T44"/>
-    <mergeCell ref="K44:L44"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="M43:P43"/>
-    <mergeCell ref="U43:X43"/>
-    <mergeCell ref="M23:P23"/>
-    <mergeCell ref="M24:P24"/>
-    <mergeCell ref="U23:X23"/>
-    <mergeCell ref="U24:X24"/>
-    <mergeCell ref="S23:T23"/>
-    <mergeCell ref="S24:T24"/>
-    <mergeCell ref="S25:T25"/>
-    <mergeCell ref="M42:P42"/>
-    <mergeCell ref="U42:X42"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="S5:T5"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="M4:P4"/>
+    <mergeCell ref="V5:W5"/>
+    <mergeCell ref="V25:W25"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="U3:X3"/>
+    <mergeCell ref="U4:X4"/>
+    <mergeCell ref="M3:P3"/>
+    <mergeCell ref="S3:T3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8159,7 +8229,7 @@
       </c>
       <c r="C3" s="35"/>
       <c r="D3" s="34" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="E3" s="36"/>
       <c r="F3" s="36"/>
@@ -8785,7 +8855,7 @@
       </c>
       <c r="C20" s="33"/>
       <c r="D20" s="33" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="E20" s="33"/>
       <c r="F20" s="33"/>
@@ -9091,7 +9161,7 @@
         <v>1500</v>
       </c>
       <c r="T29" s="6" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="U29" s="6"/>
     </row>
@@ -9174,20 +9244,20 @@
       <c r="G32" s="10"/>
       <c r="I32" s="5"/>
       <c r="J32" s="5" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="K32" s="6" t="s">
         <v>7</v>
       </c>
       <c r="L32" s="5"/>
       <c r="M32" s="5" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="N32" s="6" t="s">
         <v>20</v>
       </c>
       <c r="O32" s="16" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="P32" s="16"/>
       <c r="Q32" s="6" t="s">
@@ -9209,14 +9279,14 @@
       <c r="G33" s="10"/>
       <c r="I33" s="9"/>
       <c r="J33" s="9" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="K33" s="10" t="s">
         <v>317</v>
       </c>
       <c r="L33" s="9"/>
       <c r="M33" s="9" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="N33" s="10" t="s">
         <v>13</v>
@@ -9234,14 +9304,14 @@
       <c r="G34" s="12"/>
       <c r="I34" s="9"/>
       <c r="J34" s="9" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="K34" s="10" t="s">
         <v>318</v>
       </c>
       <c r="L34" s="9"/>
       <c r="M34" s="9" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="N34" s="10" t="s">
         <v>14</v>
@@ -9253,14 +9323,14 @@
     <row r="35" spans="2:17">
       <c r="I35" s="9"/>
       <c r="J35" s="9" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="K35" s="10" t="s">
         <v>17</v>
       </c>
       <c r="L35" s="9"/>
       <c r="M35" s="9" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="N35" s="10" t="s">
         <v>316</v>
@@ -9272,14 +9342,14 @@
     <row r="36" spans="2:17">
       <c r="I36" s="9"/>
       <c r="J36" s="9" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="K36" s="10" t="s">
         <v>18</v>
       </c>
       <c r="L36" s="9"/>
       <c r="M36" s="9" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="N36" s="10" t="s">
         <v>15</v>
@@ -9291,7 +9361,7 @@
     <row r="37" spans="2:17">
       <c r="I37" s="5"/>
       <c r="J37" s="5" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="K37" s="6"/>
       <c r="L37" s="5"/>
@@ -9304,7 +9374,7 @@
     <row r="38" spans="2:17">
       <c r="I38" s="5"/>
       <c r="J38" s="5" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>19</v>
@@ -9319,7 +9389,7 @@
     <row r="39" spans="2:17">
       <c r="I39" s="5"/>
       <c r="J39" s="5" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="K39" s="6" t="s">
         <v>385</v>
@@ -9443,12 +9513,13 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:G20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="K28:Q28"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="K29:Q29"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="O30:P30"/>
     <mergeCell ref="O5:P5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="B5:C5"/>
@@ -9462,13 +9533,12 @@
     <mergeCell ref="K4:Q4"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="K28:Q28"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="K29:Q29"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="L30:M30"/>
-    <mergeCell ref="O30:P30"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:G20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="E22:F22"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9477,36 +9547,67 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E804508-4978-40A9-8170-B191052641B8}">
-  <dimension ref="D6:X47"/>
+  <dimension ref="D3:X47"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="15" max="15" width="12.25" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
+    <row r="3" spans="4:20">
+      <c r="N3" t="s">
+        <v>872</v>
+      </c>
+      <c r="O3" s="81" t="s">
+        <v>878</v>
+      </c>
+      <c r="P3" t="s">
+        <v>874</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="4" spans="4:20">
+      <c r="N4" t="s">
+        <v>873</v>
+      </c>
+      <c r="O4" s="81" t="s">
+        <v>879</v>
+      </c>
+      <c r="P4" t="s">
+        <v>875</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>880</v>
+      </c>
+    </row>
     <row r="6" spans="4:20" ht="17.25" thickBot="1">
-      <c r="D6" s="37" t="s">
+      <c r="D6" s="69" t="s">
         <v>357</v>
       </c>
-      <c r="E6" s="37"/>
-      <c r="F6" s="37"/>
-      <c r="G6" s="37"/>
-      <c r="I6" s="37" t="s">
+      <c r="E6" s="69"/>
+      <c r="F6" s="69"/>
+      <c r="G6" s="69"/>
+      <c r="I6" s="69" t="s">
+        <v>721</v>
+      </c>
+      <c r="J6" s="69"/>
+      <c r="K6" s="69"/>
+      <c r="M6" s="69" t="s">
+        <v>359</v>
+      </c>
+      <c r="N6" s="69"/>
+      <c r="O6" s="69"/>
+      <c r="P6" s="69"/>
+      <c r="R6" s="69" t="s">
         <v>722</v>
       </c>
-      <c r="J6" s="37"/>
-      <c r="K6" s="37"/>
-      <c r="M6" s="37" t="s">
-        <v>359</v>
-      </c>
-      <c r="N6" s="37"/>
-      <c r="O6" s="37"/>
-      <c r="P6" s="37"/>
-      <c r="R6" s="37" t="s">
-        <v>723</v>
-      </c>
-      <c r="S6" s="37"/>
-      <c r="T6" s="37"/>
+      <c r="S6" s="69"/>
+      <c r="T6" s="69"/>
     </row>
     <row r="7" spans="4:20" ht="16.5" customHeight="1">
-      <c r="D7" s="68" t="s">
-        <v>720</v>
+      <c r="D7" s="37" t="s">
+        <v>719</v>
       </c>
       <c r="E7" s="21"/>
       <c r="F7" s="21"/>
@@ -9514,8 +9615,8 @@
       <c r="I7" s="26"/>
       <c r="J7" s="21"/>
       <c r="K7" s="22"/>
-      <c r="M7" s="68" t="s">
-        <v>718</v>
+      <c r="M7" s="37" t="s">
+        <v>876</v>
       </c>
       <c r="N7" s="21"/>
       <c r="O7" s="21"/>
@@ -9525,195 +9626,195 @@
       <c r="T7" s="22"/>
     </row>
     <row r="8" spans="4:20">
-      <c r="D8" s="69"/>
+      <c r="D8" s="38"/>
       <c r="G8" s="23"/>
       <c r="I8" s="24"/>
       <c r="K8" s="23"/>
-      <c r="M8" s="69"/>
+      <c r="M8" s="38"/>
       <c r="P8" s="23"/>
       <c r="R8" s="24"/>
       <c r="T8" s="23"/>
     </row>
     <row r="9" spans="4:20" ht="16.5" customHeight="1">
-      <c r="D9" s="69"/>
-      <c r="F9" s="46" t="s">
+      <c r="D9" s="38"/>
+      <c r="F9" s="49" t="s">
         <v>717</v>
       </c>
       <c r="G9" s="23"/>
       <c r="I9" s="24"/>
-      <c r="J9" s="46" t="s">
+      <c r="J9" s="49" t="s">
         <v>717</v>
       </c>
       <c r="K9" s="23"/>
-      <c r="M9" s="69"/>
-      <c r="O9" s="46" t="s">
+      <c r="M9" s="38"/>
+      <c r="O9" s="49" t="s">
         <v>717</v>
       </c>
       <c r="P9" s="23"/>
       <c r="R9" s="24"/>
-      <c r="S9" s="46" t="s">
+      <c r="S9" s="49" t="s">
         <v>717</v>
       </c>
       <c r="T9" s="23"/>
     </row>
     <row r="10" spans="4:20">
-      <c r="D10" s="69"/>
-      <c r="F10" s="57"/>
+      <c r="D10" s="38"/>
+      <c r="F10" s="50"/>
       <c r="G10" s="23"/>
       <c r="I10" s="24"/>
-      <c r="J10" s="57"/>
+      <c r="J10" s="50"/>
       <c r="K10" s="23"/>
-      <c r="M10" s="69"/>
-      <c r="O10" s="57"/>
+      <c r="M10" s="38"/>
+      <c r="O10" s="50"/>
       <c r="P10" s="23"/>
       <c r="R10" s="24"/>
-      <c r="S10" s="57"/>
+      <c r="S10" s="50"/>
       <c r="T10" s="23"/>
     </row>
     <row r="11" spans="4:20" ht="16.5" customHeight="1">
-      <c r="D11" s="69"/>
-      <c r="E11" s="44" t="s">
+      <c r="D11" s="38"/>
+      <c r="E11" s="51" t="s">
         <v>716</v>
       </c>
       <c r="G11" s="23"/>
       <c r="I11" s="24"/>
-      <c r="J11" s="44" t="s">
+      <c r="J11" s="51" t="s">
         <v>716</v>
       </c>
       <c r="K11" s="23"/>
-      <c r="M11" s="69"/>
-      <c r="N11" s="44" t="s">
-        <v>716</v>
+      <c r="M11" s="38"/>
+      <c r="N11" s="51" t="s">
+        <v>871</v>
       </c>
       <c r="P11" s="23"/>
       <c r="R11" s="24"/>
-      <c r="S11" s="44" t="s">
+      <c r="S11" s="51" t="s">
         <v>716</v>
       </c>
       <c r="T11" s="23"/>
     </row>
     <row r="12" spans="4:20">
-      <c r="D12" s="69"/>
-      <c r="E12" s="71"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="52"/>
       <c r="G12" s="23"/>
       <c r="I12" s="24"/>
-      <c r="J12" s="45"/>
+      <c r="J12" s="62"/>
       <c r="K12" s="23"/>
-      <c r="M12" s="69"/>
-      <c r="N12" s="71"/>
+      <c r="M12" s="38"/>
+      <c r="N12" s="52"/>
       <c r="P12" s="23"/>
       <c r="R12" s="24"/>
-      <c r="S12" s="45"/>
+      <c r="S12" s="62"/>
       <c r="T12" s="23"/>
     </row>
     <row r="13" spans="4:20">
-      <c r="D13" s="70"/>
+      <c r="D13" s="39"/>
       <c r="G13" s="23"/>
       <c r="I13" s="24"/>
       <c r="K13" s="23"/>
-      <c r="M13" s="70"/>
+      <c r="M13" s="39"/>
       <c r="P13" s="23"/>
       <c r="R13" s="24"/>
       <c r="T13" s="23"/>
     </row>
     <row r="14" spans="4:20" ht="16.5" customHeight="1">
       <c r="D14" s="24"/>
-      <c r="E14" s="72" t="s">
-        <v>719</v>
-      </c>
-      <c r="F14" s="73"/>
-      <c r="G14" s="74"/>
-      <c r="I14" s="58" t="s">
-        <v>725</v>
-      </c>
-      <c r="J14" s="59"/>
-      <c r="K14" s="64"/>
+      <c r="E14" s="40" t="s">
+        <v>718</v>
+      </c>
+      <c r="F14" s="41"/>
+      <c r="G14" s="42"/>
+      <c r="I14" s="53" t="s">
+        <v>724</v>
+      </c>
+      <c r="J14" s="54"/>
+      <c r="K14" s="55"/>
       <c r="M14" s="24"/>
-      <c r="N14" s="72" t="s">
-        <v>728</v>
-      </c>
-      <c r="O14" s="73"/>
-      <c r="P14" s="74"/>
-      <c r="R14" s="58" t="s">
-        <v>725</v>
-      </c>
-      <c r="S14" s="59"/>
-      <c r="T14" s="64"/>
+      <c r="N14" s="40" t="s">
+        <v>877</v>
+      </c>
+      <c r="O14" s="41"/>
+      <c r="P14" s="42"/>
+      <c r="R14" s="53" t="s">
+        <v>724</v>
+      </c>
+      <c r="S14" s="54"/>
+      <c r="T14" s="55"/>
     </row>
     <row r="15" spans="4:20">
       <c r="D15" s="24"/>
-      <c r="E15" s="75"/>
-      <c r="F15" s="76"/>
-      <c r="G15" s="77"/>
-      <c r="I15" s="51"/>
-      <c r="J15" s="52"/>
-      <c r="K15" s="53"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="45"/>
+      <c r="I15" s="56"/>
+      <c r="J15" s="57"/>
+      <c r="K15" s="58"/>
       <c r="M15" s="24"/>
-      <c r="N15" s="75"/>
-      <c r="O15" s="76"/>
-      <c r="P15" s="77"/>
-      <c r="R15" s="51"/>
-      <c r="S15" s="52"/>
-      <c r="T15" s="53"/>
+      <c r="N15" s="43"/>
+      <c r="O15" s="44"/>
+      <c r="P15" s="45"/>
+      <c r="R15" s="56"/>
+      <c r="S15" s="57"/>
+      <c r="T15" s="58"/>
     </row>
     <row r="16" spans="4:20">
       <c r="D16" s="24"/>
-      <c r="E16" s="75"/>
-      <c r="F16" s="76"/>
-      <c r="G16" s="77"/>
-      <c r="I16" s="51"/>
-      <c r="J16" s="52"/>
-      <c r="K16" s="53"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="45"/>
+      <c r="I16" s="56"/>
+      <c r="J16" s="57"/>
+      <c r="K16" s="58"/>
       <c r="M16" s="24"/>
-      <c r="N16" s="75"/>
-      <c r="O16" s="76"/>
-      <c r="P16" s="77"/>
-      <c r="R16" s="51"/>
-      <c r="S16" s="52"/>
-      <c r="T16" s="53"/>
+      <c r="N16" s="43"/>
+      <c r="O16" s="44"/>
+      <c r="P16" s="45"/>
+      <c r="R16" s="56"/>
+      <c r="S16" s="57"/>
+      <c r="T16" s="58"/>
     </row>
     <row r="17" spans="4:20" ht="17.25" thickBot="1">
       <c r="D17" s="25"/>
-      <c r="E17" s="78"/>
-      <c r="F17" s="79"/>
-      <c r="G17" s="80"/>
-      <c r="I17" s="65"/>
-      <c r="J17" s="66"/>
-      <c r="K17" s="67"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="47"/>
+      <c r="G17" s="48"/>
+      <c r="I17" s="59"/>
+      <c r="J17" s="60"/>
+      <c r="K17" s="61"/>
       <c r="M17" s="25"/>
-      <c r="N17" s="78"/>
-      <c r="O17" s="79"/>
-      <c r="P17" s="80"/>
-      <c r="R17" s="65"/>
-      <c r="S17" s="66"/>
-      <c r="T17" s="67"/>
+      <c r="N17" s="46"/>
+      <c r="O17" s="47"/>
+      <c r="P17" s="48"/>
+      <c r="R17" s="59"/>
+      <c r="S17" s="60"/>
+      <c r="T17" s="61"/>
     </row>
     <row r="19" spans="4:20" ht="17.25" thickBot="1">
-      <c r="D19" s="37" t="s">
+      <c r="D19" s="69" t="s">
         <v>368</v>
       </c>
-      <c r="E19" s="37"/>
-      <c r="F19" s="37"/>
-      <c r="H19" s="37" t="s">
+      <c r="E19" s="69"/>
+      <c r="F19" s="69"/>
+      <c r="H19" s="69" t="s">
         <v>367</v>
       </c>
-      <c r="I19" s="37"/>
-      <c r="J19" s="37"/>
-      <c r="K19" s="37"/>
-      <c r="R19" s="37" t="s">
-        <v>724</v>
-      </c>
-      <c r="S19" s="37"/>
-      <c r="T19" s="37"/>
+      <c r="I19" s="69"/>
+      <c r="J19" s="69"/>
+      <c r="K19" s="69"/>
+      <c r="R19" s="69" t="s">
+        <v>723</v>
+      </c>
+      <c r="S19" s="69"/>
+      <c r="T19" s="69"/>
     </row>
     <row r="20" spans="4:20">
-      <c r="D20" s="48" t="s">
-        <v>721</v>
-      </c>
-      <c r="E20" s="49"/>
-      <c r="F20" s="50"/>
+      <c r="D20" s="77" t="s">
+        <v>720</v>
+      </c>
+      <c r="E20" s="78"/>
+      <c r="F20" s="79"/>
       <c r="H20" s="26"/>
-      <c r="I20" s="63" t="s">
+      <c r="I20" s="68" t="s">
         <v>717</v>
       </c>
       <c r="J20" s="21"/>
@@ -9722,56 +9823,56 @@
       <c r="N20" s="21"/>
       <c r="O20" s="21"/>
       <c r="P20" s="22"/>
-      <c r="R20" s="48" t="s">
-        <v>725</v>
-      </c>
-      <c r="S20" s="49"/>
-      <c r="T20" s="50"/>
+      <c r="R20" s="77" t="s">
+        <v>724</v>
+      </c>
+      <c r="S20" s="78"/>
+      <c r="T20" s="79"/>
     </row>
     <row r="21" spans="4:20">
-      <c r="D21" s="51"/>
-      <c r="E21" s="52"/>
-      <c r="F21" s="53"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="57"/>
+      <c r="F21" s="58"/>
       <c r="H21" s="24"/>
-      <c r="I21" s="57"/>
+      <c r="I21" s="50"/>
       <c r="K21" s="23"/>
       <c r="M21" s="24"/>
       <c r="P21" s="23"/>
-      <c r="R21" s="51"/>
-      <c r="S21" s="52"/>
-      <c r="T21" s="53"/>
+      <c r="R21" s="56"/>
+      <c r="S21" s="57"/>
+      <c r="T21" s="58"/>
     </row>
     <row r="22" spans="4:20">
-      <c r="D22" s="51"/>
-      <c r="E22" s="52"/>
-      <c r="F22" s="53"/>
-      <c r="H22" s="24"/>
-      <c r="I22" s="44" t="s">
+      <c r="D22" s="56"/>
+      <c r="E22" s="57"/>
+      <c r="F22" s="58"/>
+      <c r="H22" s="74" t="s">
+        <v>725</v>
+      </c>
+      <c r="I22" s="51" t="s">
         <v>716</v>
       </c>
-      <c r="J22" s="42" t="s">
-        <v>726</v>
-      </c>
+      <c r="J22" s="74"/>
       <c r="K22" s="23"/>
       <c r="M22" s="24"/>
       <c r="P22" s="23"/>
-      <c r="R22" s="51"/>
-      <c r="S22" s="52"/>
-      <c r="T22" s="53"/>
+      <c r="R22" s="56"/>
+      <c r="S22" s="57"/>
+      <c r="T22" s="58"/>
     </row>
     <row r="23" spans="4:20">
-      <c r="D23" s="54"/>
-      <c r="E23" s="55"/>
-      <c r="F23" s="56"/>
-      <c r="H23" s="24"/>
-      <c r="I23" s="45"/>
-      <c r="J23" s="43"/>
+      <c r="D23" s="65"/>
+      <c r="E23" s="66"/>
+      <c r="F23" s="80"/>
+      <c r="H23" s="75"/>
+      <c r="I23" s="62"/>
+      <c r="J23" s="75"/>
       <c r="K23" s="23"/>
       <c r="M23" s="24"/>
       <c r="P23" s="23"/>
-      <c r="R23" s="54"/>
-      <c r="S23" s="55"/>
-      <c r="T23" s="56"/>
+      <c r="R23" s="65"/>
+      <c r="S23" s="66"/>
+      <c r="T23" s="80"/>
     </row>
     <row r="24" spans="4:20">
       <c r="D24" s="24"/>
@@ -9787,77 +9888,77 @@
     </row>
     <row r="25" spans="4:20" ht="16.5" customHeight="1">
       <c r="D25" s="24"/>
-      <c r="E25" s="44" t="s">
+      <c r="E25" s="51" t="s">
         <v>716</v>
       </c>
       <c r="F25" s="23"/>
-      <c r="H25" s="58" t="s">
-        <v>729</v>
-      </c>
-      <c r="I25" s="59"/>
-      <c r="J25" s="60"/>
+      <c r="H25" s="53" t="s">
+        <v>887</v>
+      </c>
+      <c r="I25" s="54"/>
+      <c r="J25" s="63"/>
       <c r="K25" s="23"/>
       <c r="M25" s="24"/>
       <c r="P25" s="23"/>
       <c r="R25" s="24"/>
-      <c r="S25" s="44" t="s">
+      <c r="S25" s="51" t="s">
         <v>716</v>
       </c>
       <c r="T25" s="23"/>
     </row>
     <row r="26" spans="4:20">
       <c r="D26" s="24"/>
-      <c r="E26" s="45"/>
+      <c r="E26" s="62"/>
       <c r="F26" s="23"/>
-      <c r="H26" s="51"/>
-      <c r="I26" s="52"/>
-      <c r="J26" s="61"/>
+      <c r="H26" s="56"/>
+      <c r="I26" s="57"/>
+      <c r="J26" s="64"/>
       <c r="K26" s="23"/>
       <c r="M26" s="24"/>
       <c r="P26" s="23"/>
       <c r="R26" s="24"/>
-      <c r="S26" s="45"/>
+      <c r="S26" s="62"/>
       <c r="T26" s="23"/>
     </row>
     <row r="27" spans="4:20">
       <c r="D27" s="24"/>
-      <c r="E27" s="46" t="s">
+      <c r="E27" s="49" t="s">
         <v>717</v>
       </c>
       <c r="F27" s="23"/>
-      <c r="H27" s="51"/>
-      <c r="I27" s="52"/>
-      <c r="J27" s="61"/>
-      <c r="K27" s="38" t="s">
-        <v>718</v>
+      <c r="H27" s="56"/>
+      <c r="I27" s="57"/>
+      <c r="J27" s="64"/>
+      <c r="K27" s="70" t="s">
+        <v>884</v>
       </c>
       <c r="M27" s="24"/>
       <c r="P27" s="23"/>
       <c r="R27" s="24"/>
-      <c r="S27" s="46" t="s">
+      <c r="S27" s="49" t="s">
         <v>717</v>
       </c>
       <c r="T27" s="23"/>
     </row>
     <row r="28" spans="4:20" ht="16.5" customHeight="1">
       <c r="D28" s="24"/>
-      <c r="E28" s="57"/>
+      <c r="E28" s="50"/>
       <c r="F28" s="23"/>
-      <c r="H28" s="54"/>
-      <c r="I28" s="55"/>
-      <c r="J28" s="62"/>
-      <c r="K28" s="39"/>
+      <c r="H28" s="65"/>
+      <c r="I28" s="66"/>
+      <c r="J28" s="67"/>
+      <c r="K28" s="71"/>
       <c r="M28" s="24"/>
       <c r="P28" s="23"/>
       <c r="R28" s="24"/>
-      <c r="S28" s="57"/>
+      <c r="S28" s="50"/>
       <c r="T28" s="23"/>
     </row>
     <row r="29" spans="4:20">
       <c r="D29" s="24"/>
       <c r="F29" s="23"/>
       <c r="H29" s="24"/>
-      <c r="K29" s="40"/>
+      <c r="K29" s="72"/>
       <c r="M29" s="24"/>
       <c r="P29" s="23"/>
       <c r="R29" s="24"/>
@@ -9868,10 +9969,10 @@
       <c r="E30" s="27"/>
       <c r="F30" s="28"/>
       <c r="H30" s="24"/>
-      <c r="I30" s="44" t="s">
-        <v>716</v>
-      </c>
-      <c r="K30" s="40"/>
+      <c r="I30" s="51" t="s">
+        <v>871</v>
+      </c>
+      <c r="K30" s="72"/>
       <c r="M30" s="25"/>
       <c r="N30" s="27"/>
       <c r="O30" s="27"/>
@@ -9882,47 +9983,53 @@
     </row>
     <row r="31" spans="4:20">
       <c r="H31" s="24"/>
-      <c r="I31" s="45"/>
-      <c r="K31" s="40"/>
+      <c r="I31" s="62"/>
+      <c r="K31" s="72"/>
     </row>
     <row r="32" spans="4:20">
       <c r="H32" s="24"/>
-      <c r="I32" s="46" t="s">
+      <c r="I32" s="49" t="s">
         <v>717</v>
       </c>
-      <c r="K32" s="40"/>
+      <c r="K32" s="72"/>
     </row>
     <row r="33" spans="8:24" ht="17.25" thickBot="1">
       <c r="H33" s="25"/>
-      <c r="I33" s="47"/>
+      <c r="I33" s="76"/>
       <c r="J33" s="27"/>
-      <c r="K33" s="41"/>
+      <c r="K33" s="73"/>
+    </row>
+    <row r="35" spans="8:24">
+      <c r="I35" t="s">
+        <v>882</v>
+      </c>
+      <c r="J35" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="36" spans="8:24">
+      <c r="I36" t="s">
+        <v>883</v>
+      </c>
+      <c r="J36" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="38" spans="8:24">
+      <c r="I38" t="s">
+        <v>888</v>
+      </c>
+      <c r="J38" t="s">
+        <v>889</v>
+      </c>
     </row>
     <row r="47" spans="8:24">
       <c r="X47" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="34">
-    <mergeCell ref="D7:D13"/>
-    <mergeCell ref="E14:G17"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="I14:K17"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="S11:S12"/>
-    <mergeCell ref="R14:T17"/>
-    <mergeCell ref="M7:M13"/>
-    <mergeCell ref="O9:O10"/>
-    <mergeCell ref="N11:N12"/>
-    <mergeCell ref="N14:P17"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="H25:J28"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="I22:I23"/>
-    <mergeCell ref="J11:J12"/>
+  <mergeCells count="35">
     <mergeCell ref="R6:T6"/>
     <mergeCell ref="R19:T19"/>
     <mergeCell ref="D19:F19"/>
@@ -9939,6 +10046,25 @@
     <mergeCell ref="M6:P6"/>
     <mergeCell ref="D20:F23"/>
     <mergeCell ref="E27:E28"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="H25:J28"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="S11:S12"/>
+    <mergeCell ref="R14:T17"/>
+    <mergeCell ref="M7:M13"/>
+    <mergeCell ref="O9:O10"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="N14:P17"/>
+    <mergeCell ref="D7:D13"/>
+    <mergeCell ref="E14:G17"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="I14:K17"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/PLC/IO List.xlsx
+++ b/PLC/IO List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ezen-01\Desktop\Project\PLC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19097A28-10A3-4342-936B-5164D9DC6526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{704900FD-B174-41EE-8FCC-ADE6621AE164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4920" yWindow="3825" windowWidth="21600" windowHeight="11385" activeTab="3" xr2:uid="{E8A3CD3B-D612-4B37-A180-F6C335096DC9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{E8A3CD3B-D612-4B37-A180-F6C335096DC9}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1206" uniqueCount="890">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="899">
   <si>
     <t>X10</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2584,601 +2584,641 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>2공정(접착제)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6공정(접착제)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8공정(접착제)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>AGV
-P[3]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+P[2~5]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>볼트공급
+P[2]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M301</t>
+  </si>
+  <si>
+    <t>M302</t>
+  </si>
+  <si>
+    <t>M303</t>
+  </si>
+  <si>
+    <t>M304</t>
+  </si>
+  <si>
+    <t>M305</t>
+  </si>
+  <si>
+    <t>M306</t>
+  </si>
+  <si>
+    <t>M307</t>
+  </si>
+  <si>
+    <t>M308</t>
+  </si>
+  <si>
+    <t>M309</t>
+  </si>
+  <si>
+    <t>M310</t>
+  </si>
+  <si>
+    <t>M311</t>
+  </si>
+  <si>
+    <t>M312</t>
+  </si>
+  <si>
+    <t>M313</t>
+  </si>
+  <si>
+    <t>경화1 공정 완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경화공정1 AGV 배출 신호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경화공정1 완료 후 문닫힘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경화2 공정 완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경화공정2 AGV 배출 신호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경화공정2 완료 후 문닫힘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경화3 공정 완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경화공정3 AGV 배출 신호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경화공정3 완료 후 문닫힘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M120</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M121</t>
+  </si>
+  <si>
+    <t>M122</t>
+  </si>
+  <si>
+    <t>M123</t>
+  </si>
+  <si>
+    <t>M124</t>
+  </si>
+  <si>
+    <t>M125</t>
+  </si>
+  <si>
+    <t>M126</t>
+  </si>
+  <si>
+    <t>M127</t>
+  </si>
+  <si>
+    <t>M128</t>
+  </si>
+  <si>
+    <t>AGV 내부 펄스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>T20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>T21</t>
+  </si>
+  <si>
+    <t>T22</t>
+  </si>
+  <si>
+    <t>T23</t>
+  </si>
+  <si>
+    <t>T24</t>
+  </si>
+  <si>
+    <t>T25</t>
+  </si>
+  <si>
+    <t>T26</t>
+  </si>
+  <si>
+    <t>T27</t>
+  </si>
+  <si>
+    <t>T28</t>
+  </si>
+  <si>
+    <t>T29</t>
+  </si>
+  <si>
+    <t>1공정 agv 신호 딜레이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2공정 agv 신호 딜레이</t>
+  </si>
+  <si>
+    <t>3공정 agv 신호 딜레이</t>
+  </si>
+  <si>
+    <t>4공정 agv 신호 딜레이</t>
+  </si>
+  <si>
+    <t>5공정 agv 신호 딜레이</t>
+  </si>
+  <si>
+    <t>6공정 agv 신호 딜레이</t>
+  </si>
+  <si>
+    <t>7공정 agv 신호 딜레이</t>
+  </si>
+  <si>
+    <t>8공정 agv 신호 딜레이</t>
+  </si>
+  <si>
+    <t>9공정 agv 신호 딜레이</t>
+  </si>
+  <si>
+    <t>10공정 agv 신호 딜레이</t>
+  </si>
+  <si>
+    <t>M129</t>
+  </si>
+  <si>
+    <t>프레스1(제4공정_저항 검사 공정)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>프레스2(제1공정_하우징 공정)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로봇1 작업완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로봇2 작업완료</t>
+  </si>
+  <si>
+    <t>로봇3 작업완료</t>
+  </si>
+  <si>
+    <t>로봇5 작업완료</t>
+  </si>
+  <si>
+    <t>로봇6 작업완료</t>
+  </si>
+  <si>
+    <t>로봇7 작업완료</t>
+  </si>
+  <si>
+    <t>로봇8 작업완료</t>
+  </si>
+  <si>
+    <t>로봇9 작업완료</t>
+  </si>
+  <si>
+    <t>프레스 작업완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>챔버1 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M11</t>
+  </si>
+  <si>
+    <t>M12</t>
+  </si>
+  <si>
+    <t>M13</t>
+  </si>
+  <si>
+    <t>챔버2 상태</t>
+  </si>
+  <si>
+    <t>챔버3 상태</t>
+  </si>
+  <si>
+    <t>챔버4 상태</t>
+  </si>
+  <si>
+    <t>T30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>챔버1 완료 후 딜레이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>T31</t>
+  </si>
+  <si>
+    <t>T32</t>
+  </si>
+  <si>
+    <t>T33</t>
+  </si>
+  <si>
+    <t>챔버2 완료 후 딜레이</t>
+  </si>
+  <si>
+    <t>챔버3 완료 후 딜레이</t>
+  </si>
+  <si>
+    <t>챔버4 완료 후 딜레이</t>
+  </si>
+  <si>
+    <t>M15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M16</t>
+  </si>
+  <si>
+    <t>M17</t>
+  </si>
+  <si>
+    <t>M18</t>
+  </si>
+  <si>
+    <t>챔버1 로봇 경유위치 이동 완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>챔버2 로봇 경유위치 이동 완료</t>
+  </si>
+  <si>
+    <t>챔버3 로봇 경유위치 이동 완료</t>
+  </si>
+  <si>
+    <t>챔버4 로봇 경유위치 이동 완료</t>
+  </si>
+  <si>
+    <t>M20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수작업7 START</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M21</t>
+  </si>
+  <si>
+    <t>M22</t>
+  </si>
+  <si>
+    <t>수작업8 START</t>
+  </si>
+  <si>
+    <t>수작업9 START</t>
+  </si>
+  <si>
+    <t>출하장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PASS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M90</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGV1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M91</t>
+  </si>
+  <si>
+    <t>M92</t>
+  </si>
+  <si>
+    <t>M93</t>
+  </si>
+  <si>
+    <t>M94</t>
+  </si>
+  <si>
+    <t>M95</t>
+  </si>
+  <si>
+    <t>AGV2</t>
+  </si>
+  <si>
+    <t>AGV3</t>
+  </si>
+  <si>
+    <t>AGV4</t>
+  </si>
+  <si>
+    <t>AGV5</t>
+  </si>
+  <si>
+    <t>AGV6</t>
+  </si>
+  <si>
+    <t>M1190</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M1191</t>
+  </si>
+  <si>
+    <t>M1192</t>
+  </si>
+  <si>
+    <t>M1193</t>
+  </si>
+  <si>
+    <t>M1194</t>
+  </si>
+  <si>
+    <t>M1195</t>
+  </si>
+  <si>
+    <t>M1196</t>
+  </si>
+  <si>
+    <t>M1197</t>
+  </si>
+  <si>
+    <t>M2228</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M2229</t>
+  </si>
+  <si>
+    <t>M2230</t>
+  </si>
+  <si>
+    <t>M2231</t>
+  </si>
+  <si>
+    <t>M2232</t>
+  </si>
+  <si>
+    <t>D01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGV1 기동 MAIN 신호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGV2 기동 MAIN 신호</t>
+  </si>
+  <si>
+    <t>AGV3 기동 MAIN 신호</t>
+  </si>
+  <si>
+    <t>AGV4 기동 MAIN 신호</t>
+  </si>
+  <si>
+    <t>AGV5 기동 MAIN 신호</t>
+  </si>
+  <si>
+    <t>AGV6 기동 MAIN 신호</t>
+  </si>
+  <si>
+    <t>AGV7 기동 MAIN 신호</t>
+  </si>
+  <si>
+    <t>T40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGV1 기동 MAIN 딜레이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M150</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M151</t>
+  </si>
+  <si>
+    <t>M152</t>
+  </si>
+  <si>
+    <t>M153</t>
+  </si>
+  <si>
+    <t>M154</t>
+  </si>
+  <si>
+    <t>M155</t>
+  </si>
+  <si>
+    <t>M156</t>
+  </si>
+  <si>
+    <t>경유지점
+P[1~2]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1번 배터리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2번 배터리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3번 배터리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4번 배터리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1번 커버</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2번 커버</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>볼트 체결</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경유지점
+P[0]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1번 판</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2번 판</t>
   </si>
   <si>
     <t>하우징
 대차
+P[3~4]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-&gt;3-&gt;5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGV
+P[5]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2-&gt;4-&gt;5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-&gt;3-&gt;4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>셀 대차
+P[3,5]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경유지점
 P[2]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>1-&gt;5-&gt;6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>AGV
-P[2]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2공정(접착제)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6공정(접착제)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8공정(접착제)</t>
+P[4,6]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2-&gt;7-&gt;4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>셀 대차
+P[7,8]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2-&gt;8-&gt;6</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>AGV
-P[2~5]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>볼트공급
-P[2]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M300</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M301</t>
-  </si>
-  <si>
-    <t>M302</t>
-  </si>
-  <si>
-    <t>M303</t>
-  </si>
-  <si>
-    <t>M304</t>
-  </si>
-  <si>
-    <t>M305</t>
-  </si>
-  <si>
-    <t>M306</t>
-  </si>
-  <si>
-    <t>M307</t>
-  </si>
-  <si>
-    <t>M308</t>
-  </si>
-  <si>
-    <t>M309</t>
-  </si>
-  <si>
-    <t>M310</t>
-  </si>
-  <si>
-    <t>M311</t>
-  </si>
-  <si>
-    <t>M312</t>
-  </si>
-  <si>
-    <t>M313</t>
-  </si>
-  <si>
-    <t>경화1 공정 완료</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>경화공정1 AGV 배출 신호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>경화공정1 완료 후 문닫힘</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>경화2 공정 완료</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>경화공정2 AGV 배출 신호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>경화공정2 완료 후 문닫힘</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>경화3 공정 완료</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>경화공정3 AGV 배출 신호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>경화공정3 완료 후 문닫힘</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M120</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M121</t>
-  </si>
-  <si>
-    <t>M122</t>
-  </si>
-  <si>
-    <t>M123</t>
-  </si>
-  <si>
-    <t>M124</t>
-  </si>
-  <si>
-    <t>M125</t>
-  </si>
-  <si>
-    <t>M126</t>
-  </si>
-  <si>
-    <t>M127</t>
-  </si>
-  <si>
-    <t>M128</t>
-  </si>
-  <si>
-    <t>AGV 내부 펄스</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>T20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>T21</t>
-  </si>
-  <si>
-    <t>T22</t>
-  </si>
-  <si>
-    <t>T23</t>
-  </si>
-  <si>
-    <t>T24</t>
-  </si>
-  <si>
-    <t>T25</t>
-  </si>
-  <si>
-    <t>T26</t>
-  </si>
-  <si>
-    <t>T27</t>
-  </si>
-  <si>
-    <t>T28</t>
-  </si>
-  <si>
-    <t>T29</t>
-  </si>
-  <si>
-    <t>1공정 agv 신호 딜레이</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2공정 agv 신호 딜레이</t>
-  </si>
-  <si>
-    <t>3공정 agv 신호 딜레이</t>
-  </si>
-  <si>
-    <t>4공정 agv 신호 딜레이</t>
-  </si>
-  <si>
-    <t>5공정 agv 신호 딜레이</t>
-  </si>
-  <si>
-    <t>6공정 agv 신호 딜레이</t>
-  </si>
-  <si>
-    <t>7공정 agv 신호 딜레이</t>
-  </si>
-  <si>
-    <t>8공정 agv 신호 딜레이</t>
-  </si>
-  <si>
-    <t>9공정 agv 신호 딜레이</t>
-  </si>
-  <si>
-    <t>10공정 agv 신호 딜레이</t>
-  </si>
-  <si>
-    <t>M129</t>
-  </si>
-  <si>
-    <t>프레스1(제4공정_저항 검사 공정)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>프레스2(제1공정_하우징 공정)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>로봇1 작업완료</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>로봇2 작업완료</t>
-  </si>
-  <si>
-    <t>로봇3 작업완료</t>
-  </si>
-  <si>
-    <t>로봇5 작업완료</t>
-  </si>
-  <si>
-    <t>로봇6 작업완료</t>
-  </si>
-  <si>
-    <t>로봇7 작업완료</t>
-  </si>
-  <si>
-    <t>로봇8 작업완료</t>
-  </si>
-  <si>
-    <t>로봇9 작업완료</t>
-  </si>
-  <si>
-    <t>프레스 작업완료</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>챔버1 상태</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M11</t>
-  </si>
-  <si>
-    <t>M12</t>
-  </si>
-  <si>
-    <t>M13</t>
-  </si>
-  <si>
-    <t>챔버2 상태</t>
-  </si>
-  <si>
-    <t>챔버3 상태</t>
-  </si>
-  <si>
-    <t>챔버4 상태</t>
-  </si>
-  <si>
-    <t>T30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>챔버1 완료 후 딜레이</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>T31</t>
-  </si>
-  <si>
-    <t>T32</t>
-  </si>
-  <si>
-    <t>T33</t>
-  </si>
-  <si>
-    <t>챔버2 완료 후 딜레이</t>
-  </si>
-  <si>
-    <t>챔버3 완료 후 딜레이</t>
-  </si>
-  <si>
-    <t>챔버4 완료 후 딜레이</t>
-  </si>
-  <si>
-    <t>M15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M16</t>
-  </si>
-  <si>
-    <t>M17</t>
-  </si>
-  <si>
-    <t>M18</t>
-  </si>
-  <si>
-    <t>챔버1 로봇 경유위치 이동 완료</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>챔버2 로봇 경유위치 이동 완료</t>
-  </si>
-  <si>
-    <t>챔버3 로봇 경유위치 이동 완료</t>
-  </si>
-  <si>
-    <t>챔버4 로봇 경유위치 이동 완료</t>
-  </si>
-  <si>
-    <t>M20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>수작업7 START</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M21</t>
-  </si>
-  <si>
-    <t>M22</t>
-  </si>
-  <si>
-    <t>수작업8 START</t>
-  </si>
-  <si>
-    <t>수작업9 START</t>
-  </si>
-  <si>
-    <t>출하장</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PASS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M90</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AGV1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M91</t>
-  </si>
-  <si>
-    <t>M92</t>
-  </si>
-  <si>
-    <t>M93</t>
-  </si>
-  <si>
-    <t>M94</t>
-  </si>
-  <si>
-    <t>M95</t>
-  </si>
-  <si>
-    <t>AGV2</t>
-  </si>
-  <si>
-    <t>AGV3</t>
-  </si>
-  <si>
-    <t>AGV4</t>
-  </si>
-  <si>
-    <t>AGV5</t>
-  </si>
-  <si>
-    <t>AGV6</t>
-  </si>
-  <si>
-    <t>M1190</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M1191</t>
-  </si>
-  <si>
-    <t>M1192</t>
-  </si>
-  <si>
-    <t>M1193</t>
-  </si>
-  <si>
-    <t>M1194</t>
-  </si>
-  <si>
-    <t>M1195</t>
-  </si>
-  <si>
-    <t>M1196</t>
-  </si>
-  <si>
-    <t>M1197</t>
-  </si>
-  <si>
-    <t>M2228</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M2229</t>
-  </si>
-  <si>
-    <t>M2230</t>
-  </si>
-  <si>
-    <t>M2231</t>
-  </si>
-  <si>
-    <t>M2232</t>
-  </si>
-  <si>
-    <t>D01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AGV1 기동 MAIN 신호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AGV2 기동 MAIN 신호</t>
-  </si>
-  <si>
-    <t>AGV3 기동 MAIN 신호</t>
-  </si>
-  <si>
-    <t>AGV4 기동 MAIN 신호</t>
-  </si>
-  <si>
-    <t>AGV5 기동 MAIN 신호</t>
-  </si>
-  <si>
-    <t>AGV6 기동 MAIN 신호</t>
-  </si>
-  <si>
-    <t>AGV7 기동 MAIN 신호</t>
-  </si>
-  <si>
-    <t>T40</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AGV1 기동 MAIN 딜레이</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M150</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M151</t>
-  </si>
-  <si>
-    <t>M152</t>
-  </si>
-  <si>
-    <t>M153</t>
-  </si>
-  <si>
-    <t>M154</t>
-  </si>
-  <si>
-    <t>M155</t>
-  </si>
-  <si>
-    <t>M156</t>
-  </si>
-  <si>
-    <t>경유지점
-P[1~2]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1번 배터리</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2번 배터리</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3번 배터리</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4번 배터리</t>
+P[1~24]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGV
+P[1~19]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-&gt;2-&gt;3-&gt;1-&gt;4-&gt;5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-&gt;2-&gt;4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>셀 대차
+P[2~3]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGV
+P[4]
 P[3~6]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>1-&gt;2-&gt;3-&gt;2-&gt;4-&gt;2-&gt;5-&gt;2-&gt;6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>AGV
-P[7~8]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1-&gt;3-&gt;7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2-&gt;4-&gt;8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2-&gt;6-&gt;8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1-&gt;5-&gt;7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1번 커버</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2번 커버</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>셀 대차
-P[3~4]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1-&gt;3-.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2-&gt;4-&gt;6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AGV
-P[3~6]
-P[5~6]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>볼트 체결</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1-&gt;2-&gt;3~6</t>
+P[1~8]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3294,7 +3334,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="36">
+  <borders count="38">
     <border>
       <left/>
       <right/>
@@ -3701,13 +3741,39 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3807,17 +3873,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3915,6 +3972,12 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3928,12 +3991,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3951,8 +4008,29 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4302,47 +4380,47 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:11">
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="79" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="35"/>
-      <c r="D3" s="33" t="s">
+      <c r="C3" s="80"/>
+      <c r="D3" s="78" t="s">
         <v>55</v>
       </c>
-      <c r="E3" s="33"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="33"/>
-      <c r="J3" s="33"/>
-      <c r="K3" s="33"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
+      <c r="K3" s="78"/>
     </row>
     <row r="4" spans="2:11">
-      <c r="B4" s="34" t="s">
+      <c r="B4" s="79" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="35"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="33"/>
-      <c r="K4" s="33"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
+      <c r="K4" s="78"/>
     </row>
     <row r="5" spans="2:11">
-      <c r="B5" s="34" t="s">
+      <c r="B5" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="35"/>
+      <c r="C5" s="80"/>
       <c r="D5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="34" t="s">
+      <c r="E5" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="35"/>
+      <c r="F5" s="80"/>
       <c r="G5" s="4" t="s">
         <v>10</v>
       </c>
@@ -4513,7 +4591,7 @@
         <v>121</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="I11" s="6" t="s">
         <v>448</v>
@@ -4539,7 +4617,7 @@
         <v>122</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="I12" s="6" t="s">
         <v>450</v>
@@ -4565,7 +4643,7 @@
         <v>123</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="I13" s="6" t="s">
         <v>448</v>
@@ -4591,7 +4669,7 @@
         <v>124</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="I14" s="6" t="s">
         <v>450</v>
@@ -4631,10 +4709,10 @@
         <v>126</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="J16" s="5"/>
       <c r="K16" s="6"/>
@@ -4655,10 +4733,10 @@
         <v>127</v>
       </c>
       <c r="H17" s="5" t="s">
+        <v>795</v>
+      </c>
+      <c r="I17" s="6" t="s">
         <v>798</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>801</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>509</v>
@@ -4683,10 +4761,10 @@
         <v>52</v>
       </c>
       <c r="H18" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="I18" s="6" t="s">
         <v>799</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>802</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>510</v>
@@ -4713,10 +4791,10 @@
         <v>132</v>
       </c>
       <c r="H19" s="5" t="s">
+        <v>797</v>
+      </c>
+      <c r="I19" s="6" t="s">
         <v>800</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>803</v>
       </c>
       <c r="J19" s="5" t="s">
         <v>511</v>
@@ -4787,16 +4865,16 @@
         <v>135</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="I22" s="32" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
     </row>
     <row r="23" spans="2:11">
@@ -4817,16 +4895,16 @@
         <v>136</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="I23" s="32" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
     </row>
     <row r="24" spans="2:11">
@@ -4847,16 +4925,16 @@
         <v>137</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="I24" s="32" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
     </row>
     <row r="25" spans="2:11">
@@ -4875,16 +4953,16 @@
         <v>170</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="I25" s="32" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
     </row>
     <row r="26" spans="2:11">
@@ -4905,10 +4983,10 @@
       <c r="H26" s="5"/>
       <c r="I26" s="6"/>
       <c r="J26" s="5" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
     </row>
     <row r="27" spans="2:11">
@@ -4929,10 +5007,10 @@
       <c r="H27" s="5"/>
       <c r="I27" s="6"/>
       <c r="J27" s="5" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
     </row>
     <row r="28" spans="2:11">
@@ -4953,16 +5031,16 @@
         <v>173</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
     </row>
     <row r="29" spans="2:11">
@@ -4983,16 +5061,16 @@
         <v>174</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
     </row>
     <row r="30" spans="2:11">
@@ -5013,16 +5091,16 @@
         <v>175</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
     </row>
     <row r="31" spans="2:11">
@@ -5045,10 +5123,10 @@
       <c r="H31" s="5"/>
       <c r="I31" s="6"/>
       <c r="J31" s="5" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
     </row>
     <row r="32" spans="2:11">
@@ -5093,10 +5171,10 @@
       <c r="H33" s="5"/>
       <c r="I33" s="6"/>
       <c r="J33" s="5" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="K33" s="6" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
     </row>
     <row r="34" spans="2:11">
@@ -5117,10 +5195,10 @@
       <c r="H34" s="5"/>
       <c r="I34" s="6"/>
       <c r="J34" s="5" t="s">
+        <v>803</v>
+      </c>
+      <c r="K34" s="6" t="s">
         <v>806</v>
-      </c>
-      <c r="K34" s="6" t="s">
-        <v>809</v>
       </c>
     </row>
     <row r="35" spans="2:11">
@@ -5145,10 +5223,10 @@
         <v>474</v>
       </c>
       <c r="J35" s="5" t="s">
+        <v>804</v>
+      </c>
+      <c r="K35" s="6" t="s">
         <v>807</v>
-      </c>
-      <c r="K35" s="6" t="s">
-        <v>810</v>
       </c>
     </row>
     <row r="36" spans="2:11">
@@ -5173,10 +5251,10 @@
         <v>475</v>
       </c>
       <c r="J36" s="5" t="s">
+        <v>805</v>
+      </c>
+      <c r="K36" s="6" t="s">
         <v>808</v>
-      </c>
-      <c r="K36" s="6" t="s">
-        <v>811</v>
       </c>
     </row>
     <row r="37" spans="2:11">
@@ -5249,10 +5327,10 @@
         <v>478</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="K39" s="6" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
     </row>
     <row r="40" spans="2:11">
@@ -5411,10 +5489,10 @@
         <v>191</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="J46" s="5"/>
       <c r="K46" s="6"/>
@@ -5435,10 +5513,10 @@
         <v>192</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="J47" s="5"/>
       <c r="K47" s="6"/>
@@ -5459,10 +5537,10 @@
         <v>193</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="J48" s="5"/>
       <c r="K48" s="6"/>
@@ -5479,10 +5557,10 @@
         <v>194</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="J49" s="5"/>
       <c r="K49" s="6"/>
@@ -5499,10 +5577,10 @@
         <v>195</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="J50" s="5"/>
       <c r="K50" s="6"/>
@@ -5519,10 +5597,10 @@
         <v>196</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="J51" s="5"/>
       <c r="K51" s="6"/>
@@ -5559,10 +5637,10 @@
         <v>376</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="J53" s="5"/>
       <c r="K53" s="6"/>
@@ -5581,10 +5659,10 @@
         <v>377</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="J54" s="5"/>
       <c r="K54" s="6"/>
@@ -5603,10 +5681,10 @@
         <v>378</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="J55" s="5"/>
       <c r="K55" s="6"/>
@@ -5625,10 +5703,10 @@
         <v>379</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="J56" s="5"/>
       <c r="K56" s="6"/>
@@ -5647,10 +5725,10 @@
         <v>380</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="J57" s="5"/>
       <c r="K57" s="6"/>
@@ -5659,10 +5737,10 @@
       <c r="F58" s="5"/>
       <c r="G58" s="6"/>
       <c r="H58" s="5" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="J58" s="6"/>
       <c r="K58" s="6"/>
@@ -5671,10 +5749,10 @@
       <c r="F59" s="5"/>
       <c r="G59" s="6"/>
       <c r="H59" s="5" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="J59" s="6"/>
       <c r="K59" s="6"/>
@@ -5859,84 +5937,84 @@
       <c r="F77" s="5"/>
       <c r="G77" s="6"/>
       <c r="H77" s="5" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="I77" s="6" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="J77" s="6"/>
       <c r="K77" s="6"/>
     </row>
     <row r="78" spans="6:11">
       <c r="H78" s="5" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="I78" s="6" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
     </row>
     <row r="79" spans="6:11">
       <c r="H79" s="5" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="I79" s="6" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
     </row>
     <row r="80" spans="6:11">
       <c r="H80" s="5" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="I80" s="6" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
     </row>
     <row r="81" spans="8:9">
       <c r="H81" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="I81" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="82" spans="8:9">
       <c r="H82" s="5" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="I82" s="6" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
     </row>
     <row r="83" spans="8:9">
       <c r="H83" s="5" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="I83" s="6" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
     </row>
     <row r="84" spans="8:9">
       <c r="H84" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="I84" s="6" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
     </row>
     <row r="85" spans="8:9">
       <c r="H85" s="5" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="I85" s="6" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
     </row>
     <row r="86" spans="8:9">
       <c r="H86" s="5" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="I86" s="6" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
     </row>
     <row r="87" spans="8:9">
@@ -5957,120 +6035,120 @@
     </row>
     <row r="91" spans="8:9">
       <c r="H91" s="5" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="I91" s="6" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
     </row>
     <row r="92" spans="8:9">
       <c r="H92" s="5" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="I92" s="6" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
     </row>
     <row r="93" spans="8:9">
       <c r="H93" s="5" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="I93" s="6" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
     </row>
     <row r="94" spans="8:9">
       <c r="H94" s="5" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="I94" s="6" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
     </row>
     <row r="95" spans="8:9">
       <c r="H95" s="5" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="I95" s="6" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
     </row>
     <row r="96" spans="8:9">
       <c r="H96" s="5" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="I96" s="6" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
     </row>
     <row r="97" spans="8:9">
       <c r="H97" s="5" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="I97" s="6" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
     </row>
     <row r="98" spans="8:9">
       <c r="H98" s="5" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="I98" s="6" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
     </row>
     <row r="99" spans="8:9">
       <c r="H99" s="5" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="I99" s="6" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
     </row>
     <row r="100" spans="8:9">
       <c r="H100" s="5" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="I100" s="6" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
     </row>
     <row r="101" spans="8:9">
       <c r="H101" s="5" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="I101" s="6" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
     </row>
     <row r="102" spans="8:9">
       <c r="H102" s="5" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="I102" s="6" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
     </row>
     <row r="103" spans="8:9">
       <c r="H103" s="5" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="I103" s="6" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
     </row>
     <row r="104" spans="8:9">
       <c r="H104" s="5" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="I104" s="6" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
     </row>
     <row r="105" spans="8:9">
       <c r="H105" s="5"/>
       <c r="I105" s="6" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
     </row>
   </sheetData>
@@ -6131,105 +6209,105 @@
       <c r="X2" s="12"/>
     </row>
     <row r="3" spans="3:24" s="3" customFormat="1">
-      <c r="C3" s="33" t="s">
+      <c r="C3" s="78" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33" t="s">
+      <c r="D3" s="78"/>
+      <c r="E3" s="78" t="s">
         <v>65</v>
       </c>
-      <c r="F3" s="33"/>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
-      <c r="K3" s="33" t="s">
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="K3" s="78" t="s">
         <v>40</v>
       </c>
-      <c r="L3" s="33"/>
-      <c r="M3" s="33" t="s">
+      <c r="L3" s="78"/>
+      <c r="M3" s="78" t="s">
         <v>66</v>
       </c>
-      <c r="N3" s="33"/>
-      <c r="O3" s="33"/>
-      <c r="P3" s="33"/>
-      <c r="S3" s="33" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="S3" s="78" t="s">
         <v>40</v>
       </c>
-      <c r="T3" s="33"/>
-      <c r="U3" s="33" t="s">
+      <c r="T3" s="78"/>
+      <c r="U3" s="78" t="s">
         <v>209</v>
       </c>
-      <c r="V3" s="33"/>
-      <c r="W3" s="33"/>
-      <c r="X3" s="33"/>
+      <c r="V3" s="78"/>
+      <c r="W3" s="78"/>
+      <c r="X3" s="78"/>
     </row>
     <row r="4" spans="3:24" s="3" customFormat="1">
-      <c r="C4" s="33" t="s">
+      <c r="C4" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
-      <c r="K4" s="33" t="s">
+      <c r="K4" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="L4" s="33"/>
-      <c r="M4" s="33"/>
-      <c r="N4" s="33"/>
-      <c r="O4" s="33"/>
-      <c r="P4" s="33"/>
-      <c r="S4" s="33" t="s">
+      <c r="L4" s="78"/>
+      <c r="M4" s="78"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="S4" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="T4" s="33"/>
-      <c r="U4" s="33"/>
-      <c r="V4" s="33"/>
-      <c r="W4" s="33"/>
-      <c r="X4" s="33"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="W4" s="78"/>
+      <c r="X4" s="78"/>
     </row>
     <row r="5" spans="3:24" s="2" customFormat="1">
-      <c r="C5" s="33" t="s">
+      <c r="C5" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="33"/>
+      <c r="D5" s="78"/>
       <c r="E5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="33" t="s">
+      <c r="F5" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="33"/>
+      <c r="G5" s="78"/>
       <c r="H5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K5" s="33" t="s">
+      <c r="K5" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="L5" s="33"/>
+      <c r="L5" s="78"/>
       <c r="M5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="N5" s="33" t="s">
+      <c r="N5" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="O5" s="33"/>
+      <c r="O5" s="78"/>
       <c r="P5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="S5" s="33" t="s">
+      <c r="S5" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="T5" s="33"/>
+      <c r="T5" s="78"/>
       <c r="U5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="V5" s="33" t="s">
+      <c r="V5" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="W5" s="33"/>
+      <c r="W5" s="78"/>
       <c r="X5" s="4" t="s">
         <v>10</v>
       </c>
@@ -6869,77 +6947,77 @@
       <c r="B23" s="1"/>
       <c r="E23" s="1"/>
       <c r="H23" s="1"/>
-      <c r="K23" s="33" t="s">
+      <c r="K23" s="78" t="s">
         <v>40</v>
       </c>
-      <c r="L23" s="33"/>
-      <c r="M23" s="33" t="s">
+      <c r="L23" s="78"/>
+      <c r="M23" s="78" t="s">
         <v>210</v>
       </c>
-      <c r="N23" s="33"/>
-      <c r="O23" s="33"/>
-      <c r="P23" s="33"/>
-      <c r="S23" s="33" t="s">
+      <c r="N23" s="78"/>
+      <c r="O23" s="78"/>
+      <c r="P23" s="78"/>
+      <c r="S23" s="78" t="s">
         <v>40</v>
       </c>
-      <c r="T23" s="33"/>
-      <c r="U23" s="33" t="s">
+      <c r="T23" s="78"/>
+      <c r="U23" s="78" t="s">
         <v>211</v>
       </c>
-      <c r="V23" s="33"/>
-      <c r="W23" s="33"/>
-      <c r="X23" s="33"/>
+      <c r="V23" s="78"/>
+      <c r="W23" s="78"/>
+      <c r="X23" s="78"/>
     </row>
     <row r="24" spans="2:24">
       <c r="B24" s="1"/>
       <c r="E24" s="1"/>
       <c r="H24" s="1"/>
-      <c r="K24" s="33" t="s">
+      <c r="K24" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="L24" s="33"/>
-      <c r="M24" s="33"/>
-      <c r="N24" s="33"/>
-      <c r="O24" s="33"/>
-      <c r="P24" s="33"/>
-      <c r="S24" s="33" t="s">
+      <c r="L24" s="78"/>
+      <c r="M24" s="78"/>
+      <c r="N24" s="78"/>
+      <c r="O24" s="78"/>
+      <c r="P24" s="78"/>
+      <c r="S24" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="T24" s="33"/>
-      <c r="U24" s="33"/>
-      <c r="V24" s="33"/>
-      <c r="W24" s="33"/>
-      <c r="X24" s="33"/>
+      <c r="T24" s="78"/>
+      <c r="U24" s="78"/>
+      <c r="V24" s="78"/>
+      <c r="W24" s="78"/>
+      <c r="X24" s="78"/>
     </row>
     <row r="25" spans="2:24">
       <c r="B25" s="1"/>
       <c r="E25" s="1"/>
       <c r="H25" s="1"/>
-      <c r="K25" s="33" t="s">
+      <c r="K25" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="L25" s="33"/>
+      <c r="L25" s="78"/>
       <c r="M25" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="N25" s="33" t="s">
+      <c r="N25" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="O25" s="33"/>
+      <c r="O25" s="78"/>
       <c r="P25" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="S25" s="33" t="s">
+      <c r="S25" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="T25" s="33"/>
+      <c r="T25" s="78"/>
       <c r="U25" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="V25" s="33" t="s">
+      <c r="V25" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="W25" s="33"/>
+      <c r="W25" s="78"/>
       <c r="X25" s="4" t="s">
         <v>10</v>
       </c>
@@ -7399,114 +7477,114 @@
     </row>
     <row r="42" spans="2:24">
       <c r="B42" s="8"/>
-      <c r="C42" s="33" t="s">
+      <c r="C42" s="78" t="s">
         <v>40</v>
       </c>
-      <c r="D42" s="33"/>
-      <c r="E42" s="33" t="s">
+      <c r="D42" s="78"/>
+      <c r="E42" s="78" t="s">
         <v>212</v>
       </c>
-      <c r="F42" s="33"/>
-      <c r="G42" s="33"/>
-      <c r="H42" s="33"/>
+      <c r="F42" s="78"/>
+      <c r="G42" s="78"/>
+      <c r="H42" s="78"/>
       <c r="I42" s="7"/>
       <c r="J42" s="7"/>
       <c r="K42" s="4" t="s">
         <v>40</v>
       </c>
       <c r="L42" s="4"/>
-      <c r="M42" s="33" t="s">
+      <c r="M42" s="78" t="s">
         <v>213</v>
       </c>
-      <c r="N42" s="33"/>
-      <c r="O42" s="33"/>
-      <c r="P42" s="33"/>
+      <c r="N42" s="78"/>
+      <c r="O42" s="78"/>
+      <c r="P42" s="78"/>
       <c r="Q42" s="8"/>
       <c r="S42" s="4" t="s">
         <v>40</v>
       </c>
       <c r="T42" s="4"/>
-      <c r="U42" s="33" t="s">
+      <c r="U42" s="78" t="s">
         <v>214</v>
       </c>
-      <c r="V42" s="33"/>
-      <c r="W42" s="33"/>
-      <c r="X42" s="33"/>
+      <c r="V42" s="78"/>
+      <c r="W42" s="78"/>
+      <c r="X42" s="78"/>
     </row>
     <row r="43" spans="2:24">
       <c r="B43" s="8"/>
-      <c r="C43" s="33" t="s">
+      <c r="C43" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="D43" s="33"/>
-      <c r="E43" s="33"/>
-      <c r="F43" s="33"/>
-      <c r="G43" s="33"/>
-      <c r="H43" s="33"/>
+      <c r="D43" s="78"/>
+      <c r="E43" s="78"/>
+      <c r="F43" s="78"/>
+      <c r="G43" s="78"/>
+      <c r="H43" s="78"/>
       <c r="I43" s="7"/>
       <c r="J43" s="7"/>
       <c r="K43" s="4" t="s">
         <v>39</v>
       </c>
       <c r="L43" s="4"/>
-      <c r="M43" s="33"/>
-      <c r="N43" s="33"/>
-      <c r="O43" s="33"/>
-      <c r="P43" s="33"/>
+      <c r="M43" s="78"/>
+      <c r="N43" s="78"/>
+      <c r="O43" s="78"/>
+      <c r="P43" s="78"/>
       <c r="Q43" s="8"/>
       <c r="S43" s="4" t="s">
         <v>39</v>
       </c>
       <c r="T43" s="4"/>
-      <c r="U43" s="33"/>
-      <c r="V43" s="33"/>
-      <c r="W43" s="33"/>
-      <c r="X43" s="33"/>
+      <c r="U43" s="78"/>
+      <c r="V43" s="78"/>
+      <c r="W43" s="78"/>
+      <c r="X43" s="78"/>
     </row>
     <row r="44" spans="2:24">
       <c r="B44" s="8"/>
-      <c r="C44" s="33" t="s">
+      <c r="C44" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="D44" s="33"/>
+      <c r="D44" s="78"/>
       <c r="E44" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F44" s="33" t="s">
+      <c r="F44" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="G44" s="33"/>
+      <c r="G44" s="78"/>
       <c r="H44" s="4" t="s">
         <v>10</v>
       </c>
       <c r="I44" s="7"/>
       <c r="J44" s="7"/>
-      <c r="K44" s="33" t="s">
+      <c r="K44" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="L44" s="33"/>
+      <c r="L44" s="78"/>
       <c r="M44" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="N44" s="33" t="s">
+      <c r="N44" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="O44" s="33"/>
+      <c r="O44" s="78"/>
       <c r="P44" s="4" t="s">
         <v>10</v>
       </c>
       <c r="Q44" s="8"/>
-      <c r="S44" s="33" t="s">
+      <c r="S44" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="T44" s="33"/>
+      <c r="T44" s="78"/>
       <c r="U44" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="V44" s="33" t="s">
+      <c r="V44" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="W44" s="33"/>
+      <c r="W44" s="78"/>
       <c r="X44" s="4" t="s">
         <v>10</v>
       </c>
@@ -7939,7 +8017,7 @@
         <v>620</v>
       </c>
       <c r="U52" s="10" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="V52" s="9" t="s">
         <v>327</v>
@@ -7999,7 +8077,7 @@
         <v>621</v>
       </c>
       <c r="U53" s="10" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="V53" s="9" t="s">
         <v>259</v>
@@ -8224,29 +8302,29 @@
       </c>
     </row>
     <row r="3" spans="2:21">
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="79" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="35"/>
-      <c r="D3" s="34" t="s">
-        <v>782</v>
-      </c>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="35"/>
-      <c r="I3" s="34" t="s">
+      <c r="C3" s="80"/>
+      <c r="D3" s="79" t="s">
+        <v>779</v>
+      </c>
+      <c r="E3" s="81"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="80"/>
+      <c r="I3" s="79" t="s">
         <v>40</v>
       </c>
-      <c r="J3" s="35"/>
-      <c r="K3" s="33" t="s">
+      <c r="J3" s="80"/>
+      <c r="K3" s="78" t="s">
         <v>302</v>
       </c>
-      <c r="L3" s="33"/>
-      <c r="M3" s="33"/>
-      <c r="N3" s="33"/>
-      <c r="O3" s="33"/>
-      <c r="P3" s="33"/>
-      <c r="Q3" s="33"/>
+      <c r="L3" s="78"/>
+      <c r="M3" s="78"/>
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
       <c r="S3" s="5">
         <v>0</v>
       </c>
@@ -8256,25 +8334,25 @@
       <c r="U3" s="6"/>
     </row>
     <row r="4" spans="2:21">
-      <c r="B4" s="34" t="s">
+      <c r="B4" s="79" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="35"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="35"/>
-      <c r="I4" s="34" t="s">
+      <c r="C4" s="80"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="81"/>
+      <c r="F4" s="81"/>
+      <c r="G4" s="80"/>
+      <c r="I4" s="79" t="s">
         <v>39</v>
       </c>
-      <c r="J4" s="35"/>
-      <c r="K4" s="33"/>
-      <c r="L4" s="33"/>
-      <c r="M4" s="33"/>
-      <c r="N4" s="33"/>
-      <c r="O4" s="33"/>
-      <c r="P4" s="33"/>
-      <c r="Q4" s="33"/>
+      <c r="J4" s="80"/>
+      <c r="K4" s="78"/>
+      <c r="L4" s="78"/>
+      <c r="M4" s="78"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
       <c r="S4" s="5">
         <v>100</v>
       </c>
@@ -8286,38 +8364,38 @@
       </c>
     </row>
     <row r="5" spans="2:21">
-      <c r="B5" s="34" t="s">
+      <c r="B5" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="35"/>
+      <c r="C5" s="80"/>
       <c r="D5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="34" t="s">
+      <c r="E5" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="35"/>
+      <c r="F5" s="80"/>
       <c r="G5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="I5" s="34" t="s">
+      <c r="I5" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="35"/>
+      <c r="J5" s="80"/>
       <c r="K5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L5" s="34" t="s">
+      <c r="L5" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="M5" s="35"/>
+      <c r="M5" s="80"/>
       <c r="N5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="O5" s="34" t="s">
+      <c r="O5" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="P5" s="35"/>
+      <c r="P5" s="80"/>
       <c r="Q5" s="4" t="s">
         <v>10</v>
       </c>
@@ -8850,16 +8928,16 @@
       </c>
     </row>
     <row r="20" spans="2:21">
-      <c r="B20" s="33" t="s">
+      <c r="B20" s="78" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="33"/>
-      <c r="D20" s="33" t="s">
-        <v>781</v>
-      </c>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="33"/>
+      <c r="C20" s="78"/>
+      <c r="D20" s="78" t="s">
+        <v>778</v>
+      </c>
+      <c r="E20" s="78"/>
+      <c r="F20" s="78"/>
+      <c r="G20" s="78"/>
       <c r="I20" s="5"/>
       <c r="J20" s="5"/>
       <c r="K20" s="6"/>
@@ -8880,14 +8958,14 @@
       </c>
     </row>
     <row r="21" spans="2:21">
-      <c r="B21" s="33" t="s">
+      <c r="B21" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="33"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33"/>
-      <c r="G21" s="33"/>
+      <c r="C21" s="78"/>
+      <c r="D21" s="78"/>
+      <c r="E21" s="78"/>
+      <c r="F21" s="78"/>
+      <c r="G21" s="78"/>
       <c r="I21" s="5"/>
       <c r="J21" s="5"/>
       <c r="K21" s="6"/>
@@ -8908,17 +8986,17 @@
       </c>
     </row>
     <row r="22" spans="2:21">
-      <c r="B22" s="33" t="s">
+      <c r="B22" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="33"/>
+      <c r="C22" s="78"/>
       <c r="D22" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E22" s="33" t="s">
+      <c r="E22" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="F22" s="33"/>
+      <c r="F22" s="78"/>
       <c r="G22" s="4" t="s">
         <v>10</v>
       </c>
@@ -9112,19 +9190,19 @@
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
       <c r="G28" s="10"/>
-      <c r="I28" s="34" t="s">
+      <c r="I28" s="79" t="s">
         <v>40</v>
       </c>
-      <c r="J28" s="35"/>
-      <c r="K28" s="33" t="s">
+      <c r="J28" s="80"/>
+      <c r="K28" s="78" t="s">
         <v>302</v>
       </c>
-      <c r="L28" s="33"/>
-      <c r="M28" s="33"/>
-      <c r="N28" s="33"/>
-      <c r="O28" s="33"/>
-      <c r="P28" s="33"/>
-      <c r="Q28" s="33"/>
+      <c r="L28" s="78"/>
+      <c r="M28" s="78"/>
+      <c r="N28" s="78"/>
+      <c r="O28" s="78"/>
+      <c r="P28" s="78"/>
+      <c r="Q28" s="78"/>
       <c r="S28" s="5">
         <v>1400</v>
       </c>
@@ -9146,22 +9224,22 @@
         <v>645</v>
       </c>
       <c r="G29" s="10"/>
-      <c r="I29" s="34" t="s">
+      <c r="I29" s="79" t="s">
         <v>39</v>
       </c>
-      <c r="J29" s="35"/>
-      <c r="K29" s="33"/>
-      <c r="L29" s="33"/>
-      <c r="M29" s="33"/>
-      <c r="N29" s="33"/>
-      <c r="O29" s="33"/>
-      <c r="P29" s="33"/>
-      <c r="Q29" s="33"/>
+      <c r="J29" s="80"/>
+      <c r="K29" s="78"/>
+      <c r="L29" s="78"/>
+      <c r="M29" s="78"/>
+      <c r="N29" s="78"/>
+      <c r="O29" s="78"/>
+      <c r="P29" s="78"/>
+      <c r="Q29" s="78"/>
       <c r="S29" s="5">
         <v>1500</v>
       </c>
       <c r="T29" s="6" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="U29" s="6"/>
     </row>
@@ -9178,24 +9256,24 @@
       <c r="G30" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I30" s="34" t="s">
+      <c r="I30" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="J30" s="35"/>
+      <c r="J30" s="80"/>
       <c r="K30" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L30" s="34" t="s">
+      <c r="L30" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="M30" s="35"/>
+      <c r="M30" s="80"/>
       <c r="N30" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="O30" s="34" t="s">
+      <c r="O30" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="P30" s="35"/>
+      <c r="P30" s="80"/>
       <c r="Q30" s="4" t="s">
         <v>10</v>
       </c>
@@ -9244,20 +9322,20 @@
       <c r="G32" s="10"/>
       <c r="I32" s="5"/>
       <c r="J32" s="5" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="K32" s="6" t="s">
         <v>7</v>
       </c>
       <c r="L32" s="5"/>
       <c r="M32" s="5" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="N32" s="6" t="s">
         <v>20</v>
       </c>
       <c r="O32" s="16" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="P32" s="16"/>
       <c r="Q32" s="6" t="s">
@@ -9279,14 +9357,14 @@
       <c r="G33" s="10"/>
       <c r="I33" s="9"/>
       <c r="J33" s="9" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="K33" s="10" t="s">
         <v>317</v>
       </c>
       <c r="L33" s="9"/>
       <c r="M33" s="9" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="N33" s="10" t="s">
         <v>13</v>
@@ -9304,14 +9382,14 @@
       <c r="G34" s="12"/>
       <c r="I34" s="9"/>
       <c r="J34" s="9" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="K34" s="10" t="s">
         <v>318</v>
       </c>
       <c r="L34" s="9"/>
       <c r="M34" s="9" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="N34" s="10" t="s">
         <v>14</v>
@@ -9323,14 +9401,14 @@
     <row r="35" spans="2:17">
       <c r="I35" s="9"/>
       <c r="J35" s="9" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="K35" s="10" t="s">
         <v>17</v>
       </c>
       <c r="L35" s="9"/>
       <c r="M35" s="9" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="N35" s="10" t="s">
         <v>316</v>
@@ -9342,14 +9420,14 @@
     <row r="36" spans="2:17">
       <c r="I36" s="9"/>
       <c r="J36" s="9" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="K36" s="10" t="s">
         <v>18</v>
       </c>
       <c r="L36" s="9"/>
       <c r="M36" s="9" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="N36" s="10" t="s">
         <v>15</v>
@@ -9361,7 +9439,7 @@
     <row r="37" spans="2:17">
       <c r="I37" s="5"/>
       <c r="J37" s="5" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="K37" s="6"/>
       <c r="L37" s="5"/>
@@ -9374,7 +9452,7 @@
     <row r="38" spans="2:17">
       <c r="I38" s="5"/>
       <c r="J38" s="5" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>19</v>
@@ -9389,7 +9467,7 @@
     <row r="39" spans="2:17">
       <c r="I39" s="5"/>
       <c r="J39" s="5" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="K39" s="6" t="s">
         <v>385</v>
@@ -9550,64 +9628,77 @@
   <dimension ref="D3:X47"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
+    <col min="14" max="14" width="9.75" customWidth="1"/>
     <col min="15" max="15" width="12.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="4:20">
+      <c r="E3" t="s">
+        <v>877</v>
+      </c>
+      <c r="F3" t="s">
+        <v>880</v>
+      </c>
       <c r="N3" t="s">
+        <v>869</v>
+      </c>
+      <c r="O3" s="33" t="s">
+        <v>883</v>
+      </c>
+      <c r="P3" t="s">
+        <v>871</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="4" spans="4:20">
+      <c r="E4" t="s">
+        <v>878</v>
+      </c>
+      <c r="F4" t="s">
+        <v>882</v>
+      </c>
+      <c r="N4" t="s">
+        <v>870</v>
+      </c>
+      <c r="O4" s="33" t="s">
+        <v>886</v>
+      </c>
+      <c r="P4" t="s">
         <v>872</v>
       </c>
-      <c r="O3" s="81" t="s">
-        <v>878</v>
-      </c>
-      <c r="P3" t="s">
-        <v>874</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>881</v>
-      </c>
-    </row>
-    <row r="4" spans="4:20">
-      <c r="N4" t="s">
-        <v>873</v>
-      </c>
-      <c r="O4" s="81" t="s">
+      <c r="Q4" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="6" spans="4:20" ht="17.25" thickBot="1">
+      <c r="D6" s="68" t="s">
+        <v>357</v>
+      </c>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
+      <c r="I6" s="68" t="s">
+        <v>718</v>
+      </c>
+      <c r="J6" s="68"/>
+      <c r="K6" s="68"/>
+      <c r="M6" s="68" t="s">
+        <v>359</v>
+      </c>
+      <c r="N6" s="68"/>
+      <c r="O6" s="68"/>
+      <c r="P6" s="68"/>
+      <c r="R6" s="68" t="s">
+        <v>719</v>
+      </c>
+      <c r="S6" s="68"/>
+      <c r="T6" s="68"/>
+    </row>
+    <row r="7" spans="4:20" ht="16.5" customHeight="1">
+      <c r="D7" s="34" t="s">
         <v>879</v>
-      </c>
-      <c r="P4" t="s">
-        <v>875</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>880</v>
-      </c>
-    </row>
-    <row r="6" spans="4:20" ht="17.25" thickBot="1">
-      <c r="D6" s="69" t="s">
-        <v>357</v>
-      </c>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
-      <c r="I6" s="69" t="s">
-        <v>721</v>
-      </c>
-      <c r="J6" s="69"/>
-      <c r="K6" s="69"/>
-      <c r="M6" s="69" t="s">
-        <v>359</v>
-      </c>
-      <c r="N6" s="69"/>
-      <c r="O6" s="69"/>
-      <c r="P6" s="69"/>
-      <c r="R6" s="69" t="s">
-        <v>722</v>
-      </c>
-      <c r="S6" s="69"/>
-      <c r="T6" s="69"/>
-    </row>
-    <row r="7" spans="4:20" ht="16.5" customHeight="1">
-      <c r="D7" s="37" t="s">
-        <v>719</v>
       </c>
       <c r="E7" s="21"/>
       <c r="F7" s="21"/>
@@ -9615,206 +9706,212 @@
       <c r="I7" s="26"/>
       <c r="J7" s="21"/>
       <c r="K7" s="22"/>
-      <c r="M7" s="37" t="s">
-        <v>876</v>
+      <c r="M7" s="34" t="s">
+        <v>889</v>
       </c>
       <c r="N7" s="21"/>
       <c r="O7" s="21"/>
-      <c r="P7" s="22"/>
+      <c r="P7" s="34" t="s">
+        <v>884</v>
+      </c>
       <c r="R7" s="26"/>
       <c r="S7" s="21"/>
       <c r="T7" s="22"/>
     </row>
     <row r="8" spans="4:20">
-      <c r="D8" s="38"/>
+      <c r="D8" s="35"/>
       <c r="G8" s="23"/>
       <c r="I8" s="24"/>
       <c r="K8" s="23"/>
-      <c r="M8" s="38"/>
-      <c r="P8" s="23"/>
+      <c r="M8" s="35"/>
+      <c r="P8" s="35"/>
       <c r="R8" s="24"/>
       <c r="T8" s="23"/>
     </row>
     <row r="9" spans="4:20" ht="16.5" customHeight="1">
-      <c r="D9" s="38"/>
-      <c r="F9" s="49" t="s">
+      <c r="D9" s="35"/>
+      <c r="F9" s="46" t="s">
         <v>717</v>
       </c>
       <c r="G9" s="23"/>
       <c r="I9" s="24"/>
-      <c r="J9" s="49" t="s">
+      <c r="J9" s="46" t="s">
         <v>717</v>
       </c>
       <c r="K9" s="23"/>
-      <c r="M9" s="38"/>
-      <c r="O9" s="49" t="s">
+      <c r="M9" s="35"/>
+      <c r="O9" s="84" t="s">
         <v>717</v>
       </c>
-      <c r="P9" s="23"/>
+      <c r="P9" s="35"/>
       <c r="R9" s="24"/>
-      <c r="S9" s="49" t="s">
+      <c r="S9" s="46" t="s">
         <v>717</v>
       </c>
       <c r="T9" s="23"/>
     </row>
     <row r="10" spans="4:20">
-      <c r="D10" s="38"/>
-      <c r="F10" s="50"/>
+      <c r="D10" s="35"/>
+      <c r="F10" s="47"/>
       <c r="G10" s="23"/>
       <c r="I10" s="24"/>
-      <c r="J10" s="50"/>
+      <c r="J10" s="47"/>
       <c r="K10" s="23"/>
-      <c r="M10" s="38"/>
-      <c r="O10" s="50"/>
-      <c r="P10" s="23"/>
+      <c r="M10" s="35"/>
+      <c r="O10" s="85"/>
+      <c r="P10" s="35"/>
       <c r="R10" s="24"/>
-      <c r="S10" s="50"/>
+      <c r="S10" s="47"/>
       <c r="T10" s="23"/>
     </row>
-    <row r="11" spans="4:20" ht="16.5" customHeight="1">
-      <c r="D11" s="38"/>
-      <c r="E11" s="51" t="s">
-        <v>716</v>
+    <row r="11" spans="4:20">
+      <c r="D11" s="35"/>
+      <c r="E11" s="48" t="s">
+        <v>868</v>
       </c>
       <c r="G11" s="23"/>
       <c r="I11" s="24"/>
-      <c r="J11" s="51" t="s">
+      <c r="J11" s="48" t="s">
+        <v>876</v>
+      </c>
+      <c r="K11" s="23"/>
+      <c r="M11" s="35"/>
+      <c r="N11" s="48" t="s">
+        <v>885</v>
+      </c>
+      <c r="O11" s="82" t="s">
         <v>716</v>
       </c>
-      <c r="K11" s="23"/>
-      <c r="M11" s="38"/>
-      <c r="N11" s="51" t="s">
-        <v>871</v>
-      </c>
-      <c r="P11" s="23"/>
+      <c r="P11" s="35"/>
       <c r="R11" s="24"/>
-      <c r="S11" s="51" t="s">
-        <v>716</v>
+      <c r="S11" s="48" t="s">
+        <v>876</v>
       </c>
       <c r="T11" s="23"/>
     </row>
     <row r="12" spans="4:20">
-      <c r="D12" s="38"/>
-      <c r="E12" s="52"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="49"/>
       <c r="G12" s="23"/>
       <c r="I12" s="24"/>
-      <c r="J12" s="62"/>
+      <c r="J12" s="59"/>
       <c r="K12" s="23"/>
-      <c r="M12" s="38"/>
-      <c r="N12" s="52"/>
-      <c r="P12" s="23"/>
+      <c r="M12" s="35"/>
+      <c r="N12" s="49"/>
+      <c r="O12" s="83"/>
+      <c r="P12" s="35"/>
       <c r="R12" s="24"/>
-      <c r="S12" s="62"/>
+      <c r="S12" s="59"/>
       <c r="T12" s="23"/>
     </row>
     <row r="13" spans="4:20">
-      <c r="D13" s="39"/>
+      <c r="D13" s="36"/>
       <c r="G13" s="23"/>
       <c r="I13" s="24"/>
       <c r="K13" s="23"/>
-      <c r="M13" s="39"/>
-      <c r="P13" s="23"/>
+      <c r="M13" s="36"/>
+      <c r="P13" s="36"/>
       <c r="R13" s="24"/>
       <c r="T13" s="23"/>
     </row>
     <row r="14" spans="4:20" ht="16.5" customHeight="1">
       <c r="D14" s="24"/>
-      <c r="E14" s="40" t="s">
-        <v>718</v>
-      </c>
-      <c r="F14" s="41"/>
-      <c r="G14" s="42"/>
-      <c r="I14" s="53" t="s">
-        <v>724</v>
-      </c>
-      <c r="J14" s="54"/>
-      <c r="K14" s="55"/>
+      <c r="E14" s="37" t="s">
+        <v>881</v>
+      </c>
+      <c r="F14" s="38"/>
+      <c r="G14" s="39"/>
+      <c r="I14" s="50" t="s">
+        <v>892</v>
+      </c>
+      <c r="J14" s="51"/>
+      <c r="K14" s="52"/>
       <c r="M14" s="24"/>
-      <c r="N14" s="40" t="s">
-        <v>877</v>
-      </c>
-      <c r="O14" s="41"/>
-      <c r="P14" s="42"/>
-      <c r="R14" s="53" t="s">
-        <v>724</v>
-      </c>
-      <c r="S14" s="54"/>
-      <c r="T14" s="55"/>
+      <c r="N14" s="37" t="s">
+        <v>887</v>
+      </c>
+      <c r="O14" s="38"/>
+      <c r="P14" s="39"/>
+      <c r="R14" s="50" t="s">
+        <v>891</v>
+      </c>
+      <c r="S14" s="51"/>
+      <c r="T14" s="52"/>
     </row>
     <row r="15" spans="4:20">
       <c r="D15" s="24"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="45"/>
-      <c r="I15" s="56"/>
-      <c r="J15" s="57"/>
-      <c r="K15" s="58"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="42"/>
+      <c r="I15" s="53"/>
+      <c r="J15" s="54"/>
+      <c r="K15" s="55"/>
       <c r="M15" s="24"/>
-      <c r="N15" s="43"/>
-      <c r="O15" s="44"/>
-      <c r="P15" s="45"/>
-      <c r="R15" s="56"/>
-      <c r="S15" s="57"/>
-      <c r="T15" s="58"/>
+      <c r="N15" s="40"/>
+      <c r="O15" s="41"/>
+      <c r="P15" s="42"/>
+      <c r="R15" s="53"/>
+      <c r="S15" s="54"/>
+      <c r="T15" s="55"/>
     </row>
     <row r="16" spans="4:20">
       <c r="D16" s="24"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="45"/>
-      <c r="I16" s="56"/>
-      <c r="J16" s="57"/>
-      <c r="K16" s="58"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="42"/>
+      <c r="I16" s="53"/>
+      <c r="J16" s="54"/>
+      <c r="K16" s="55"/>
       <c r="M16" s="24"/>
-      <c r="N16" s="43"/>
-      <c r="O16" s="44"/>
-      <c r="P16" s="45"/>
-      <c r="R16" s="56"/>
-      <c r="S16" s="57"/>
-      <c r="T16" s="58"/>
+      <c r="N16" s="40"/>
+      <c r="O16" s="41"/>
+      <c r="P16" s="42"/>
+      <c r="R16" s="53"/>
+      <c r="S16" s="54"/>
+      <c r="T16" s="55"/>
     </row>
     <row r="17" spans="4:20" ht="17.25" thickBot="1">
       <c r="D17" s="25"/>
-      <c r="E17" s="46"/>
-      <c r="F17" s="47"/>
-      <c r="G17" s="48"/>
-      <c r="I17" s="59"/>
-      <c r="J17" s="60"/>
-      <c r="K17" s="61"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="45"/>
+      <c r="I17" s="56"/>
+      <c r="J17" s="57"/>
+      <c r="K17" s="58"/>
       <c r="M17" s="25"/>
-      <c r="N17" s="46"/>
-      <c r="O17" s="47"/>
-      <c r="P17" s="48"/>
-      <c r="R17" s="59"/>
-      <c r="S17" s="60"/>
-      <c r="T17" s="61"/>
+      <c r="N17" s="43"/>
+      <c r="O17" s="44"/>
+      <c r="P17" s="45"/>
+      <c r="R17" s="56"/>
+      <c r="S17" s="57"/>
+      <c r="T17" s="58"/>
     </row>
     <row r="19" spans="4:20" ht="17.25" thickBot="1">
-      <c r="D19" s="69" t="s">
+      <c r="D19" s="68" t="s">
         <v>368</v>
       </c>
-      <c r="E19" s="69"/>
-      <c r="F19" s="69"/>
-      <c r="H19" s="69" t="s">
+      <c r="E19" s="68"/>
+      <c r="F19" s="68"/>
+      <c r="H19" s="68" t="s">
         <v>367</v>
       </c>
-      <c r="I19" s="69"/>
-      <c r="J19" s="69"/>
-      <c r="K19" s="69"/>
-      <c r="R19" s="69" t="s">
-        <v>723</v>
-      </c>
-      <c r="S19" s="69"/>
-      <c r="T19" s="69"/>
+      <c r="I19" s="68"/>
+      <c r="J19" s="68"/>
+      <c r="K19" s="68"/>
+      <c r="R19" s="68" t="s">
+        <v>720</v>
+      </c>
+      <c r="S19" s="68"/>
+      <c r="T19" s="68"/>
     </row>
     <row r="20" spans="4:20">
-      <c r="D20" s="77" t="s">
-        <v>720</v>
-      </c>
-      <c r="E20" s="78"/>
-      <c r="F20" s="79"/>
+      <c r="D20" s="74" t="s">
+        <v>898</v>
+      </c>
+      <c r="E20" s="75"/>
+      <c r="F20" s="76"/>
       <c r="H20" s="26"/>
-      <c r="I20" s="68" t="s">
+      <c r="I20" s="65" t="s">
         <v>717</v>
       </c>
       <c r="J20" s="21"/>
@@ -9823,56 +9920,56 @@
       <c r="N20" s="21"/>
       <c r="O20" s="21"/>
       <c r="P20" s="22"/>
-      <c r="R20" s="77" t="s">
-        <v>724</v>
-      </c>
-      <c r="S20" s="78"/>
-      <c r="T20" s="79"/>
+      <c r="R20" s="74" t="s">
+        <v>721</v>
+      </c>
+      <c r="S20" s="75"/>
+      <c r="T20" s="76"/>
     </row>
     <row r="21" spans="4:20">
-      <c r="D21" s="56"/>
-      <c r="E21" s="57"/>
-      <c r="F21" s="58"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="55"/>
       <c r="H21" s="24"/>
-      <c r="I21" s="50"/>
+      <c r="I21" s="47"/>
       <c r="K21" s="23"/>
       <c r="M21" s="24"/>
       <c r="P21" s="23"/>
-      <c r="R21" s="56"/>
-      <c r="S21" s="57"/>
-      <c r="T21" s="58"/>
+      <c r="R21" s="53"/>
+      <c r="S21" s="54"/>
+      <c r="T21" s="55"/>
     </row>
     <row r="22" spans="4:20">
-      <c r="D22" s="56"/>
-      <c r="E22" s="57"/>
-      <c r="F22" s="58"/>
-      <c r="H22" s="74" t="s">
-        <v>725</v>
-      </c>
-      <c r="I22" s="51" t="s">
+      <c r="D22" s="53"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="55"/>
+      <c r="H22" s="66" t="s">
+        <v>722</v>
+      </c>
+      <c r="I22" s="48" t="s">
         <v>716</v>
       </c>
-      <c r="J22" s="74"/>
+      <c r="J22" s="66"/>
       <c r="K22" s="23"/>
       <c r="M22" s="24"/>
       <c r="P22" s="23"/>
-      <c r="R22" s="56"/>
-      <c r="S22" s="57"/>
-      <c r="T22" s="58"/>
+      <c r="R22" s="53"/>
+      <c r="S22" s="54"/>
+      <c r="T22" s="55"/>
     </row>
     <row r="23" spans="4:20">
-      <c r="D23" s="65"/>
-      <c r="E23" s="66"/>
-      <c r="F23" s="80"/>
-      <c r="H23" s="75"/>
-      <c r="I23" s="62"/>
-      <c r="J23" s="75"/>
+      <c r="D23" s="62"/>
+      <c r="E23" s="63"/>
+      <c r="F23" s="77"/>
+      <c r="H23" s="67"/>
+      <c r="I23" s="59"/>
+      <c r="J23" s="67"/>
       <c r="K23" s="23"/>
       <c r="M23" s="24"/>
       <c r="P23" s="23"/>
-      <c r="R23" s="65"/>
-      <c r="S23" s="66"/>
-      <c r="T23" s="80"/>
+      <c r="R23" s="62"/>
+      <c r="S23" s="63"/>
+      <c r="T23" s="77"/>
     </row>
     <row r="24" spans="4:20">
       <c r="D24" s="24"/>
@@ -9888,77 +9985,77 @@
     </row>
     <row r="25" spans="4:20" ht="16.5" customHeight="1">
       <c r="D25" s="24"/>
-      <c r="E25" s="51" t="s">
-        <v>716</v>
+      <c r="E25" s="48" t="s">
+        <v>876</v>
       </c>
       <c r="F25" s="23"/>
-      <c r="H25" s="53" t="s">
-        <v>887</v>
-      </c>
-      <c r="I25" s="54"/>
-      <c r="J25" s="63"/>
+      <c r="H25" s="50" t="s">
+        <v>896</v>
+      </c>
+      <c r="I25" s="51"/>
+      <c r="J25" s="60"/>
       <c r="K25" s="23"/>
       <c r="M25" s="24"/>
       <c r="P25" s="23"/>
       <c r="R25" s="24"/>
-      <c r="S25" s="51" t="s">
+      <c r="S25" s="48" t="s">
         <v>716</v>
       </c>
       <c r="T25" s="23"/>
     </row>
     <row r="26" spans="4:20">
       <c r="D26" s="24"/>
-      <c r="E26" s="62"/>
+      <c r="E26" s="59"/>
       <c r="F26" s="23"/>
-      <c r="H26" s="56"/>
-      <c r="I26" s="57"/>
-      <c r="J26" s="64"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="54"/>
+      <c r="J26" s="61"/>
       <c r="K26" s="23"/>
       <c r="M26" s="24"/>
       <c r="P26" s="23"/>
       <c r="R26" s="24"/>
-      <c r="S26" s="62"/>
+      <c r="S26" s="59"/>
       <c r="T26" s="23"/>
     </row>
     <row r="27" spans="4:20">
       <c r="D27" s="24"/>
-      <c r="E27" s="49" t="s">
+      <c r="E27" s="46" t="s">
         <v>717</v>
       </c>
       <c r="F27" s="23"/>
-      <c r="H27" s="56"/>
-      <c r="I27" s="57"/>
-      <c r="J27" s="64"/>
-      <c r="K27" s="70" t="s">
-        <v>884</v>
+      <c r="H27" s="53"/>
+      <c r="I27" s="54"/>
+      <c r="J27" s="61"/>
+      <c r="K27" s="69" t="s">
+        <v>895</v>
       </c>
       <c r="M27" s="24"/>
       <c r="P27" s="23"/>
       <c r="R27" s="24"/>
-      <c r="S27" s="49" t="s">
+      <c r="S27" s="46" t="s">
         <v>717</v>
       </c>
       <c r="T27" s="23"/>
     </row>
     <row r="28" spans="4:20" ht="16.5" customHeight="1">
       <c r="D28" s="24"/>
-      <c r="E28" s="50"/>
+      <c r="E28" s="47"/>
       <c r="F28" s="23"/>
-      <c r="H28" s="65"/>
-      <c r="I28" s="66"/>
-      <c r="J28" s="67"/>
-      <c r="K28" s="71"/>
+      <c r="H28" s="62"/>
+      <c r="I28" s="63"/>
+      <c r="J28" s="64"/>
+      <c r="K28" s="70"/>
       <c r="M28" s="24"/>
       <c r="P28" s="23"/>
       <c r="R28" s="24"/>
-      <c r="S28" s="50"/>
+      <c r="S28" s="47"/>
       <c r="T28" s="23"/>
     </row>
     <row r="29" spans="4:20">
       <c r="D29" s="24"/>
       <c r="F29" s="23"/>
       <c r="H29" s="24"/>
-      <c r="K29" s="72"/>
+      <c r="K29" s="71"/>
       <c r="M29" s="24"/>
       <c r="P29" s="23"/>
       <c r="R29" s="24"/>
@@ -9969,10 +10066,10 @@
       <c r="E30" s="27"/>
       <c r="F30" s="28"/>
       <c r="H30" s="24"/>
-      <c r="I30" s="51" t="s">
-        <v>871</v>
-      </c>
-      <c r="K30" s="72"/>
+      <c r="I30" s="48" t="s">
+        <v>716</v>
+      </c>
+      <c r="K30" s="71"/>
       <c r="M30" s="25"/>
       <c r="N30" s="27"/>
       <c r="O30" s="27"/>
@@ -9983,53 +10080,56 @@
     </row>
     <row r="31" spans="4:20">
       <c r="H31" s="24"/>
-      <c r="I31" s="62"/>
-      <c r="K31" s="72"/>
+      <c r="I31" s="59"/>
+      <c r="K31" s="71"/>
     </row>
     <row r="32" spans="4:20">
       <c r="H32" s="24"/>
-      <c r="I32" s="49" t="s">
+      <c r="I32" s="46" t="s">
         <v>717</v>
       </c>
-      <c r="K32" s="72"/>
+      <c r="K32" s="71"/>
+      <c r="R32" t="s">
+        <v>893</v>
+      </c>
     </row>
     <row r="33" spans="8:24" ht="17.25" thickBot="1">
       <c r="H33" s="25"/>
-      <c r="I33" s="76"/>
+      <c r="I33" s="73"/>
       <c r="J33" s="27"/>
-      <c r="K33" s="73"/>
+      <c r="K33" s="72"/>
     </row>
     <row r="35" spans="8:24">
       <c r="I35" t="s">
-        <v>882</v>
+        <v>873</v>
       </c>
       <c r="J35" t="s">
-        <v>885</v>
+        <v>894</v>
       </c>
     </row>
     <row r="36" spans="8:24">
       <c r="I36" t="s">
+        <v>874</v>
+      </c>
+      <c r="J36" t="s">
         <v>883</v>
-      </c>
-      <c r="J36" t="s">
-        <v>886</v>
       </c>
     </row>
     <row r="38" spans="8:24">
       <c r="I38" t="s">
-        <v>888</v>
+        <v>875</v>
       </c>
       <c r="J38" t="s">
-        <v>889</v>
+        <v>897</v>
       </c>
     </row>
     <row r="47" spans="8:24">
       <c r="X47" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="35">
+  <mergeCells count="37">
     <mergeCell ref="R6:T6"/>
     <mergeCell ref="R19:T19"/>
     <mergeCell ref="D19:F19"/>
@@ -10059,6 +10159,8 @@
     <mergeCell ref="O9:O10"/>
     <mergeCell ref="N11:N12"/>
     <mergeCell ref="N14:P17"/>
+    <mergeCell ref="P7:P13"/>
+    <mergeCell ref="O11:O12"/>
     <mergeCell ref="D7:D13"/>
     <mergeCell ref="E14:G17"/>
     <mergeCell ref="F9:F10"/>

--- a/PLC/IO List.xlsx
+++ b/PLC/IO List.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ezen-01\Desktop\Project\PLC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EZENIC\Desktop\Project-Second\PLC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{704900FD-B174-41EE-8FCC-ADE6621AE164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{042E96CD-4AEF-4E7F-97EC-B5177B512C45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{E8A3CD3B-D612-4B37-A180-F6C335096DC9}"/>
+    <workbookView xWindow="30" yWindow="0" windowWidth="17250" windowHeight="15585" activeTab="2" xr2:uid="{E8A3CD3B-D612-4B37-A180-F6C335096DC9}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="899">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1373" uniqueCount="974">
   <si>
     <t>X10</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1133,10 +1133,6 @@
   </si>
   <si>
     <t>Y226</t>
-  </si>
-  <si>
-    <t>AGV</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>X200</t>
@@ -1750,10 +1746,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>AGV 내부 기동 신호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>M102</t>
   </si>
   <si>
@@ -3220,6 +3212,259 @@
     <t>AGV
 P[1~8]</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGV2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGV3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGV4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGV5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M1200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M1201</t>
+  </si>
+  <si>
+    <t>M1202</t>
+  </si>
+  <si>
+    <t>M1203</t>
+  </si>
+  <si>
+    <t>M1204</t>
+  </si>
+  <si>
+    <t>M1205</t>
+  </si>
+  <si>
+    <t>M1206</t>
+  </si>
+  <si>
+    <t>M1207</t>
+  </si>
+  <si>
+    <t>M2235</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M2236</t>
+  </si>
+  <si>
+    <t>M2237</t>
+  </si>
+  <si>
+    <t>M2238</t>
+  </si>
+  <si>
+    <t>M2239</t>
+  </si>
+  <si>
+    <t>M1210</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M1211</t>
+  </si>
+  <si>
+    <t>M1212</t>
+  </si>
+  <si>
+    <t>M1213</t>
+  </si>
+  <si>
+    <t>M1214</t>
+  </si>
+  <si>
+    <t>M1215</t>
+  </si>
+  <si>
+    <t>M1216</t>
+  </si>
+  <si>
+    <t>M1217</t>
+  </si>
+  <si>
+    <t>D10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도착위치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M2242</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M2243</t>
+  </si>
+  <si>
+    <t>M2244</t>
+  </si>
+  <si>
+    <t>M2245</t>
+  </si>
+  <si>
+    <t>M2246</t>
+  </si>
+  <si>
+    <t>M1220</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M1221</t>
+  </si>
+  <si>
+    <t>M1222</t>
+  </si>
+  <si>
+    <t>M1223</t>
+  </si>
+  <si>
+    <t>M1224</t>
+  </si>
+  <si>
+    <t>M1225</t>
+  </si>
+  <si>
+    <t>M1226</t>
+  </si>
+  <si>
+    <t>M1227</t>
+  </si>
+  <si>
+    <t>M2250</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M2251</t>
+  </si>
+  <si>
+    <t>M2252</t>
+  </si>
+  <si>
+    <t>M2253</t>
+  </si>
+  <si>
+    <t>M2254</t>
+  </si>
+  <si>
+    <t>AGV2 기동 MAIN 딜레이</t>
+  </si>
+  <si>
+    <t>AGV3 기동 MAIN 딜레이</t>
+  </si>
+  <si>
+    <t>AGV4 기동 MAIN 딜레이</t>
+  </si>
+  <si>
+    <t>AGV5 기동 MAIN 딜레이</t>
+  </si>
+  <si>
+    <t>T41</t>
+  </si>
+  <si>
+    <t>T42</t>
+  </si>
+  <si>
+    <t>T43</t>
+  </si>
+  <si>
+    <t>T44</t>
+  </si>
+  <si>
+    <t>M160</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGV2 내부펄스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M161</t>
+  </si>
+  <si>
+    <t>M162</t>
+  </si>
+  <si>
+    <t>M163</t>
+  </si>
+  <si>
+    <t>AGV3 내부펄스</t>
+  </si>
+  <si>
+    <t>AGV4 내부펄스</t>
+  </si>
+  <si>
+    <t>AGV5 내부펄스</t>
+  </si>
+  <si>
+    <t>M226</t>
+  </si>
+  <si>
+    <t>M227</t>
+  </si>
+  <si>
+    <t>M228</t>
+  </si>
+  <si>
+    <t>AGV1 내부 기동 신호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGV2 내부 기동 신호</t>
+  </si>
+  <si>
+    <t>AGV3 내부 기동 신호</t>
+  </si>
+  <si>
+    <t>AGV4 내부 기동 신호</t>
+  </si>
+  <si>
+    <t>AGV5 내부 기동 신호</t>
+  </si>
+  <si>
+    <t>M229</t>
   </si>
 </sst>
 </file>
@@ -3876,6 +4121,99 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3883,6 +4221,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3912,100 +4259,10 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4019,18 +4276,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4366,7 +4611,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{228BF0B7-E586-4CC1-BF31-0F024BABECA2}">
-  <dimension ref="B3:K105"/>
+  <dimension ref="B3:K123"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="3" width="9" style="1"/>
@@ -4380,47 +4625,47 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:11">
-      <c r="B3" s="79" t="s">
+      <c r="B3" s="83" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="80"/>
-      <c r="D3" s="78" t="s">
+      <c r="C3" s="84"/>
+      <c r="D3" s="82" t="s">
         <v>55</v>
       </c>
-      <c r="E3" s="78"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="78"/>
-      <c r="H3" s="78"/>
-      <c r="I3" s="78"/>
-      <c r="J3" s="78"/>
-      <c r="K3" s="78"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="82"/>
     </row>
     <row r="4" spans="2:11">
-      <c r="B4" s="79" t="s">
+      <c r="B4" s="83" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="80"/>
-      <c r="D4" s="78"/>
-      <c r="E4" s="78"/>
-      <c r="F4" s="78"/>
-      <c r="G4" s="78"/>
-      <c r="H4" s="78"/>
-      <c r="I4" s="78"/>
-      <c r="J4" s="78"/>
-      <c r="K4" s="78"/>
+      <c r="C4" s="84"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="82"/>
+      <c r="K4" s="82"/>
     </row>
     <row r="5" spans="2:11">
-      <c r="B5" s="79" t="s">
+      <c r="B5" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="80"/>
+      <c r="C5" s="84"/>
       <c r="D5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="79" t="s">
+      <c r="E5" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="80"/>
+      <c r="F5" s="84"/>
       <c r="G5" s="4" t="s">
         <v>10</v>
       </c>
@@ -4443,7 +4688,7 @@
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="6" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>31</v>
@@ -4453,16 +4698,16 @@
         <v>49</v>
       </c>
       <c r="H6" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="I6" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="I6" s="6" t="s">
-        <v>383</v>
-      </c>
       <c r="J6" s="5" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="7" spans="2:11">
@@ -4481,16 +4726,16 @@
         <v>50</v>
       </c>
       <c r="H7" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="I7" s="6" t="s">
         <v>447</v>
       </c>
-      <c r="I7" s="6" t="s">
-        <v>448</v>
-      </c>
       <c r="J7" s="5" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="8" spans="2:11">
@@ -4499,7 +4744,7 @@
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>33</v>
@@ -4509,16 +4754,16 @@
         <v>51</v>
       </c>
       <c r="H8" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="I8" s="6" t="s">
         <v>449</v>
       </c>
-      <c r="I8" s="6" t="s">
-        <v>450</v>
-      </c>
       <c r="J8" s="5" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="9" spans="2:11">
@@ -4527,7 +4772,7 @@
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>118</v>
@@ -4537,16 +4782,16 @@
         <v>119</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="10" spans="2:11">
@@ -4555,7 +4800,7 @@
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>34</v>
@@ -4565,16 +4810,16 @@
         <v>120</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="11" spans="2:11">
@@ -4591,16 +4836,16 @@
         <v>121</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="12" spans="2:11">
@@ -4617,16 +4862,16 @@
         <v>122</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="13" spans="2:11">
@@ -4643,16 +4888,16 @@
         <v>123</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="14" spans="2:11">
@@ -4669,10 +4914,10 @@
         <v>124</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="J14" s="5"/>
       <c r="K14" s="6"/>
@@ -4709,10 +4954,10 @@
         <v>126</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="J16" s="5"/>
       <c r="K16" s="6"/>
@@ -4733,16 +4978,16 @@
         <v>127</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="18" spans="2:11">
@@ -4761,16 +5006,16 @@
         <v>52</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="J18" s="5" t="s">
+        <v>508</v>
+      </c>
+      <c r="K18" s="6" t="s">
         <v>510</v>
-      </c>
-      <c r="K18" s="6" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="19" spans="2:11">
@@ -4785,22 +5030,22 @@
         <v>140</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>132</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="20" spans="2:11">
@@ -4815,7 +5060,7 @@
         <v>141</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>133</v>
@@ -4837,7 +5082,7 @@
         <v>142</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>134</v>
@@ -4859,22 +5104,22 @@
         <v>143</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>135</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="I22" s="32" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
     </row>
     <row r="23" spans="2:11">
@@ -4889,22 +5134,22 @@
         <v>129</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>136</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="I23" s="32" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="24" spans="2:11">
@@ -4919,22 +5164,22 @@
         <v>130</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>137</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="I24" s="32" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
     </row>
     <row r="25" spans="2:11">
@@ -4953,16 +5198,16 @@
         <v>170</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="I25" s="32" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
     </row>
     <row r="26" spans="2:11">
@@ -4983,10 +5228,10 @@
       <c r="H26" s="5"/>
       <c r="I26" s="6"/>
       <c r="J26" s="5" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
     </row>
     <row r="27" spans="2:11">
@@ -5007,10 +5252,10 @@
       <c r="H27" s="5"/>
       <c r="I27" s="6"/>
       <c r="J27" s="5" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
     </row>
     <row r="28" spans="2:11">
@@ -5018,7 +5263,7 @@
         <v>6</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>107</v>
@@ -5031,16 +5276,16 @@
         <v>173</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
     </row>
     <row r="29" spans="2:11">
@@ -5048,7 +5293,7 @@
         <v>104</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>108</v>
@@ -5061,16 +5306,16 @@
         <v>174</v>
       </c>
       <c r="H29" s="5" t="s">
+        <v>817</v>
+      </c>
+      <c r="I29" s="6" t="s">
         <v>819</v>
       </c>
-      <c r="I29" s="6" t="s">
-        <v>821</v>
-      </c>
       <c r="J29" s="5" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
     </row>
     <row r="30" spans="2:11">
@@ -5078,7 +5323,7 @@
         <v>105</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>109</v>
@@ -5091,16 +5336,16 @@
         <v>175</v>
       </c>
       <c r="H30" s="5" t="s">
+        <v>818</v>
+      </c>
+      <c r="I30" s="6" t="s">
         <v>820</v>
       </c>
-      <c r="I30" s="6" t="s">
-        <v>822</v>
-      </c>
       <c r="J30" s="5" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
     </row>
     <row r="31" spans="2:11">
@@ -5108,7 +5353,7 @@
         <v>106</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>110</v>
@@ -5123,10 +5368,10 @@
       <c r="H31" s="5"/>
       <c r="I31" s="6"/>
       <c r="J31" s="5" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
     </row>
     <row r="32" spans="2:11">
@@ -5134,7 +5379,7 @@
         <v>25</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>111</v>
@@ -5156,7 +5401,7 @@
         <v>26</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>112</v>
@@ -5171,10 +5416,10 @@
       <c r="H33" s="5"/>
       <c r="I33" s="6"/>
       <c r="J33" s="5" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="K33" s="6" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
     </row>
     <row r="34" spans="2:11">
@@ -5183,7 +5428,7 @@
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="6" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E34" s="5" t="s">
         <v>151</v>
@@ -5195,10 +5440,10 @@
       <c r="H34" s="5"/>
       <c r="I34" s="6"/>
       <c r="J34" s="5" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
     </row>
     <row r="35" spans="2:11">
@@ -5207,7 +5452,7 @@
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E35" s="5" t="s">
         <v>152</v>
@@ -5217,16 +5462,16 @@
         <v>180</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="K35" s="6" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
     </row>
     <row r="36" spans="2:11">
@@ -5235,7 +5480,7 @@
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="6" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E36" s="5" t="s">
         <v>153</v>
@@ -5245,16 +5490,16 @@
         <v>181</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="K36" s="6" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
     </row>
     <row r="37" spans="2:11">
@@ -5263,7 +5508,7 @@
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="6" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E37" s="5" t="s">
         <v>154</v>
@@ -5273,10 +5518,10 @@
         <v>182</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="J37" s="5"/>
       <c r="K37" s="6"/>
@@ -5287,7 +5532,7 @@
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="6" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E38" s="5" t="s">
         <v>155</v>
@@ -5297,10 +5542,10 @@
         <v>183</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="J38" s="5"/>
       <c r="K38" s="6"/>
@@ -5311,7 +5556,7 @@
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="6" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E39" s="5" t="s">
         <v>156</v>
@@ -5321,16 +5566,16 @@
         <v>184</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="K39" s="6" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
     </row>
     <row r="40" spans="2:11">
@@ -5349,13 +5594,17 @@
         <v>185</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="J40" s="5"/>
-      <c r="K40" s="6"/>
+        <v>477</v>
+      </c>
+      <c r="J40" s="5" t="s">
+        <v>953</v>
+      </c>
+      <c r="K40" s="6" t="s">
+        <v>949</v>
+      </c>
     </row>
     <row r="41" spans="2:11">
       <c r="B41" s="5" t="s">
@@ -5373,13 +5622,17 @@
         <v>186</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>480</v>
-      </c>
-      <c r="J41" s="5"/>
-      <c r="K41" s="6"/>
+        <v>478</v>
+      </c>
+      <c r="J41" s="5" t="s">
+        <v>954</v>
+      </c>
+      <c r="K41" s="6" t="s">
+        <v>950</v>
+      </c>
     </row>
     <row r="42" spans="2:11">
       <c r="B42" s="5" t="s">
@@ -5397,21 +5650,25 @@
         <v>187</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>481</v>
-      </c>
-      <c r="J42" s="5"/>
-      <c r="K42" s="6"/>
+        <v>479</v>
+      </c>
+      <c r="J42" s="5" t="s">
+        <v>955</v>
+      </c>
+      <c r="K42" s="6" t="s">
+        <v>951</v>
+      </c>
     </row>
     <row r="43" spans="2:11">
       <c r="B43" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C43" s="5"/>
       <c r="D43" s="6" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E43" s="31" t="s">
         <v>160</v>
@@ -5421,45 +5678,49 @@
         <v>188</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>482</v>
-      </c>
-      <c r="J43" s="5"/>
-      <c r="K43" s="6"/>
+        <v>480</v>
+      </c>
+      <c r="J43" s="5" t="s">
+        <v>956</v>
+      </c>
+      <c r="K43" s="6" t="s">
+        <v>952</v>
+      </c>
     </row>
     <row r="44" spans="2:11">
       <c r="B44" s="5" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C44" s="5"/>
       <c r="D44" s="6" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E44" s="31" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F44" s="5"/>
       <c r="G44" s="6" t="s">
         <v>189</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="J44" s="5"/>
       <c r="K44" s="6"/>
     </row>
     <row r="45" spans="2:11">
       <c r="B45" s="5" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C45" s="5"/>
       <c r="D45" s="6" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E45" s="31" t="s">
         <v>161</v>
@@ -5475,11 +5736,11 @@
     </row>
     <row r="46" spans="2:11">
       <c r="B46" s="5" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C46" s="5"/>
       <c r="D46" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E46" s="31" t="s">
         <v>162</v>
@@ -5489,21 +5750,21 @@
         <v>191</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="J46" s="5"/>
       <c r="K46" s="6"/>
     </row>
     <row r="47" spans="2:11">
       <c r="B47" s="5" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C47" s="5"/>
       <c r="D47" s="6" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E47" s="31" t="s">
         <v>163</v>
@@ -5513,21 +5774,21 @@
         <v>192</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="J47" s="5"/>
       <c r="K47" s="6"/>
     </row>
     <row r="48" spans="2:11">
       <c r="B48" s="5" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C48" s="5"/>
       <c r="D48" s="6" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E48" s="31" t="s">
         <v>166</v>
@@ -5537,10 +5798,10 @@
         <v>193</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="J48" s="5"/>
       <c r="K48" s="6"/>
@@ -5557,10 +5818,10 @@
         <v>194</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="J49" s="5"/>
       <c r="K49" s="6"/>
@@ -5577,10 +5838,10 @@
         <v>195</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="J50" s="5"/>
       <c r="K50" s="6"/>
@@ -5597,10 +5858,10 @@
         <v>196</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="J51" s="5"/>
       <c r="K51" s="6"/>
@@ -5610,13 +5871,13 @@
       <c r="C52" s="5"/>
       <c r="D52" s="6"/>
       <c r="E52" s="31" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H52" s="5"/>
       <c r="I52" s="6"/>
@@ -5631,16 +5892,16 @@
         <v>164</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="J53" s="5"/>
       <c r="K53" s="6"/>
@@ -5653,16 +5914,16 @@
         <v>165</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="J54" s="5"/>
       <c r="K54" s="6"/>
@@ -5672,19 +5933,19 @@
       <c r="C55" s="5"/>
       <c r="D55" s="6"/>
       <c r="E55" s="31" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="J55" s="5"/>
       <c r="K55" s="6"/>
@@ -5694,19 +5955,19 @@
       <c r="C56" s="5"/>
       <c r="D56" s="6"/>
       <c r="E56" s="31" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="J56" s="5"/>
       <c r="K56" s="6"/>
@@ -5716,19 +5977,19 @@
       <c r="C57" s="5"/>
       <c r="D57" s="6"/>
       <c r="E57" s="31" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="G57" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="J57" s="5"/>
       <c r="K57" s="6"/>
@@ -5737,10 +5998,10 @@
       <c r="F58" s="5"/>
       <c r="G58" s="6"/>
       <c r="H58" s="5" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="J58" s="6"/>
       <c r="K58" s="6"/>
@@ -5749,10 +6010,10 @@
       <c r="F59" s="5"/>
       <c r="G59" s="6"/>
       <c r="H59" s="5" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="J59" s="6"/>
       <c r="K59" s="6"/>
@@ -5808,12 +6069,6 @@
     <row r="66" spans="6:11">
       <c r="F66" s="5"/>
       <c r="G66" s="6"/>
-      <c r="H66" s="5" t="s">
-        <v>453</v>
-      </c>
-      <c r="I66" s="6" t="s">
-        <v>456</v>
-      </c>
       <c r="J66" s="6"/>
       <c r="K66" s="6"/>
     </row>
@@ -5821,10 +6076,10 @@
       <c r="F67" s="5"/>
       <c r="G67" s="6"/>
       <c r="H67" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="I67" s="6" t="s">
         <v>454</v>
-      </c>
-      <c r="I67" s="6" t="s">
-        <v>455</v>
       </c>
       <c r="J67" s="6"/>
       <c r="K67" s="6"/>
@@ -5833,10 +6088,10 @@
       <c r="F68" s="5"/>
       <c r="G68" s="6"/>
       <c r="H68" s="5" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="I68" s="6" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="J68" s="6"/>
       <c r="K68" s="6"/>
@@ -5845,10 +6100,10 @@
       <c r="F69" s="5"/>
       <c r="G69" s="6"/>
       <c r="H69" s="5" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="J69" s="6"/>
       <c r="K69" s="6"/>
@@ -5857,10 +6112,10 @@
       <c r="F70" s="5"/>
       <c r="G70" s="6"/>
       <c r="H70" s="5" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="J70" s="6"/>
       <c r="K70" s="6"/>
@@ -5869,10 +6124,10 @@
       <c r="F71" s="5"/>
       <c r="G71" s="6"/>
       <c r="H71" s="5" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="J71" s="6"/>
       <c r="K71" s="6"/>
@@ -5881,10 +6136,10 @@
       <c r="F72" s="5"/>
       <c r="G72" s="6"/>
       <c r="H72" s="5" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="I72" s="6" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="J72" s="6"/>
       <c r="K72" s="6"/>
@@ -5893,10 +6148,10 @@
       <c r="F73" s="5"/>
       <c r="G73" s="6"/>
       <c r="H73" s="5" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="I73" s="6" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="J73" s="6"/>
       <c r="K73" s="6"/>
@@ -5905,10 +6160,10 @@
       <c r="F74" s="5"/>
       <c r="G74" s="6"/>
       <c r="H74" s="5" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="I74" s="6" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="J74" s="6"/>
       <c r="K74" s="6"/>
@@ -5917,10 +6172,10 @@
       <c r="F75" s="5"/>
       <c r="G75" s="6"/>
       <c r="H75" s="5" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="I75" s="6" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="J75" s="6"/>
       <c r="K75" s="6"/>
@@ -5937,84 +6192,84 @@
       <c r="F77" s="5"/>
       <c r="G77" s="6"/>
       <c r="H77" s="5" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="I77" s="6" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="J77" s="6"/>
       <c r="K77" s="6"/>
     </row>
     <row r="78" spans="6:11">
       <c r="H78" s="5" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="I78" s="6" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="79" spans="6:11">
       <c r="H79" s="5" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="I79" s="6" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="80" spans="6:11">
       <c r="H80" s="5" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="I80" s="6" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
     </row>
     <row r="81" spans="8:9">
       <c r="H81" s="5" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="I81" s="6" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="82" spans="8:9">
       <c r="H82" s="5" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="I82" s="6" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="83" spans="8:9">
       <c r="H83" s="5" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="I83" s="6" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="84" spans="8:9">
       <c r="H84" s="5" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="I84" s="6" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="85" spans="8:9">
       <c r="H85" s="5" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="I85" s="6" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="86" spans="8:9">
       <c r="H86" s="5" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="I86" s="6" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="87" spans="8:9">
@@ -6022,133 +6277,197 @@
       <c r="I87" s="6"/>
     </row>
     <row r="88" spans="8:9">
-      <c r="H88" s="5"/>
-      <c r="I88" s="6"/>
+      <c r="H88" s="5" t="s">
+        <v>957</v>
+      </c>
+      <c r="I88" s="6" t="s">
+        <v>958</v>
+      </c>
     </row>
     <row r="89" spans="8:9">
-      <c r="H89" s="5"/>
-      <c r="I89" s="6"/>
+      <c r="H89" s="5" t="s">
+        <v>959</v>
+      </c>
+      <c r="I89" s="6" t="s">
+        <v>962</v>
+      </c>
     </row>
     <row r="90" spans="8:9">
-      <c r="H90" s="5"/>
-      <c r="I90" s="6"/>
+      <c r="H90" s="5" t="s">
+        <v>960</v>
+      </c>
+      <c r="I90" s="6" t="s">
+        <v>963</v>
+      </c>
     </row>
     <row r="91" spans="8:9">
       <c r="H91" s="5" t="s">
-        <v>724</v>
+        <v>961</v>
       </c>
       <c r="I91" s="6" t="s">
-        <v>738</v>
+        <v>964</v>
       </c>
     </row>
     <row r="92" spans="8:9">
-      <c r="H92" s="5" t="s">
-        <v>725</v>
-      </c>
-      <c r="I92" s="6" t="s">
-        <v>739</v>
-      </c>
+      <c r="H92" s="5"/>
+      <c r="I92" s="6"/>
     </row>
     <row r="93" spans="8:9">
       <c r="H93" s="5" t="s">
-        <v>726</v>
+        <v>452</v>
       </c>
       <c r="I93" s="6" t="s">
-        <v>740</v>
+        <v>968</v>
       </c>
     </row>
     <row r="94" spans="8:9">
       <c r="H94" s="5" t="s">
-        <v>727</v>
+        <v>965</v>
       </c>
       <c r="I94" s="6" t="s">
-        <v>741</v>
+        <v>969</v>
       </c>
     </row>
     <row r="95" spans="8:9">
       <c r="H95" s="5" t="s">
-        <v>728</v>
+        <v>966</v>
       </c>
       <c r="I95" s="6" t="s">
-        <v>742</v>
+        <v>970</v>
       </c>
     </row>
     <row r="96" spans="8:9">
       <c r="H96" s="5" t="s">
-        <v>729</v>
+        <v>967</v>
       </c>
       <c r="I96" s="6" t="s">
-        <v>743</v>
+        <v>971</v>
       </c>
     </row>
     <row r="97" spans="8:9">
       <c r="H97" s="5" t="s">
+        <v>973</v>
+      </c>
+      <c r="I97" s="6" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="109" spans="8:9">
+      <c r="H109" s="5" t="s">
+        <v>722</v>
+      </c>
+      <c r="I109" s="6" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="110" spans="8:9">
+      <c r="H110" s="5" t="s">
+        <v>723</v>
+      </c>
+      <c r="I110" s="6" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="111" spans="8:9">
+      <c r="H111" s="5" t="s">
+        <v>724</v>
+      </c>
+      <c r="I111" s="6" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="112" spans="8:9">
+      <c r="H112" s="5" t="s">
+        <v>725</v>
+      </c>
+      <c r="I112" s="6" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="113" spans="8:9">
+      <c r="H113" s="5" t="s">
+        <v>726</v>
+      </c>
+      <c r="I113" s="6" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="114" spans="8:9">
+      <c r="H114" s="5" t="s">
+        <v>727</v>
+      </c>
+      <c r="I114" s="6" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="115" spans="8:9">
+      <c r="H115" s="5" t="s">
+        <v>728</v>
+      </c>
+      <c r="I115" s="6" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="116" spans="8:9">
+      <c r="H116" s="5" t="s">
+        <v>729</v>
+      </c>
+      <c r="I116" s="6" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="117" spans="8:9">
+      <c r="H117" s="5" t="s">
         <v>730</v>
       </c>
-      <c r="I97" s="6" t="s">
+      <c r="I117" s="6" t="s">
         <v>744</v>
       </c>
     </row>
-    <row r="98" spans="8:9">
-      <c r="H98" s="5" t="s">
+    <row r="118" spans="8:9">
+      <c r="H118" s="5" t="s">
         <v>731</v>
       </c>
-      <c r="I98" s="6" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="99" spans="8:9">
-      <c r="H99" s="5" t="s">
+      <c r="I118" s="6" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="119" spans="8:9">
+      <c r="H119" s="5" t="s">
         <v>732</v>
       </c>
-      <c r="I99" s="6" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="100" spans="8:9">
-      <c r="H100" s="5" t="s">
+      <c r="I119" s="6" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="120" spans="8:9">
+      <c r="H120" s="5" t="s">
         <v>733</v>
       </c>
-      <c r="I100" s="6" t="s">
+      <c r="I120" s="6" t="s">
         <v>738</v>
       </c>
     </row>
-    <row r="101" spans="8:9">
-      <c r="H101" s="5" t="s">
+    <row r="121" spans="8:9">
+      <c r="H121" s="5" t="s">
         <v>734</v>
       </c>
-      <c r="I101" s="6" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="102" spans="8:9">
-      <c r="H102" s="5" t="s">
+      <c r="I121" s="6" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="122" spans="8:9">
+      <c r="H122" s="5" t="s">
         <v>735</v>
       </c>
-      <c r="I102" s="6" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="103" spans="8:9">
-      <c r="H103" s="5" t="s">
-        <v>736</v>
-      </c>
-      <c r="I103" s="6" t="s">
+      <c r="I122" s="6" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="123" spans="8:9">
+      <c r="H123" s="5"/>
+      <c r="I123" s="6" t="s">
         <v>738</v>
-      </c>
-    </row>
-    <row r="104" spans="8:9">
-      <c r="H104" s="5" t="s">
-        <v>737</v>
-      </c>
-      <c r="I104" s="6" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="105" spans="8:9">
-      <c r="H105" s="5"/>
-      <c r="I105" s="6" t="s">
-        <v>740</v>
       </c>
     </row>
   </sheetData>
@@ -6209,135 +6528,135 @@
       <c r="X2" s="12"/>
     </row>
     <row r="3" spans="3:24" s="3" customFormat="1">
-      <c r="C3" s="78" t="s">
+      <c r="C3" s="82" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="78"/>
-      <c r="E3" s="78" t="s">
+      <c r="D3" s="82"/>
+      <c r="E3" s="82" t="s">
         <v>65</v>
       </c>
-      <c r="F3" s="78"/>
-      <c r="G3" s="78"/>
-      <c r="H3" s="78"/>
-      <c r="K3" s="78" t="s">
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
+      <c r="K3" s="82" t="s">
         <v>40</v>
       </c>
-      <c r="L3" s="78"/>
-      <c r="M3" s="78" t="s">
+      <c r="L3" s="82"/>
+      <c r="M3" s="82" t="s">
         <v>66</v>
       </c>
-      <c r="N3" s="78"/>
-      <c r="O3" s="78"/>
-      <c r="P3" s="78"/>
-      <c r="S3" s="78" t="s">
+      <c r="N3" s="82"/>
+      <c r="O3" s="82"/>
+      <c r="P3" s="82"/>
+      <c r="S3" s="82" t="s">
         <v>40</v>
       </c>
-      <c r="T3" s="78"/>
-      <c r="U3" s="78" t="s">
+      <c r="T3" s="82"/>
+      <c r="U3" s="82" t="s">
         <v>209</v>
       </c>
-      <c r="V3" s="78"/>
-      <c r="W3" s="78"/>
-      <c r="X3" s="78"/>
+      <c r="V3" s="82"/>
+      <c r="W3" s="82"/>
+      <c r="X3" s="82"/>
     </row>
     <row r="4" spans="3:24" s="3" customFormat="1">
-      <c r="C4" s="78" t="s">
+      <c r="C4" s="82" t="s">
         <v>39</v>
       </c>
-      <c r="D4" s="78"/>
-      <c r="E4" s="78"/>
-      <c r="F4" s="78"/>
-      <c r="G4" s="78"/>
-      <c r="H4" s="78"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="82"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
-      <c r="K4" s="78" t="s">
+      <c r="K4" s="82" t="s">
         <v>39</v>
       </c>
-      <c r="L4" s="78"/>
-      <c r="M4" s="78"/>
-      <c r="N4" s="78"/>
-      <c r="O4" s="78"/>
-      <c r="P4" s="78"/>
-      <c r="S4" s="78" t="s">
+      <c r="L4" s="82"/>
+      <c r="M4" s="82"/>
+      <c r="N4" s="82"/>
+      <c r="O4" s="82"/>
+      <c r="P4" s="82"/>
+      <c r="S4" s="82" t="s">
         <v>39</v>
       </c>
-      <c r="T4" s="78"/>
-      <c r="U4" s="78"/>
-      <c r="V4" s="78"/>
-      <c r="W4" s="78"/>
-      <c r="X4" s="78"/>
+      <c r="T4" s="82"/>
+      <c r="U4" s="82"/>
+      <c r="V4" s="82"/>
+      <c r="W4" s="82"/>
+      <c r="X4" s="82"/>
     </row>
     <row r="5" spans="3:24" s="2" customFormat="1">
-      <c r="C5" s="78" t="s">
+      <c r="C5" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="78"/>
+      <c r="D5" s="82"/>
       <c r="E5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="78" t="s">
+      <c r="F5" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="78"/>
+      <c r="G5" s="82"/>
       <c r="H5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K5" s="78" t="s">
+      <c r="K5" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="L5" s="78"/>
+      <c r="L5" s="82"/>
       <c r="M5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="N5" s="78" t="s">
+      <c r="N5" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="O5" s="78"/>
+      <c r="O5" s="82"/>
       <c r="P5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="S5" s="78" t="s">
+      <c r="S5" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="T5" s="78"/>
+      <c r="T5" s="82"/>
       <c r="U5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="V5" s="78" t="s">
+      <c r="V5" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="W5" s="78"/>
+      <c r="W5" s="82"/>
       <c r="X5" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="3:24" s="2" customFormat="1">
       <c r="C6" s="4" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
       <c r="K6" s="4" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
       <c r="O6" s="4"/>
       <c r="P6" s="4"/>
       <c r="S6" s="4" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="U6" s="4"/>
       <c r="V6" s="4"/>
@@ -6349,7 +6668,7 @@
         <v>56</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>7</v>
@@ -6358,7 +6677,7 @@
         <v>57</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>20</v>
@@ -6367,7 +6686,7 @@
         <v>67</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="M7" s="6" t="s">
         <v>7</v>
@@ -6376,7 +6695,7 @@
         <v>74</v>
       </c>
       <c r="O7" s="5" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="P7" s="6" t="s">
         <v>20</v>
@@ -6385,7 +6704,7 @@
         <v>199</v>
       </c>
       <c r="T7" s="5" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="U7" s="6" t="s">
         <v>7</v>
@@ -6394,7 +6713,7 @@
         <v>205</v>
       </c>
       <c r="W7" s="5" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="X7" s="6" t="s">
         <v>20</v>
@@ -6405,7 +6724,7 @@
         <v>291</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>8</v>
@@ -6414,7 +6733,7 @@
         <v>58</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>13</v>
@@ -6423,7 +6742,7 @@
         <v>68</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="M8" s="6" t="s">
         <v>8</v>
@@ -6432,16 +6751,16 @@
         <v>75</v>
       </c>
       <c r="O8" s="5" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="P8" s="6" t="s">
         <v>13</v>
       </c>
       <c r="S8" s="5" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="T8" s="5" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="U8" s="6" t="s">
         <v>8</v>
@@ -6450,7 +6769,7 @@
         <v>236</v>
       </c>
       <c r="W8" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="X8" s="6" t="s">
         <v>13</v>
@@ -6461,7 +6780,7 @@
         <v>292</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>16</v>
@@ -6470,7 +6789,7 @@
         <v>59</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>14</v>
@@ -6479,7 +6798,7 @@
         <v>69</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="M9" s="10" t="s">
         <v>16</v>
@@ -6488,7 +6807,7 @@
         <v>76</v>
       </c>
       <c r="O9" s="5" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="P9" s="6" t="s">
         <v>14</v>
@@ -6497,7 +6816,7 @@
         <v>238</v>
       </c>
       <c r="T9" s="9" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="U9" s="10" t="s">
         <v>16</v>
@@ -6506,7 +6825,7 @@
         <v>237</v>
       </c>
       <c r="W9" s="5" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="X9" s="6" t="s">
         <v>14</v>
@@ -6517,7 +6836,7 @@
         <v>293</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>17</v>
@@ -6526,7 +6845,7 @@
         <v>60</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="H10" s="10" t="s">
         <v>12</v>
@@ -6535,7 +6854,7 @@
         <v>70</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="M10" s="10" t="s">
         <v>17</v>
@@ -6544,7 +6863,7 @@
         <v>77</v>
       </c>
       <c r="O10" s="9" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="P10" s="10" t="s">
         <v>12</v>
@@ -6553,7 +6872,7 @@
         <v>232</v>
       </c>
       <c r="T10" s="9" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="U10" s="10" t="s">
         <v>17</v>
@@ -6562,7 +6881,7 @@
         <v>233</v>
       </c>
       <c r="W10" s="9" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="X10" s="10" t="s">
         <v>12</v>
@@ -6570,10 +6889,10 @@
     </row>
     <row r="11" spans="3:24">
       <c r="C11" s="5" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>18</v>
@@ -6582,7 +6901,7 @@
         <v>61</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="H11" s="10" t="s">
         <v>11</v>
@@ -6591,7 +6910,7 @@
         <v>71</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="M11" s="6" t="s">
         <v>18</v>
@@ -6600,7 +6919,7 @@
         <v>78</v>
       </c>
       <c r="O11" s="9" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="P11" s="10" t="s">
         <v>11</v>
@@ -6609,7 +6928,7 @@
         <v>234</v>
       </c>
       <c r="T11" s="5" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="U11" s="6" t="s">
         <v>18</v>
@@ -6618,7 +6937,7 @@
         <v>235</v>
       </c>
       <c r="W11" s="9" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="X11" s="10" t="s">
         <v>11</v>
@@ -6629,45 +6948,45 @@
         <v>294</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E12" s="10"/>
       <c r="F12" s="9"/>
       <c r="G12" s="9" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="H12" s="10"/>
       <c r="K12" s="9" t="s">
         <v>72</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="M12" s="10"/>
       <c r="N12" s="9"/>
       <c r="O12" s="9" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="P12" s="10"/>
       <c r="S12" s="9" t="s">
         <v>202</v>
       </c>
       <c r="T12" s="9" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="U12" s="10"/>
       <c r="V12" s="9"/>
       <c r="W12" s="9" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="X12" s="10"/>
     </row>
     <row r="13" spans="3:24">
       <c r="C13" s="9" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>22</v>
@@ -6676,7 +6995,7 @@
         <v>62</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="H13" s="10" t="s">
         <v>15</v>
@@ -6685,7 +7004,7 @@
         <v>197</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="M13" s="10" t="s">
         <v>22</v>
@@ -6694,7 +7013,7 @@
         <v>79</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="P13" s="10" t="s">
         <v>15</v>
@@ -6703,7 +7022,7 @@
         <v>203</v>
       </c>
       <c r="T13" s="9" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="U13" s="10" t="s">
         <v>22</v>
@@ -6712,7 +7031,7 @@
         <v>206</v>
       </c>
       <c r="W13" s="9" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="X13" s="10" t="s">
         <v>15</v>
@@ -6720,10 +7039,10 @@
     </row>
     <row r="14" spans="3:24">
       <c r="C14" s="9" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>21</v>
@@ -6732,16 +7051,16 @@
         <v>63</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H14" s="10" t="s">
         <v>23</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="M14" s="10" t="s">
         <v>21</v>
@@ -6750,7 +7069,7 @@
         <v>80</v>
       </c>
       <c r="O14" s="9" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="P14" s="10" t="s">
         <v>23</v>
@@ -6759,7 +7078,7 @@
         <v>204</v>
       </c>
       <c r="T14" s="9" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="U14" s="10" t="s">
         <v>21</v>
@@ -6768,7 +7087,7 @@
         <v>207</v>
       </c>
       <c r="W14" s="9" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="X14" s="10" t="s">
         <v>23</v>
@@ -6779,7 +7098,7 @@
         <v>73</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>19</v>
@@ -6788,16 +7107,16 @@
         <v>64</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="H15" s="10" t="s">
         <v>24</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="M15" s="6" t="s">
         <v>19</v>
@@ -6806,16 +7125,16 @@
         <v>198</v>
       </c>
       <c r="O15" s="9" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="P15" s="10" t="s">
         <v>24</v>
       </c>
       <c r="S15" s="5" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="T15" s="5" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="U15" s="6" t="s">
         <v>19</v>
@@ -6824,7 +7143,7 @@
         <v>208</v>
       </c>
       <c r="W15" s="9" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="X15" s="10" t="s">
         <v>24</v>
@@ -6832,31 +7151,31 @@
     </row>
     <row r="16" spans="3:24">
       <c r="C16" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F16" s="9"/>
       <c r="G16" s="9"/>
       <c r="H16" s="10"/>
       <c r="K16" s="5" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="L16" s="5"/>
       <c r="M16" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="N16" s="9"/>
       <c r="O16" s="9"/>
       <c r="P16" s="10"/>
       <c r="S16" s="5" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="T16" s="5"/>
       <c r="U16" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="V16" s="9"/>
       <c r="W16" s="9"/>
@@ -6947,77 +7266,77 @@
       <c r="B23" s="1"/>
       <c r="E23" s="1"/>
       <c r="H23" s="1"/>
-      <c r="K23" s="78" t="s">
+      <c r="K23" s="82" t="s">
         <v>40</v>
       </c>
-      <c r="L23" s="78"/>
-      <c r="M23" s="78" t="s">
+      <c r="L23" s="82"/>
+      <c r="M23" s="82" t="s">
         <v>210</v>
       </c>
-      <c r="N23" s="78"/>
-      <c r="O23" s="78"/>
-      <c r="P23" s="78"/>
-      <c r="S23" s="78" t="s">
+      <c r="N23" s="82"/>
+      <c r="O23" s="82"/>
+      <c r="P23" s="82"/>
+      <c r="S23" s="82" t="s">
         <v>40</v>
       </c>
-      <c r="T23" s="78"/>
-      <c r="U23" s="78" t="s">
+      <c r="T23" s="82"/>
+      <c r="U23" s="82" t="s">
         <v>211</v>
       </c>
-      <c r="V23" s="78"/>
-      <c r="W23" s="78"/>
-      <c r="X23" s="78"/>
+      <c r="V23" s="82"/>
+      <c r="W23" s="82"/>
+      <c r="X23" s="82"/>
     </row>
     <row r="24" spans="2:24">
       <c r="B24" s="1"/>
       <c r="E24" s="1"/>
       <c r="H24" s="1"/>
-      <c r="K24" s="78" t="s">
+      <c r="K24" s="82" t="s">
         <v>39</v>
       </c>
-      <c r="L24" s="78"/>
-      <c r="M24" s="78"/>
-      <c r="N24" s="78"/>
-      <c r="O24" s="78"/>
-      <c r="P24" s="78"/>
-      <c r="S24" s="78" t="s">
+      <c r="L24" s="82"/>
+      <c r="M24" s="82"/>
+      <c r="N24" s="82"/>
+      <c r="O24" s="82"/>
+      <c r="P24" s="82"/>
+      <c r="S24" s="82" t="s">
         <v>39</v>
       </c>
-      <c r="T24" s="78"/>
-      <c r="U24" s="78"/>
-      <c r="V24" s="78"/>
-      <c r="W24" s="78"/>
-      <c r="X24" s="78"/>
+      <c r="T24" s="82"/>
+      <c r="U24" s="82"/>
+      <c r="V24" s="82"/>
+      <c r="W24" s="82"/>
+      <c r="X24" s="82"/>
     </row>
     <row r="25" spans="2:24">
       <c r="B25" s="1"/>
       <c r="E25" s="1"/>
       <c r="H25" s="1"/>
-      <c r="K25" s="78" t="s">
+      <c r="K25" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="L25" s="78"/>
+      <c r="L25" s="82"/>
       <c r="M25" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="N25" s="78" t="s">
+      <c r="N25" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="O25" s="78"/>
+      <c r="O25" s="82"/>
       <c r="P25" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="S25" s="78" t="s">
+      <c r="S25" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="T25" s="78"/>
+      <c r="T25" s="82"/>
       <c r="U25" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="V25" s="78" t="s">
+      <c r="V25" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="W25" s="78"/>
+      <c r="W25" s="82"/>
       <c r="X25" s="4" t="s">
         <v>10</v>
       </c>
@@ -7027,20 +7346,20 @@
       <c r="E26" s="1"/>
       <c r="H26" s="1"/>
       <c r="K26" s="4" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="L26" s="4" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="M26" s="4"/>
       <c r="N26" s="4"/>
       <c r="O26" s="4"/>
       <c r="P26" s="4"/>
       <c r="S26" s="4" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="T26" s="4" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="U26" s="4"/>
       <c r="V26" s="4"/>
@@ -7055,7 +7374,7 @@
         <v>215</v>
       </c>
       <c r="L27" s="5" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="M27" s="6" t="s">
         <v>7</v>
@@ -7064,7 +7383,7 @@
         <v>222</v>
       </c>
       <c r="O27" s="5" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="P27" s="6" t="s">
         <v>20</v>
@@ -7073,7 +7392,7 @@
         <v>268</v>
       </c>
       <c r="T27" s="5" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="U27" s="6" t="s">
         <v>7</v>
@@ -7082,7 +7401,7 @@
         <v>228</v>
       </c>
       <c r="W27" s="5" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="X27" s="6" t="s">
         <v>20</v>
@@ -7096,7 +7415,7 @@
         <v>261</v>
       </c>
       <c r="L28" s="5" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="M28" s="6" t="s">
         <v>8</v>
@@ -7105,25 +7424,25 @@
         <v>223</v>
       </c>
       <c r="O28" s="5" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>13</v>
       </c>
       <c r="S28" s="5" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="T28" s="5" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="U28" s="6" t="s">
         <v>8</v>
       </c>
       <c r="V28" s="5" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="W28" s="5" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="X28" s="6" t="s">
         <v>13</v>
@@ -7137,7 +7456,7 @@
         <v>262</v>
       </c>
       <c r="L29" s="9" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="M29" s="10" t="s">
         <v>16</v>
@@ -7146,16 +7465,16 @@
         <v>224</v>
       </c>
       <c r="O29" s="5" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="P29" s="6" t="s">
         <v>14</v>
       </c>
       <c r="S29" s="9" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="T29" s="9" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="U29" s="10" t="s">
         <v>16</v>
@@ -7164,7 +7483,7 @@
         <v>240</v>
       </c>
       <c r="W29" s="5" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="X29" s="6" t="s">
         <v>14</v>
@@ -7178,7 +7497,7 @@
         <v>263</v>
       </c>
       <c r="L30" s="9" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="M30" s="10" t="s">
         <v>17</v>
@@ -7187,16 +7506,16 @@
         <v>225</v>
       </c>
       <c r="O30" s="9" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="P30" s="10" t="s">
         <v>12</v>
       </c>
       <c r="S30" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="T30" s="9" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="U30" s="10" t="s">
         <v>17</v>
@@ -7205,7 +7524,7 @@
         <v>241</v>
       </c>
       <c r="W30" s="9" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="X30" s="10" t="s">
         <v>12</v>
@@ -7219,7 +7538,7 @@
         <v>264</v>
       </c>
       <c r="L31" s="5" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="M31" s="6" t="s">
         <v>18</v>
@@ -7228,16 +7547,16 @@
         <v>226</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="P31" s="10" t="s">
         <v>11</v>
       </c>
       <c r="S31" s="5" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="T31" s="5" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="U31" s="6" t="s">
         <v>18</v>
@@ -7246,7 +7565,7 @@
         <v>242</v>
       </c>
       <c r="W31" s="9" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="X31" s="10" t="s">
         <v>11</v>
@@ -7260,24 +7579,24 @@
         <v>265</v>
       </c>
       <c r="L32" s="9" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="M32" s="10"/>
       <c r="N32" s="9"/>
       <c r="O32" s="9" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="P32" s="10"/>
       <c r="S32" s="9" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="T32" s="9" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="U32" s="10"/>
       <c r="V32" s="9"/>
       <c r="W32" s="9" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="X32" s="10"/>
     </row>
@@ -7289,7 +7608,7 @@
         <v>266</v>
       </c>
       <c r="L33" s="9" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="M33" s="10" t="s">
         <v>22</v>
@@ -7298,16 +7617,16 @@
         <v>227</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="P33" s="10" t="s">
         <v>15</v>
       </c>
       <c r="S33" s="9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="T33" s="9" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="U33" s="10" t="s">
         <v>22</v>
@@ -7316,7 +7635,7 @@
         <v>229</v>
       </c>
       <c r="W33" s="9" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="X33" s="10" t="s">
         <v>15</v>
@@ -7330,7 +7649,7 @@
         <v>267</v>
       </c>
       <c r="L34" s="9" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="M34" s="10" t="s">
         <v>21</v>
@@ -7339,16 +7658,16 @@
         <v>239</v>
       </c>
       <c r="O34" s="9" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="P34" s="10" t="s">
         <v>23</v>
       </c>
       <c r="S34" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="T34" s="9" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="U34" s="10" t="s">
         <v>21</v>
@@ -7357,7 +7676,7 @@
         <v>230</v>
       </c>
       <c r="W34" s="9" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="X34" s="10" t="s">
         <v>23</v>
@@ -7371,7 +7690,7 @@
         <v>268</v>
       </c>
       <c r="L35" s="5" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="M35" s="6" t="s">
         <v>19</v>
@@ -7380,16 +7699,16 @@
         <v>221</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>24</v>
       </c>
       <c r="S35" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="T35" s="5" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="U35" s="6" t="s">
         <v>19</v>
@@ -7398,7 +7717,7 @@
         <v>231</v>
       </c>
       <c r="W35" s="9" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="X35" s="10" t="s">
         <v>24</v>
@@ -7409,21 +7728,21 @@
       <c r="E36" s="1"/>
       <c r="H36" s="1"/>
       <c r="K36" s="5" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="L36" s="5"/>
       <c r="M36" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="N36" s="9"/>
       <c r="O36" s="9"/>
       <c r="P36" s="10"/>
       <c r="S36" s="5" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="T36" s="5"/>
       <c r="U36" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="V36" s="9"/>
       <c r="W36" s="9"/>
@@ -7477,114 +7796,114 @@
     </row>
     <row r="42" spans="2:24">
       <c r="B42" s="8"/>
-      <c r="C42" s="78" t="s">
+      <c r="C42" s="82" t="s">
         <v>40</v>
       </c>
-      <c r="D42" s="78"/>
-      <c r="E42" s="78" t="s">
+      <c r="D42" s="82"/>
+      <c r="E42" s="82" t="s">
         <v>212</v>
       </c>
-      <c r="F42" s="78"/>
-      <c r="G42" s="78"/>
-      <c r="H42" s="78"/>
+      <c r="F42" s="82"/>
+      <c r="G42" s="82"/>
+      <c r="H42" s="82"/>
       <c r="I42" s="7"/>
       <c r="J42" s="7"/>
       <c r="K42" s="4" t="s">
         <v>40</v>
       </c>
       <c r="L42" s="4"/>
-      <c r="M42" s="78" t="s">
+      <c r="M42" s="82" t="s">
         <v>213</v>
       </c>
-      <c r="N42" s="78"/>
-      <c r="O42" s="78"/>
-      <c r="P42" s="78"/>
+      <c r="N42" s="82"/>
+      <c r="O42" s="82"/>
+      <c r="P42" s="82"/>
       <c r="Q42" s="8"/>
       <c r="S42" s="4" t="s">
         <v>40</v>
       </c>
       <c r="T42" s="4"/>
-      <c r="U42" s="78" t="s">
+      <c r="U42" s="82" t="s">
         <v>214</v>
       </c>
-      <c r="V42" s="78"/>
-      <c r="W42" s="78"/>
-      <c r="X42" s="78"/>
+      <c r="V42" s="82"/>
+      <c r="W42" s="82"/>
+      <c r="X42" s="82"/>
     </row>
     <row r="43" spans="2:24">
       <c r="B43" s="8"/>
-      <c r="C43" s="78" t="s">
+      <c r="C43" s="82" t="s">
         <v>39</v>
       </c>
-      <c r="D43" s="78"/>
-      <c r="E43" s="78"/>
-      <c r="F43" s="78"/>
-      <c r="G43" s="78"/>
-      <c r="H43" s="78"/>
+      <c r="D43" s="82"/>
+      <c r="E43" s="82"/>
+      <c r="F43" s="82"/>
+      <c r="G43" s="82"/>
+      <c r="H43" s="82"/>
       <c r="I43" s="7"/>
       <c r="J43" s="7"/>
       <c r="K43" s="4" t="s">
         <v>39</v>
       </c>
       <c r="L43" s="4"/>
-      <c r="M43" s="78"/>
-      <c r="N43" s="78"/>
-      <c r="O43" s="78"/>
-      <c r="P43" s="78"/>
+      <c r="M43" s="82"/>
+      <c r="N43" s="82"/>
+      <c r="O43" s="82"/>
+      <c r="P43" s="82"/>
       <c r="Q43" s="8"/>
       <c r="S43" s="4" t="s">
         <v>39</v>
       </c>
       <c r="T43" s="4"/>
-      <c r="U43" s="78"/>
-      <c r="V43" s="78"/>
-      <c r="W43" s="78"/>
-      <c r="X43" s="78"/>
+      <c r="U43" s="82"/>
+      <c r="V43" s="82"/>
+      <c r="W43" s="82"/>
+      <c r="X43" s="82"/>
     </row>
     <row r="44" spans="2:24">
       <c r="B44" s="8"/>
-      <c r="C44" s="78" t="s">
+      <c r="C44" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="D44" s="78"/>
+      <c r="D44" s="82"/>
       <c r="E44" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F44" s="78" t="s">
+      <c r="F44" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="G44" s="78"/>
+      <c r="G44" s="82"/>
       <c r="H44" s="4" t="s">
         <v>10</v>
       </c>
       <c r="I44" s="7"/>
       <c r="J44" s="7"/>
-      <c r="K44" s="78" t="s">
+      <c r="K44" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="L44" s="78"/>
+      <c r="L44" s="82"/>
       <c r="M44" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="N44" s="78" t="s">
+      <c r="N44" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="O44" s="78"/>
+      <c r="O44" s="82"/>
       <c r="P44" s="4" t="s">
         <v>10</v>
       </c>
       <c r="Q44" s="8"/>
-      <c r="S44" s="78" t="s">
+      <c r="S44" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="T44" s="78"/>
+      <c r="T44" s="82"/>
       <c r="U44" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="V44" s="78" t="s">
+      <c r="V44" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="W44" s="78"/>
+      <c r="W44" s="82"/>
       <c r="X44" s="4" t="s">
         <v>10</v>
       </c>
@@ -7592,10 +7911,10 @@
     <row r="45" spans="2:24">
       <c r="B45" s="8"/>
       <c r="C45" s="4" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
@@ -7604,10 +7923,10 @@
       <c r="I45" s="7"/>
       <c r="J45" s="7"/>
       <c r="K45" s="4" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="M45" s="4"/>
       <c r="N45" s="4"/>
@@ -7615,10 +7934,10 @@
       <c r="P45" s="4"/>
       <c r="Q45" s="8"/>
       <c r="S45" s="4" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="T45" s="4" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="U45" s="4"/>
       <c r="V45" s="4"/>
@@ -7631,7 +7950,7 @@
         <v>269</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>7</v>
@@ -7640,7 +7959,7 @@
         <v>243</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="H46" s="6" t="s">
         <v>20</v>
@@ -7651,7 +7970,7 @@
         <v>277</v>
       </c>
       <c r="L46" s="5" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="M46" s="6" t="s">
         <v>7</v>
@@ -7660,7 +7979,7 @@
         <v>251</v>
       </c>
       <c r="O46" s="5" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>20</v>
@@ -7670,7 +7989,7 @@
         <v>280</v>
       </c>
       <c r="T46" s="5" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="U46" s="6" t="s">
         <v>7</v>
@@ -7679,7 +7998,7 @@
         <v>258</v>
       </c>
       <c r="W46" s="5" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="X46" s="6" t="s">
         <v>20</v>
@@ -7691,7 +8010,7 @@
         <v>270</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="E47" s="6" t="s">
         <v>8</v>
@@ -7700,7 +8019,7 @@
         <v>244</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="H47" s="6" t="s">
         <v>13</v>
@@ -7708,10 +8027,10 @@
       <c r="I47" s="7"/>
       <c r="J47" s="7"/>
       <c r="K47" s="5" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="L47" s="5" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="M47" s="6" t="s">
         <v>8</v>
@@ -7720,7 +8039,7 @@
         <v>252</v>
       </c>
       <c r="O47" s="5" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="P47" s="6" t="s">
         <v>13</v>
@@ -7730,16 +8049,16 @@
         <v>281</v>
       </c>
       <c r="T47" s="5" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="U47" s="6" t="s">
         <v>8</v>
       </c>
       <c r="V47" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="W47" s="5" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="X47" s="6" t="s">
         <v>13</v>
@@ -7751,7 +8070,7 @@
         <v>271</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="E48" s="10" t="s">
         <v>16</v>
@@ -7760,7 +8079,7 @@
         <v>245</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="H48" s="6" t="s">
         <v>14</v>
@@ -7768,10 +8087,10 @@
       <c r="I48" s="7"/>
       <c r="J48" s="7"/>
       <c r="K48" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L48" s="9" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="M48" s="10" t="s">
         <v>16</v>
@@ -7780,7 +8099,7 @@
         <v>253</v>
       </c>
       <c r="O48" s="5" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>14</v>
@@ -7790,16 +8109,16 @@
         <v>282</v>
       </c>
       <c r="T48" s="9" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="U48" s="10" t="s">
         <v>22</v>
       </c>
       <c r="V48" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="W48" s="5" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="X48" s="6" t="s">
         <v>14</v>
@@ -7811,7 +8130,7 @@
         <v>272</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>17</v>
@@ -7820,7 +8139,7 @@
         <v>246</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="H49" s="10" t="s">
         <v>12</v>
@@ -7828,10 +8147,10 @@
       <c r="I49" s="7"/>
       <c r="J49" s="7"/>
       <c r="K49" s="9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="L49" s="9" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="M49" s="10" t="s">
         <v>17</v>
@@ -7840,7 +8159,7 @@
         <v>254</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>12</v>
@@ -7850,16 +8169,16 @@
         <v>283</v>
       </c>
       <c r="T49" s="9" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="U49" s="10" t="s">
         <v>21</v>
       </c>
       <c r="V49" s="9" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="W49" s="9" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="X49" s="10" t="s">
         <v>12</v>
@@ -7871,7 +8190,7 @@
         <v>273</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>18</v>
@@ -7880,7 +8199,7 @@
         <v>247</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="H50" s="10" t="s">
         <v>11</v>
@@ -7888,10 +8207,10 @@
       <c r="I50" s="7"/>
       <c r="J50" s="7"/>
       <c r="K50" s="5" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="L50" s="5" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="M50" s="6" t="s">
         <v>18</v>
@@ -7900,7 +8219,7 @@
         <v>255</v>
       </c>
       <c r="O50" s="9" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="P50" s="10" t="s">
         <v>11</v>
@@ -7910,16 +8229,16 @@
         <v>284</v>
       </c>
       <c r="T50" s="5" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="U50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="V50" s="9" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="W50" s="9" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="X50" s="10" t="s">
         <v>11</v>
@@ -7931,26 +8250,26 @@
         <v>274</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E51" s="10"/>
       <c r="F51" s="9"/>
       <c r="G51" s="9" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="H51" s="10"/>
       <c r="I51" s="7"/>
       <c r="J51" s="7"/>
       <c r="K51" s="9" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="L51" s="9" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="M51" s="10"/>
       <c r="N51" s="9"/>
       <c r="O51" s="9" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="P51" s="10"/>
       <c r="Q51" s="8"/>
@@ -7958,14 +8277,14 @@
         <v>285</v>
       </c>
       <c r="T51" s="9" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="U51" s="10" t="s">
         <v>16</v>
       </c>
       <c r="V51" s="9"/>
       <c r="W51" s="9" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="X51" s="10"/>
     </row>
@@ -7975,7 +8294,7 @@
         <v>275</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E52" s="10" t="s">
         <v>22</v>
@@ -7984,7 +8303,7 @@
         <v>248</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="H52" s="10" t="s">
         <v>15</v>
@@ -7995,7 +8314,7 @@
         <v>278</v>
       </c>
       <c r="L52" s="9" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="M52" s="10" t="s">
         <v>22</v>
@@ -8004,7 +8323,7 @@
         <v>256</v>
       </c>
       <c r="O52" s="9" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="P52" s="10" t="s">
         <v>15</v>
@@ -8014,16 +8333,16 @@
         <v>286</v>
       </c>
       <c r="T52" s="9" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="U52" s="10" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="V52" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="W52" s="9" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="X52" s="10" t="s">
         <v>15</v>
@@ -8035,7 +8354,7 @@
         <v>276</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>21</v>
@@ -8044,7 +8363,7 @@
         <v>249</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="H53" s="10" t="s">
         <v>23</v>
@@ -8055,16 +8374,16 @@
         <v>279</v>
       </c>
       <c r="L53" s="9" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="M53" s="10" t="s">
         <v>21</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>23</v>
@@ -8074,16 +8393,16 @@
         <v>287</v>
       </c>
       <c r="T53" s="9" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="U53" s="10" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="V53" s="9" t="s">
         <v>259</v>
       </c>
       <c r="W53" s="9" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="X53" s="10" t="s">
         <v>23</v>
@@ -8095,7 +8414,7 @@
         <v>277</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>19</v>
@@ -8104,7 +8423,7 @@
         <v>250</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="H54" s="10" t="s">
         <v>24</v>
@@ -8115,7 +8434,7 @@
         <v>280</v>
       </c>
       <c r="L54" s="5" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="M54" s="6" t="s">
         <v>19</v>
@@ -8124,17 +8443,17 @@
         <v>257</v>
       </c>
       <c r="O54" s="9" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="P54" s="10" t="s">
         <v>24</v>
       </c>
       <c r="Q54" s="8"/>
       <c r="S54" s="5" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="T54" s="5" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="U54" s="6" t="s">
         <v>19</v>
@@ -8143,7 +8462,7 @@
         <v>260</v>
       </c>
       <c r="W54" s="9" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="X54" s="10" t="s">
         <v>24</v>
@@ -8152,11 +8471,11 @@
     <row r="55" spans="2:24">
       <c r="B55" s="8"/>
       <c r="C55" s="5" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F55" s="9"/>
       <c r="G55" s="9"/>
@@ -8168,18 +8487,18 @@
       </c>
       <c r="L55" s="5"/>
       <c r="M55" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="N55" s="9"/>
       <c r="O55" s="9"/>
       <c r="P55" s="10"/>
       <c r="Q55" s="8"/>
       <c r="S55" s="5" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="T55" s="5"/>
       <c r="U55" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="V55" s="9"/>
       <c r="W55" s="9"/>
@@ -8211,6 +8530,34 @@
     </row>
   </sheetData>
   <mergeCells count="44">
+    <mergeCell ref="V5:W5"/>
+    <mergeCell ref="V25:W25"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="U3:X3"/>
+    <mergeCell ref="U4:X4"/>
+    <mergeCell ref="M3:P3"/>
+    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="S5:T5"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="M4:P4"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="E4:H4"/>
     <mergeCell ref="N44:O44"/>
     <mergeCell ref="V44:W44"/>
     <mergeCell ref="S44:T44"/>
@@ -8227,34 +8574,6 @@
     <mergeCell ref="S25:T25"/>
     <mergeCell ref="M42:P42"/>
     <mergeCell ref="U42:X42"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="E42:H42"/>
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="S5:T5"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="M4:P4"/>
-    <mergeCell ref="V5:W5"/>
-    <mergeCell ref="V25:W25"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="U3:X3"/>
-    <mergeCell ref="U4:X4"/>
-    <mergeCell ref="M3:P3"/>
-    <mergeCell ref="S3:T3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8263,7 +8582,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EA47EA4-7B31-40FE-9AED-CE45ED8264B2}">
-  <dimension ref="B2:U49"/>
+  <dimension ref="B2:U124"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="4" max="4" width="20.625" customWidth="1"/>
@@ -8292,110 +8611,110 @@
       <c r="P2" s="14"/>
       <c r="Q2" s="14"/>
       <c r="S2" s="17" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="T2" s="18" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="U2" s="18" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="3" spans="2:21">
-      <c r="B3" s="79" t="s">
+      <c r="B3" s="83" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="80"/>
-      <c r="D3" s="79" t="s">
-        <v>779</v>
-      </c>
-      <c r="E3" s="81"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="80"/>
-      <c r="I3" s="79" t="s">
+      <c r="C3" s="84"/>
+      <c r="D3" s="83" t="s">
+        <v>777</v>
+      </c>
+      <c r="E3" s="85"/>
+      <c r="F3" s="85"/>
+      <c r="G3" s="84"/>
+      <c r="I3" s="83" t="s">
         <v>40</v>
       </c>
-      <c r="J3" s="80"/>
-      <c r="K3" s="78" t="s">
-        <v>302</v>
-      </c>
-      <c r="L3" s="78"/>
-      <c r="M3" s="78"/>
-      <c r="N3" s="78"/>
-      <c r="O3" s="78"/>
-      <c r="P3" s="78"/>
-      <c r="Q3" s="78"/>
+      <c r="J3" s="84"/>
+      <c r="K3" s="82" t="s">
+        <v>825</v>
+      </c>
+      <c r="L3" s="82"/>
+      <c r="M3" s="82"/>
+      <c r="N3" s="82"/>
+      <c r="O3" s="82"/>
+      <c r="P3" s="82"/>
+      <c r="Q3" s="82"/>
       <c r="S3" s="5">
         <v>0</v>
       </c>
       <c r="T3" s="6" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="U3" s="6"/>
     </row>
     <row r="4" spans="2:21">
-      <c r="B4" s="79" t="s">
+      <c r="B4" s="83" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="80"/>
-      <c r="D4" s="79"/>
-      <c r="E4" s="81"/>
-      <c r="F4" s="81"/>
-      <c r="G4" s="80"/>
-      <c r="I4" s="79" t="s">
+      <c r="C4" s="84"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="84"/>
+      <c r="I4" s="83" t="s">
         <v>39</v>
       </c>
-      <c r="J4" s="80"/>
-      <c r="K4" s="78"/>
-      <c r="L4" s="78"/>
-      <c r="M4" s="78"/>
-      <c r="N4" s="78"/>
-      <c r="O4" s="78"/>
-      <c r="P4" s="78"/>
-      <c r="Q4" s="78"/>
+      <c r="J4" s="84"/>
+      <c r="K4" s="82"/>
+      <c r="L4" s="82"/>
+      <c r="M4" s="82"/>
+      <c r="N4" s="82"/>
+      <c r="O4" s="82"/>
+      <c r="P4" s="82"/>
+      <c r="Q4" s="82"/>
       <c r="S4" s="5">
         <v>100</v>
       </c>
       <c r="T4" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="U4" s="6" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="5" spans="2:21">
-      <c r="B5" s="79" t="s">
+      <c r="B5" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="80"/>
+      <c r="C5" s="84"/>
       <c r="D5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="79" t="s">
+      <c r="E5" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="80"/>
+      <c r="F5" s="84"/>
       <c r="G5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="I5" s="79" t="s">
+      <c r="I5" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="80"/>
+      <c r="J5" s="84"/>
       <c r="K5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L5" s="79" t="s">
+      <c r="L5" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="M5" s="80"/>
+      <c r="M5" s="84"/>
       <c r="N5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="O5" s="79" t="s">
+      <c r="O5" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="P5" s="80"/>
+      <c r="P5" s="84"/>
       <c r="Q5" s="4" t="s">
         <v>10</v>
       </c>
@@ -8403,56 +8722,56 @@
         <v>200</v>
       </c>
       <c r="T5" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="U5" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="6" spans="2:21">
       <c r="B6" s="4" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="G6" s="4"/>
       <c r="I6" s="4" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="N6" s="4"/>
       <c r="O6" s="4" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="Q6" s="4"/>
       <c r="S6" s="5">
         <v>300</v>
       </c>
       <c r="T6" s="6" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="U6" s="6" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="7" spans="2:21">
@@ -8460,53 +8779,53 @@
         <v>295</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>7</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>20</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="K7" s="6" t="s">
         <v>7</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="N7" s="6" t="s">
         <v>20</v>
       </c>
       <c r="O7" s="16" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="P7" s="16"/>
       <c r="Q7" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="S7" s="5">
         <v>400</v>
       </c>
       <c r="T7" s="6" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="U7" s="6" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="8" spans="2:21">
@@ -8514,49 +8833,53 @@
         <v>296</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>290</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="G8" s="10" t="s">
         <v>13</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="L8" s="9" t="s">
         <v>301</v>
       </c>
       <c r="M8" s="9" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="N8" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="6"/>
+      <c r="O8" s="16" t="s">
+        <v>922</v>
+      </c>
       <c r="P8" s="6"/>
-      <c r="Q8" s="6"/>
+      <c r="Q8" s="6" t="s">
+        <v>923</v>
+      </c>
       <c r="S8" s="5">
         <v>500</v>
       </c>
       <c r="T8" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="U8" s="6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="9" spans="2:21">
@@ -8564,34 +8887,34 @@
         <v>297</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>289</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="G9" s="10" t="s">
         <v>14</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="M9" s="9" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="N9" s="10" t="s">
         <v>14</v>
@@ -8603,10 +8926,10 @@
         <v>600</v>
       </c>
       <c r="T9" s="6" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="U9" s="6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="10" spans="2:21">
@@ -8614,37 +8937,37 @@
         <v>298</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>300</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="G10" s="10" t="s">
         <v>288</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="K10" s="10" t="s">
         <v>17</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="M10" s="9" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="N10" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O10" s="6"/>
       <c r="P10" s="6"/>
@@ -8653,10 +8976,10 @@
         <v>601</v>
       </c>
       <c r="T10" s="6" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="U10" s="20" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="11" spans="2:21">
@@ -8664,34 +8987,34 @@
         <v>299</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="G11" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="K11" s="10" t="s">
         <v>18</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M11" s="9" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="N11" s="10" t="s">
         <v>15</v>
@@ -8703,18 +9026,18 @@
         <v>610</v>
       </c>
       <c r="T11" s="6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="U11" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="12" spans="2:21">
       <c r="B12" s="5" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>19</v>
@@ -8723,10 +9046,10 @@
       <c r="F12" s="5"/>
       <c r="G12" s="6"/>
       <c r="I12" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="K12" s="6"/>
       <c r="L12" s="5"/>
@@ -8739,10 +9062,10 @@
         <v>611</v>
       </c>
       <c r="T12" s="6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="U12" s="6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="13" spans="2:21">
@@ -8753,10 +9076,10 @@
       <c r="F13" s="5"/>
       <c r="G13" s="6"/>
       <c r="I13" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="K13" s="6" t="s">
         <v>19</v>
@@ -8771,10 +9094,10 @@
         <v>620</v>
       </c>
       <c r="T13" s="6" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="U13" s="6" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="14" spans="2:21">
@@ -8785,13 +9108,13 @@
       <c r="F14" s="5"/>
       <c r="G14" s="6"/>
       <c r="I14" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>708</v>
+      </c>
+      <c r="K14" s="6" t="s">
         <v>384</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>710</v>
-      </c>
-      <c r="K14" s="6" t="s">
-        <v>385</v>
       </c>
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
@@ -8803,10 +9126,10 @@
         <v>621</v>
       </c>
       <c r="T14" s="6" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="U14" s="6" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="15" spans="2:21">
@@ -8829,10 +9152,10 @@
         <v>630</v>
       </c>
       <c r="T15" s="6" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="16" spans="2:21">
@@ -8855,10 +9178,10 @@
         <v>631</v>
       </c>
       <c r="T16" s="6" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="U16" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="17" spans="2:21">
@@ -8875,10 +9198,10 @@
         <v>640</v>
       </c>
       <c r="T17" s="6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="U17" s="6" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="18" spans="2:21">
@@ -8895,10 +9218,10 @@
         <v>641</v>
       </c>
       <c r="T18" s="6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="U18" s="6" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="19" spans="2:21">
@@ -8921,23 +9244,23 @@
         <v>650</v>
       </c>
       <c r="T19" s="6" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="U19" s="6" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="20" spans="2:21">
-      <c r="B20" s="78" t="s">
+      <c r="B20" s="82" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="78"/>
-      <c r="D20" s="78" t="s">
-        <v>778</v>
-      </c>
-      <c r="E20" s="78"/>
-      <c r="F20" s="78"/>
-      <c r="G20" s="78"/>
+      <c r="C20" s="82"/>
+      <c r="D20" s="82" t="s">
+        <v>776</v>
+      </c>
+      <c r="E20" s="82"/>
+      <c r="F20" s="82"/>
+      <c r="G20" s="82"/>
       <c r="I20" s="5"/>
       <c r="J20" s="5"/>
       <c r="K20" s="6"/>
@@ -8951,21 +9274,21 @@
         <v>651</v>
       </c>
       <c r="T20" s="6" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="U20" s="6" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="21" spans="2:21">
-      <c r="B21" s="78" t="s">
+      <c r="B21" s="82" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="78"/>
-      <c r="D21" s="78"/>
-      <c r="E21" s="78"/>
-      <c r="F21" s="78"/>
-      <c r="G21" s="78"/>
+      <c r="C21" s="82"/>
+      <c r="D21" s="82"/>
+      <c r="E21" s="82"/>
+      <c r="F21" s="82"/>
+      <c r="G21" s="82"/>
       <c r="I21" s="5"/>
       <c r="J21" s="5"/>
       <c r="K21" s="6"/>
@@ -8979,24 +9302,24 @@
         <v>700</v>
       </c>
       <c r="T21" s="6" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="U21" s="6" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="22" spans="2:21">
-      <c r="B22" s="78" t="s">
+      <c r="B22" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="78"/>
+      <c r="C22" s="82"/>
       <c r="D22" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E22" s="78" t="s">
+      <c r="E22" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="F22" s="78"/>
+      <c r="F22" s="82"/>
       <c r="G22" s="4" t="s">
         <v>10</v>
       </c>
@@ -9013,18 +9336,18 @@
         <v>800</v>
       </c>
       <c r="T22" s="6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="U22" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="23" spans="2:21">
       <c r="B23" s="4" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
@@ -9043,10 +9366,10 @@
         <v>900</v>
       </c>
       <c r="T23" s="6" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="U23" s="6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="24" spans="2:21">
@@ -9054,7 +9377,7 @@
         <v>200</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>7</v>
@@ -9063,7 +9386,7 @@
         <v>216</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>20</v>
@@ -9081,10 +9404,10 @@
         <v>1000</v>
       </c>
       <c r="T24" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="U24" s="6" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="25" spans="2:21">
@@ -9092,7 +9415,7 @@
         <v>201</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>290</v>
@@ -9101,7 +9424,7 @@
         <v>217</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="G25" s="10" t="s">
         <v>13</v>
@@ -9110,18 +9433,18 @@
         <v>1100</v>
       </c>
       <c r="T25" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="U25" s="6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="26" spans="2:21">
       <c r="B26" s="9" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="D26" s="10" t="s">
         <v>289</v>
@@ -9130,7 +9453,7 @@
         <v>218</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="G26" s="10" t="s">
         <v>14</v>
@@ -9139,10 +9462,10 @@
         <v>1200</v>
       </c>
       <c r="T26" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="U26" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="27" spans="2:21">
@@ -9153,7 +9476,7 @@
         <v>219</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="G27" s="10" t="s">
         <v>288</v>
@@ -9171,18 +9494,18 @@
         <v>1300</v>
       </c>
       <c r="T27" s="6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="U27" s="6" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="28" spans="2:21">
       <c r="B28" s="5" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>18</v>
@@ -9190,56 +9513,56 @@
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
       <c r="G28" s="10"/>
-      <c r="I28" s="79" t="s">
+      <c r="I28" s="83" t="s">
         <v>40</v>
       </c>
-      <c r="J28" s="80"/>
-      <c r="K28" s="78" t="s">
-        <v>302</v>
-      </c>
-      <c r="L28" s="78"/>
-      <c r="M28" s="78"/>
-      <c r="N28" s="78"/>
-      <c r="O28" s="78"/>
-      <c r="P28" s="78"/>
-      <c r="Q28" s="78"/>
+      <c r="J28" s="84"/>
+      <c r="K28" s="82" t="s">
+        <v>897</v>
+      </c>
+      <c r="L28" s="82"/>
+      <c r="M28" s="82"/>
+      <c r="N28" s="82"/>
+      <c r="O28" s="82"/>
+      <c r="P28" s="82"/>
+      <c r="Q28" s="82"/>
       <c r="S28" s="5">
         <v>1400</v>
       </c>
       <c r="T28" s="6" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="U28" s="6"/>
     </row>
     <row r="29" spans="2:21">
       <c r="B29" s="9" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="D29" s="10"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="G29" s="10"/>
-      <c r="I29" s="79" t="s">
+      <c r="I29" s="83" t="s">
         <v>39</v>
       </c>
-      <c r="J29" s="80"/>
-      <c r="K29" s="78"/>
-      <c r="L29" s="78"/>
-      <c r="M29" s="78"/>
-      <c r="N29" s="78"/>
-      <c r="O29" s="78"/>
-      <c r="P29" s="78"/>
-      <c r="Q29" s="78"/>
+      <c r="J29" s="84"/>
+      <c r="K29" s="82"/>
+      <c r="L29" s="82"/>
+      <c r="M29" s="82"/>
+      <c r="N29" s="82"/>
+      <c r="O29" s="82"/>
+      <c r="P29" s="82"/>
+      <c r="Q29" s="82"/>
       <c r="S29" s="5">
         <v>1500</v>
       </c>
       <c r="T29" s="6" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="U29" s="6"/>
     </row>
@@ -9251,29 +9574,29 @@
         <v>220</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="G30" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I30" s="79" t="s">
+      <c r="I30" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="J30" s="80"/>
+      <c r="J30" s="84"/>
       <c r="K30" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L30" s="79" t="s">
+      <c r="L30" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="M30" s="80"/>
+      <c r="M30" s="84"/>
       <c r="N30" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="O30" s="79" t="s">
+      <c r="O30" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="P30" s="80"/>
+      <c r="P30" s="84"/>
       <c r="Q30" s="4" t="s">
         <v>10</v>
       </c>
@@ -9286,33 +9609,33 @@
       <c r="F31" s="9"/>
       <c r="G31" s="10"/>
       <c r="I31" s="4" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="M31" s="4" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="N31" s="4"/>
       <c r="O31" s="4" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="P31" s="4" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="Q31" s="4"/>
     </row>
     <row r="32" spans="2:21">
       <c r="B32" s="5" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>19</v>
@@ -9322,56 +9645,60 @@
       <c r="G32" s="10"/>
       <c r="I32" s="5"/>
       <c r="J32" s="5" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="K32" s="6" t="s">
         <v>7</v>
       </c>
       <c r="L32" s="5"/>
       <c r="M32" s="5" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="N32" s="6" t="s">
         <v>20</v>
       </c>
       <c r="O32" s="16" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="P32" s="16"/>
       <c r="Q32" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="33" spans="2:17">
       <c r="B33" s="5" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E33" s="9"/>
       <c r="F33" s="9"/>
       <c r="G33" s="10"/>
       <c r="I33" s="9"/>
       <c r="J33" s="9" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="L33" s="9"/>
       <c r="M33" s="9" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="N33" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="O33" s="6"/>
+      <c r="O33" s="16" t="s">
+        <v>924</v>
+      </c>
       <c r="P33" s="6"/>
-      <c r="Q33" s="6"/>
+      <c r="Q33" s="6" t="s">
+        <v>923</v>
+      </c>
     </row>
     <row r="34" spans="2:17">
       <c r="B34" s="11"/>
@@ -9382,14 +9709,14 @@
       <c r="G34" s="12"/>
       <c r="I34" s="9"/>
       <c r="J34" s="9" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="K34" s="10" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="L34" s="9"/>
       <c r="M34" s="9" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="N34" s="10" t="s">
         <v>14</v>
@@ -9401,17 +9728,17 @@
     <row r="35" spans="2:17">
       <c r="I35" s="9"/>
       <c r="J35" s="9" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="K35" s="10" t="s">
         <v>17</v>
       </c>
       <c r="L35" s="9"/>
       <c r="M35" s="9" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O35" s="6"/>
       <c r="P35" s="6"/>
@@ -9420,14 +9747,14 @@
     <row r="36" spans="2:17">
       <c r="I36" s="9"/>
       <c r="J36" s="9" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="K36" s="10" t="s">
         <v>18</v>
       </c>
       <c r="L36" s="9"/>
       <c r="M36" s="9" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="N36" s="10" t="s">
         <v>15</v>
@@ -9439,7 +9766,7 @@
     <row r="37" spans="2:17">
       <c r="I37" s="5"/>
       <c r="J37" s="5" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="K37" s="6"/>
       <c r="L37" s="5"/>
@@ -9452,7 +9779,7 @@
     <row r="38" spans="2:17">
       <c r="I38" s="5"/>
       <c r="J38" s="5" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>19</v>
@@ -9467,10 +9794,10 @@
     <row r="39" spans="2:17">
       <c r="I39" s="5"/>
       <c r="J39" s="5" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="K39" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L39" s="5"/>
       <c r="M39" s="5"/>
@@ -9589,15 +9916,1058 @@
       <c r="P49" s="12"/>
       <c r="Q49" s="12"/>
     </row>
+    <row r="52" spans="9:17">
+      <c r="I52" s="11"/>
+      <c r="J52" s="11"/>
+      <c r="K52" s="12"/>
+      <c r="L52" s="11"/>
+      <c r="M52" s="11"/>
+      <c r="N52" s="13"/>
+      <c r="O52" s="14"/>
+      <c r="P52" s="14"/>
+      <c r="Q52" s="14"/>
+    </row>
+    <row r="53" spans="9:17">
+      <c r="I53" s="83" t="s">
+        <v>40</v>
+      </c>
+      <c r="J53" s="84"/>
+      <c r="K53" s="82" t="s">
+        <v>898</v>
+      </c>
+      <c r="L53" s="82"/>
+      <c r="M53" s="82"/>
+      <c r="N53" s="82"/>
+      <c r="O53" s="82"/>
+      <c r="P53" s="82"/>
+      <c r="Q53" s="82"/>
+    </row>
+    <row r="54" spans="9:17">
+      <c r="I54" s="83" t="s">
+        <v>39</v>
+      </c>
+      <c r="J54" s="84"/>
+      <c r="K54" s="82"/>
+      <c r="L54" s="82"/>
+      <c r="M54" s="82"/>
+      <c r="N54" s="82"/>
+      <c r="O54" s="82"/>
+      <c r="P54" s="82"/>
+      <c r="Q54" s="82"/>
+    </row>
+    <row r="55" spans="9:17">
+      <c r="I55" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="J55" s="84"/>
+      <c r="K55" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L55" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="M55" s="84"/>
+      <c r="N55" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="O55" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="P55" s="84"/>
+      <c r="Q55" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56" spans="9:17">
+      <c r="I56" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="J56" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="K56" s="4"/>
+      <c r="L56" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="M56" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="N56" s="4"/>
+      <c r="O56" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="P56" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="Q56" s="4"/>
+    </row>
+    <row r="57" spans="9:17">
+      <c r="I57" s="5"/>
+      <c r="J57" s="5" t="s">
+        <v>901</v>
+      </c>
+      <c r="K57" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="L57" s="5"/>
+      <c r="M57" s="5" t="s">
+        <v>909</v>
+      </c>
+      <c r="N57" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="O57" s="16" t="s">
+        <v>930</v>
+      </c>
+      <c r="P57" s="16"/>
+      <c r="Q57" s="6" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="58" spans="9:17">
+      <c r="I58" s="9"/>
+      <c r="J58" s="9" t="s">
+        <v>902</v>
+      </c>
+      <c r="K58" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="L58" s="9"/>
+      <c r="M58" s="9" t="s">
+        <v>910</v>
+      </c>
+      <c r="N58" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="O58" s="16" t="s">
+        <v>925</v>
+      </c>
+      <c r="P58" s="6"/>
+      <c r="Q58" s="6" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="59" spans="9:17">
+      <c r="I59" s="9"/>
+      <c r="J59" s="9" t="s">
+        <v>903</v>
+      </c>
+      <c r="K59" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="L59" s="9"/>
+      <c r="M59" s="9" t="s">
+        <v>911</v>
+      </c>
+      <c r="N59" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="O59" s="6"/>
+      <c r="P59" s="6"/>
+      <c r="Q59" s="6"/>
+    </row>
+    <row r="60" spans="9:17">
+      <c r="I60" s="9"/>
+      <c r="J60" s="9" t="s">
+        <v>904</v>
+      </c>
+      <c r="K60" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="L60" s="9"/>
+      <c r="M60" s="9" t="s">
+        <v>912</v>
+      </c>
+      <c r="N60" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="O60" s="6"/>
+      <c r="P60" s="6"/>
+      <c r="Q60" s="6"/>
+    </row>
+    <row r="61" spans="9:17">
+      <c r="I61" s="9"/>
+      <c r="J61" s="9" t="s">
+        <v>905</v>
+      </c>
+      <c r="K61" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="L61" s="9"/>
+      <c r="M61" s="9" t="s">
+        <v>913</v>
+      </c>
+      <c r="N61" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="O61" s="6"/>
+      <c r="P61" s="6"/>
+      <c r="Q61" s="6"/>
+    </row>
+    <row r="62" spans="9:17">
+      <c r="I62" s="5"/>
+      <c r="J62" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="K62" s="6"/>
+      <c r="L62" s="5"/>
+      <c r="M62" s="5"/>
+      <c r="N62" s="6"/>
+      <c r="O62" s="6"/>
+      <c r="P62" s="6"/>
+      <c r="Q62" s="6"/>
+    </row>
+    <row r="63" spans="9:17">
+      <c r="I63" s="5"/>
+      <c r="J63" s="5" t="s">
+        <v>907</v>
+      </c>
+      <c r="K63" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L63" s="5"/>
+      <c r="M63" s="5"/>
+      <c r="N63" s="6"/>
+      <c r="O63" s="6"/>
+      <c r="P63" s="6"/>
+      <c r="Q63" s="6"/>
+    </row>
+    <row r="64" spans="9:17">
+      <c r="I64" s="5"/>
+      <c r="J64" s="5" t="s">
+        <v>908</v>
+      </c>
+      <c r="K64" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="L64" s="5"/>
+      <c r="M64" s="5"/>
+      <c r="N64" s="6"/>
+      <c r="O64" s="6"/>
+      <c r="P64" s="6"/>
+      <c r="Q64" s="6"/>
+    </row>
+    <row r="65" spans="9:17">
+      <c r="I65" s="5"/>
+      <c r="J65" s="5"/>
+      <c r="K65" s="6"/>
+      <c r="L65" s="5"/>
+      <c r="M65" s="5"/>
+      <c r="N65" s="6"/>
+      <c r="O65" s="6"/>
+      <c r="P65" s="6"/>
+      <c r="Q65" s="6"/>
+    </row>
+    <row r="66" spans="9:17">
+      <c r="I66" s="5"/>
+      <c r="J66" s="5"/>
+      <c r="K66" s="6"/>
+      <c r="L66" s="5"/>
+      <c r="M66" s="5"/>
+      <c r="N66" s="6"/>
+      <c r="O66" s="6"/>
+      <c r="P66" s="6"/>
+      <c r="Q66" s="6"/>
+    </row>
+    <row r="67" spans="9:17">
+      <c r="I67" s="5"/>
+      <c r="J67" s="5"/>
+      <c r="K67" s="6"/>
+      <c r="L67" s="5"/>
+      <c r="M67" s="5"/>
+      <c r="N67" s="6"/>
+      <c r="O67" s="6"/>
+      <c r="P67" s="6"/>
+      <c r="Q67" s="6"/>
+    </row>
+    <row r="68" spans="9:17">
+      <c r="I68" s="5"/>
+      <c r="J68" s="5"/>
+      <c r="K68" s="6"/>
+      <c r="L68" s="5"/>
+      <c r="M68" s="5"/>
+      <c r="N68" s="6"/>
+      <c r="O68" s="6"/>
+      <c r="P68" s="6"/>
+      <c r="Q68" s="6"/>
+    </row>
+    <row r="69" spans="9:17">
+      <c r="I69" s="5"/>
+      <c r="J69" s="5"/>
+      <c r="K69" s="6"/>
+      <c r="L69" s="5"/>
+      <c r="M69" s="5"/>
+      <c r="N69" s="6"/>
+      <c r="O69" s="6"/>
+      <c r="P69" s="6"/>
+      <c r="Q69" s="6"/>
+    </row>
+    <row r="70" spans="9:17">
+      <c r="I70" s="5"/>
+      <c r="J70" s="5"/>
+      <c r="K70" s="6"/>
+      <c r="L70" s="5"/>
+      <c r="M70" s="5"/>
+      <c r="N70" s="6"/>
+      <c r="O70" s="6"/>
+      <c r="P70" s="6"/>
+      <c r="Q70" s="6"/>
+    </row>
+    <row r="71" spans="9:17">
+      <c r="I71" s="5"/>
+      <c r="J71" s="5"/>
+      <c r="K71" s="6"/>
+      <c r="L71" s="5"/>
+      <c r="M71" s="5"/>
+      <c r="N71" s="6"/>
+      <c r="O71" s="6"/>
+      <c r="P71" s="6"/>
+      <c r="Q71" s="6"/>
+    </row>
+    <row r="72" spans="9:17">
+      <c r="I72" s="5"/>
+      <c r="J72" s="5"/>
+      <c r="K72" s="6"/>
+      <c r="L72" s="5"/>
+      <c r="M72" s="5"/>
+      <c r="N72" s="6"/>
+      <c r="O72" s="6"/>
+      <c r="P72" s="6"/>
+      <c r="Q72" s="6"/>
+    </row>
+    <row r="73" spans="9:17">
+      <c r="I73" s="5"/>
+      <c r="J73" s="5"/>
+      <c r="K73" s="6"/>
+      <c r="L73" s="5"/>
+      <c r="M73" s="5"/>
+      <c r="N73" s="6"/>
+      <c r="O73" s="6"/>
+      <c r="P73" s="6"/>
+      <c r="Q73" s="6"/>
+    </row>
+    <row r="74" spans="9:17">
+      <c r="I74" s="15"/>
+      <c r="J74" s="15"/>
+      <c r="K74" s="12"/>
+      <c r="L74" s="11"/>
+      <c r="M74" s="11"/>
+      <c r="N74" s="12"/>
+      <c r="O74" s="12"/>
+      <c r="P74" s="12"/>
+      <c r="Q74" s="12"/>
+    </row>
+    <row r="77" spans="9:17">
+      <c r="I77" s="11"/>
+      <c r="J77" s="11"/>
+      <c r="K77" s="12"/>
+      <c r="L77" s="11"/>
+      <c r="M77" s="11"/>
+      <c r="N77" s="13"/>
+      <c r="O77" s="14"/>
+      <c r="P77" s="14"/>
+      <c r="Q77" s="14"/>
+    </row>
+    <row r="78" spans="9:17">
+      <c r="I78" s="83" t="s">
+        <v>40</v>
+      </c>
+      <c r="J78" s="84"/>
+      <c r="K78" s="82" t="s">
+        <v>899</v>
+      </c>
+      <c r="L78" s="82"/>
+      <c r="M78" s="82"/>
+      <c r="N78" s="82"/>
+      <c r="O78" s="82"/>
+      <c r="P78" s="82"/>
+      <c r="Q78" s="82"/>
+    </row>
+    <row r="79" spans="9:17">
+      <c r="I79" s="83" t="s">
+        <v>39</v>
+      </c>
+      <c r="J79" s="84"/>
+      <c r="K79" s="82"/>
+      <c r="L79" s="82"/>
+      <c r="M79" s="82"/>
+      <c r="N79" s="82"/>
+      <c r="O79" s="82"/>
+      <c r="P79" s="82"/>
+      <c r="Q79" s="82"/>
+    </row>
+    <row r="80" spans="9:17">
+      <c r="I80" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="J80" s="84"/>
+      <c r="K80" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L80" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="M80" s="84"/>
+      <c r="N80" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="O80" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="P80" s="84"/>
+      <c r="Q80" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="81" spans="9:17">
+      <c r="I81" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="J81" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="K81" s="4"/>
+      <c r="L81" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="M81" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="N81" s="4"/>
+      <c r="O81" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="P81" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="Q81" s="4"/>
+    </row>
+    <row r="82" spans="9:17">
+      <c r="I82" s="5"/>
+      <c r="J82" s="5" t="s">
+        <v>914</v>
+      </c>
+      <c r="K82" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="L82" s="5"/>
+      <c r="M82" s="5" t="s">
+        <v>931</v>
+      </c>
+      <c r="N82" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="O82" s="16" t="s">
+        <v>929</v>
+      </c>
+      <c r="P82" s="16"/>
+      <c r="Q82" s="6" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="83" spans="9:17">
+      <c r="I83" s="9"/>
+      <c r="J83" s="9" t="s">
+        <v>915</v>
+      </c>
+      <c r="K83" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="L83" s="9"/>
+      <c r="M83" s="9" t="s">
+        <v>932</v>
+      </c>
+      <c r="N83" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="O83" s="16" t="s">
+        <v>926</v>
+      </c>
+      <c r="P83" s="6"/>
+      <c r="Q83" s="6" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="84" spans="9:17">
+      <c r="I84" s="9"/>
+      <c r="J84" s="9" t="s">
+        <v>916</v>
+      </c>
+      <c r="K84" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="L84" s="9"/>
+      <c r="M84" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="N84" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="O84" s="6"/>
+      <c r="P84" s="6"/>
+      <c r="Q84" s="6"/>
+    </row>
+    <row r="85" spans="9:17">
+      <c r="I85" s="9"/>
+      <c r="J85" s="9" t="s">
+        <v>917</v>
+      </c>
+      <c r="K85" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="L85" s="9"/>
+      <c r="M85" s="9" t="s">
+        <v>934</v>
+      </c>
+      <c r="N85" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="O85" s="6"/>
+      <c r="P85" s="6"/>
+      <c r="Q85" s="6"/>
+    </row>
+    <row r="86" spans="9:17">
+      <c r="I86" s="9"/>
+      <c r="J86" s="9" t="s">
+        <v>918</v>
+      </c>
+      <c r="K86" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="L86" s="9"/>
+      <c r="M86" s="9" t="s">
+        <v>935</v>
+      </c>
+      <c r="N86" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="O86" s="6"/>
+      <c r="P86" s="6"/>
+      <c r="Q86" s="6"/>
+    </row>
+    <row r="87" spans="9:17">
+      <c r="I87" s="5"/>
+      <c r="J87" s="5" t="s">
+        <v>919</v>
+      </c>
+      <c r="K87" s="6"/>
+      <c r="L87" s="5"/>
+      <c r="M87" s="5"/>
+      <c r="N87" s="6"/>
+      <c r="O87" s="6"/>
+      <c r="P87" s="6"/>
+      <c r="Q87" s="6"/>
+    </row>
+    <row r="88" spans="9:17">
+      <c r="I88" s="5"/>
+      <c r="J88" s="5" t="s">
+        <v>920</v>
+      </c>
+      <c r="K88" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L88" s="5"/>
+      <c r="M88" s="5"/>
+      <c r="N88" s="6"/>
+      <c r="O88" s="6"/>
+      <c r="P88" s="6"/>
+      <c r="Q88" s="6"/>
+    </row>
+    <row r="89" spans="9:17">
+      <c r="I89" s="5"/>
+      <c r="J89" s="5" t="s">
+        <v>921</v>
+      </c>
+      <c r="K89" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="L89" s="5"/>
+      <c r="M89" s="5"/>
+      <c r="N89" s="6"/>
+      <c r="O89" s="6"/>
+      <c r="P89" s="6"/>
+      <c r="Q89" s="6"/>
+    </row>
+    <row r="90" spans="9:17">
+      <c r="I90" s="5"/>
+      <c r="J90" s="5"/>
+      <c r="K90" s="6"/>
+      <c r="L90" s="5"/>
+      <c r="M90" s="5"/>
+      <c r="N90" s="6"/>
+      <c r="O90" s="6"/>
+      <c r="P90" s="6"/>
+      <c r="Q90" s="6"/>
+    </row>
+    <row r="91" spans="9:17">
+      <c r="I91" s="5"/>
+      <c r="J91" s="5"/>
+      <c r="K91" s="6"/>
+      <c r="L91" s="5"/>
+      <c r="M91" s="5"/>
+      <c r="N91" s="6"/>
+      <c r="O91" s="6"/>
+      <c r="P91" s="6"/>
+      <c r="Q91" s="6"/>
+    </row>
+    <row r="92" spans="9:17">
+      <c r="I92" s="5"/>
+      <c r="J92" s="5"/>
+      <c r="K92" s="6"/>
+      <c r="L92" s="5"/>
+      <c r="M92" s="5"/>
+      <c r="N92" s="6"/>
+      <c r="O92" s="6"/>
+      <c r="P92" s="6"/>
+      <c r="Q92" s="6"/>
+    </row>
+    <row r="93" spans="9:17">
+      <c r="I93" s="5"/>
+      <c r="J93" s="5"/>
+      <c r="K93" s="6"/>
+      <c r="L93" s="5"/>
+      <c r="M93" s="5"/>
+      <c r="N93" s="6"/>
+      <c r="O93" s="6"/>
+      <c r="P93" s="6"/>
+      <c r="Q93" s="6"/>
+    </row>
+    <row r="94" spans="9:17">
+      <c r="I94" s="5"/>
+      <c r="J94" s="5"/>
+      <c r="K94" s="6"/>
+      <c r="L94" s="5"/>
+      <c r="M94" s="5"/>
+      <c r="N94" s="6"/>
+      <c r="O94" s="6"/>
+      <c r="P94" s="6"/>
+      <c r="Q94" s="6"/>
+    </row>
+    <row r="95" spans="9:17">
+      <c r="I95" s="5"/>
+      <c r="J95" s="5"/>
+      <c r="K95" s="6"/>
+      <c r="L95" s="5"/>
+      <c r="M95" s="5"/>
+      <c r="N95" s="6"/>
+      <c r="O95" s="6"/>
+      <c r="P95" s="6"/>
+      <c r="Q95" s="6"/>
+    </row>
+    <row r="96" spans="9:17">
+      <c r="I96" s="5"/>
+      <c r="J96" s="5"/>
+      <c r="K96" s="6"/>
+      <c r="L96" s="5"/>
+      <c r="M96" s="5"/>
+      <c r="N96" s="6"/>
+      <c r="O96" s="6"/>
+      <c r="P96" s="6"/>
+      <c r="Q96" s="6"/>
+    </row>
+    <row r="97" spans="9:17">
+      <c r="I97" s="5"/>
+      <c r="J97" s="5"/>
+      <c r="K97" s="6"/>
+      <c r="L97" s="5"/>
+      <c r="M97" s="5"/>
+      <c r="N97" s="6"/>
+      <c r="O97" s="6"/>
+      <c r="P97" s="6"/>
+      <c r="Q97" s="6"/>
+    </row>
+    <row r="98" spans="9:17">
+      <c r="I98" s="5"/>
+      <c r="J98" s="5"/>
+      <c r="K98" s="6"/>
+      <c r="L98" s="5"/>
+      <c r="M98" s="5"/>
+      <c r="N98" s="6"/>
+      <c r="O98" s="6"/>
+      <c r="P98" s="6"/>
+      <c r="Q98" s="6"/>
+    </row>
+    <row r="99" spans="9:17">
+      <c r="I99" s="15"/>
+      <c r="J99" s="15"/>
+      <c r="K99" s="12"/>
+      <c r="L99" s="11"/>
+      <c r="M99" s="11"/>
+      <c r="N99" s="12"/>
+      <c r="O99" s="12"/>
+      <c r="P99" s="12"/>
+      <c r="Q99" s="12"/>
+    </row>
+    <row r="102" spans="9:17">
+      <c r="I102" s="11"/>
+      <c r="J102" s="11"/>
+      <c r="K102" s="12"/>
+      <c r="L102" s="11"/>
+      <c r="M102" s="11"/>
+      <c r="N102" s="13"/>
+      <c r="O102" s="14"/>
+      <c r="P102" s="14"/>
+      <c r="Q102" s="14"/>
+    </row>
+    <row r="103" spans="9:17">
+      <c r="I103" s="83" t="s">
+        <v>40</v>
+      </c>
+      <c r="J103" s="84"/>
+      <c r="K103" s="82" t="s">
+        <v>900</v>
+      </c>
+      <c r="L103" s="82"/>
+      <c r="M103" s="82"/>
+      <c r="N103" s="82"/>
+      <c r="O103" s="82"/>
+      <c r="P103" s="82"/>
+      <c r="Q103" s="82"/>
+    </row>
+    <row r="104" spans="9:17">
+      <c r="I104" s="83" t="s">
+        <v>39</v>
+      </c>
+      <c r="J104" s="84"/>
+      <c r="K104" s="82"/>
+      <c r="L104" s="82"/>
+      <c r="M104" s="82"/>
+      <c r="N104" s="82"/>
+      <c r="O104" s="82"/>
+      <c r="P104" s="82"/>
+      <c r="Q104" s="82"/>
+    </row>
+    <row r="105" spans="9:17">
+      <c r="I105" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="J105" s="84"/>
+      <c r="K105" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L105" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="M105" s="84"/>
+      <c r="N105" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="O105" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="P105" s="84"/>
+      <c r="Q105" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="106" spans="9:17">
+      <c r="I106" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="J106" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="K106" s="4"/>
+      <c r="L106" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="M106" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="N106" s="4"/>
+      <c r="O106" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="P106" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="Q106" s="4"/>
+    </row>
+    <row r="107" spans="9:17">
+      <c r="I107" s="5"/>
+      <c r="J107" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="K107" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="L107" s="5"/>
+      <c r="M107" s="5" t="s">
+        <v>944</v>
+      </c>
+      <c r="N107" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="O107" s="16" t="s">
+        <v>928</v>
+      </c>
+      <c r="P107" s="16"/>
+      <c r="Q107" s="6" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="108" spans="9:17">
+      <c r="I108" s="9"/>
+      <c r="J108" s="9" t="s">
+        <v>937</v>
+      </c>
+      <c r="K108" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="L108" s="9"/>
+      <c r="M108" s="9" t="s">
+        <v>945</v>
+      </c>
+      <c r="N108" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="O108" s="16" t="s">
+        <v>927</v>
+      </c>
+      <c r="P108" s="6"/>
+      <c r="Q108" s="6" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="109" spans="9:17">
+      <c r="I109" s="9"/>
+      <c r="J109" s="9" t="s">
+        <v>938</v>
+      </c>
+      <c r="K109" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="L109" s="9"/>
+      <c r="M109" s="9" t="s">
+        <v>946</v>
+      </c>
+      <c r="N109" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="O109" s="6"/>
+      <c r="P109" s="6"/>
+      <c r="Q109" s="6"/>
+    </row>
+    <row r="110" spans="9:17">
+      <c r="I110" s="9"/>
+      <c r="J110" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="K110" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="L110" s="9"/>
+      <c r="M110" s="9" t="s">
+        <v>947</v>
+      </c>
+      <c r="N110" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="O110" s="6"/>
+      <c r="P110" s="6"/>
+      <c r="Q110" s="6"/>
+    </row>
+    <row r="111" spans="9:17">
+      <c r="I111" s="9"/>
+      <c r="J111" s="9" t="s">
+        <v>940</v>
+      </c>
+      <c r="K111" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="L111" s="9"/>
+      <c r="M111" s="9" t="s">
+        <v>948</v>
+      </c>
+      <c r="N111" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="O111" s="6"/>
+      <c r="P111" s="6"/>
+      <c r="Q111" s="6"/>
+    </row>
+    <row r="112" spans="9:17">
+      <c r="I112" s="5"/>
+      <c r="J112" s="5" t="s">
+        <v>941</v>
+      </c>
+      <c r="K112" s="6"/>
+      <c r="L112" s="5"/>
+      <c r="M112" s="5"/>
+      <c r="N112" s="6"/>
+      <c r="O112" s="6"/>
+      <c r="P112" s="6"/>
+      <c r="Q112" s="6"/>
+    </row>
+    <row r="113" spans="9:17">
+      <c r="I113" s="5"/>
+      <c r="J113" s="5" t="s">
+        <v>942</v>
+      </c>
+      <c r="K113" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L113" s="5"/>
+      <c r="M113" s="5"/>
+      <c r="N113" s="6"/>
+      <c r="O113" s="6"/>
+      <c r="P113" s="6"/>
+      <c r="Q113" s="6"/>
+    </row>
+    <row r="114" spans="9:17">
+      <c r="I114" s="5"/>
+      <c r="J114" s="5" t="s">
+        <v>943</v>
+      </c>
+      <c r="K114" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="L114" s="5"/>
+      <c r="M114" s="5"/>
+      <c r="N114" s="6"/>
+      <c r="O114" s="6"/>
+      <c r="P114" s="6"/>
+      <c r="Q114" s="6"/>
+    </row>
+    <row r="115" spans="9:17">
+      <c r="I115" s="5"/>
+      <c r="J115" s="5"/>
+      <c r="K115" s="6"/>
+      <c r="L115" s="5"/>
+      <c r="M115" s="5"/>
+      <c r="N115" s="6"/>
+      <c r="O115" s="6"/>
+      <c r="P115" s="6"/>
+      <c r="Q115" s="6"/>
+    </row>
+    <row r="116" spans="9:17">
+      <c r="I116" s="5"/>
+      <c r="J116" s="5"/>
+      <c r="K116" s="6"/>
+      <c r="L116" s="5"/>
+      <c r="M116" s="5"/>
+      <c r="N116" s="6"/>
+      <c r="O116" s="6"/>
+      <c r="P116" s="6"/>
+      <c r="Q116" s="6"/>
+    </row>
+    <row r="117" spans="9:17">
+      <c r="I117" s="5"/>
+      <c r="J117" s="5"/>
+      <c r="K117" s="6"/>
+      <c r="L117" s="5"/>
+      <c r="M117" s="5"/>
+      <c r="N117" s="6"/>
+      <c r="O117" s="6"/>
+      <c r="P117" s="6"/>
+      <c r="Q117" s="6"/>
+    </row>
+    <row r="118" spans="9:17">
+      <c r="I118" s="5"/>
+      <c r="J118" s="5"/>
+      <c r="K118" s="6"/>
+      <c r="L118" s="5"/>
+      <c r="M118" s="5"/>
+      <c r="N118" s="6"/>
+      <c r="O118" s="6"/>
+      <c r="P118" s="6"/>
+      <c r="Q118" s="6"/>
+    </row>
+    <row r="119" spans="9:17">
+      <c r="I119" s="5"/>
+      <c r="J119" s="5"/>
+      <c r="K119" s="6"/>
+      <c r="L119" s="5"/>
+      <c r="M119" s="5"/>
+      <c r="N119" s="6"/>
+      <c r="O119" s="6"/>
+      <c r="P119" s="6"/>
+      <c r="Q119" s="6"/>
+    </row>
+    <row r="120" spans="9:17">
+      <c r="I120" s="5"/>
+      <c r="J120" s="5"/>
+      <c r="K120" s="6"/>
+      <c r="L120" s="5"/>
+      <c r="M120" s="5"/>
+      <c r="N120" s="6"/>
+      <c r="O120" s="6"/>
+      <c r="P120" s="6"/>
+      <c r="Q120" s="6"/>
+    </row>
+    <row r="121" spans="9:17">
+      <c r="I121" s="5"/>
+      <c r="J121" s="5"/>
+      <c r="K121" s="6"/>
+      <c r="L121" s="5"/>
+      <c r="M121" s="5"/>
+      <c r="N121" s="6"/>
+      <c r="O121" s="6"/>
+      <c r="P121" s="6"/>
+      <c r="Q121" s="6"/>
+    </row>
+    <row r="122" spans="9:17">
+      <c r="I122" s="5"/>
+      <c r="J122" s="5"/>
+      <c r="K122" s="6"/>
+      <c r="L122" s="5"/>
+      <c r="M122" s="5"/>
+      <c r="N122" s="6"/>
+      <c r="O122" s="6"/>
+      <c r="P122" s="6"/>
+      <c r="Q122" s="6"/>
+    </row>
+    <row r="123" spans="9:17">
+      <c r="I123" s="5"/>
+      <c r="J123" s="5"/>
+      <c r="K123" s="6"/>
+      <c r="L123" s="5"/>
+      <c r="M123" s="5"/>
+      <c r="N123" s="6"/>
+      <c r="O123" s="6"/>
+      <c r="P123" s="6"/>
+      <c r="Q123" s="6"/>
+    </row>
+    <row r="124" spans="9:17">
+      <c r="I124" s="15"/>
+      <c r="J124" s="15"/>
+      <c r="K124" s="12"/>
+      <c r="L124" s="11"/>
+      <c r="M124" s="11"/>
+      <c r="N124" s="12"/>
+      <c r="O124" s="12"/>
+      <c r="P124" s="12"/>
+      <c r="Q124" s="12"/>
+    </row>
   </sheetData>
-  <mergeCells count="26">
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="K28:Q28"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="K29:Q29"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="L30:M30"/>
-    <mergeCell ref="O30:P30"/>
+  <mergeCells count="47">
+    <mergeCell ref="I103:J103"/>
+    <mergeCell ref="K103:Q103"/>
+    <mergeCell ref="I104:J104"/>
+    <mergeCell ref="K104:Q104"/>
+    <mergeCell ref="I105:J105"/>
+    <mergeCell ref="L105:M105"/>
+    <mergeCell ref="O105:P105"/>
+    <mergeCell ref="I78:J78"/>
+    <mergeCell ref="K78:Q78"/>
+    <mergeCell ref="I79:J79"/>
+    <mergeCell ref="K79:Q79"/>
+    <mergeCell ref="I80:J80"/>
+    <mergeCell ref="L80:M80"/>
+    <mergeCell ref="O80:P80"/>
+    <mergeCell ref="I53:J53"/>
+    <mergeCell ref="K53:Q53"/>
+    <mergeCell ref="I54:J54"/>
+    <mergeCell ref="K54:Q54"/>
+    <mergeCell ref="I55:J55"/>
+    <mergeCell ref="L55:M55"/>
+    <mergeCell ref="O55:P55"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:G20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="E22:F22"/>
     <mergeCell ref="O5:P5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="B5:C5"/>
@@ -9611,12 +10981,13 @@
     <mergeCell ref="K4:Q4"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:G20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="K28:Q28"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="K29:Q29"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="O30:P30"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9634,71 +11005,71 @@
   <sheetData>
     <row r="3" spans="4:20">
       <c r="E3" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="F3" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="N3" t="s">
+        <v>867</v>
+      </c>
+      <c r="O3" s="33" t="s">
+        <v>881</v>
+      </c>
+      <c r="P3" t="s">
         <v>869</v>
       </c>
-      <c r="O3" s="33" t="s">
-        <v>883</v>
-      </c>
-      <c r="P3" t="s">
-        <v>871</v>
-      </c>
       <c r="Q3" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="4" spans="4:20">
       <c r="E4" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="F4" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="N4" t="s">
+        <v>868</v>
+      </c>
+      <c r="O4" s="33" t="s">
+        <v>884</v>
+      </c>
+      <c r="P4" t="s">
         <v>870</v>
       </c>
-      <c r="O4" s="33" t="s">
-        <v>886</v>
-      </c>
-      <c r="P4" t="s">
-        <v>872</v>
-      </c>
       <c r="Q4" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
     </row>
     <row r="6" spans="4:20" ht="17.25" thickBot="1">
-      <c r="D6" s="68" t="s">
-        <v>357</v>
-      </c>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
-      <c r="I6" s="68" t="s">
-        <v>718</v>
-      </c>
-      <c r="J6" s="68"/>
-      <c r="K6" s="68"/>
-      <c r="M6" s="68" t="s">
-        <v>359</v>
-      </c>
-      <c r="N6" s="68"/>
-      <c r="O6" s="68"/>
-      <c r="P6" s="68"/>
-      <c r="R6" s="68" t="s">
-        <v>719</v>
-      </c>
-      <c r="S6" s="68"/>
-      <c r="T6" s="68"/>
+      <c r="D6" s="34" t="s">
+        <v>356</v>
+      </c>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="34"/>
+      <c r="I6" s="34" t="s">
+        <v>716</v>
+      </c>
+      <c r="J6" s="34"/>
+      <c r="K6" s="34"/>
+      <c r="M6" s="34" t="s">
+        <v>358</v>
+      </c>
+      <c r="N6" s="34"/>
+      <c r="O6" s="34"/>
+      <c r="P6" s="34"/>
+      <c r="R6" s="34" t="s">
+        <v>717</v>
+      </c>
+      <c r="S6" s="34"/>
+      <c r="T6" s="34"/>
     </row>
     <row r="7" spans="4:20" ht="16.5" customHeight="1">
-      <c r="D7" s="34" t="s">
-        <v>879</v>
+      <c r="D7" s="65" t="s">
+        <v>877</v>
       </c>
       <c r="E7" s="21"/>
       <c r="F7" s="21"/>
@@ -9706,213 +11077,213 @@
       <c r="I7" s="26"/>
       <c r="J7" s="21"/>
       <c r="K7" s="22"/>
-      <c r="M7" s="34" t="s">
-        <v>889</v>
+      <c r="M7" s="65" t="s">
+        <v>887</v>
       </c>
       <c r="N7" s="21"/>
       <c r="O7" s="21"/>
-      <c r="P7" s="34" t="s">
-        <v>884</v>
+      <c r="P7" s="65" t="s">
+        <v>882</v>
       </c>
       <c r="R7" s="26"/>
       <c r="S7" s="21"/>
       <c r="T7" s="22"/>
     </row>
     <row r="8" spans="4:20">
-      <c r="D8" s="35"/>
+      <c r="D8" s="66"/>
       <c r="G8" s="23"/>
       <c r="I8" s="24"/>
       <c r="K8" s="23"/>
-      <c r="M8" s="35"/>
-      <c r="P8" s="35"/>
+      <c r="M8" s="66"/>
+      <c r="P8" s="66"/>
       <c r="R8" s="24"/>
       <c r="T8" s="23"/>
     </row>
     <row r="9" spans="4:20" ht="16.5" customHeight="1">
-      <c r="D9" s="35"/>
-      <c r="F9" s="46" t="s">
-        <v>717</v>
+      <c r="D9" s="66"/>
+      <c r="F9" s="43" t="s">
+        <v>715</v>
       </c>
       <c r="G9" s="23"/>
       <c r="I9" s="24"/>
-      <c r="J9" s="46" t="s">
-        <v>717</v>
+      <c r="J9" s="43" t="s">
+        <v>715</v>
       </c>
       <c r="K9" s="23"/>
-      <c r="M9" s="35"/>
-      <c r="O9" s="84" t="s">
-        <v>717</v>
-      </c>
-      <c r="P9" s="35"/>
+      <c r="M9" s="66"/>
+      <c r="O9" s="68" t="s">
+        <v>715</v>
+      </c>
+      <c r="P9" s="66"/>
       <c r="R9" s="24"/>
-      <c r="S9" s="46" t="s">
-        <v>717</v>
+      <c r="S9" s="43" t="s">
+        <v>715</v>
       </c>
       <c r="T9" s="23"/>
     </row>
     <row r="10" spans="4:20">
-      <c r="D10" s="35"/>
-      <c r="F10" s="47"/>
+      <c r="D10" s="66"/>
+      <c r="F10" s="54"/>
       <c r="G10" s="23"/>
       <c r="I10" s="24"/>
-      <c r="J10" s="47"/>
+      <c r="J10" s="54"/>
       <c r="K10" s="23"/>
-      <c r="M10" s="35"/>
-      <c r="O10" s="85"/>
-      <c r="P10" s="35"/>
+      <c r="M10" s="66"/>
+      <c r="O10" s="69"/>
+      <c r="P10" s="66"/>
       <c r="R10" s="24"/>
-      <c r="S10" s="47"/>
+      <c r="S10" s="54"/>
       <c r="T10" s="23"/>
     </row>
     <row r="11" spans="4:20">
-      <c r="D11" s="35"/>
-      <c r="E11" s="48" t="s">
-        <v>868</v>
+      <c r="D11" s="66"/>
+      <c r="E11" s="41" t="s">
+        <v>866</v>
       </c>
       <c r="G11" s="23"/>
       <c r="I11" s="24"/>
-      <c r="J11" s="48" t="s">
-        <v>876</v>
+      <c r="J11" s="41" t="s">
+        <v>874</v>
       </c>
       <c r="K11" s="23"/>
-      <c r="M11" s="35"/>
-      <c r="N11" s="48" t="s">
-        <v>885</v>
-      </c>
-      <c r="O11" s="82" t="s">
-        <v>716</v>
-      </c>
-      <c r="P11" s="35"/>
+      <c r="M11" s="66"/>
+      <c r="N11" s="41" t="s">
+        <v>883</v>
+      </c>
+      <c r="O11" s="80" t="s">
+        <v>714</v>
+      </c>
+      <c r="P11" s="66"/>
       <c r="R11" s="24"/>
-      <c r="S11" s="48" t="s">
-        <v>876</v>
+      <c r="S11" s="41" t="s">
+        <v>874</v>
       </c>
       <c r="T11" s="23"/>
     </row>
     <row r="12" spans="4:20">
-      <c r="D12" s="35"/>
-      <c r="E12" s="49"/>
+      <c r="D12" s="66"/>
+      <c r="E12" s="70"/>
       <c r="G12" s="23"/>
       <c r="I12" s="24"/>
-      <c r="J12" s="59"/>
+      <c r="J12" s="42"/>
       <c r="K12" s="23"/>
-      <c r="M12" s="35"/>
-      <c r="N12" s="49"/>
-      <c r="O12" s="83"/>
-      <c r="P12" s="35"/>
+      <c r="M12" s="66"/>
+      <c r="N12" s="70"/>
+      <c r="O12" s="81"/>
+      <c r="P12" s="66"/>
       <c r="R12" s="24"/>
-      <c r="S12" s="59"/>
+      <c r="S12" s="42"/>
       <c r="T12" s="23"/>
     </row>
     <row r="13" spans="4:20">
-      <c r="D13" s="36"/>
+      <c r="D13" s="67"/>
       <c r="G13" s="23"/>
       <c r="I13" s="24"/>
       <c r="K13" s="23"/>
-      <c r="M13" s="36"/>
-      <c r="P13" s="36"/>
+      <c r="M13" s="67"/>
+      <c r="P13" s="67"/>
       <c r="R13" s="24"/>
       <c r="T13" s="23"/>
     </row>
     <row r="14" spans="4:20" ht="16.5" customHeight="1">
       <c r="D14" s="24"/>
-      <c r="E14" s="37" t="s">
-        <v>881</v>
-      </c>
-      <c r="F14" s="38"/>
-      <c r="G14" s="39"/>
-      <c r="I14" s="50" t="s">
-        <v>892</v>
-      </c>
-      <c r="J14" s="51"/>
-      <c r="K14" s="52"/>
+      <c r="E14" s="71" t="s">
+        <v>879</v>
+      </c>
+      <c r="F14" s="72"/>
+      <c r="G14" s="73"/>
+      <c r="I14" s="55" t="s">
+        <v>890</v>
+      </c>
+      <c r="J14" s="56"/>
+      <c r="K14" s="61"/>
       <c r="M14" s="24"/>
-      <c r="N14" s="37" t="s">
-        <v>887</v>
-      </c>
-      <c r="O14" s="38"/>
-      <c r="P14" s="39"/>
-      <c r="R14" s="50" t="s">
-        <v>891</v>
-      </c>
-      <c r="S14" s="51"/>
-      <c r="T14" s="52"/>
+      <c r="N14" s="71" t="s">
+        <v>885</v>
+      </c>
+      <c r="O14" s="72"/>
+      <c r="P14" s="73"/>
+      <c r="R14" s="55" t="s">
+        <v>889</v>
+      </c>
+      <c r="S14" s="56"/>
+      <c r="T14" s="61"/>
     </row>
     <row r="15" spans="4:20">
       <c r="D15" s="24"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="42"/>
-      <c r="I15" s="53"/>
-      <c r="J15" s="54"/>
-      <c r="K15" s="55"/>
+      <c r="E15" s="74"/>
+      <c r="F15" s="75"/>
+      <c r="G15" s="76"/>
+      <c r="I15" s="48"/>
+      <c r="J15" s="49"/>
+      <c r="K15" s="50"/>
       <c r="M15" s="24"/>
-      <c r="N15" s="40"/>
-      <c r="O15" s="41"/>
-      <c r="P15" s="42"/>
-      <c r="R15" s="53"/>
-      <c r="S15" s="54"/>
-      <c r="T15" s="55"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="75"/>
+      <c r="P15" s="76"/>
+      <c r="R15" s="48"/>
+      <c r="S15" s="49"/>
+      <c r="T15" s="50"/>
     </row>
     <row r="16" spans="4:20">
       <c r="D16" s="24"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="42"/>
-      <c r="I16" s="53"/>
-      <c r="J16" s="54"/>
-      <c r="K16" s="55"/>
+      <c r="E16" s="74"/>
+      <c r="F16" s="75"/>
+      <c r="G16" s="76"/>
+      <c r="I16" s="48"/>
+      <c r="J16" s="49"/>
+      <c r="K16" s="50"/>
       <c r="M16" s="24"/>
-      <c r="N16" s="40"/>
-      <c r="O16" s="41"/>
-      <c r="P16" s="42"/>
-      <c r="R16" s="53"/>
-      <c r="S16" s="54"/>
-      <c r="T16" s="55"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="75"/>
+      <c r="P16" s="76"/>
+      <c r="R16" s="48"/>
+      <c r="S16" s="49"/>
+      <c r="T16" s="50"/>
     </row>
     <row r="17" spans="4:20" ht="17.25" thickBot="1">
       <c r="D17" s="25"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="45"/>
-      <c r="I17" s="56"/>
-      <c r="J17" s="57"/>
-      <c r="K17" s="58"/>
+      <c r="E17" s="77"/>
+      <c r="F17" s="78"/>
+      <c r="G17" s="79"/>
+      <c r="I17" s="62"/>
+      <c r="J17" s="63"/>
+      <c r="K17" s="64"/>
       <c r="M17" s="25"/>
-      <c r="N17" s="43"/>
-      <c r="O17" s="44"/>
-      <c r="P17" s="45"/>
-      <c r="R17" s="56"/>
-      <c r="S17" s="57"/>
-      <c r="T17" s="58"/>
+      <c r="N17" s="77"/>
+      <c r="O17" s="78"/>
+      <c r="P17" s="79"/>
+      <c r="R17" s="62"/>
+      <c r="S17" s="63"/>
+      <c r="T17" s="64"/>
     </row>
     <row r="19" spans="4:20" ht="17.25" thickBot="1">
-      <c r="D19" s="68" t="s">
-        <v>368</v>
-      </c>
-      <c r="E19" s="68"/>
-      <c r="F19" s="68"/>
-      <c r="H19" s="68" t="s">
+      <c r="D19" s="34" t="s">
         <v>367</v>
       </c>
-      <c r="I19" s="68"/>
-      <c r="J19" s="68"/>
-      <c r="K19" s="68"/>
-      <c r="R19" s="68" t="s">
-        <v>720</v>
-      </c>
-      <c r="S19" s="68"/>
-      <c r="T19" s="68"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="H19" s="34" t="s">
+        <v>366</v>
+      </c>
+      <c r="I19" s="34"/>
+      <c r="J19" s="34"/>
+      <c r="K19" s="34"/>
+      <c r="R19" s="34" t="s">
+        <v>718</v>
+      </c>
+      <c r="S19" s="34"/>
+      <c r="T19" s="34"/>
     </row>
     <row r="20" spans="4:20">
-      <c r="D20" s="74" t="s">
-        <v>898</v>
-      </c>
-      <c r="E20" s="75"/>
-      <c r="F20" s="76"/>
+      <c r="D20" s="45" t="s">
+        <v>896</v>
+      </c>
+      <c r="E20" s="46"/>
+      <c r="F20" s="47"/>
       <c r="H20" s="26"/>
-      <c r="I20" s="65" t="s">
-        <v>717</v>
+      <c r="I20" s="60" t="s">
+        <v>715</v>
       </c>
       <c r="J20" s="21"/>
       <c r="K20" s="22"/>
@@ -9920,56 +11291,56 @@
       <c r="N20" s="21"/>
       <c r="O20" s="21"/>
       <c r="P20" s="22"/>
-      <c r="R20" s="74" t="s">
-        <v>721</v>
-      </c>
-      <c r="S20" s="75"/>
-      <c r="T20" s="76"/>
+      <c r="R20" s="45" t="s">
+        <v>719</v>
+      </c>
+      <c r="S20" s="46"/>
+      <c r="T20" s="47"/>
     </row>
     <row r="21" spans="4:20">
-      <c r="D21" s="53"/>
-      <c r="E21" s="54"/>
-      <c r="F21" s="55"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="49"/>
+      <c r="F21" s="50"/>
       <c r="H21" s="24"/>
-      <c r="I21" s="47"/>
+      <c r="I21" s="54"/>
       <c r="K21" s="23"/>
       <c r="M21" s="24"/>
       <c r="P21" s="23"/>
-      <c r="R21" s="53"/>
-      <c r="S21" s="54"/>
-      <c r="T21" s="55"/>
+      <c r="R21" s="48"/>
+      <c r="S21" s="49"/>
+      <c r="T21" s="50"/>
     </row>
     <row r="22" spans="4:20">
-      <c r="D22" s="53"/>
-      <c r="E22" s="54"/>
-      <c r="F22" s="55"/>
-      <c r="H22" s="66" t="s">
-        <v>722</v>
-      </c>
-      <c r="I22" s="48" t="s">
-        <v>716</v>
-      </c>
-      <c r="J22" s="66"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="49"/>
+      <c r="F22" s="50"/>
+      <c r="H22" s="39" t="s">
+        <v>720</v>
+      </c>
+      <c r="I22" s="41" t="s">
+        <v>714</v>
+      </c>
+      <c r="J22" s="39"/>
       <c r="K22" s="23"/>
       <c r="M22" s="24"/>
       <c r="P22" s="23"/>
-      <c r="R22" s="53"/>
-      <c r="S22" s="54"/>
-      <c r="T22" s="55"/>
+      <c r="R22" s="48"/>
+      <c r="S22" s="49"/>
+      <c r="T22" s="50"/>
     </row>
     <row r="23" spans="4:20">
-      <c r="D23" s="62"/>
-      <c r="E23" s="63"/>
-      <c r="F23" s="77"/>
-      <c r="H23" s="67"/>
-      <c r="I23" s="59"/>
-      <c r="J23" s="67"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="52"/>
+      <c r="F23" s="53"/>
+      <c r="H23" s="40"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="40"/>
       <c r="K23" s="23"/>
       <c r="M23" s="24"/>
       <c r="P23" s="23"/>
-      <c r="R23" s="62"/>
-      <c r="S23" s="63"/>
-      <c r="T23" s="77"/>
+      <c r="R23" s="51"/>
+      <c r="S23" s="52"/>
+      <c r="T23" s="53"/>
     </row>
     <row r="24" spans="4:20">
       <c r="D24" s="24"/>
@@ -9985,77 +11356,77 @@
     </row>
     <row r="25" spans="4:20" ht="16.5" customHeight="1">
       <c r="D25" s="24"/>
-      <c r="E25" s="48" t="s">
-        <v>876</v>
+      <c r="E25" s="41" t="s">
+        <v>874</v>
       </c>
       <c r="F25" s="23"/>
-      <c r="H25" s="50" t="s">
-        <v>896</v>
-      </c>
-      <c r="I25" s="51"/>
-      <c r="J25" s="60"/>
+      <c r="H25" s="55" t="s">
+        <v>894</v>
+      </c>
+      <c r="I25" s="56"/>
+      <c r="J25" s="57"/>
       <c r="K25" s="23"/>
       <c r="M25" s="24"/>
       <c r="P25" s="23"/>
       <c r="R25" s="24"/>
-      <c r="S25" s="48" t="s">
-        <v>716</v>
+      <c r="S25" s="41" t="s">
+        <v>714</v>
       </c>
       <c r="T25" s="23"/>
     </row>
     <row r="26" spans="4:20">
       <c r="D26" s="24"/>
-      <c r="E26" s="59"/>
+      <c r="E26" s="42"/>
       <c r="F26" s="23"/>
-      <c r="H26" s="53"/>
-      <c r="I26" s="54"/>
-      <c r="J26" s="61"/>
+      <c r="H26" s="48"/>
+      <c r="I26" s="49"/>
+      <c r="J26" s="58"/>
       <c r="K26" s="23"/>
       <c r="M26" s="24"/>
       <c r="P26" s="23"/>
       <c r="R26" s="24"/>
-      <c r="S26" s="59"/>
+      <c r="S26" s="42"/>
       <c r="T26" s="23"/>
     </row>
     <row r="27" spans="4:20">
       <c r="D27" s="24"/>
-      <c r="E27" s="46" t="s">
-        <v>717</v>
+      <c r="E27" s="43" t="s">
+        <v>715</v>
       </c>
       <c r="F27" s="23"/>
-      <c r="H27" s="53"/>
-      <c r="I27" s="54"/>
-      <c r="J27" s="61"/>
-      <c r="K27" s="69" t="s">
-        <v>895</v>
+      <c r="H27" s="48"/>
+      <c r="I27" s="49"/>
+      <c r="J27" s="58"/>
+      <c r="K27" s="35" t="s">
+        <v>893</v>
       </c>
       <c r="M27" s="24"/>
       <c r="P27" s="23"/>
       <c r="R27" s="24"/>
-      <c r="S27" s="46" t="s">
-        <v>717</v>
+      <c r="S27" s="43" t="s">
+        <v>715</v>
       </c>
       <c r="T27" s="23"/>
     </row>
     <row r="28" spans="4:20" ht="16.5" customHeight="1">
       <c r="D28" s="24"/>
-      <c r="E28" s="47"/>
+      <c r="E28" s="54"/>
       <c r="F28" s="23"/>
-      <c r="H28" s="62"/>
-      <c r="I28" s="63"/>
-      <c r="J28" s="64"/>
-      <c r="K28" s="70"/>
+      <c r="H28" s="51"/>
+      <c r="I28" s="52"/>
+      <c r="J28" s="59"/>
+      <c r="K28" s="36"/>
       <c r="M28" s="24"/>
       <c r="P28" s="23"/>
       <c r="R28" s="24"/>
-      <c r="S28" s="47"/>
+      <c r="S28" s="54"/>
       <c r="T28" s="23"/>
     </row>
     <row r="29" spans="4:20">
       <c r="D29" s="24"/>
       <c r="F29" s="23"/>
       <c r="H29" s="24"/>
-      <c r="K29" s="71"/>
+      <c r="K29" s="37"/>
       <c r="M29" s="24"/>
       <c r="P29" s="23"/>
       <c r="R29" s="24"/>
@@ -10066,10 +11437,10 @@
       <c r="E30" s="27"/>
       <c r="F30" s="28"/>
       <c r="H30" s="24"/>
-      <c r="I30" s="48" t="s">
-        <v>716</v>
-      </c>
-      <c r="K30" s="71"/>
+      <c r="I30" s="41" t="s">
+        <v>714</v>
+      </c>
+      <c r="K30" s="37"/>
       <c r="M30" s="25"/>
       <c r="N30" s="27"/>
       <c r="O30" s="27"/>
@@ -10080,56 +11451,77 @@
     </row>
     <row r="31" spans="4:20">
       <c r="H31" s="24"/>
-      <c r="I31" s="59"/>
-      <c r="K31" s="71"/>
+      <c r="I31" s="42"/>
+      <c r="K31" s="37"/>
     </row>
     <row r="32" spans="4:20">
       <c r="H32" s="24"/>
-      <c r="I32" s="46" t="s">
-        <v>717</v>
-      </c>
-      <c r="K32" s="71"/>
+      <c r="I32" s="43" t="s">
+        <v>715</v>
+      </c>
+      <c r="K32" s="37"/>
       <c r="R32" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
     </row>
     <row r="33" spans="8:24" ht="17.25" thickBot="1">
       <c r="H33" s="25"/>
-      <c r="I33" s="73"/>
+      <c r="I33" s="44"/>
       <c r="J33" s="27"/>
-      <c r="K33" s="72"/>
+      <c r="K33" s="38"/>
     </row>
     <row r="35" spans="8:24">
       <c r="I35" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="J35" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="36" spans="8:24">
       <c r="I36" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="J36" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
     </row>
     <row r="38" spans="8:24">
       <c r="I38" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="J38" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
     </row>
     <row r="47" spans="8:24">
       <c r="X47" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="D7:D13"/>
+    <mergeCell ref="E14:G17"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="I14:K17"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="S11:S12"/>
+    <mergeCell ref="R14:T17"/>
+    <mergeCell ref="M7:M13"/>
+    <mergeCell ref="O9:O10"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="N14:P17"/>
+    <mergeCell ref="P7:P13"/>
+    <mergeCell ref="O11:O12"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="H25:J28"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="H22:H23"/>
     <mergeCell ref="R6:T6"/>
     <mergeCell ref="R19:T19"/>
     <mergeCell ref="D19:F19"/>
@@ -10146,27 +11538,6 @@
     <mergeCell ref="M6:P6"/>
     <mergeCell ref="D20:F23"/>
     <mergeCell ref="E27:E28"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="H25:J28"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="I22:I23"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="S11:S12"/>
-    <mergeCell ref="R14:T17"/>
-    <mergeCell ref="M7:M13"/>
-    <mergeCell ref="O9:O10"/>
-    <mergeCell ref="N11:N12"/>
-    <mergeCell ref="N14:P17"/>
-    <mergeCell ref="P7:P13"/>
-    <mergeCell ref="O11:O12"/>
-    <mergeCell ref="D7:D13"/>
-    <mergeCell ref="E14:G17"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="I14:K17"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/PLC/IO List.xlsx
+++ b/PLC/IO List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EZENIC\Desktop\Project-Second\PLC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{042E96CD-4AEF-4E7F-97EC-B5177B512C45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0297120E-D72A-4E01-8210-4DBEC589B241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="0" windowWidth="17250" windowHeight="15585" activeTab="2" xr2:uid="{E8A3CD3B-D612-4B37-A180-F6C335096DC9}"/>
+    <workbookView xWindow="6120" yWindow="2130" windowWidth="17250" windowHeight="11295" xr2:uid="{E8A3CD3B-D612-4B37-A180-F6C335096DC9}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1373" uniqueCount="974">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1383" uniqueCount="984">
   <si>
     <t>X10</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3465,6 +3465,42 @@
   </si>
   <si>
     <t>M229</t>
+  </si>
+  <si>
+    <t>M170</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGV1 5공정 배출 가능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M171</t>
+  </si>
+  <si>
+    <t>M172</t>
+  </si>
+  <si>
+    <t>M173</t>
+  </si>
+  <si>
+    <t>M174</t>
+  </si>
+  <si>
+    <t>AGV2 5공정 배출 가능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGV3 5공정 배출 가능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGV4 5공정 배출 가능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGV5 5공정 배출 가능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -6312,43 +6348,83 @@
       <c r="H92" s="5"/>
       <c r="I92" s="6"/>
     </row>
-    <row r="93" spans="8:9">
-      <c r="H93" s="5" t="s">
+    <row r="95" spans="8:9">
+      <c r="H95" s="1" t="s">
+        <v>974</v>
+      </c>
+      <c r="I95" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="96" spans="8:9">
+      <c r="H96" s="1" t="s">
+        <v>976</v>
+      </c>
+      <c r="I96" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="97" spans="8:9">
+      <c r="H97" s="1" t="s">
+        <v>977</v>
+      </c>
+      <c r="I97" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="98" spans="8:9">
+      <c r="H98" s="1" t="s">
+        <v>978</v>
+      </c>
+      <c r="I98" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="99" spans="8:9">
+      <c r="H99" s="1" t="s">
+        <v>979</v>
+      </c>
+      <c r="I99" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="101" spans="8:9">
+      <c r="H101" s="5" t="s">
         <v>452</v>
       </c>
-      <c r="I93" s="6" t="s">
+      <c r="I101" s="6" t="s">
         <v>968</v>
       </c>
     </row>
-    <row r="94" spans="8:9">
-      <c r="H94" s="5" t="s">
+    <row r="102" spans="8:9">
+      <c r="H102" s="5" t="s">
         <v>965</v>
       </c>
-      <c r="I94" s="6" t="s">
+      <c r="I102" s="6" t="s">
         <v>969</v>
       </c>
     </row>
-    <row r="95" spans="8:9">
-      <c r="H95" s="5" t="s">
+    <row r="103" spans="8:9">
+      <c r="H103" s="5" t="s">
         <v>966</v>
       </c>
-      <c r="I95" s="6" t="s">
+      <c r="I103" s="6" t="s">
         <v>970</v>
       </c>
     </row>
-    <row r="96" spans="8:9">
-      <c r="H96" s="5" t="s">
+    <row r="104" spans="8:9">
+      <c r="H104" s="5" t="s">
         <v>967</v>
       </c>
-      <c r="I96" s="6" t="s">
+      <c r="I104" s="6" t="s">
         <v>971</v>
       </c>
     </row>
-    <row r="97" spans="8:9">
-      <c r="H97" s="5" t="s">
+    <row r="105" spans="8:9">
+      <c r="H105" s="5" t="s">
         <v>973</v>
       </c>
-      <c r="I97" s="6" t="s">
+      <c r="I105" s="6" t="s">
         <v>972</v>
       </c>
     </row>
